--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -426,14 +426,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[{'Requirement ID': '1', 'Title': 'NGB Keyed Bottles with Enhanced Page Yield', 'Description': 'Develop new NGB keyed bottles supporting 6,000 pages for Black and 6,000 pages for CMY, with bottle size for CMY supporting over 8,000 pages.', 'Rationale': 'Increases ink capacity and reduces frequency of bottle replacement, improving customer satisfaction and lowering operational costs.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Product Management, End Users', 'Dependencies': 'Requires compatibility with existing and new printer hardware, bottle keying mechanism, and IDS system.', 'Acceptance Criteria': 'Bottles must fit in the designated slots, deliver the specified page yields, and pass reliability testing for spill-free operation.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '2', 'Title': 'Spill-Free Reliability for Ink Bottles', 'Description': 'Ensure all new ink bottles and filling processes are spill-free, including reliability validation for NOA-F with metal foiled labyrinth and lid label.', 'Rationale': 'Prevents ink spillage, reduces mess for users, and enhances product reputation for quality.', 'Priority': 'High', 'Stakeholders': 'End Users, R&amp;D, Service', 'Dependencies': 'Bottle and tank design, manufacturing process controls.', 'Acceptance Criteria': 'No ink spillage during standard and stress use-case scenarios, validated in lab and field tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '3', 'Title': 'NOA-F Service Parts Availability', 'Description': 'NOA-F (with metal foiled labyrinth and lid label) must be available as a service part for warranty support.', 'Rationale': 'Ensures serviceability and customer support continuity during warranty period.', 'Priority': 'High', 'Stakeholders': 'Service, Warranty, End Users', 'Dependencies': 'NOA-F design finalization, supply chain setup.', 'Acceptance Criteria': 'NOA-F parts can be ordered and replaced during warranty service events.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '4', 'Title': 'Acumen 6 Integration on Lid', 'Description': 'Integrate Acumen 6 technology on the ink bottle lid for improved product tracking and authentication.', 'Rationale': 'Enhances anti-counterfeiting and supply chain traceability.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Supply Chain, Security', 'Dependencies': 'Lid design, Acumen 6 tech integration, software support.', 'Acceptance Criteria': 'All bottles shipped have Acumen 6 enabled lids and can be authenticated via HP systems.', 'Confidence': 0.8, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '5', 'Title': 'Factory Line Modification for NOA-F and Magi Ink Cart', 'Description': 'Modify SA14 factory line to accommodate NOA-F, add Magi ink cartridge and labeling tool in Orcus 5, and create molds for 1 to 4 new keyed caps.', 'Rationale': 'Supports production scalability and introduction of new bottle and cap designs.', 'Priority': 'High', 'Stakeholders': 'Manufacturing, R&amp;D, Operations', 'Dependencies': 'Design freeze for NOA-F, Magi ink cart, and cap keying.', 'Acceptance Criteria': 'Factory lines operational with new modifications, producing conforming products.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '6', 'Title': 'Support for Customer Replaceable PHA and NOA-F', 'Description': 'Enable customers to replace PHA (Printhead Assembly) and NOA-F components to enhance serviceability and reduce downtime.', 'Rationale': 'Improves user experience by reducing service turnaround time and cost.', 'Priority': 'High', 'Stakeholders': 'End Users, Service, Product Management', 'Dependencies': 'Design for user-accessible components, documentation, and training.', 'Acceptance Criteria': 'Customers can replace PHA and NOA-F following provided instructions without specialized tools.', 'Confidence': 0.92, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '7', 'Title': 'Warranty Page Life Goal of 80K Pages', 'Description': 'Set a new warranty page life goal for the product at 80,000 pages.', 'Rationale': 'Extends product value and competitiveness in the market.', 'Priority': 'High', 'Stakeholders': 'Product Management, End Users, Warranty', 'Dependencies': 'Component durability, consumable capacity, reliability engineering.', 'Acceptance Criteria': 'Product operates within specifications for at least 80,000 pages under normal usage.', 'Confidence': 0.88, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '8', 'Title': 'Reddington ID with Increased Tank Size', 'Description': 'Implement Reddington ID with an increased tank size to accommodate higher ink capacity, with no change to Marconi-HI ADF.', 'Rationale': 'Supports higher page yields and aligns with new bottle capacities.', 'Priority': 'Medium', 'Stakeholders': 'Product Management, R&amp;D, Design', 'Dependencies': 'Tank design, industrial design integration, ADF compatibility.', 'Acceptance Criteria': 'Printer tank accommodates new bottle sizes and maintains industrial design standards.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '9', 'Title': 'EPEAT3, LOT4, and Blue Angel Certification for PDL SKU', 'Description': 'Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental certification requirements.', 'Rationale': 'Meets regulatory and market-driven eco-labeling demands, enhancing product appeal in key markets.', 'Priority': 'High', 'Stakeholders': 'Compliance, Marketing, Product Management', 'Dependencies': 'Product design, materials selection, documentation for certification.', 'Acceptance Criteria': 'Product is certified and listed under EPEAT3, LOT4, and Blue Angel before launch.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '10', 'Title': 'Input/Output Tray Changes for Tank Protrusion', 'Description': 'Redesign input and output trays to align with the protrusion caused by the enlarged ink tank.', 'Rationale': 'Maintains usability and ensures smooth paper handling despite tank size changes.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Design, End Users', 'Dependencies': 'Tank size finalization, mechanical design updates.', 'Acceptance Criteria': 'Trays function correctly with new tank configuration and pass paper handling tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '11', 'Title': '4.3” CGD Display Integration', 'Description': 'Integrate a 4.3-inch Color Graphic Display (CGD) into the printer interface.', 'Rationale': 'Improves user interaction and accessibility, aligning with modern UI expectations.', 'Priority': 'Medium', 'Stakeholders': 'End Users, Product Management, UI/UX', 'Dependencies': 'Display hardware sourcing, firmware support, mechanical design.', 'Acceptance Criteria': 'All units ship with fully functional 4.3” CGD, validated in usability tests.', 'Confidence': 0.8, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '12', 'Title': 'New Tube Routing and Integration', 'Description': 'Leverage Sayan Sibstar tubes and introduce new tube routing and integration for the ink delivery system.', 'Rationale': 'Optimizes ink flow, reliability, and supports new tank/bottle formats.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'Tube design, platform integration, reliability validation.', 'Acceptance Criteria': 'Ink flows reliably through new routing with no leaks or clogs under all operating conditions.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '13', 'Title': 'Service Station Aerosol Management Enhancement', 'Description': 'Modify service station aerosol management and spit platform to accommodate changes due to new tank design.', 'Rationale': 'Prevents ink mist and aerosol from affecting printer internals, maintaining print quality and reliability.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Service, Quality Assurance', 'Dependencies': 'Tank design, service station redesign.', 'Acceptance Criteria': 'No measurable increase in aerosol contamination in internal tests compared to previous models.', 'Confidence': 0.8, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '14', 'Title': 'Paperpath Durability for Increased Page Life', 'Description': 'Upgrade paperpath components to support increased product page life (80K pages).', 'Rationale': 'Ensures consistent performance and reduces maintenance over the product’s extended life.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, End Users, Service', 'Dependencies': 'Component selection, durability testing.', 'Acceptance Criteria': 'Paperpath operates within specifications for 80,000 pages with minimal maintenance.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '15', 'Title': 'Ink Maintenance as a Serviceable Part Post-80K Life', 'Description': 'Design ink maintenance components to be serviceable at service centers after the product reaches 80,000 pages.', 'Rationale': 'Extends product lifecycle and supports post-warranty service models.', 'Priority': 'Medium', 'Stakeholders': 'Service, End Users, Product Management', 'Dependencies': 'Component modularity, service documentation.', 'Acceptance Criteria': 'Service centers can replace maintenance parts post-80K life with standard tools and procedures.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '16', 'Title': 'New IDS Make-Break and FI Connection', 'Description': 'Implement new IDS (Ink Delivery System) make-break and FI (Filling Interface) connection, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.', 'Rationale': 'Supports larger ink tanks and prevents incorrect bottle installation.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing, End Users', 'Dependencies': 'IDS and FI design, tank keying, SHAID integration.', 'Acceptance Criteria': 'IDS/FI connections are reliable, prevent misinstallation, and pass all functional tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '17', 'Title': 'New IDS Startup Algorithm and Air Management', 'Description': 'Develop a new IDS startup algorithm and air management approach to optimize system priming and minimize startup issues.', 'Rationale': 'Improves reliability and print quality from first use, reducing startup failures.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Quality Assurance, End Users', 'Dependencies': 'IDS hardware, firmware development.', 'Acceptance Criteria': 'Startup algorithm reliably primes system and manages air, validated in lab and field tests.', 'Confidence': 0.88, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '18', 'Title': 'New Print Quality Goals and Depletion to Meet Page Yield Definition', 'Description': 'Define and implement new print quality (PQ) goals and depletion management to align with updated page yield definitions.', 'Rationale': 'Ensures print quality is maintained throughout the product life and at specified yields.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Quality Assurance, Product Management', 'Dependencies': 'PQ metric definition, firmware updates, consumable monitoring.', 'Acceptance Criteria': 'Print quality remains within defined limits for the stated yield; depletion is accurately reported.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '19', 'Title': 'Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, and Stingray Wi-Fi Module', 'Description': 'Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, and Stingray Wi-Fi module for the new product.', 'Rationale': 'Leverages proven hardware, reduces development time and cost.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Manufacturing, Product Management', 'Dependencies': 'Component compatibility, firmware support.', 'Acceptance Criteria': 'All reused components function as specified in the new product context.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '20', 'Title': 'Security Enhancements with Gauss4.xx (HW &amp; FW)', 'Description': 'Integrate Gauss4.xx hardware and firmware security features into the product.', 'Rationale': 'Improves product security and compliance with modern IT requirements.', 'Priority': 'High', 'Stakeholders': 'IT Security, Product Management, Enterprise Customers', 'Dependencies': 'Gauss4.xx integration, hardware/firmware updates.', 'Acceptance Criteria': 'Product passes all internal and external security audits with Gauss4.xx features enabled.', 'Confidence': 0.88, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '21', 'Title': 'Support for PaaS Business Model and SMB/Enterprise Solutions', 'Description': 'Enable support for Printer-as-a-Service (PaaS) business model, including SMB manageability, onboarding paths, and enterprise solutions (WJA, HPSM, JAM).', 'Rationale': 'Expands addressable market and meets evolving customer needs for managed print solutions.', 'Priority': 'High', 'Stakeholders': 'Business Development, Enterprise Customers, SMB, Service', 'Dependencies': 'Solution software, onboarding workflow, integration with HP platforms.', 'Acceptance Criteria': 'Product supports all listed business models and solutions, validated in pilot deployments.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1-2'}, {'Requirement ID': '22', 'Title': 'High Throughput: 25/20ppm (PDL: 25/19ppm)', 'Description': 'Achieve print speeds of 25ppm (pages per minute) for standard, and 25/19ppm for PDL SKU.', 'Rationale': 'Meets competitive benchmarks and customer expectations for performance.', 'Priority': 'High', 'Stakeholders': 'Product Management, End Users, Marketing', 'Dependencies': 'Engine tuning, firmware optimization.', 'Acceptance Criteria': 'Printers achieve specified speeds in standardized benchmark tests.', 'Confidence': 0.92, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '23', 'Title': 'SuperAmp PHA Life at 65K Pages', 'Description': 'Ensure SuperAmp Printhead Assembly (PHA) achieves a life of 65,000 pages.', 'Rationale': 'Aligns with constrained business priority for durability and service cost reduction.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Service, Product Management', 'Dependencies': 'PHA design, materials selection, reliability validation.', 'Acceptance Criteria': 'SuperAmp PHA prints at least 65,000 pages without failure in reliability tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}, {'Requirement ID': '24', 'Title': 'Warranty Life of 2 Years', 'Description': 'Provide a warranty life of 2 years for the product.', 'Rationale': 'Meets market and customer expectations for reliability and support.', 'Priority': 'High', 'Stakeholders': 'Product Management, End Users, Service', 'Dependencies': 'Product reliability, component durability, service infrastructure.', 'Acceptance Criteria': 'Product is covered under warranty for 2 years from purchase date, with full support provided.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}, {'Requirement ID': '25', 'Title': 'Serviceability - Maintenance Box', 'Description': 'Include a maintenance box that is easily serviceable by users or service technicians.', 'Rationale': 'Improves ease of maintenance and reduces service costs.', 'Priority': 'Medium', 'Stakeholders': 'Service, End Users, R&amp;D', 'Dependencies': 'Maintenance box design, documentation.', 'Acceptance Criteria': 'Maintenance box can be replaced or serviced with minimal effort and standard tools.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}]</t>
+          <t>[{'Requirement ID': '1', 'Title': 'NGB Keyed Ink Bottles', 'Description': 'The printer must support new NGB keyed ink bottles with 6K Black and 6K CMY page yield, and CMY bottle size greater than 8K.', 'Rationale': 'To enable spill-free, reliable ink replacement and support high yield for customers, reducing maintenance frequency and enhancing user experience.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, End Users, Product Management', 'Dependencies': 'Requires new bottle design, compatible bottle interface on printer, and supply chain updates.', 'Acceptance Criteria': 'Given the printer, when a user inserts a new NGB keyed bottle, it should fit only in the correct slot, operate spill-free, and deliver at least the specified page yields.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '2', 'Title': 'Spill-Free Reliability for Ink Bottles', 'Description': 'The ink bottle system must provide spill-free reliability during user replacement and operation.', 'Rationale': 'To avoid mess, improve safety, and enhance customer satisfaction during ink refilling.', 'Priority': 'High', 'Stakeholders': 'End Users, Customer Support', 'Dependencies': 'Depends on bottle and tank interface design, IDS startup algorithm.', 'Acceptance Criteria': 'When a user replaces or refills ink, no ink should leak or spill under normal usage conditions.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '3', 'Title': 'NOA-F with Metal Foiled Labyrinth and Lid Label', 'Description': 'Integrate NOA-F (New Output Assembly - Filter) with a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanisms.', 'Rationale': 'Improves reliability and ensures secure, tamper-evident assembly for ink handling.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'Requires updated NOA-F design and manufacturing process changes.', 'Acceptance Criteria': 'NOA-F component must include specified features and pass reliability and assembly tests without requiring changes to push-push and TDF.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '4', 'Title': 'Reuse SuperAmp Si PHA', 'Description': 'The printer must reuse the SuperAmp Si Printhead Assembly (PHA) from previous models.', 'Rationale': 'To leverage proven technology and reduce R&amp;D and manufacturing costs.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing, Cost Management', 'Dependencies': 'Compatibility with new ink system and electronics.', 'Acceptance Criteria': 'SuperAmp Si PHA is integrated and passes functional and reliability tests in the new printer.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '5', 'Title': 'Reuse Magi/Nessie Inks Without Reformulation', 'Description': 'The printer must use existing Magi and Nessie pigment inks without any reformulation.', 'Rationale': 'To streamline supply chain and ensure ink compatibility with existing products.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Supply Chain, Manufacturing', 'Dependencies': 'Ink system compatibility, IDS modeling for startup and EOL.', 'Acceptance Criteria': 'Printer operates reliably with current Magi/Nessie inks and meets print quality and yield targets.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '6', 'Title': 'Reliability and Modeling for IDS and Air Management', 'Description': 'Reliability, WVTR (Water Vapor Transmission Rate), Air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F EOL, must be performed.', 'Rationale': 'To ensure long-term reliability and optimal performance of ink delivery and air management systems.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'IDS and air management system design, simulation tools.', 'Acceptance Criteria': 'All models and reliability tests completed and validated for startup and EOL scenarios.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '7', 'Title': 'Ink Stability Modeling for Tank and PQ Impact', 'Description': 'Model ink stability in the tank and assess impact on Print Quality (PQ).', 'Rationale': 'To ensure long-term print quality and ink reliability in the new tank system.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'Requires tank design and ink chemistry data.', 'Acceptance Criteria': 'Ink stability model is completed and reviewed, with documented impact on PQ.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '8', 'Title': 'NOA-F as Service Part in Warranty Support', 'Description': 'NOA-F must be available as a service part for warranty support.', 'Rationale': 'To facilitate efficient repairs and maintain product uptime during warranty period.', 'Priority': 'High', 'Stakeholders': 'Service, Warranty, End Users', 'Dependencies': 'Service supply chain, NOA-F component inventory.', 'Acceptance Criteria': 'NOA-F can be ordered and replaced as a warranty part with documented procedures.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '9', 'Title': 'Acumen 6 on Lid', 'Description': 'Integrate Acumen 6 (presumably a sensor or label technology) onto the printer lid.', 'Rationale': 'Likely for enhanced tracking, authentication, or serviceability.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Service, Manufacturing', 'Dependencies': 'Lid design and Acumen 6 technology integration.', 'Acceptance Criteria': 'Acumen 6 is present, functional, and passes all QA tests on the lid.', 'Confidence': 0.8, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '10', 'Title': 'Factory Line Modifications for NOA-F and New Ink Systems', 'Description': 'Modify existing SA14 production line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and create molds for 1-4 new keyed caps.', 'Rationale': 'To enable production of new components and ensure manufacturing readiness.', 'Priority': 'High', 'Stakeholders': 'Manufacturing, Operations', 'Dependencies': 'Production line redesign and tooling procurement.', 'Acceptance Criteria': 'Production lines are updated, validated, and capable of producing new components at required volumes.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '11', 'Title': 'Support Customer Replaceable PHA and NOA-F', 'Description': 'Design the printer so that customers can replace the Printhead Assembly (PHA) and NOA-F themselves.', 'Rationale': 'Improves serviceability, reduces downtime, and lowers service costs.', 'Priority': 'High', 'Stakeholders': 'End Users, Service, Product Management', 'Dependencies': 'Component design for user replacement, documentation.', 'Acceptance Criteria': 'Given a customer, when following instructions, they can successfully replace PHA and NOA-F without tools beyond those supplied.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '12', 'Title': 'Warranty Page Life Goal of 80k Pages', 'Description': 'The printer must support a new warranty page life goal of 80,000 pages.', 'Rationale': 'To offer a competitive warranty and reduce total cost of ownership for customers.', 'Priority': 'High', 'Stakeholders': 'Product Management, End Users, Service', 'Dependencies': 'Component durability, consumables design.', 'Acceptance Criteria': 'Printer operates reliably for at least 80,000 pages under normal usage conditions within warranty period.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '13', 'Title': 'Support for PaaS (Printing as a Service) Model', 'Description': 'Enable the printer to be used within a PaaS (Printing as a Service) business model.', 'Rationale': 'To support evolving business models and increase recurring revenue opportunities.', 'Priority': 'Medium', 'Stakeholders': 'Business Development, Product Management, Service', 'Dependencies': 'Integration with PaaS platform, billing, and serviceability features.', 'Acceptance Criteria': 'Printer can be enrolled, monitored, and managed via HP’s PaaS infrastructure.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '14', 'Title': 'Product Reddington ID with Tank Size Increase', 'Description': 'Product must have Reddington ID with an increased tank size and no change to Marconi-HI ADF.', 'Rationale': 'To support higher ink capacity and maintain compatibility with existing document feeder.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Product Management, End Users', 'Dependencies': 'Tank redesign, chassis integration.', 'Acceptance Criteria': 'Product passes ID review, tank increase is implemented, and ADF compatibility is validated.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '15', 'Title': 'EPEAT3, LOT4, and Blue Angel Compliance', 'Description': 'Product must meet EPEAT3, LOT4, and Blue Angel environmental and efficiency requirements for PDL SKU.', 'Rationale': 'To meet regulatory and market environmental standards.', 'Priority': 'High', 'Stakeholders': 'Compliance, Product Management, Marketing', 'Dependencies': 'Design for compliance, documentation, and testing.', 'Acceptance Criteria': 'Product is certified for EPEAT3, LOT4, and Blue Angel for relevant SKUs.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '16', 'Title': 'Input and Output Tray Changes for Tank Protrusion', 'Description': 'Modify input and output trays to align with new tank protrusion and optimize size.', 'Rationale': 'To ensure mechanical compatibility and space efficiency with the larger tank.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'Tray and tank design, mechanical integration.', 'Acceptance Criteria': 'Trays fit and function correctly with new tank design and pass all functional tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '17', 'Title': '4.3” CGD Display Integration', 'Description': 'Integrate a 4.3-inch CGD (Color Graphic Display) into the product.', 'Rationale': 'To provide an enhanced user interface and improve usability.', 'Priority': 'Medium', 'Stakeholders': 'End Users, Product Management', 'Dependencies': 'Display sourcing, UI design.', 'Acceptance Criteria': '4.3” CGD is integrated and passes usability and QA tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '18', 'Title': 'Four-Tube Platform with Sayan Sibstar Tubes', 'Description': 'Leverage a four-tube platform using Sayan Sibstar tubes, with new tube routing and integration.', 'Rationale': 'To support the new ink delivery system and tank configuration.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'Tube design, routing, and integration with IDS.', 'Acceptance Criteria': 'Four-tube system is implemented and validated for flow rate, reliability, and integration.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '19', 'Title': 'Aerosol Management in Service Station', 'Description': 'Update service station for aerosol management, with changes to spit platform due to tank.', 'Rationale': 'To maintain internal cleanliness and print quality as tank design changes.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Service, Quality Assurance', 'Dependencies': 'Service station and spit platform redesign.', 'Acceptance Criteria': 'Aerosol management system functions as intended and passes internal contamination tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '20', 'Title': 'Carriage Dynamics and Force Model Update', 'Description': 'Update carriage dynamics and force model to account for new tube routing and weight changes.', 'Rationale': 'To ensure printhead movement remains precise and reliable with new hardware configuration.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Mechanical Engineering', 'Dependencies': 'Carriage and tube design, simulation tools.', 'Acceptance Criteria': 'Carriage force model validated and printer passes printhead movement accuracy tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '21', 'Title': 'Paper Path for Increased Page Life', 'Description': 'Modify the paper path to support increased page life (80k pages).', 'Rationale': 'To ensure durability and reliability over the extended warranty period.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing, Service', 'Dependencies': 'Paper path design and materials.', 'Acceptance Criteria': 'Paper path passes durability tests for at least 80,000 pages.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '22', 'Title': 'Ink Maintenance Serviceable Part Post-80k Life', 'Description': 'Design the ink maintenance component as a serviceable part to be replaced after 80,000 page life.', 'Rationale': 'To maintain printer performance and extend usable life beyond warranty.', 'Priority': 'Medium', 'Stakeholders': 'Service, End Users', 'Dependencies': 'Component design, service documentation.', 'Acceptance Criteria': 'Ink maintenance part can be serviced/replaced after 80k pages, with instructions provided.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '23', 'Title': 'New Make-Break and FI Connection for IDS', 'Description': 'Implement new make-break and FI (Fluidic Interface) connection for the Ink Delivery System, leveraging LEBI ink-tank with increased size, keying, and LOI (Level of Integration).', 'Rationale': 'To support the new ink system and ensure reliable connections.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'IDS and tank design, connector sourcing.', 'Acceptance Criteria': 'All connections are reliable, pass leak and flow tests, and are keyed for correct assembly.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '24', 'Title': 'New IDS Startup Algorithm and Air Management', 'Description': 'Develop a new startup algorithm and air management process for the Ink Delivery System.', 'Rationale': 'To ensure reliable printer startup and minimize air-related print defects.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'IDS design, firmware development.', 'Acceptance Criteria': 'Startup algorithm is implemented, tested, and meets startup reliability criteria.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '25', 'Title': 'New Print Quality Goals and Depletion Definition', 'Description': 'Set new print quality goals and depletion metrics to meet the defined page yield.', 'Rationale': 'To ensure customer satisfaction and accurate yield reporting.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Product Management, QA', 'Dependencies': 'PQ testing, IDS and ink system performance.', 'Acceptance Criteria': 'Print quality and depletion meet or exceed defined targets in all test scenarios.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '26', 'Title': 'Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU', 'Description': 'Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new platform.', 'Rationale': 'To reduce development costs and leverage proven electronics.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing, Cost Management', 'Dependencies': 'Compatibility with new printer architecture.', 'Acceptance Criteria': 'All reused components are integrated and pass functional and reliability tests.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '27', 'Title': 'Stingray Wi-Fi Module Integration', 'Description': 'Integrate Stingray Wi-Fi module into the product.', 'Rationale': 'To provide wireless connectivity and support modern network standards.', 'Priority': 'High', 'Stakeholders': 'End Users, Product Management', 'Dependencies': 'Wi-Fi module sourcing and firmware integration.', 'Acceptance Criteria': 'Wi-Fi module is integrated, passes connectivity, and security tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '28', 'Title': 'Dune Firmware Platform', 'Description': 'Utilize Dune as the firmware platform for the printer.', 'Rationale': 'To standardize firmware development and leverage existing platform features.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Firmware Development', 'Dependencies': 'Firmware compatibility with hardware.', 'Acceptance Criteria': 'Printer operates reliably with Dune firmware and passes all functional tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '29', 'Title': 'Gauss4.xx Security (HW &amp; FW)', 'Description': 'Implement Gauss4.xx hardware and firmware security features.', 'Rationale': 'To ensure robust security for device, data, and network interactions.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Security, End Users', 'Dependencies': 'Security feature integration in hardware and firmware.', 'Acceptance Criteria': 'All Gauss4.xx security features are implemented and pass security validation tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '30', 'Title': 'Business Model and Solution Integration', 'Description': 'Support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome/Flexworker, and onboarding via multiple HP/SMB/ECP paths.', 'Rationale': 'To address a broad customer base and support diverse use cases.', 'Priority': 'Medium', 'Stakeholders': 'Product Management, Business Development, Service', 'Dependencies': 'Software and services integration, onboarding documentation.', 'Acceptance Criteria': 'Printer can be configured and managed for all business models and onboarding paths.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '31', 'Title': 'Scan, SMB Manageability, and Enterprise Support', 'Description': 'Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).', 'Rationale': 'To provide comprehensive functionality for business and enterprise users.', 'Priority': 'Medium', 'Stakeholders': 'End Users, IT, Product Management', 'Dependencies': 'Software integration, driver development.', 'Acceptance Criteria': 'All solutions are integrated, functional, and pass user acceptance tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '32', 'Title': 'Client and Driver Support', 'Description': 'Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.', 'Rationale': 'To ensure compatibility with existing and future HP software ecosystems.', 'Priority': 'Medium', 'Stakeholders': 'End Users, IT, Product Management', 'Dependencies': 'Driver and client software integration.', 'Acceptance Criteria': 'All listed clients and drivers are supported and pass installation and functionality tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '33', 'Title': 'Speed: 25/20 ppm (PDL: 25/19 ppm)', 'Description': 'Printer must achieve print speeds of 25 ppm (pages per minute) for standard and 25/19 ppm for PDL (Page Description Language) modes.', 'Rationale': 'To meet competitive performance benchmarks and customer expectations.', 'Priority': 'High', 'Stakeholders': 'Product Management, End Users', 'Dependencies': 'Print engine design, firmware optimization.', 'Acceptance Criteria': 'Printer achieves specified speeds in all relevant test scenarios.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '34', 'Title': 'SuperAmp PHA Life at 65K Pages', 'Description': 'SuperAmp PHA must have a minimum life of 65,000 pages.', 'Rationale': 'To ensure long-term reliability and reduce maintenance frequency.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Product Management, Service', 'Dependencies': 'PHA component quality and durability.', 'Acceptance Criteria': 'SuperAmp PHA passes life tests for at least 65,000 pages.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}, {'Requirement ID': '35', 'Title': 'Warranty Life: 2 Years or 80k Pages', 'Description': 'Warranty must cover 2 years or 80,000 pages, whichever comes first.', 'Rationale': 'To offer a competitive warranty and align with industry standards.', 'Priority': 'High', 'Stakeholders': 'Product Management, End Users, Service', 'Dependencies': 'Component reliability and service processes.', 'Acceptance Criteria': 'Warranty documentation and service processes support 2 years or 80,000 pages.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}, {'Requirement ID': '36', 'Title': 'Serviceability: Maintenance Box', 'Description': 'Printer must include a serviceable maintenance box for easy user or technician replacement.', 'Rationale': 'To reduce downtime and simplify maintenance.', 'Priority': 'Medium', 'Stakeholders': 'End Users, Service', 'Dependencies': 'Maintenance box design and documentation.', 'Acceptance Criteria': 'Maintenance box is easily accessible and replaceable, passing serviceability tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}, {'Requirement ID': '37', 'Title': 'Host 12K-CMYK and Trade Page 6K Support (Flexible)', 'Description': 'Support for 12,000 page yield for CMYK and 6,000 trade pages is desirable, but flexible based on business needs.', 'Rationale': 'To offer higher yield options for certain markets or customer segments.', 'Priority': 'Low', 'Stakeholders': 'Product Management, Business Development', 'Dependencies': 'Ink system and consumables design.', 'Acceptance Criteria': 'Printer can be configured for these yields if required by business strategy.', 'Confidence': 0.7, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[{'No': '1', 'Title': 'Business Ink Tank Printer for SMB', 'Description': "Develop HP's first business ink tank printer (Magellan) specifically targeting unmanaged and lightly managed SMBs (5-250 employees, 6-15 printers, AMPV ~500 pages) without dedicated IT teams.", 'Rationale': "Address a gap in HP's portfolio for SMBs seeking ROI, efficiency, and low TCO, and to compete in the CISS PLE Hi segment.", 'Priority': 'High', 'Stakeholders': ['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA'], 'Dependencies': 'None', 'Acceptance Criteria': 'A business ink tank printer is developed and launched, available for SMB customers, with documented targeting and positioning for the unmanaged/lightly managed SMB segment.', 'Confidence': 0.95, 'citation': 'Magellan MRD, Page 4, 5, 6, 7'}, {'No': '2', 'Title': 'AI Productivity and Manageability Solutions', 'Description': 'Integrate best-in-class AI solutions for productivity, scan workflow, and printer manageability, focused on SMB ease-of-use and future-proofing.', 'Rationale': 'SMBs require easy management and productivity tools due to lack of IT resources; AI-driven features are a key differentiator.', 'Priority': 'High', 'Stakeholders': ['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': 'Product includes AI-driven features for print and scan workflows, and manageability, validated through user testing with SMBs.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 4, 7, 11'}, {'No': '3', 'Title': 'Lowest Business Total Cost of Ownership (TCO)', 'Description': "Design Magellan to deliver HP's lowest business TCO with minimal intervention required from users.", 'Rationale': 'SMBs value cost efficiency and minimal maintenance; TCO is a major purchase driver.', 'Priority': 'High', 'Stakeholders': ['Marketing', 'BA'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': "Independent TCO analysis demonstrates that Magellan has the lowest business TCO in HP's portfolio for SMB use cases.", 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 4, 7, 11'}, {'No': '4', 'Title': 'Sustainability – 60% Recycled Content Plastic (RCP)', 'Description': 'Ensure Magellan achieves at least 60% recycled content plastic (RCP) in its construction, exceeding key competitors (Epson 30%).', 'Rationale': 'Sustainability is a top customer priority and a competitive differentiator.', 'Priority': 'High', 'Stakeholders': ['Prod Steward', 'Marketing'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': 'Product BOM and third-party verification confirm 60%+ RCP in all applicable plastic parts.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 11'}, {'No': '5', 'Title': 'Customer Replaceable Maintenance Box', 'Description': 'Design the maintenance box to be easily replaceable by the customer, with service center (MINK) backup if out of warranty.', 'Rationale': 'Minimizing downtime and simplifying maintenance is critical for SMBs without IT support.', 'Priority': 'High', 'Stakeholders': ['Quality', 'Supplies Quality'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': 'Field testing shows that over 95% of customers can replace the maintenance box without technical support.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '6', 'Title': 'Keyed Bottles for Ink Refilling', 'Description': 'Use keyed bottles to prevent incorrect ink refilling and ensure user-friendly, error-proof operation.', 'Rationale': 'Reduces user errors and support calls, enhancing SMB experience.', 'Priority': 'Medium', 'Stakeholders': ['Supplies Quality', 'Quality'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': 'Keyed bottles are implemented and testing shows zero cross-contamination in user trials.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '7', 'Title': 'SMB Portal for Device Management', 'Description': 'Provide a consolidated SMB portal for managing printers, targeting non-IT users for easy fleet management.', 'Rationale': 'SMBs need simple, centralized device management due to lack of IT resources.', 'Priority': 'High', 'Stakeholders': ['GXD', 'Marketing', 'Quality', 'R&amp;D Telemetry'], 'Dependencies': 'Business Ink Tank Printer for SMB, AI Productivity and Manageability Solutions', 'Acceptance Criteria': 'Portal is available at launch, usability tested with SMB office managers and generalist IT users, and meets satisfaction benchmarks.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 7, 10, 11'}, {'No': '8', 'Title': 'Advanced Telemetry Requirements', 'Description': 'Implement advanced telemetry features for monitoring device health, usage, and proactive support.', 'Rationale': 'Telemetry enables predictive maintenance, lower support costs, and better product insights for HP and customers.', 'Priority': 'High', 'Stakeholders': ['R&amp;D Telemetry', 'Quality'], 'Dependencies': 'Business Ink Tank Printer for SMB, SMB Portal for Device Management', 'Acceptance Criteria': 'Telemetry system collects and reports device health, usage, and error data to HP and users, with data privacy compliance.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 3, 12'}, {'No': '9', 'Title': 'Support for PaaS (Platform as a Service)', 'Description': "Magellan must support HP's PaaS offerings, including integration with SMB2.0 Solutions and Advanced View SMB portal.", 'Rationale': 'PaaS is a strategic direction for HP and a requirement for future SMB offerings.', 'Priority': 'Medium', 'Stakeholders': ['Marketing', 'GXD', 'BA'], 'Dependencies': 'SMB Portal for Device Management', 'Acceptance Criteria': "Magellan is compatible with HP's PaaS solutions and passes integration tests with SMB2.0 and Advanced View.", 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4, 10'}, {'No': '10', 'Title': 'PDL/PS Support for Specific SKUs', 'Description': 'For PDL SKUs, Magellan must support PDL/PS and achieve print speeds of 25/20 ppm (improved over current 25/19).', 'Rationale': 'PDL/PS support and improved speed are required for certain business workflows and competitive positioning.', 'Priority': 'Medium', 'Stakeholders': ['GXD', 'BA'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': 'PDL SKUs achieve specified print speeds in independent testing and support PDL/PS as documented.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '11', 'Title': 'Blue Angel Certification for PDL SKU', 'Description': 'Ensure Magellan PDL SKU achieves Blue Angel environmental certification.', 'Rationale': 'Environmental certifications are important for business customers and certain geographies.', 'Priority': 'Medium', 'Stakeholders': ['Tech Reg', 'Prod Steward'], 'Dependencies': 'PDL/PS Support for Specific SKUs', 'Acceptance Criteria': 'PDL SKU receives Blue Angel certification prior to launch.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '12', 'Title': 'Mobile Printing via HP App', 'Description': 'Support mobile printing workflows through the HP App for SMB users.', 'Rationale': 'Mobile printing is increasingly important for SMBs with hybrid workforces.', 'Priority': 'Medium', 'Stakeholders': ['Marketing', 'GXD'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': 'HP App supports Magellan printers for mobile print workflows with successful user acceptance testing.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 9'}, {'No': '13', 'Title': 'Maintenance Free or Reduced Maintenance Design', 'Description': 'Design Magellan to be maintenance free or require less maintenance (fewer parts to replace over product life).', 'Rationale': 'Reduces SMB user burden and increases uptime.', 'Priority': 'Medium', 'Stakeholders': ['Quality', 'Supplies Quality'], 'Dependencies': 'Business Ink Tank Printer for SMB', 'Acceptance Criteria': 'Product design validated by engineering to require less maintenance than comparable models; field data supports lower maintenance rates.', 'Confidence': 0.7, 'citation': 'Magellan MRD, Page 11'}]</t>
+          <t>[{'No': '1', 'Title': 'AI Productivity Solutions', 'Description': 'Integrate advanced AI-driven productivity solutions, including Perfect Print and Perfect Scan, into the Magellan printer to enhance workflow efficiency and manageability for SMB users.', 'Rationale': 'AI features will provide a competitive edge and meet the productivity needs of SMBs with limited IT resources.', 'Priority': 'High', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, BA', 'Dependencies': 'Requires integration with device firmware and SMB portal; dependent on AI software readiness.', 'Acceptance Criteria': 'Printer offers AI-powered Perfect Print and Perfect Scan features accessible through device interface and SMB portal; verified through user acceptance testing.', 'Confidence': 0.95, 'citation': 'Magellan MRD, Page 4, 7, 11'}, {'No': '2', 'Title': 'SMB Portal for Printer Management', 'Description': 'Develop a consolidated SMB portal for easy management, monitoring, and support of multiple printers in unmanaged/lightly managed SMB environments.', 'Rationale': 'Target customers lack dedicated IT; a simple, unified portal will reduce management overhead and improve customer satisfaction.', 'Priority': 'High', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, DVAR, BA', 'Dependencies': 'Requires backend infrastructure and integration with printer firmware.', 'Acceptance Criteria': 'Portal allows registration, configuration, monitoring, and support for all Magellan printers in a small business environment; tested with real SMB users.', 'Confidence': 0.95, 'citation': 'Magellan MRD, Page 7, 10, 11'}, {'No': '3', 'Title': 'Lowest Business TCO (Total Cost of Ownership)', 'Description': "Design the Magellan printer to deliver HP's lowest business TCO via efficient ink tank technology, minimal intervention, and cost-effective supplies.", 'Rationale': 'Cost efficiency is a key purchase driver for SMBs; will differentiate Magellan from competitors.', 'Priority': 'High', 'Stakeholders': 'Marketing, Supplies Quality, BA', 'Dependencies': 'Dependent on ink tank system design and supply chain.', 'Acceptance Criteria': "Independent cost analysis shows Magellan has the lowest TCO in HP's SMB portfolio; validated through competitive benchmarking.", 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 4, 7, 11'}, {'No': '4', 'Title': 'Sustainability – 60% Recycled Content Plastic (RCP)', 'Description': 'Ensure the Magellan printer is manufactured with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%, Canon TBC).', 'Rationale': 'Sustainability is a growing priority for SMBs and provides a strong competitive differentiator.', 'Priority': 'High', 'Stakeholders': 'Marketing, Prod Steward, Tech Reg, Quality', 'Dependencies': 'Requires sourcing and manufacturing process changes to meet RCP target.', 'Acceptance Criteria': 'Bill of materials and third-party audit confirm 60% RCP in final product.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 11'}, {'No': '5', 'Title': 'Customer Replaceable Maintenance Box', 'Description': 'Introduce a replaceable maintenance box that can be swapped by the customer, minimizing downtime and service costs.', 'Rationale': 'Reduces reliance on service centers and appeals to SMBs with limited IT support.', 'Priority': 'Medium', 'Stakeholders': 'Quality, Supplies Quality, DVAR, BA', 'Dependencies': 'Requires design validation for user replaceability and safety.', 'Acceptance Criteria': 'End users can replace maintenance box without tools; verified by usability testing.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 4'}, {'No': '6', 'Title': 'Warranty: 80k Pages or 2 Years', 'Description': 'Offer a warranty covering 80,000 pages or 2 years, whichever comes first, for the Magellan printer.', 'Rationale': 'Provides assurance to SMBs and supports the value proposition of reliability and low TCO.', 'Priority': 'High', 'Stakeholders': 'Quality, Marketing, BA', 'Dependencies': 'Warranty terms must be supported by hardware reliability testing.', 'Acceptance Criteria': 'Warranty documentation and marketing materials reflect 80k/2yr terms; validated by legal/quality teams.', 'Confidence': 0.95, 'citation': 'Magellan MRD, Page 4'}, {'No': '7', 'Title': 'Keyed Bottles for Ink Refilling', 'Description': 'Implement keyed ink bottles to prevent incorrect refilling and ensure system reliability.', 'Rationale': 'Reduces user error, protects print quality, and minimizes support calls.', 'Priority': 'Medium', 'Stakeholders': 'Supplies Quality, Quality, BA', 'Dependencies': 'Requires bottle and tank redesign; supply chain adaptation.', 'Acceptance Criteria': 'Only correct bottle fits corresponding tank; verified by mechanical testing.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 4'}, {'No': '8', 'Title': 'Support for SMB2.0 Solutions and Advanced View SMB Portal (Non-PDL SKU)', 'Description': 'Ensure non-PDL SKU supports SMB2.0 solutions and the Advanced View SMB portal for enhanced business functionality.', 'Rationale': 'Enhances business productivity and device manageability for non-PDL customers.', 'Priority': 'Medium', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, BA', 'Dependencies': 'Requires software/firmware development for compatibility.', 'Acceptance Criteria': 'Non-PDL SKU passes certification for SMB2.0 and Advanced View portal integration.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 4'}, {'No': '9', 'Title': 'PaaS (Platform as a Service) Support', 'Description': 'Enable Platform as a Service (PaaS) capabilities for Magellan printers to facilitate cloud-based management and services.', 'Rationale': "Aligns with HP's strategic goal for PaaS acceleration and provides recurring value to SMB customers.", 'Priority': 'High', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, BA, DVAR', 'Dependencies': 'Requires cloud infrastructure integration and security compliance.', 'Acceptance Criteria': "Magellan printers can be managed and serviced via HP's PaaS platform; validated by integration tests.", 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 4, 6, 10'}, {'No': '10', 'Title': 'PDL SKU: Improved Print Speed and PDL/PS Support', 'Description': 'For PDL SKU, deliver minimum print speeds of 25/20 ppm (improved from 25/19) and ensure support for PDL/PS.', 'Rationale': 'Addresses business segment needs for faster, professional printing and compatibility with enterprise workflows.', 'Priority': 'Medium', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, BA', 'Dependencies': 'Requires hardware and firmware optimization for speed and PDL/PS support.', 'Acceptance Criteria': 'PDL SKU achieves 25/20 ppm and passes PDL/PS compatibility tests.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 4'}, {'No': '11', 'Title': 'Blue Angel Certification (PDL SKU)', 'Description': 'Obtain Blue Angel certification for the PDL SKU to meet environmental and energy efficiency standards.', 'Rationale': "Required for sales in certain regions and supports HP's sustainability messaging.", 'Priority': 'Medium', 'Stakeholders': 'Tech Reg, Prod Steward, Marketing, Quality', 'Dependencies': 'Must meet Blue Angel requirements through design and testing.', 'Acceptance Criteria': 'PDL SKU listed as Blue Angel certified by official registry.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 4'}, {'No': '12', 'Title': 'Mobile Printing via HP App', 'Description': 'Ensure Magellan printers support mobile printing through the HP App for ease of use and remote access.', 'Rationale': 'Meets SMB user demand for flexible, on-the-go printing.', 'Priority': 'Medium', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, BA', 'Dependencies': 'Requires integration with HP App ecosystem.', 'Acceptance Criteria': 'Printer is discoverable and usable from HP App on iOS/Android; verified by functional testing.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 9'}, {'No': '13', 'Title': 'High Serviceability: PHA and MINK at Service Centre', 'Description': 'Design for high serviceability, allowing PHA (customer replaceable) and MINK (service center replaceable) parts, with target for most to be customer replaceable if out of warranty.', 'Rationale': 'Minimizes downtime and cost for SMBs; improves customer satisfaction.', 'Priority': 'Medium', 'Stakeholders': 'Quality, Supplies Quality, DVAR, BA', 'Dependencies': 'Design validation for replaceability and safety.', 'Acceptance Criteria': 'Parts classified and tested as PHA or MINK; service documentation updated.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 4'}, {'No': '14', 'Title': 'Telemetry and Analytics Requirements', 'Description': 'Implement telemetry features for device health, usage, and predictive maintenance reporting.', 'Rationale': 'Enables proactive support, improves reliability, and supports managed service offerings.', 'Priority': 'High', 'Stakeholders': 'R&amp;D Telemetry, BA, DVAR', 'Dependencies': 'Requires secure data collection and cloud integration.', 'Acceptance Criteria': 'Telemetry data is collected, transmitted securely, and accessible via SMB portal; validated by data integrity and privacy tests.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 3, 12'}]</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,27 +413,2613 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>requirements</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[{'Requirement ID': '1', 'Title': 'NGB Keyed Bottles with High Page Yield', 'Description': 'The printer must support new NGB keyed bottles with a 6,000-page yield for Black and CMY, and CMY bottles with a capacity greater than 8,000 pages.', 'Rationale': 'Higher yield bottles reduce user intervention and increase cost-effectiveness for high-volume users.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Product Management, End Users', 'Dependencies': 'Requires compatibility with new keyed bottle designs and ink tank integration.', 'Acceptance Criteria': 'Given a new NGB keyed bottle is installed, the printer should recognize the bottle and deliver at least 6,000 pages for Black and CMY, with CMY bottle capacity exceeding 8,000 pages.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '2', 'Title': 'Spill-Free Reliability for Ink Bottles', 'Description': 'The ink bottle and tank system must be designed to ensure spill-free operation during bottle installation and ink refilling.', 'Rationale': 'Spill-free design improves user experience and reduces mess and potential damage.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, End Users, Customer Support', 'Dependencies': 'Integration with NOA-F and bottle design.', 'Acceptance Criteria': 'Given a user installs or refills ink, there should be no observable ink spillage under normal operating conditions.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '3', 'Title': 'NOA-F with Metal Foiled Labyrinth and Lid Label', 'Description': 'Implement a NOA-F (Non-Original Authentication Feature) with a metal foiled labyrinth and a lid label; no changes to click-on push-push and TDF mechanisms.', 'Rationale': 'Improves anti-counterfeiting and ensures secure bottle authentication.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Security, Product Management', 'Dependencies': 'Dependent on NOA-F design and manufacturing.', 'Acceptance Criteria': 'Given a bottle with NOA-F, the printer must authenticate it using the metal foiled labyrinth and lid label, and the click-on mechanisms must remain unchanged.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '4', 'Title': 'Reuse SuperAmp Si PHA and Magi/Nessie Ink Formulations', 'Description': 'The printer must reuse SuperAmp Si PHA and Magi/Nessie ink formulations without requiring ink reformulation.', 'Rationale': 'Reduces R&amp;D costs and leverages proven technologies.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'Compatibility with new bottle and tank systems.', 'Acceptance Criteria': 'Given the existing SuperAmp Si PHA and Magi/Nessie inks, they must be compatible and perform to current standards in the new printer.', 'Confidence': 0.95, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '5', 'Title': 'Reliability and Performance Characterization', 'Description': 'Reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) must be characterized and modeled, including startup and NOA-F end-of-life scenarios.', 'Rationale': 'Ensures consistent performance and reliability over the product lifecycle.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'Requires new testing and modeling processes.', 'Acceptance Criteria': 'All key parameters must be characterized and meet predefined thresholds for startup and end-of-life.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '6', 'Title': 'Ink Stability Modeling for Tank and PQ Impact', 'Description': 'Model ink stability in the tank and assess its impact on print quality (PQ).', 'Rationale': 'Maintains high print quality and reduces ink-related failures.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'Requires data from ink stability tests.', 'Acceptance Criteria': 'Ink stability models must predict PQ outcomes with &gt;95% accuracy in lab tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '7', 'Title': 'Support for Service and Contractual Obligations', 'Description': 'The printer and its consumables must support service/contractual requirements, including NOA-F as service parts under warranty.', 'Rationale': 'Ensures compliance with HP’s warranty and service programs.', 'Priority': 'High', 'Stakeholders': 'Customer Support, Service, Product Management', 'Dependencies': 'NOA-F design and service part logistics.', 'Acceptance Criteria': 'NOA-F parts must be available and serviceable under warranty claims.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '8', 'Title': 'Acumen 6 Integration on Lid', 'Description': 'Integrate Acumen 6 technology on the ink bottle lid.', 'Rationale': 'Enhances bottle authentication and traceability.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Security', 'Dependencies': 'Integration with lid design and manufacturing.', 'Acceptance Criteria': 'Acumen 6 must be present and functional on all bottle lids shipped with the product.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '9', 'Title': 'Factory Line Modification for NOA-F and New Bottles', 'Description': 'Modify existing SA 14 line for NOA-F and add Magi ink cartridge and labeling tool in Orcus 5. Mold for 1 to 4 new keyed caps required.', 'Rationale': 'Enables production of new consumables and ensures factory readiness.', 'Priority': 'High', 'Stakeholders': 'Manufacturing, Operations, R&amp;D', 'Dependencies': 'Requires equipment upgrades and process changes.', 'Acceptance Criteria': 'Factory lines must be capable of producing NOA-F and new bottles with required caps and labeling.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '10', 'Title': 'Support Customer Replaceable PHA and NOA-F', 'Description': 'Design the printer to allow customers to replace PHA and NOA-F components easily.', 'Rationale': 'Improves serviceability and reduces downtime for end users.', 'Priority': 'High', 'Stakeholders': 'End Users, Customer Support', 'Dependencies': 'Component design and user documentation.', 'Acceptance Criteria': 'Customers must be able to replace PHA and NOA-F without tools or technical assistance, as verified by usability tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '11', 'Title': 'New Warranty Page Life Goal: 80K Pages', 'Description': 'The printer must support a new warranty page life goal of 80,000 pages.', 'Rationale': 'Aligns with market expectations for reliability and reduces total cost of ownership.', 'Priority': 'High', 'Stakeholders': 'Product Management, End Users, Service', 'Dependencies': 'Component durability and consumable life.', 'Acceptance Criteria': 'Printer must reliably print 80,000 pages without major failures under standard usage.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '12', 'Title': 'Support for PaaS Business Model', 'Description': 'Enable printer and software features to support Printer-as-a-Service (PaaS) offerings, including scheduling and management.', 'Rationale': 'Supports new business models and revenue streams.', 'Priority': 'Medium', 'Stakeholders': 'Business Development, IT, Enterprise Customers', 'Dependencies': 'Integration with HP’s PaaS infrastructure.', 'Acceptance Criteria': 'Printer can be managed, monitored, and billed as a service via HP’s platform.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '13', 'Title': 'Increased Tank Size and Size Optimization', 'Description': 'Increase the tank size (Reddington ID) and optimize overall printer size to accommodate the tank, with no change to Marconi-HI ADF.', 'Rationale': 'Supports higher ink capacity without impacting core features.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Product Management, End Users', 'Dependencies': 'Mechanical design and integration with input/output trays.', 'Acceptance Criteria': 'Printer tank is increased in size, with input/output trays adjusted as needed, and no impact to ADF function.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '14', 'Title': 'EPS Foam Packaging', 'Description': 'Use EPS foam packaging for shipping and handling of the printer.', 'Rationale': 'Improves product protection during transit.', 'Priority': 'Low', 'Stakeholders': 'Logistics, Manufacturing', 'Dependencies': 'Packaging design and supply chain.', 'Acceptance Criteria': 'All shipped units are packaged with EPS foam and pass drop/shock tests.', 'Confidence': 0.8, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '15', 'Title': 'EPEAT3 and LOT4 Environmental Compliance, Blue Angel for PDL SKU', 'Description': 'Ensure the printer complies with EPEAT3, LOT4, and Blue Angel (for PDL SKU) environmental standards.', 'Rationale': 'Meets regulatory and market requirements for sustainability.', 'Priority': 'High', 'Stakeholders': 'Regulatory, Product Management, Marketing', 'Dependencies': 'Design and material selection.', 'Acceptance Criteria': 'Printer achieves EPEAT3, LOT4, and Blue Angel certifications as applicable.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '16', 'Title': 'Input/Output Tray Changes for Tank Protrusion', 'Description': 'Modify input and output trays to align with the protruding tank design.', 'Rationale': 'Ensures usability and compatibility with new tank size.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Product Management, End Users', 'Dependencies': 'Mechanical design changes.', 'Acceptance Criteria': 'Trays function correctly and accommodate tank protrusion without impacting paper handling.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '17', 'Title': '4.3” CGD Display', 'Description': 'Integrate a 4.3-inch CGD (color graphical display) into the printer.', 'Rationale': 'Enhances user interface and ease of use.', 'Priority': 'Medium', 'Stakeholders': 'End Users, Product Management', 'Dependencies': 'Display integration and firmware support.', 'Acceptance Criteria': 'Printer features a 4.3” CGD that passes usability and display quality tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '18', 'Title': 'Platform: 4 Tubes with New Routing and Integration', 'Description': 'Leverage Sayan Sibstar tubes with new routing and integration for the ink delivery system.', 'Rationale': 'Improves ink flow and reliability.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'Tube design and printer integration.', 'Acceptance Criteria': 'Printer uses four tubes with new routing and passes flow and reliability tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '19', 'Title': 'Service Station Aerosol Management', 'Description': 'Implement aerosol management in the service station, with platform changes due to tank design.', 'Rationale': 'Reduces ink aerosol emissions and maintains print quality.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'Service station design changes.', 'Acceptance Criteria': 'Aerosol emissions are within HP’s safety and quality standards during service operations.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '20', 'Title': 'Carriage Dynamic and Force Model with Tube and New Weights', 'Description': 'Develop and validate a dynamic and force model for the carriage, accounting for new tube routing and increased weights.', 'Rationale': 'Ensures reliable carriage motion and print accuracy.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'Mechanical modeling and validation.', 'Acceptance Criteria': 'Carriage operates within force and motion tolerances under all configurations.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '21', 'Title': 'Paperpath Support for Increased Page Life', 'Description': 'Modify paperpath to support increased page life of 80,000 pages.', 'Rationale': 'Ensures reliable operation over extended use.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Quality Assurance, End Users', 'Dependencies': 'Paperpath component durability.', 'Acceptance Criteria': 'Paperpath components function reliably for at least 80,000 pages in testing.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '22', 'Title': 'Serviceable Ink Maintenance Part (Post 80k Life)', 'Description': 'Design an ink maintenance part that can be serviced or replaced at a service center after 80,000 pages.', 'Rationale': 'Extends printer life and reduces service costs for users.', 'Priority': 'Medium', 'Stakeholders': 'Service, End Users', 'Dependencies': 'Service center capabilities and part design.', 'Acceptance Criteria': 'Ink maintenance part is replaceable at service centers after 80,000 pages as verified by service protocols.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '23', 'Title': 'New Make-Break and FI Connection in IDS', 'Description': 'Implement a new make-break and FI (fluidic interconnect) connection in the Ink Delivery System.', 'Rationale': 'Improves reliability and maintainability of the ink system.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'IDS redesign.', 'Acceptance Criteria': 'IDS passes reliability and leak tests with new connections.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '24', 'Title': 'Leverage LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID', 'Description': 'Utilize LEBI ink-tank with increased size, keying, and LOI SHAID for enhanced security and capacity.', 'Rationale': 'Increases security and supports higher ink volumes.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Security, Manufacturing', 'Dependencies': 'Tank and SHAID integration.', 'Acceptance Criteria': 'LEBI ink-tank meets increased capacity and security criteria in lab tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '25', 'Title': 'New IDS Startup Algorithm and Air Management', 'Description': 'Develop a new startup algorithm and air management system for the Ink Delivery System.', 'Rationale': 'Improves startup reliability and prevents air entrapment.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Quality Assurance', 'Dependencies': 'Firmware and IDS design.', 'Acceptance Criteria': 'Printer passes startup tests with new IDS algorithm and no air entrapment issues.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '26', 'Title': 'New Servicing and Startup Algorithm', 'Description': 'Implement new algorithms for printer servicing and startup to support new hardware and consumables.', 'Rationale': 'Ensures smooth operation and reduces servicing errors.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Service, End Users', 'Dependencies': 'Firmware development.', 'Acceptance Criteria': 'Printer completes servicing and startup with new algorithms and no errors in field tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '27', 'Title': 'New Print Quality Goals and Depletion Metrics', 'Description': 'Establish new print quality (PQ) goals and depletion metrics to align with updated page yield definitions.', 'Rationale': 'Ensures consistent output quality and accurate yield reporting.', 'Priority': 'High', 'Stakeholders': 'R&amp;D, Quality Assurance, Product Management', 'Dependencies': 'PQ testing and metric definition.', 'Acceptance Criteria': 'Printer meets new PQ goals and depletion is accurately reported per defined metrics.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '28', 'Title': 'Reuse of Marconi Hi PDL and Tux dASIC, Hannibal aASIC, Raccoon PSU', 'Description': 'Reuse Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new printer.', 'Rationale': 'Leverages proven hardware and reduces development costs.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Manufacturing', 'Dependencies': 'Compatibility with new systems.', 'Acceptance Criteria': 'All reused components function within specification in the new printer.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '29', 'Title': 'Stingray Wi-Fi Module Integration', 'Description': 'Integrate the Stingray Wi-Fi module into the printer for wireless connectivity.', 'Rationale': 'Provides modern wireless networking capabilities.', 'Priority': 'Medium', 'Stakeholders': 'End Users, IT, Product Management', 'Dependencies': 'Firmware and hardware integration.', 'Acceptance Criteria': 'Printer connects to Wi-Fi networks using Stingray module and passes connectivity tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '30', 'Title': 'FW Dune Firmware Platform', 'Description': 'Use the Dune firmware platform for printer operation.', 'Rationale': 'Ensures compatibility with HP firmware standards and feature sets.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D, Firmware, Product Management', 'Dependencies': 'Firmware integration and validation.', 'Acceptance Criteria': 'Printer operates reliably using Dune firmware in all standard scenarios.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '31', 'Title': 'Gauss4.xx Security (HW &amp; FW)', 'Description': 'Implement Gauss4.xx security features at both hardware and firmware levels.', 'Rationale': 'Protects against security threats and ensures compliance with HP security standards.', 'Priority': 'High', 'Stakeholders': 'Security, IT, R&amp;D', 'Dependencies': 'HW/FW integration and validation.', 'Acceptance Criteria': 'Printer passes all Gauss4.xx security compliance tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '32', 'Title': 'SMB and Enterprise Solution Support', 'Description': 'Provide solutions for SMB manageability and enterprise support, including WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM.', 'Rationale': 'Addresses needs of business customers and enhances manageability.', 'Priority': 'Medium', 'Stakeholders': 'SMB, Enterprise Customers, IT, Product Management', 'Dependencies': 'Solution integration and software support.', 'Acceptance Criteria': 'Printer integrates with WJA, HPSM, and JAM and passes manageability tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '33', 'Title': 'Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD', 'Description': 'Ensure compatibility and support for a range of HP clients and drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD.', 'Rationale': 'Maximizes ecosystem compatibility and ease of deployment.', 'Priority': 'Medium', 'Stakeholders': 'IT, End Users, Product Management', 'Dependencies': 'Driver development and testing.', 'Acceptance Criteria': 'Printer installs and operates correctly with all listed clients and drivers.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '34', 'Title': 'High Throughput: 25/20 ppm (PDL: 25/19 ppm)', 'Description': 'Achieve print speeds of 25/20 pages per minute (PDL: 25/19 ppm).', 'Rationale': 'Meets market expectations for speed in the target segments.', 'Priority': 'High', 'Stakeholders': 'End Users, Product Management', 'Dependencies': 'Mechanical and firmware optimization.', 'Acceptance Criteria': 'Printer achieves specified speeds in standard performance tests.', 'Confidence': 0.9, 'citation': 'Magellan_SI_1-pager.pdf, page 1'}, {'Requirement ID': '35', 'Title': 'Host 12K-CMYK and Trade Page 6K (Flexible)', 'Description': 'Support for hosting 12,000-page CMYK and trade page 6,000 yields as a flexible requirement.', 'Rationale': 'Expands product offering and addresses diverse customer needs.', 'Priority': 'Low', 'Stakeholders': 'Product Management, Marketing', 'Dependencies': 'Ink system and yield validation.', 'Acceptance Criteria': 'Printer can support 12K-CMYK and 6K trade page yields if required by market.', 'Confidence': 0.7, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}, {'Requirement ID': '36', 'Title': 'Serviceability: Maintenance Box', 'Description': 'Design the printer for easy maintenance box replacement to improve serviceability.', 'Rationale': 'Reduces downtime and maintenance effort for users and service providers.', 'Priority': 'Medium', 'Stakeholders': 'Service, End Users', 'Dependencies': 'Maintenance box design and documentation.', 'Acceptance Criteria': 'Maintenance box can be replaced without tools and passes serviceability tests.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}, {'Requirement ID': '37', 'Title': 'Warranty Life: 2 Years (Optimized)', 'Description': 'Support a warranty life of 2 years for the printer.', 'Rationale': 'Competitive warranty period increases customer confidence and marketability.', 'Priority': 'Medium', 'Stakeholders': 'Product Management, End Users, Service', 'Dependencies': 'Component reliability and support infrastructure.', 'Acceptance Criteria': 'Printer operates within specification for 2 years under normal usage.', 'Confidence': 0.85, 'citation': 'Magellan_SI_1-pager.pdf, page 2'}]</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printer for SMBs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Develop HP's first business ink tank printer targeted at unmanaged to lightly managed micro/small businesses (SMBs) with 5-250 employees, 6-15 printers, and AMPV of 500 pages.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Addresses a gap in HP's portfolio for CISS PLE Hi segment and meets the needs of SMBs lacking dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>A new business ink tank printer is developed and launched, specifically marketed and positioned for SMBs as described.</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 5, 6, 7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[{'No': '1', 'Title': 'AI Productivity and Manageability Solutions', 'Description': 'Integrate advanced AI-driven productivity features and scan workflow solutions that enhance print, scan, and device management for SMB customers. Includes AI-powered print and scan optimization, and proactive support features.', 'Rationale': 'SMBs require easy-to-use, efficient solutions that reduce manual intervention and streamline workflows, especially with limited IT resources.', 'Priority': 'High', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, Quality, BA', 'Dependencies': 'Requires SMB portal, device telemetry, and AI software integration.', 'Acceptance Criteria': 'AI features demonstrably reduce manual steps in common workflows by at least 30% in user testing; AI-driven recommendations and error handling available in product UI.', 'Confidence': 0.95, 'citation': 'Magellan MRD, Page 4, 7, 10, 11'}, {'No': '2', 'Title': 'Lowest Business TCO (Total Cost of Ownership)', 'Description': 'Design the printer to deliver the lowest total cost of ownership for SMBs, including high-yield ink tanks, minimal maintenance, and energy efficiency.', 'Rationale': 'Cost efficiency is a top priority for SMBs with limited budgets; a low TCO is a key differentiator in the segment.', 'Priority': 'High', 'Stakeholders': 'Marketing, BA, Supplies Quality', 'Dependencies': 'Requires efficient ink tank design, maintenance-free or low-maintenance hardware, and energy-efficient components.', 'Acceptance Criteria': 'Third-party TCO analysis confirms at least 10% lower TCO compared to top competitors under typical SMB usage.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 4, 11'}, {'No': '3', 'Title': 'Customer Replaceable Maintenance Box', 'Description': 'Introduce a replaceable maintenance box that can be easily swapped by the customer without service technician intervention.', 'Rationale': 'Reduces downtime and service costs for SMBs without dedicated IT support.', 'Priority': 'High', 'Stakeholders': 'Quality, R&amp;D Telemetry, Tech Reg, Marketing', 'Dependencies': 'Requires new hardware design and service documentation.', 'Acceptance Criteria': '80% of surveyed SMB users can replace the maintenance box successfully within 5 minutes using only the provided instructions.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '4', 'Title': 'SMB Device Management Portal', 'Description': 'Develop a consolidated web-based portal for SMBs to manage their fleet of printers, monitor usage, receive alerts, and access support.', 'Rationale': 'Unmanaged and lightly managed SMBs need simple, centralized management tools to operate efficiently without dedicated IT staff.', 'Priority': 'High', 'Stakeholders': 'Marketing, GXD, R&amp;D Telemetry, BA', 'Dependencies': 'Requires device telemetry integration and secure web portal development.', 'Acceptance Criteria': 'Portal supports registration, usage monitoring, and alerting for at least 15 devices per account; &gt;90% of beta users report satisfaction with portal usability.', 'Confidence': 0.9, 'citation': 'Magellan MRD, Page 7, 10'}, {'No': '5', 'Title': 'High Serviceability – PHA and MINK', 'Description': 'Enable key printer components (PHA) to be customer replaceable and MINK to be service center replaceable, with a target of making MINK customer replaceable if out of warranty.', 'Rationale': 'Improves uptime and reduces operational costs for SMBs; aligns with limited IT resources in target segment.', 'Priority': 'Medium', 'Stakeholders': 'Quality, R&amp;D Telemetry, Tech Reg, Prod Steward', 'Dependencies': 'Requires modular hardware design and clear service documentation.', 'Acceptance Criteria': 'Service time for PHA replacement by customer &lt;10 minutes; MINK replacement process documented and validated for service centers.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '6', 'Title': 'Keyed Ink Bottles', 'Description': 'Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.', 'Rationale': 'Reduces errors and service calls due to incorrect ink usage; improves customer experience and device reliability.', 'Priority': 'Medium', 'Stakeholders': 'Supplies Quality, Quality, Marketing', 'Dependencies': 'Requires new bottle design and packaging changes.', 'Acceptance Criteria': 'No more than 1% of support calls related to ink refilling errors in first 12 months post-launch.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 4'}, {'No': '7', 'Title': 'Support for PaaS (Printing as a Service)', 'Description': "Ensure the printer supports integration with HP's Printing as a Service (PaaS) offerings, including remote monitoring, automated supplies replenishment, and usage analytics.", 'Rationale': 'Enables recurring revenue models and provides SMBs with predictable costs and proactive support.', 'Priority': 'Medium', 'Stakeholders': 'Marketing, R&amp;D Telemetry, BA, DVAR', 'Dependencies': 'Requires connectivity, telemetry, and integration with HP PaaS backend.', 'Acceptance Criteria': 'Printer can be onboarded to HP PaaS platform and supports automated supplies ordering and usage reporting.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 4, 10'}, {'No': '8', 'Title': 'PDL/PS Support and Speed Improvements', 'Description': 'For PDL SKUs, support PCL/PS printing languages and achieve print speeds of 25/20 ppm (improved from current 25/19).', 'Rationale': 'Meets the needs of more demanding SMB environments and ensures compatibility with business applications.', 'Priority': 'Medium', 'Stakeholders': 'Marketing, GXD, BA', 'Dependencies': 'Requires firmware and hardware updates for speed and language support.', 'Acceptance Criteria': 'PDL SKU achieves rated speeds in independent benchmark tests; PCL/PS compatibility validated with major OS and applications.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '9', 'Title': 'Blue Angel Certification', 'Description': 'Obtain Blue Angel eco-label certification for the PDL SKU, demonstrating compliance with environmental and sustainability standards.', 'Rationale': 'Addresses growing customer and regulatory demand for sustainable products; provides a competitive differentiator.', 'Priority': 'Medium', 'Stakeholders': 'Prod Steward, Tech Reg, Marketing', 'Dependencies': 'Requires product design and documentation to meet Blue Angel requirements.', 'Acceptance Criteria': 'PDL SKU receives official Blue Angel certification prior to launch.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4'}, {'No': '10', 'Title': 'High Recycled Content Plastic (RCP)', 'Description': 'Design the printer with at least 60% recycled content plastic, exceeding competitors like Epson (30%).', 'Rationale': "Supports HP's sustainability goals and appeals to environmentally conscious SMB customers.", 'Priority': 'High', 'Stakeholders': 'Prod Steward, Marketing, Quality', 'Dependencies': 'Requires sourcing and validation of high-RCP materials.', 'Acceptance Criteria': 'Bill of materials and third-party audit confirm at least 60% RCP in product housing.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 11'}, {'No': '11', 'Title': 'Mobile Printing and HP App Integration', 'Description': 'Enable seamless mobile printing and management through the HP App, supporting major mobile platforms and workflows.', 'Rationale': 'SMBs require flexible, on-the-go printing and device management, especially with hybrid work trends.', 'Priority': 'Medium', 'Stakeholders': 'Marketing, GXD, BA', 'Dependencies': 'Requires mobile app development and printer connectivity features.', 'Acceptance Criteria': 'Printer is discoverable and usable via HP App on iOS/Android; &gt;90% success rate in mobile print tasks during user testing.', 'Confidence': 0.85, 'citation': 'Magellan MRD, Page 9, 10'}, {'No': '12', 'Title': 'Advanced Telemetry for Device Health and Usage', 'Description': 'Incorporate advanced telemetry features to monitor device health, usage patterns, and proactively alert users/service providers of issues.', 'Rationale': 'Enables predictive maintenance, reduces downtime, and supports manageability for SMBs.', 'Priority': 'Medium', 'Stakeholders': 'R&amp;D Telemetry, Quality, BA, DVAR', 'Dependencies': 'Requires secure data transmission and integration with management portal.', 'Acceptance Criteria': 'Telemetry data available to users and HP backend; &gt;95% accuracy in predictive failure alerts in pilot deployments.', 'Confidence': 0.8, 'citation': 'Magellan MRD, Page 4, 12'}]</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI Productivity &amp; Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-driven productivity features, including Perfect Print and Perfect Scan, and provide best-in-class scan workflow and manageability solutions.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Differentiates HP's offering and addresses customer needs for easier business management and efficiency.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Marketing, R&amp;D Telemetry, GXD, BA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Development of AI software and integration with printer firmware.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AI features (Perfect Print/Scan) and manageability solutions are available at launch, validated by user testing and documentation.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Design the printer to deliver HP's lowest business TCO, minimizing intervention and maintenance for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a top priority for SMBs and a key differentiator in a competitive market.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Marketing, BA, Quality</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Printer hardware design, ink tank efficiency, consumables pricing.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Documented TCO analysis showing Magellan has the lowest business TCO among HP's SMB printers.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ensure the printer is manufactured with at least 60% recycled content plastic, exceeding competitor benchmarks.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sustainability is a key customer value and competitive differentiator (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Quality</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sourcing of recycled materials, manufacturing processes.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bill of materials and independent verification confirm 60% or greater RCP in product.</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Include a user-replaceable maintenance box to reduce service calls and downtime for SMBs.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Addresses new customer segment needs and supports ease of maintenance for non-IT users.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Quality, Marketing, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Printer design, supply chain for maintenance boxes.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Maintenance box is user-replaceable, with supporting documentation and positive user feedback from pilot testing.</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal for Device Management</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Develop a consolidated portal for SMBs to manage their printers, targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Simplifies device management for non-IT decision makers and enhances customer experience.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Portal software development, integration with device telemetry.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Portal is available at launch, supports management of multiple devices, and receives positive usability testing results.</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Offer warranty coverage of 80,000 pages or 2 years (whichever is first), and enable customer-replaceable parts (PHA) with MINK service center support if out of warranty.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs for SMBs, aligns with market expectations.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Service infrastructure, part supply chain, documentation.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Warranty terms are clearly communicated, and customer-replaceable parts are supported in product documentation and service training.</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure user safety and product reliability.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Prevents user error and potential product damage, supporting quality and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Supplies Quality, Quality, Marketing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ink bottle and printer hardware design.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ink bottles are uniquely keyed and only compatible with intended printer models; verified by testing.</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PDL SKU Performance Improvements</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>For PDL SKUs, deliver print speeds of at least 25 ppm (pages per minute) for black and 20 ppm for color, with PDL/PS support and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ensures competitive performance and meets regulatory/environmental standards for business users.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tech Reg, Quality, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hardware and firmware development, certification process.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PDL SKUs achieve specified print speeds and obtain Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Advanced Solutions Support</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Non-PDL SKUs must support SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Platform as a Service) features.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Extends manageability and solutions offering to a broader product range, increasing value for SMBs.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Software development, portal integration.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Non-PDL SKUs are compatible with SMB2.0 Solutions and portal, and support PaaS features at launch.</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI Solutions for Print, Scan, Support</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Develop and integrate AI-powered solutions for print, scan, and support workflows to enhance productivity and user experience.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Leverages emerging technology to deliver superior user experiences and business outcomes.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Marketing, GXD, BA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AI software development, integration with device and portal.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AI-powered print, scan, and support features are available at launch and validated through user testing.</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 10, 11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing capabilities through the HP App, supporting key SMB use cases.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Addresses the growing trend of mobile device usage in SMBs and enhances convenience.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HP App integration, printer firmware support.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully functional via HP App and verified by interoperability testing.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Implement telemetry features to collect device usage and health data for proactive support and analytics.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enables predictive maintenance, enhances serviceability, and supports ongoing product improvement.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Device firmware, portal integration, data privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected securely, accessible via portal, and used for analytics; compliant with data regulations.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Maintenance-Free or Less Maintenance Design</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Design the printer to require minimal maintenance, with fewer parts to replace over its lifetime (subject to ongoing investigation).</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Reduces total cost of ownership and appeals to SMBs without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hardware design, parts durability testing.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Documented reduction in maintenance frequency and parts replacement compared to prior models; validated by pilot testing.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with Specific Page Yields</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for Black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>To meet new market demands for higher yield and minimize user intervention, supporting longer print cycles.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ink compatibility, bottle manufacturing, printer hardware design</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NGB keyed bottles are available in specified capacities and pass yield validation tests with supported printers.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Bottles</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Design ink bottles and filling mechanisms to ensure spill-free operation during user replacement.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service calls due to spills or contamination.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>End Users, Service, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bottle and tank interface design</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>User testing demonstrates no ink spills during standard replacement procedures.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Integrate NOA-F component with metal foiled labyrinth and lid label, maintaining existing click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enhances security and reliability of ink delivery, leveraging proven mechanisms.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NOA-F supplier, mechanical design</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NOA-F units pass mechanical and reliability tests with new features.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Inks</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Continue use of SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages existing validated components.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Compatibility with new hardware and bottle design</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>No reformulation required; components pass integration tests in new printer.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Reliability &amp; Performance Modeling</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Model and validate reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, IDS, startup, and NOA-F EOL (End of Life).</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ensures robust performance and longevity of ink system under various conditions.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Access to data, simulation tools, test hardware</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>All models are validated and performance meets defined thresholds under test conditions.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Develop models to predict ink stability in tank, including impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Prevents print quality degradation and supports longer tank lifespans.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ink chemistry, tank design</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Stability models predict no significant PQ impact over defined service intervals.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts for Warranty Support</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NOA-F components must be available as service parts for in-warranty repairs and replacements.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Supports serviceability and warranty commitments for customers.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Service, Warranty, Supply Chain</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Inventory management, service logistics</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NOA-F parts are stocked and available for warranty service requests.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Integrate Acumen 6 feature into the ink bottle lid for enhanced tracking or authentication.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Improves supply chain traceability and counterfeit prevention.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Supply Chain, Security, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lid design, Acumen 6 integration</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Acumen 6 functionality is validated in production lids.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Modify existing SA14 factory line to support NOA-F; add Magi ink cartridge and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Enables efficient manufacturing and assembly of new features.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Manufacturing, Operations</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Factory layout, equipment procurement</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Factory lines are updated and pass production readiness reviews.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>New Mold for Keyed Caps</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Develop molds for 1 to 4 new keyed ink bottle caps as part of the new bottle system.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Supports new bottle keying and prevents incorrect bottle usage.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cap design, mold fabrication</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>New caps are produced and validated for fit and function.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ensure that both PHA and NOA-F are user-replaceable components in the field.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>End Users, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Component design, user documentation</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Users can replace PHA and NOA-F following provided instructions with no tools required.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Set new warranty page life target at 80,000 pages for the Magellan printer series.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Aligns with competitive benchmarks and customer expectations for durability.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Product Management, QA, End Users</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Component reliability, consumables yield</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Printers achieve 80,000 pages without failure under warranty conditions.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Size Increase for Tank with Reddington ID</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Increase tank size to support higher capacity, maintaining Reddington ID design cues.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Supports longer print cycles and larger bottle sizes.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>R&amp;D, Industrial Design, Product Management</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chassis design, industrial design review</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Tank accommodates larger bottles and passes fit validation.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging for shipping and protection of the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Improves product protection during shipping and meets regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Logistics, QA, Packaging</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Supplier selection, packaging design</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>EPS foam packaging passes drop and vibration tests.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel environmental requirements for the PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Facilitates sales in regulated markets and supports corporate sustainability goals.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Compliance, Product Management, QA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Design for environment, certification process</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Products are certified to EPEAT3, LOT4, and Blue Angel standards prior to launch.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Modify input and output trays to accommodate tank protrusion resulting from increased size.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and user convenience.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>R&amp;D, Industrial Design, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tray design, tank size finalization</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Trays function properly with new tank design and pass user testing.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display Integration</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3” CGD (Color Graphic Display) as standard for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Enhances user interface and supports advanced printer functions.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, UI/UX</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Display sourcing, firmware integration</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Display is functional and passes usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>New Tube Routing and Integration</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new routing and integration for the 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Improves ink flow efficiency and supports new tank layout.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tube design, routing validation</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Tube routing supports required flow rates and passes assembly tests.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Update service station to manage aerosols generated due to new tank and spit platform changes.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Prevents contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA, Service</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Service station design, aerosol management solutions</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Aerosol levels remain within safe limits during operation.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Model and validate carriage dynamics and forces with new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with updated hardware.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carriage design, tube layout</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Carriage operates within force limits and passes reliability tests.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Paperpath Support for Increased Page Life</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Update paperpath design to support increased page life and durability.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Enables the new 80,000-page warranty life goal.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA, Product Management</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paperpath materials, mechanical design</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Paperpath components pass accelerated life testing for 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part Post 80K Life</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Make ink maintenance a serviceable part at service centers after 80,000-page printer life.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Reduces total cost of ownership and supports extended use beyond warranty.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Service documentation, part supply</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance part post-80K life.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>New IDS Make-Break and FI Connection</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Implement new make-break and fluidic interconnect (FI) connection in IDS, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Improves reliability and prevents incorrect connections.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Service</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>IDS design, LEBI ink-tank, SHAID integration</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>IDS passes connection and reliability tests with new features.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Develop new startup algorithm and air management system for IDS to ensure optimal ink flow and minimize startup issues.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Enhances startup reliability and print readiness.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA, Service</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>IDS hardware, firmware development</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Startup success rate exceeds 99% in field testing.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals &amp; Depletion Definition</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Establish new print quality goals and depletion definitions to align with updated page yield targets.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ensures customer satisfaction and accurate yield reporting.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA, Product Management</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Test protocol, yield modeling</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics are met in standardized test runs.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Continue use of Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the Magellan platform.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven components.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hardware compatibility</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Components function correctly in Magellan platform integration tests.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity in the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Supports modern connectivity standards and enhances user experience.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, IT</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Wi-Fi module sourcing, firmware integration</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Wi-Fi module passes connectivity and interoperability tests.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FW Dune and Gauss4.xx Security Integration</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Integrate FW Dune and Gauss4.xx security features into hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ensures device and data security, meeting corporate and regulatory standards.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>IT Security, Compliance, Product Management</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Firmware development, security validation</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Security features pass penetration and compliance testing.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Support PaaS, WorkFromHome, and Flexworker Services</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Enable support for PaaS business models and usage scenarios such as WorkFromHome and Flexworker.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Aligns with evolving customer needs and business models.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Business, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Service enablement, software integration</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Printer supports remote management and subscription services as specified.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SMB and Enterprise Solution Integration</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Integrate SMB manageability and enterprise support features, including WJA, HPSM, and JAM.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Expands addressable market and meets enterprise IT requirements.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Enterprise Customers, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Solution integration, driver support</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Enterprise management features function as intended in customer environments.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Support for Multiple Client Drivers</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD client drivers.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Maximizes interoperability and ease of deployment across customer environments.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>IT, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Driver development, OS compatibility</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>All listed drivers are supported and pass functional testing.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Schedule Adherence for S’27 Launch</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Meet aggressive time-to-market goals for S’27 with minimal investment, as outlined in the program schedule.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Critical for competitive positioning and revenue targets.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Program Management, Product Management, Executive Team</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>All development and manufacturing readiness activities</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>All milestones in the S’27 schedule are met with no major delays.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve a minimum life of 65,000 pages as a hard constraint.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ensures core component reliability and meets business priorities.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA, Product Management</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PHA design, component reliability</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA meets or exceeds 65,000-page life in testing.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Warranty for Magellan printers must cover 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and business optimization priorities.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Warranty Service</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Component reliability, warranty policy</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system reflect 2-year/80,000-page coverage.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 ppm (PDL: 25/19 ppm)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Printer must achieve throughput speeds of 25/20 pages per minute (PDL: 25/19 ppm).</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Meets performance expectations for target market segments.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Print engine design, firmware</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Printers achieve specified throughput in standardized tests.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Serviceability via Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Enable serviceability through a maintenance box for easier maintenance and reduced downtime.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Improves customer satisfaction and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Maintenance box design, service documentation</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Maintenance box can be serviced or replaced as per service guidelines.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,17 +491,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity and manageability solutions, including AI-driven print and scan workflows, to simplify business operations for SMB customers.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for Black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
+          <t>To meet market demand for higher yield and reduce frequency of replacements, improving customer satisfaction and cost efficiency.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,17 +511,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and device management systems.</t>
+          <t>Requires bottle redesign and compatibility with new IDS and tank system.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Demonstrated deployment of AI-driven productivity features in print and scan workflows; user testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
+          <t>Bottles must be validated to deliver at least 6,000 pages for Black and CMY, with CMY bottle size supporting &gt;8,000 pages in controlled tests.</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -529,14 +529,10 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,17 +547,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deliver HP’s lowest business TCO through a combination of cost-efficient ink tank technology and minimal maintenance requirements.</t>
+          <t>Ensure all ink bottles and refilling processes are spill-free to enhance reliability and user experience.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cost efficiency is a primary decision driver for SMBs with limited budgets.</t>
+          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service costs.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -571,32 +567,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Marketing, DVAR, BA</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Dependent on ink tank system design and maintenance strategy.</t>
+          <t>Bottle design, IDS, NOA-F integration.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Independent benchmark shows TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
+          <t>No ink spillage observed in 99% of refilling scenarios during reliability testing.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -611,17 +603,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>High Serviceability and Customer Replaceable Parts</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Design the printer for high serviceability with customer-replaceable key components (e.g., maintenance box, printhead assembly), and ensure service center support for non-customer-replaceable items.</t>
+          <t>Integrate a metal foiled labyrinth and lid label into the NOA-F component, with no changes to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
+          <t>Enhances part reliability, security, and traceability without redesigning key mechanisms.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -631,17 +623,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
+          <t>R&amp;D, Manufacturing, Quality</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Requires modular hardware design and clear documentation.</t>
+          <t>Existing NOA-F design, TDF, push-push mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>At least 80% of common maintenance tasks can be performed by end users; documentation and training materials provided.</t>
+          <t>NOA-F must pass validation with new labyrinth and lid label while maintaining existing functional interfaces.</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -649,14 +641,10 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -671,17 +659,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SMB Portal for Device Management</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers, targeting office managers and generalist IT users in SMBs.</t>
+          <t>Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new platform.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
+          <t>Reduces R&amp;D cost and leverages proven, reliable components.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -691,32 +679,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Requires integration with telemetry and device firmware.</t>
+          <t>Compatibility with new bottle and IDS systems.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks must meet all print quality and reliability standards in Magellan platform.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -731,37 +715,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles for Error Prevention</t>
+          <t>Enhanced Reliability and Characterization Modeling</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
+          <t>Characterize and model reliability, WVTR, air gain, flow rate, IDS, startup, and NOA-F end-of-life (EOL) parameters.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Reduces service incidents and improves user experience for non-technical users.</t>
+          <t>Ensures system robustness, longevity, and supports warranty claims.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Supplies Quality, Quality, Prod Steward</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Requires new bottle and tank interface design.</t>
+          <t>Integration with IDS, tank, and bottle systems.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Field testing shows &lt;2% incorrect refill incidents over 12 months of use.</t>
+          <t>Models must be validated and predictive within +/-10% of observed reliability outcomes in pilot runs.</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -769,14 +753,10 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -791,17 +771,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal</t>
+          <t>Ink Stability Modeling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ensure printer supports Platform-as-a-Service (PaaS) and the new Advanced View SMB portal for enhanced business solutions.</t>
+          <t>Model ink stability in tanks and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
+          <t>Ensures long-term print quality and reduces field failures.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -811,32 +791,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Marketing, GXD, BA, R&amp;D Telemetry</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Requires software and firmware compatibility with HP’s evolving platforms.</t>
+          <t>Tank design, ink properties, IDS interface.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
+          <t>Ink stability modeling must predict PQ impact over 2-year warranty life with &lt;5% deviation from field data.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -851,17 +827,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PDL/PS Support and Improved Print Speed</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>For PDL SKU, provide PDL/PS (Page Description Language/PostScript) support and improve print speed to 25/20 ppm (from current 25/19).</t>
+          <t>Provide NOA-F as service parts for in-warranty support.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
+          <t>Reduces downtime and improves customer experience by enabling field replacement.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -871,17 +847,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, Marketing, DVAR</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware enhancements.</t>
+          <t>NOA-F part inventory, service logistics.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PDL SKU demonstrates print speed of at least 25/20 ppm and passes PDL/PS compatibility tests.</t>
+          <t>NOA-F service parts available and replaceable within warranty support SLAs.</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -889,14 +865,10 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -911,17 +883,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blue Angel Environmental Certification</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Obtain Blue Angel certification for the printer to meet environmental and sustainability standards.</t>
+          <t>Integrate Acumen 6 technology into the ink bottle lid for improved traceability or anti-counterfeiting.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
+          <t>Enhances product security and traceability in the supply chain.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -931,32 +903,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prod Steward, Tech Reg, Quality</t>
+          <t>Quality, Supply Chain, Security</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Requires compliance with Blue Angel criteria.</t>
+          <t>Lid design, Acumen 6 technology integration.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blue Angel certification awarded by launch date.</t>
+          <t>Acumen 6 features must be verifiable on all production lids and pass security audits.</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -971,17 +939,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High Recycled Content in Plastics (60% RCP)</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer’s plastics are made from recycled content, exceeding key competitors.</t>
+          <t>Modify SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Mold 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
+          <t>Ensures manufacturing capability for new components and bottle designs.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -991,17 +959,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Quality</t>
+          <t>Manufacturing, R&amp;D, Supply Chain</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Requires supply chain and materials engineering alignment.</t>
+          <t>Existing line configuration, new component designs.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audit confirm ≥60% RCP in plastics.</t>
+          <t>SA14 and Orcus 5 lines operational with new components and pass production validation.</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1009,14 +977,10 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1031,17 +995,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI Solutions for Print, Scan, and Support</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deploy AI-driven solutions in print, scan, and support functions to optimize workflows and reduce manual intervention.</t>
+          <t>Design PHA and NOA-F to be customer replaceable, enhancing serviceability.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
+          <t>Improves user experience and reduces service costs.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1051,32 +1015,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, Marketing, BA</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Requires integration with device firmware and cloud services.</t>
+          <t>PHA and NOA-F design, service documentation.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AI features are operational at launch and reduce manual steps by at least 30% in key workflows.</t>
+          <t>End users can replace PHA and NOA-F using provided instructions with &lt;5% error rate in usability tests.</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1091,17 +1051,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>New Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
+          <t>Set new warranty page life goal for the printer at 80,000 pages.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
+          <t>Aligns with market expectations for durability and reduces TCO for customers.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1111,32 +1071,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Marketing, GXD, BA</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Requires app integration and device firmware support.</t>
+          <t>Component reliability, maintenance schedule.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
+          <t>Printer must operate without critical failure for at least 80,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1151,52 +1107,48 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Warranty and Serviceability Thresholds</t>
+          <t>Product Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Provide a warranty of 80,000 pages or 2 years (whichever comes first) and establish serviceability thresholds for key components.</t>
+          <t>Adopt Reddington ID for product with increased tank size, while keeping Marconi-HI ADF unchanged.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ensures predictable support costs and aligns with SMB expectations for reliability.</t>
+          <t>Supports higher ink capacity and page yield without redesigning ADF.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Requires warranty policy alignment and service documentation.</t>
+          <t>Tank redesign, Reddington ID integration.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Warranty terms published and service processes validated before launch.</t>
+          <t>Product ID and tank design validated in pilot production; ADF remains unchanged.</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1211,17 +1163,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maintenance-Free or Low Maintenance Design</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Design the printer to be maintenance-free or require minimal maintenance, with fewer parts to replace over product life.</t>
+          <t>Use EPS foam packaging for the product.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reduces total cost of ownership and appeals to SMBs lacking technical staff.</t>
+          <t>Improves product protection during shipping and handling.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1231,17 +1183,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, Prod Steward, Marketing</t>
+          <t>Manufacturing, Logistics, Quality</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Subject to feasibility investigation and hardware design constraints.</t>
+          <t>Packaging design, supply chain sourcing.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Maintenance requirements are at least 30% lower than comparable products; validated by field testing.</t>
+          <t>EPS foam packaging passes ISTA transit and drop tests.</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1249,10 +1201,2690 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REQ-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental standards (PDL SKU).</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Compliance is necessary for market access and corporate sustainability goals.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulatory, Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Design, materials, documentation.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Product certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Modify input and output trays to align with new tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and maintains compact footprint.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, End Users</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tank design, tray redesign.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank in user tests and fit within defined product envelope.</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REQ-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3” CGD (Color Graphic Display) into the product.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Enhances user interface and usability.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>UI design, display sourcing.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Display is functional, clear, and passes user experience tests.</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REQ-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4-Tube Platform with New Routing and Integration</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Supports increased ink flow and reliability with new tank design.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tube design, tank integration.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>New routing and integration validated in reliability and flow tests.</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REQ-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Update service station for improved aerosol management and adapt platform for tank changes.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Reduces maintenance and improves print environment cleanliness.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Quality</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Service station design, tank integration.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Aerosol levels remain within safety thresholds during operation.</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>REQ-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Carriage design, tube routing, weight distribution.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Carriage operates reliably and meets print quality standards in system tests.</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>REQ-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Paperpath Support for Increased Page Life</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Update paperpath design to support increased 80,000-page life goal.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability over extended use.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Service</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paperpath materials, wear modeling.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Paperpath passes accelerated life testing for 80,000 pages without critical failure.</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>REQ-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ink Maintenance as Serviceable Part (Post 80k Life)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Extends product life and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Maintenance part design, service documentation.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance part within standard service time.</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>REQ-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Introduce 140ml black bottles and new, larger CMY bottles for the ink system.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bottle design, tank compatibility.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Bottles validated for compatibility and yield in system tests.</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>REQ-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New Make-Break and FI Connection in IDS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Develop new make-break and FI (fluidic interconnect) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Improves reliability, prevents mis-filling, and supports larger tank sizes.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Quality</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>IDS, LEBI ink-tank, SHAID integration.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Connections pass reliability and mis-fill prevention tests.</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REQ-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Implement new IDS startup algorithm and air management system.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and air handling for new tank and bottle system.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Quality</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>IDS, tank, bottle integration.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Startup and air management pass reliability and air ingress tests.</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>REQ-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New Servicing and Startup Algorithm</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Develop new algorithms for servicing and startup to support new platform requirements.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Improves reliability and user experience with new system components.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, End Users</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Firmware, IDS, tank integration.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Algorithms validated in service and startup scenarios with &lt;2% failure rate.</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>REQ-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New Print Quality Goals and Depletion Definitions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Set new print quality (PQ) goals and depletion definitions to align with updated page yield targets.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ensures consistent output quality and accurate yield metrics.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Product Management</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PQ testing, depletion modeling.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics validated in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>REQ-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU hardware in the new platform.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Leverages proven hardware to reduce development cost and risk.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Compatibility with new platform design.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Hardware passes system integration and functional validation.</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>REQ-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Provides modern connectivity options for users.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, IT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Firmware, hardware interface design.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Wi-Fi module passes connectivity and performance tests.</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>REQ-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dune Firmware Platform</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Utilize Dune firmware platform for the printer.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ensures compatibility and leverages existing firmware capabilities.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>R&amp;D, Firmware, Product Management</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Firmware integration, hardware compatibility.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Firmware passes system and feature validation tests.</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>REQ-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Meets enterprise security requirements and protects user data.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>IT, Security, Enterprise Customers</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Hardware and firmware design, compliance standards.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Security features pass penetration and compliance tests.</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>REQ-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Design solutions, services, and business models to address needs of consumer, SMB, and enterprise markets.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports diverse customer requirements.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Product Management, Sales, Marketing</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Feature set, service offerings, pricing models.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Solutions and services available and validated for each segment at launch.</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>REQ-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SMB Manageability and Enterprise Support</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Include SMB manageability and enterprise support features such as WJA, HPSM, and JAM.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Meets IT requirements for business customers and enhances manageability.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SMB, Enterprise Customers, IT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Software integration, feature development.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Manageability features functional and validated in enterprise test environments.</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>REQ-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients &amp; Drivers</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Supports wide range of deployment scenarios and user environments.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IT, End Users, Support</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Driver and client integration.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>All clients and drivers pass compatibility and installation tests.</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>REQ-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Protect Micro/SMB Segments and HP's Ink/Laser Profit Pool</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Design product features and pricing to protect HP's micro/SMB segments and profit pool from competitors.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Strategic business objective to maintain market share and profitability.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Feature set, pricing, market analysis.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Market share and profit pool metrics maintained or improved post-launch.</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>REQ-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lead with LaserJet, Flank with PDL in Medium and Enterprise Segments</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Strategically position LaserJet as lead and PDL as flank in medium and enterprise segments to win over competitors like Epson as CISS grows.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Supports HP's competitive positioning in the growing CISS market.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing, Sales</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Product positioning, marketing strategy.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Market share in medium/enterprise segments grows versus competitors.</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>REQ-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Grow Profitable CISS Share in New Segments</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Expand CISS offerings to new segments to grow HP's profitable market share.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Increases revenue and market penetration.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Product Management, Business Leadership, Sales</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Feature development, market research.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CISS share in new segments increases post-launch.</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>REQ-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Highly Leverage Watt-LE Mech Platform and Marconi-Hi Product</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Leverage Watt-LE mechanical platform and Marconi-Hi product (Reddington ID) for new Magellan solution.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Speeds development and reduces investment by reusing proven platforms.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, Manufacturing</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Platform compatibility, feature integration.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Platform integration validated in system tests.</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>REQ-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Integrate CISS IDS, NOA-F, and ink tanks into the new product platform.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Supports modern CISS features and improves product competitiveness.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Component integration, system design.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>All components function as integrated system in validation tests.</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>REQ-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New NGB Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Develop new NGB keyed ink bottles for the platform.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Prevents mis-filling and supports new tank and IDS system.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, End Users</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bottle design, IDS, tank integration.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Keyed bottles prevent mis-filling in &gt;99% test cases.</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>REQ-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Schedule as Constrained Priority</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Adhere to schedule as the least flexible business constraint for the program.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ensures timely market entry and supports business objectives.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Program Management, R&amp;D, Business Leadership</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>All development activities, resource allocation.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>All key milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>REQ-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K as Constrained Priority</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages as a constrained program requirement.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Critical for warranty, reliability, and cost targets.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Product Management</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA design, reliability modeling.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes life testing for 65,000 pages with &lt;1% failure rate.</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>REQ-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years and 80,000 Pages as Optimized Priority</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Optimize for warranty life of 2 years and 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Meets customer expectations for durability and value.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>End Users, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Component reliability, maintenance schedule.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Product passes reliability testing for 2 years/80,000 pages without critical failure.</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>REQ-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Optimize for print throughput of 25/20 ppm (PDL: 25/19 ppm).</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Competitive performance metric for target market.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Print engine, firmware, hardware.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Printer achieves rated throughput in standard performance tests.</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>REQ-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box) as Optimized Priority</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Optimize serviceability, focusing on maintenance box accessibility and replacement.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Reduces service time and improves customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Maintenance box design, service documentation.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Maintenance box is replaceable within defined service time.</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>REQ-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SMB Solution as Optimized Priority</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB market needs.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Increases product adoption and satisfaction in SMB segment.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Feature set, solution integration.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SMB features validated in customer pilots and feedback.</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>REQ-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PaaS (Platform as a Service) as Optimized Priority</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Optimize for PaaS business model and schedule.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Enables new revenue streams and flexible deployment.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Product Management, Business Leadership, IT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Feature enablement, service integration.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>PaaS features operational and validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>REQ-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K as Flexible Priority</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Host 12,000-page CMYK and trade page 6,000 as flexible priorities for the program.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Provides flexibility for future product enhancements or market demands.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Business Leadership</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Future development, market trends.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12K-CMYK and 6K trade page features can be enabled as needed.</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-powered productivity and manageability solutions, including AI-driven print and scan workflows, to simplify business operations for SMB customers.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Requires integration with SMB portal and device management systems.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Demonstrated deployment of AI-driven productivity features in print and scan workflows; user testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Deliver HP’s lowest business TCO through a combination of cost-efficient ink tank technology and minimal maintenance requirements.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a primary decision driver for SMBs with limited budgets.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Marketing, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Dependent on ink tank system design and maintenance strategy.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Independent benchmark shows TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>High Serviceability and Customer Replaceable Parts</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Design the printer for high serviceability with customer-replaceable key components (e.g., maintenance box, printhead assembly), and ensure service center support for non-customer-replaceable items.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Requires modular hardware design and clear documentation.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>At least 80% of common maintenance tasks can be performed by end users; documentation and training materials provided.</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SMB Portal for Device Management</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Develop a consolidated SMB portal for managing multiple printers, targeting office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Requires integration with telemetry and device firmware.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles for Error Prevention</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Reduces service incidents and improves user experience for non-technical users.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Supplies Quality, Quality, Prod Steward</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Requires new bottle and tank interface design.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Field testing shows &lt;2% incorrect refill incidents over 12 months of use.</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Support for PaaS and Advanced View SMB Portal</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ensure printer supports Platform-as-a-Service (PaaS) and the new Advanced View SMB portal for enhanced business solutions.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA, R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Requires software and firmware compatibility with HP’s evolving platforms.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PDL/PS Support and Improved Print Speed</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>For PDL SKU, provide PDL/PS (Page Description Language/PostScript) support and improve print speed to 25/20 ppm (from current 25/19).</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Marketing, DVAR</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Requires hardware and firmware enhancements.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PDL SKU demonstrates print speed of at least 25/20 ppm and passes PDL/PS compatibility tests.</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Blue Angel Environmental Certification</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Obtain Blue Angel certification for the printer to meet environmental and sustainability standards.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Prod Steward, Tech Reg, Quality</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Requires compliance with Blue Angel criteria.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Blue Angel certification awarded by launch date.</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>High Recycled Content in Plastics (60% RCP)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ensure that at least 60% of the printer’s plastics are made from recycled content, exceeding key competitors.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Quality</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Requires supply chain and materials engineering alignment.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Bill of materials and third-party audit confirm ≥60% RCP in plastics.</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>Magellan MRD, Page 11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AI Solutions for Print, Scan, and Support</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Deploy AI-driven solutions in print, scan, and support functions to optimize workflows and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Requires integration with device firmware and cloud services.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>AI features are operational at launch and reduce manual steps by at least 30% in key workflows.</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>REQ-011</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Requires app integration and device firmware support.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability Thresholds</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Provide a warranty of 80,000 pages or 2 years (whichever comes first) and establish serviceability thresholds for key components.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ensures predictable support costs and aligns with SMB expectations for reliability.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Requires warranty policy alignment and service documentation.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Warranty terms published and service processes validated before launch.</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Maintenance-Free or Low Maintenance Design</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Design the printer to be maintenance-free or require minimal maintenance, with fewer parts to replace over product life.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Reduces total cost of ownership and appeals to SMBs lacking technical staff.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, Marketing</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Subject to feasibility investigation and hardware design constraints.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Maintenance requirements are at least 30% lower than comparable products; validated by field testing.</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,17 +491,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for Black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+          <t>The printer must integrate advanced AI-driven productivity features, scan workflow enhancements, and manageability solutions to ease business operations for SMBs.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>To meet market demand for higher yield and reduce frequency of replacements, improving customer satisfaction and cost efficiency.</t>
+          <t>Addresses the core value proposition of making business management easier for SMBs and differentiates from competitors.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,17 +511,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Requires bottle redesign and compatibility with new IDS and tank system.</t>
+          <t>Requires integration with SMB portal and AI solution stack.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bottles must be validated to deliver at least 6,000 pages for Black and CMY, with CMY bottle size supporting &gt;8,000 pages in controlled tests.</t>
+          <t>Demonstrated AI productivity features in print and scan workflows; end-user can manage devices through provided solutions; meets user scenario tests.</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -529,10 +529,14 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,17 +551,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Lowest Business TCO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ensure all ink bottles and refilling processes are spill-free to enhance reliability and user experience.</t>
+          <t>The printer must deliver the lowest total cost of ownership (TCO) for SMB customers compared to HP's other business printers.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service costs.</t>
+          <t>Cost efficiency is a top priority for SMBs and a key differentiator.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -567,28 +571,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Marketing, BA, Quality</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, NOA-F integration.</t>
+          <t>Supply chain, pricing, and consumable costs.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No ink spillage observed in 99% of refilling scenarios during reliability testing.</t>
+          <t>Independent TCO analysis demonstrates lowest TCO among HP business printers for target use-case (AMPV ~500 pages/month).</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,17 +611,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate a metal foiled labyrinth and lid label into the NOA-F component, with no changes to click-on push-push and TDF mechanisms.</t>
+          <t>The printer must feature a maintenance box that can be replaced by customers without technical assistance, with service center fallback if needed.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enhances part reliability, security, and traceability without redesigning key mechanisms.</t>
+          <t>Reduces downtime and service costs for SMBs with limited IT resources.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -623,28 +631,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality</t>
+          <t>Quality, R&amp;D Telemetry, Supplies Quality</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Existing NOA-F design, TDF, push-push mechanisms.</t>
+          <t>Design for serviceability, supply chain for replaceable parts.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NOA-F must pass validation with new labyrinth and lid label while maintaining existing functional interfaces.</t>
+          <t>User can replace maintenance box following provided instructions; no tools or minimal tools required; validated in usability testing.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -659,17 +671,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new platform.</t>
+          <t>The printer must use keyed ink bottles to prevent incorrect refilling and ensure user safety and product reliability.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost and leverages proven, reliable components.</t>
+          <t>Prevents user error and damage, supports warranty claims, and enhances customer experience.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -679,17 +691,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>Supplies Quality, Quality, BA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and IDS systems.</t>
+          <t>Ink bottle design, printer hardware design.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks must meet all print quality and reliability standards in Magellan platform.</t>
+          <t>Only correct ink bottle fits and dispenses; passes misfill prevention tests.</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -697,10 +709,14 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -715,17 +731,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Enhanced Reliability and Characterization Modeling</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Characterize and model reliability, WVTR, air gain, flow rate, IDS, startup, and NOA-F end-of-life (EOL) parameters.</t>
+          <t>A consolidated web-based portal must be provided for SMBs to manage and monitor their fleet of printers, tailored for non-IT users.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ensures system robustness, longevity, and supports warranty claims.</t>
+          <t>Enables SMBs to self-manage devices without dedicated IT staff, reducing support costs.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -735,28 +751,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Integration with IDS, tank, and bottle systems.</t>
+          <t>Cloud services, device firmware integration, user authentication.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Models must be validated and predictive within +/-10% of observed reliability outcomes in pilot runs.</t>
+          <t>Portal is accessible, user-friendly, supports core management tasks (status, configuration, alerts) for 6-15 printers.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, 10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -771,48 +791,52 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling</t>
+          <t>PaaS (Platform as a Service) Support</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Model ink stability in tanks and assess impact on print quality (PQ).</t>
+          <t>The printer and associated software must support integration with HP's PaaS offerings for enhanced solutions and services.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ensures long-term print quality and reduces field failures.</t>
+          <t>Supports HP's goal for PaaS acceleration and coverage; enables future solution monetization.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality</t>
+          <t>Tech Reg, Prod Steward, BA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tank design, ink properties, IDS interface.</t>
+          <t>Cloud infrastructure, HP PaaS APIs.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Ink stability modeling must predict PQ impact over 2-year warranty life with &lt;5% deviation from field data.</t>
+          <t>Printer can be registered and managed via HP's PaaS platform; integration validated in end-to-end tests.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 6, 10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -827,48 +851,52 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>PDL/PS Support and Improved Print Speed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts for in-warranty support.</t>
+          <t>For PDL SKU, the printer must support PDL/PS and achieve print speeds of at least 25/20 ppm (improved from current 25/19).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reduces downtime and improves customer experience by enabling field replacement.</t>
+          <t>Meets business productivity needs and competitive benchmarks for print speed and compatibility.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>R&amp;D Telemetry, DVAR, Tech Reg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F part inventory, service logistics.</t>
+          <t>Hardware design, firmware, driver support.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NOA-F service parts available and replaceable within warranty support SLAs.</t>
+          <t>PDL/PS compatibility verified; print speed meets or exceeds 25/20 ppm in standard test scenarios.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -883,17 +911,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology into the ink bottle lid for improved traceability or anti-counterfeiting.</t>
+          <t>The printer must meet Blue Angel environmental certification requirements for the relevant SKU.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Enhances product security and traceability in the supply chain.</t>
+          <t>Supports sustainability goals and competitive positioning, particularly in regulated markets.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -903,17 +931,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Quality, Supply Chain, Security</t>
+          <t>Prod Steward, Quality, Marketing</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 technology integration.</t>
+          <t>Design, materials selection, manufacturing processes.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Acumen 6 features must be verifiable on all production lids and pass security audits.</t>
+          <t>Certification documentation received; product listed as Blue Angel compliant.</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -921,10 +949,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -939,17 +971,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Modify SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Mold 1 to 4 new keyed caps.</t>
+          <t>Printer must utilize at least 60% recycled content plastic in its construction, exceeding key competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ensures manufacturing capability for new components and bottle designs.</t>
+          <t>Differentiates HP on sustainability and supports marketing claims.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -959,17 +991,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D, Supply Chain</t>
+          <t>Prod Steward, Marketing, BA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Existing line configuration, new component designs.</t>
+          <t>Supply chain, materials engineering.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SA14 and Orcus 5 lines operational with new components and pass production validation.</t>
+          <t>BOM and supplier documentation confirm 60% RCP; validated by internal audit.</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -977,10 +1009,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -995,17 +1031,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Design PHA and NOA-F to be customer replaceable, enhancing serviceability.</t>
+          <t>The printer must feature AI-powered solutions for optimizing print quality and scan accuracy, branded as Perfect Print and Perfect Scan.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces service costs.</t>
+          <t>Addresses top customer needs for quality and efficiency; supports key differentiator claims.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1015,17 +1051,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Marketing, GXD, R&amp;D Telemetry</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PHA and NOA-F design, service documentation.</t>
+          <t>AI model integration, firmware/software development.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F using provided instructions with &lt;5% error rate in usability tests.</t>
+          <t>Demonstrated improvement in print/scan quality in benchmark tests; feature accessible via UI/portal.</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1033,10 +1069,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1051,48 +1091,52 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal of 80,000 Pages</t>
+          <t>Maintenance Free or Less Maintenance Design</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Set new warranty page life goal for the printer at 80,000 pages.</t>
+          <t>Design the printer to be maintenance free or require less maintenance (i.e., fewer parts to replace over product lifetime).</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aligns with market expectations for durability and reduces TCO for customers.</t>
+          <t>Reduces burden on SMBs with limited technical resources and aligns with competitor differentiation.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Component reliability, maintenance schedule.</t>
+          <t>Component design, reliability engineering.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Printer must operate without critical failure for at least 80,000 pages in accelerated life testing.</t>
+          <t>Product requires fewer maintenance interventions than comparable models; validated by field test data.</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1107,48 +1151,52 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Product Reddington ID with Increased Tank Size</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID for product with increased tank size, while keeping Marconi-HI ADF unchanged.</t>
+          <t>The printer must include a warranty covering either 80,000 pages or 2 years, whichever comes first.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Supports higher ink capacity and page yield without redesigning ADF.</t>
+          <t>Provides assurance to SMB customers and supports reliability claims.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Quality, Marketing, BA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tank redesign, Reddington ID integration.</t>
+          <t>Service policies, reliability engineering.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Product ID and tank design validated in pilot production; ADF remains unchanged.</t>
+          <t>Warranty terms published; support system configured to track both criteria.</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1163,48 +1211,52 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for the product.</t>
+          <t>Printer must support mobile printing via HP App and standard mobile platforms.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Improves product protection during shipping and handling.</t>
+          <t>Addresses evolving work patterns and customer expectations for mobility.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics, Quality</t>
+          <t>Marketing, GXD, BA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Packaging design, supply chain sourcing.</t>
+          <t>App development, firmware integration.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EPS foam packaging passes ISTA transit and drop tests.</t>
+          <t>Printer discoverable and usable from HP App and mobile OS print dialogs; passes connectivity and print tests from mobile devices.</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1219,97 +1271,101 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental standards (PDL SKU).</t>
+          <t>Printer must support telemetry data collection for fleet management, diagnostics, and usage analytics.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Compliance is necessary for market access and corporate sustainability goals.</t>
+          <t>Enables proactive support, device management, and product improvement.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>R&amp;D Telemetry, DVAR, BA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Design, materials, documentation.</t>
+          <t>Firmware, cloud integration, privacy compliance.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Product certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+          <t>Telemetry data is collected, securely transmitted, and accessible via management portal; passes privacy and compliance review.</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REQ-015</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with new tank protrusion and optimize size.</t>
+          <t>Develop NGB keyed ink bottles with 6,000-page yield for Black and CMY, with CMY bottle size supporting over 8,000 pages.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and maintains compact footprint.</t>
+          <t>Higher page yields reduce customer intervention and lower total cost of ownership, supporting competitive differentiation.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tank design, tray redesign.</t>
+          <t>Requires compatibility with existing and new printer platforms.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Trays function correctly with new tank in user tests and fit within defined product envelope.</t>
+          <t>Bottles must deliver at least 6,000 pages for Black and CMY, and CMY bottle size must exceed 8,000 pages as validated by ISO testing.</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1321,51 +1377,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REQ-016</t>
+          <t>REQ-002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Spill-Free Reliability for Bottles</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3” CGD (Color Graphic Display) into the product.</t>
+          <t>Design ink bottles and system to ensure spill-free reliability during user handling and refilling.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Enhances user interface and usability.</t>
+          <t>Minimizes mess and waste, improving customer satisfaction and reducing service costs.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UI design, display sourcing.</t>
+          <t>Depends on bottle design and printer ink tank interface.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Display is functional, clear, and passes user experience tests.</t>
+          <t>No ink spillage occurs during standard refill process in usability and reliability testing.</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1377,27 +1433,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REQ-017</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4-Tube Platform with New Routing and Integration</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube platform.</t>
+          <t>Implement NOA-F (Non-Original Accessory-Filter) with a metal foiled labyrinth and lid label, with no changes to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Supports increased ink flow and reliability with new tank design.</t>
+          <t>Enhances security, anti-counterfeit, and operational reliability.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1407,21 +1463,21 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Security, Service</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tube design, tank integration.</t>
+          <t>Requires integration with current NOA-F and push-push mechanisms.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>New routing and integration validated in reliability and flow tests.</t>
+          <t>NOA-F must pass security validation and function seamlessly with existing mechanisms.</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1433,51 +1489,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REQ-018</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Update service station for improved aerosol management and adapt platform for tank changes.</t>
+          <t>Enable customer replacement of Print Head Assembly (PHA) and NOA-F parts to enhance serviceability.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reduces maintenance and improves print environment cleanliness.</t>
+          <t>Reduces downtime and service costs, improves user experience.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Service station design, tank integration.</t>
+          <t>Requires modular hardware design and user instructions.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aerosol levels remain within safety thresholds during operation.</t>
+          <t>Customers can replace PHA and NOA-F without tools, as verified by usability studies.</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1489,51 +1545,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REQ-019</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Design product to support a new warranty page life goal of 80,000 pages per device.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+          <t>Aligns with competitive benchmarks and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Manufacturing</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage design, tube routing, weight distribution.</t>
+          <t>Impacts parts durability and consumables yield.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Carriage operates reliably and meets print quality standards in system tests.</t>
+          <t>Device passes accelerated life tests simulating 80,000 printed pages without major failure.</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1545,51 +1601,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REQ-020</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paperpath Support for Increased Page Life</t>
+          <t>Size Optimization for Larger Tank</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Update paperpath design to support increased 80,000-page life goal.</t>
+          <t>Increase tank size to support higher ink capacity, with associated changes to input and output trays to accommodate tank protrusion.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ensures durability and reliability over extended use.</t>
+          <t>Supports higher page yield and reduces refill frequency.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paperpath materials, wear modeling.</t>
+          <t>Requires redesign of trays and enclosure.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Paperpath passes accelerated life testing for 80,000 pages without critical failure.</t>
+          <t>Printer footprint remains within specified dimensions while supporting larger tank and functional trays.</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1601,27 +1657,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REQ-021</t>
+          <t>REQ-007</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part (Post 80k Life)</t>
+          <t>4.3” CGD Touchscreen Interface</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80,000 pages.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) touchscreen for improved user interface.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Extends product life and reduces total cost of ownership for customers.</t>
+          <t>Enhances usability and supports advanced features.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1631,21 +1687,21 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>End Users, UX/UI Team, Product Management</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maintenance part design, service documentation.</t>
+          <t>Requires updated firmware and hardware.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance part within standard service time.</t>
+          <t>All key functions accessible via the 4.3” touchscreen, validated by usability testing.</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1657,51 +1713,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REQ-022</t>
+          <t>REQ-008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Introduce 140ml black bottles and new, larger CMY bottles for the ink system.</t>
+          <t>Implement aerosol management in the service station with platform changes due to larger tank.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Supports higher page yields and reduces refill frequency.</t>
+          <t>Prevents ink aerosol contamination and maintains print quality and reliability.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bottle design, tank compatibility.</t>
+          <t>Requires changes to service station design.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bottles validated for compatibility and yield in system tests.</t>
+          <t>Aerosol levels remain within acceptable limits during maintenance cycles.</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1713,27 +1769,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REQ-023</t>
+          <t>REQ-009</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection in IDS</t>
+          <t>Paper Path for Increased Page Life</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Develop new make-break and FI (fluidic interconnect) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Redesign paper path components to support increased page life target of 80,000 pages.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Improves reliability, prevents mis-filling, and supports larger tank sizes.</t>
+          <t>Ensures durability and reliability over the extended warranty period.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1743,21 +1799,21 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IDS, LEBI ink-tank, SHAID integration.</t>
+          <t>Impacts material selection and mechanical design.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Connections pass reliability and mis-fill prevention tests.</t>
+          <t>Paper path components pass durability testing for 80,000 pages without failure.</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1769,47 +1825,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REQ-024</t>
+          <t>REQ-010</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Ink Maintenance as Serviceable Part Post-80k Life</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Implement new IDS startup algorithm and air management system.</t>
+          <t>Design ink maintenance components to be serviceable after 80,000-page life, available at service centers.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and air handling for new tank and bottle system.</t>
+          <t>Extends device life beyond warranty and reduces e-waste.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality</t>
+          <t>Service, End Users, Sustainability Team</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>IDS, tank, bottle integration.</t>
+          <t>Requires modular design and availability of service parts.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Startup and air management pass reliability and air ingress tests.</t>
+          <t>Service centers can replace ink maintenance parts post-warranty, as validated by service documentation.</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1825,27 +1881,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REQ-025</t>
+          <t>REQ-011</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>New IDS Make-break and FI Connection</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Develop new algorithms for servicing and startup to support new platform requirements.</t>
+          <t>Develop new IDS (Ink Delivery System) make-break and fluidic interconnect (FI) connection with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Improves reliability and user experience with new system components.</t>
+          <t>Supports new tank design and ensures secure, reliable ink delivery.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1855,21 +1911,21 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Firmware, IDS, tank integration.</t>
+          <t>Requires compatibility with new tank and bottle designs.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Algorithms validated in service and startup scenarios with &lt;2% failure rate.</t>
+          <t>IDS connections pass leak and connectivity tests for all supported configurations.</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1881,47 +1937,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REQ-026</t>
+          <t>REQ-012</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definitions</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and depletion definitions to align with updated page yield targets.</t>
+          <t>Implement a new IDS startup algorithm and air management system for optimized priming and reliability.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ensures consistent output quality and accurate yield metrics.</t>
+          <t>Improves first-time setup experience and reduces startup failures.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PQ testing, depletion modeling.</t>
+          <t>Requires firmware and IDS hardware updates.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics validated in lab and field tests.</t>
+          <t>Startup algorithm completes successfully in 99% of new device installations.</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1937,51 +1993,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>REQ-027</t>
+          <t>REQ-013</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU hardware in the new platform.</t>
+          <t>Define and implement new print quality (PQ) goals and depletion metrics to align with page yield definition.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leverages proven hardware to reduce development cost and risk.</t>
+          <t>Ensures consistent output and aligns with marketing claims.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Marketing, Quality Assurance</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Compatibility with new platform design.</t>
+          <t>Requires test protocol updates.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Hardware passes system integration and functional validation.</t>
+          <t>Print quality and depletion meet or exceed defined metrics in 95% of test runs.</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1993,51 +2049,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REQ-028</t>
+          <t>REQ-014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for PDL SKU.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Provides modern connectivity options for users.</t>
+          <t>Supports environmental sustainability goals and required certifications for market access.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>End Users, Product Management, IT</t>
+          <t>Sustainability Team, Regulatory, Product Management</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Firmware, hardware interface design.</t>
+          <t>Requires documentation and design alignment to standards.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Wi-Fi module passes connectivity and performance tests.</t>
+          <t>Product passes third-party certification for EPEAT3, LOT4, and Blue Angel.</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2049,27 +2105,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REQ-029</t>
+          <t>REQ-015</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dune Firmware Platform</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Utilize Dune firmware platform for the printer.</t>
+          <t>Use EPS foam for product packaging to improve protection during shipping.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ensures compatibility and leverages existing firmware capabilities.</t>
+          <t>Reduces damage during transit and supports logistics requirements.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2079,21 +2135,21 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Product Management</t>
+          <t>Logistics, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Firmware integration, hardware compatibility.</t>
+          <t>Requires packaging design update.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Firmware passes system and feature validation tests.</t>
+          <t>Product passes drop and vibration tests with EPS foam packaging.</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2105,51 +2161,51 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REQ-030</t>
+          <t>REQ-016</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Support for SMB, Consumer, and Enterprise Services</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Provide solutions and business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker options.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Meets enterprise security requirements and protects user data.</t>
+          <t>Expands market reach and offers flexible service models.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IT, Security, Enterprise Customers</t>
+          <t>Business Development, Service, End Users</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hardware and firmware design, compliance standards.</t>
+          <t>Requires integration with HPX, HP One, SMB Portal, and ECP.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Security features pass penetration and compliance tests.</t>
+          <t>Service options are available and functional for all target segments at launch.</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2161,47 +2217,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>REQ-031</t>
+          <t>REQ-017</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>Scan Solution and SMB Manageability</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Design solutions, services, and business models to address needs of consumer, SMB, and enterprise markets.</t>
+          <t>Integrate scan solution and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Expands addressable market and supports diverse customer requirements.</t>
+          <t>Meets needs of SMB and enterprise customers for device management and workflow integration.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>Enterprise IT, SMB Customers, Product Management</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Feature set, service offerings, pricing models.</t>
+          <t>Requires software and firmware integration.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Solutions and services available and validated for each segment at launch.</t>
+          <t>Device supports scan and management features as validated by functional testing.</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2217,51 +2273,51 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REQ-032</t>
+          <t>REQ-018</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SMB Manageability and Enterprise Support</t>
+          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients and Drivers</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Include SMB manageability and enterprise support features such as WJA, HPSM, and JAM.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad deployment.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Meets IT requirements for business customers and enhances manageability.</t>
+          <t>Supports diverse customer IT environments and simplifies deployment.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SMB, Enterprise Customers, IT</t>
+          <t>IT Administrators, End Users, Product Management</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Software integration, feature development.</t>
+          <t>Requires driver and client software updates.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Manageability features functional and validated in enterprise test environments.</t>
+          <t>Device installs and operates with all listed clients and drivers in supported OS environments.</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2273,27 +2329,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>REQ-033</t>
+          <t>REQ-019</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients &amp; Drivers</t>
+          <t>Leverage Sayan Sibstar Tubes with New Routing</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Utilize Sayan Sibstar tubes for ink delivery, with new routing and integration for the 4-tube platform.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Supports wide range of deployment scenarios and user environments.</t>
+          <t>Improves ink delivery reliability and supports new tank design.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2303,21 +2359,21 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IT, End Users, Support</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Driver and client integration.</t>
+          <t>Requires mechanical and routing design updates.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>All clients and drivers pass compatibility and installation tests.</t>
+          <t>Ink delivery system operates without leaks or flow interruptions in all test scenarios.</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2329,55 +2385,55 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>REQ-034</t>
+          <t>REQ-020</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Protect Micro/SMB Segments and HP's Ink/Laser Profit Pool</t>
+          <t>Factory Configuration for NOA-F, Magi and Nessie Ink Cart, and Labelling Tool</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Design product features and pricing to protect HP's micro/SMB segments and profit pool from competitors.</t>
+          <t>Modify existing factory line SA14 for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide mold for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strategic business objective to maintain market share and profitability.</t>
+          <t>Ensures efficient manufacturing and supports new product features.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Business Leadership, Product Management, Sales</t>
+          <t>Manufacturing, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Feature set, pricing, market analysis.</t>
+          <t>Requires factory process updates and tooling investments.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Market share and profit pool metrics maintained or improved post-launch.</t>
+          <t>Factory lines are updated and validated for new production requirements before mass production.</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,55 +2441,55 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REQ-035</t>
+          <t>REQ-021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lead with LaserJet, Flank with PDL in Medium and Enterprise Segments</t>
+          <t>Support for SuperAmp PHA, Magi, and Nessie Pigment Inks</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Strategically position LaserJet as lead and PDL as flank in medium and enterprise segments to win over competitors like Epson as CISS grows.</t>
+          <t>Ensure product supports SuperAmp PHA, Magi, and Nessie pigment inks with new 140ml K bottles and new CMY bottles.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Supports HP's competitive positioning in the growing CISS market.</t>
+          <t>Maintains ink compatibility and supports high yield requirements.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>R&amp;D, Consumables Team, End Users</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Product positioning, marketing strategy.</t>
+          <t>Requires ink system and firmware compatibility.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Market share in medium/enterprise segments grows versus competitors.</t>
+          <t>Device operates reliably with all specified inks and bottle sizes.</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,27 +2497,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>REQ-036</t>
+          <t>REQ-022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Grow Profitable CISS Share in New Segments</t>
+          <t>Reuse Marconi Hi PDL and Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Expand CISS offerings to new segments to grow HP's profitable market share.</t>
+          <t>Leverage existing Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU components for cost and time savings.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Increases revenue and market penetration.</t>
+          <t>Reduces development cost and time by reusing proven components.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2471,25 +2527,25 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Product Management, Business Leadership, Sales</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Feature development, market research.</t>
+          <t>Requires compatibility validation with new design.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CISS share in new segments increases post-launch.</t>
+          <t>All reused components pass functional and integration testing in new product.</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,27 +2553,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>REQ-037</t>
+          <t>REQ-023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Highly Leverage Watt-LE Mech Platform and Marconi-Hi Product</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Leverage Watt-LE mechanical platform and Marconi-Hi product (Reddington ID) for new Magellan solution.</t>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Speeds development and reduces investment by reusing proven platforms.</t>
+          <t>Supports modern connectivity requirements for all customer segments.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2527,25 +2583,25 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Platform compatibility, feature integration.</t>
+          <t>Requires hardware and firmware integration.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Platform integration validated in system tests.</t>
+          <t>Device connects to Wi-Fi networks using Stingray module in all supported regions.</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,47 +2609,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>REQ-038</t>
+          <t>REQ-024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+          <t>Firmware (FW) Dune Platform</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and ink tanks into the new product platform.</t>
+          <t>Utilize Dune firmware platform for device operation and feature support.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Supports modern CISS features and improves product competitiveness.</t>
+          <t>Ensures consistent firmware experience and supports new hardware features.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Firmware Team, End Users</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Component integration, system design.</t>
+          <t>Requires firmware customization and validation.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>All components function as integrated system in validation tests.</t>
+          <t>Device operates reliably with Dune firmware and supports all required features.</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2601,7 +2657,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,27 +2665,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>REQ-039</t>
+          <t>REQ-025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New NGB Keyed Ink Bottles</t>
+          <t>Gauss4.xx Security for Hardware and Firmware</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles for the platform.</t>
+          <t>Implement Gauss4.xx security features for both hardware and firmware.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prevents mis-filling and supports new tank and IDS system.</t>
+          <t>Protects against unauthorized access and enhances device security posture.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2639,17 +2695,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Security Team, IT, Enterprise Customers</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, tank integration.</t>
+          <t>Requires security validation and integration.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Keyed bottles prevent mis-filling in &gt;99% test cases.</t>
+          <t>Device passes HP security certification for Gauss4.xx features.</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2657,7 +2713,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,27 +2721,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>REQ-040</t>
+          <t>REQ-026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Schedule as Constrained Priority</t>
+          <t>Schedule Adherence (Q3'25-Q4'27)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Adhere to schedule as the least flexible business constraint for the program.</t>
+          <t>Meet program schedule with key checkpoints from Q3'25 to Q4'27 as detailed in project plan.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ensures timely market entry and supports business objectives.</t>
+          <t>Ensures timely market entry and aligns with business objectives.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2695,17 +2751,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Program Management, R&amp;D, Business Leadership</t>
+          <t>Program Management, R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>All development activities, resource allocation.</t>
+          <t>All development and validation activities must align to schedule.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>All key milestones met as per published schedule.</t>
+          <t>All program milestones are completed on or before scheduled dates.</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2713,7 +2769,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,27 +2777,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>REQ-041</t>
+          <t>REQ-027</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K as Constrained Priority</t>
+          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages as a constrained program requirement.</t>
+          <t>Design SuperAmp PHA to support a life of 65,000 pages as a fixed constraint.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Critical for warranty, reliability, and cost targets.</t>
+          <t>Sets a boundary for PHA durability and impacts service strategy.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2751,21 +2807,21 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>R&amp;D, Service, Product Management</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SuperAmp PHA design, reliability modeling.</t>
+          <t>Impacts warranty and service parts planning.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing for 65,000 pages with &lt;1% failure rate.</t>
+          <t>SuperAmp PHA passes durability tests for 65,000 pages in accelerated testing.</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2777,27 +2833,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>REQ-042</t>
+          <t>REQ-028</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years and 80,000 Pages as Optimized Priority</t>
+          <t>Warranty Life of 2 Years or Page Target</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Optimize for warranty life of 2 years and 80,000 pages.</t>
+          <t>Product warranty to cover 2 years or the specified page life, whichever comes first.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Meets customer expectations for durability and value.</t>
+          <t>Aligns with industry norms and customer expectations.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2807,21 +2863,21 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Component reliability, maintenance schedule.</t>
+          <t>Impacts reliability and service parts planning.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Product passes reliability testing for 2 years/80,000 pages without critical failure.</t>
+          <t>Warranty documentation clearly states coverage terms and is validated by legal and service teams.</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2833,55 +2889,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>REQ-043</t>
+          <t>REQ-029</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
+          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Optimize for print throughput of 25/20 ppm (PDL: 25/19 ppm).</t>
+          <t>Printer must achieve a throughput of 25/20 pages per minute (ppm), with PDL variant achieving 25/19 ppm.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Competitive performance metric for target market.</t>
+          <t>Meets competitive benchmarks for speed.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>End Users, Product Management, R&amp;D</t>
+          <t>End Users, Product Management, Marketing</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Print engine, firmware, hardware.</t>
+          <t>Requires hardware and firmware optimization.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Printer achieves rated throughput in standard performance tests.</t>
+          <t>Device achieves specified throughput in ISO speed tests.</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,27 +2945,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>REQ-044</t>
+          <t>REQ-030</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serviceability (Maintenance Box) as Optimized Priority</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Optimize serviceability, focusing on maintenance box accessibility and replacement.</t>
+          <t>Ensure printer includes a serviceable maintenance box for ink waste and maintenance cycles.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Reduces service time and improves customer satisfaction.</t>
+          <t>Improves uptime and reduces service intervention frequency.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2919,21 +2975,21 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Service, End Users, R&amp;D</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation.</t>
+          <t>Requires modular design for easy replacement.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Maintenance box is replaceable within defined service time.</t>
+          <t>Maintenance box can be replaced by service personnel within 10 minutes as validated by service testing.</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2941,954 +2997,6 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>REQ-045</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>SMB Solution as Optimized Priority</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Optimize product features and solutions for SMB market needs.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Increases product adoption and satisfaction in SMB segment.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SMB Customers, Product Management, Sales</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Feature set, solution integration.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>SMB features validated in customer pilots and feedback.</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>REQ-046</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PaaS (Platform as a Service) as Optimized Priority</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Optimize for PaaS business model and schedule.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Enables new revenue streams and flexible deployment.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Product Management, Business Leadership, IT</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Feature enablement, service integration.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>PaaS features operational and validated in pilot deployments.</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>REQ-047</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Host 12K-CMYK and Trade Page 6K as Flexible Priority</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Host 12,000-page CMYK and trade page 6,000 as flexible priorities for the program.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Provides flexibility for future product enhancements or market demands.</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Product Management, R&amp;D, Business Leadership</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Future development, market trends.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>12K-CMYK and 6K trade page features can be enabled as needed.</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>REQ-001</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AI Productivity and Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Integrate advanced AI-powered productivity and manageability solutions, including AI-driven print and scan workflows, to simplify business operations for SMB customers.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Requires integration with SMB portal and device management systems.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Demonstrated deployment of AI-driven productivity features in print and scan workflows; user testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>REQ-002</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Deliver HP’s lowest business TCO through a combination of cost-efficient ink tank technology and minimal maintenance requirements.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Cost efficiency is a primary decision driver for SMBs with limited budgets.</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Marketing, DVAR, BA</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Dependent on ink tank system design and maintenance strategy.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Independent benchmark shows TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>REQ-003</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>High Serviceability and Customer Replaceable Parts</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Design the printer for high serviceability with customer-replaceable key components (e.g., maintenance box, printhead assembly), and ensure service center support for non-customer-replaceable items.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Requires modular hardware design and clear documentation.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>At least 80% of common maintenance tasks can be performed by end users; documentation and training materials provided.</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>REQ-004</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>SMB Portal for Device Management</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers, targeting office managers and generalist IT users in SMBs.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Requires integration with telemetry and device firmware.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>REQ-005</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Keyed Ink Bottles for Error Prevention</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Reduces service incidents and improves user experience for non-technical users.</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Supplies Quality, Quality, Prod Steward</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Requires new bottle and tank interface design.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Field testing shows &lt;2% incorrect refill incidents over 12 months of use.</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>REQ-006</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Support for PaaS and Advanced View SMB Portal</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Ensure printer supports Platform-as-a-Service (PaaS) and the new Advanced View SMB portal for enhanced business solutions.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, BA, R&amp;D Telemetry</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Requires software and firmware compatibility with HP’s evolving platforms.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>REQ-007</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>PDL/PS Support and Improved Print Speed</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>For PDL SKU, provide PDL/PS (Page Description Language/PostScript) support and improve print speed to 25/20 ppm (from current 25/19).</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, Marketing, DVAR</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Requires hardware and firmware enhancements.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>PDL SKU demonstrates print speed of at least 25/20 ppm and passes PDL/PS compatibility tests.</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>REQ-008</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Blue Angel Environmental Certification</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Obtain Blue Angel certification for the printer to meet environmental and sustainability standards.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Prod Steward, Tech Reg, Quality</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Requires compliance with Blue Angel criteria.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Blue Angel certification awarded by launch date.</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>REQ-009</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>High Recycled Content in Plastics (60% RCP)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Ensure that at least 60% of the printer’s plastics are made from recycled content, exceeding key competitors.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Prod Steward, Marketing, Quality</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Requires supply chain and materials engineering alignment.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Bill of materials and third-party audit confirm ≥60% RCP in plastics.</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>REQ-010</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AI Solutions for Print, Scan, and Support</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Deploy AI-driven solutions in print, scan, and support functions to optimize workflows and reduce manual intervention.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, GXD, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Requires integration with device firmware and cloud services.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>AI features are operational at launch and reduce manual steps by at least 30% in key workflows.</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>REQ-011</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Mobile Printing via HP App</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, BA</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Requires app integration and device firmware support.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>REQ-012</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Warranty and Serviceability Thresholds</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Provide a warranty of 80,000 pages or 2 years (whichever comes first) and establish serviceability thresholds for key components.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Ensures predictable support costs and aligns with SMB expectations for reliability.</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Requires warranty policy alignment and service documentation.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Warranty terms published and service processes validated before launch.</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>REQ-013</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Maintenance-Free or Low Maintenance Design</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Design the printer to be maintenance-free or require minimal maintenance, with fewer parts to replace over product life.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Reduces total cost of ownership and appeals to SMBs lacking technical staff.</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Quality, Supplies Quality, Prod Steward, Marketing</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Subject to feasibility investigation and hardware design constraints.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Maintenance requirements are at least 30% lower than comparable products; validated by field testing.</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,63 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Requirement ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>citation</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -481,2522 +481,2786 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The printer must integrate advanced AI-driven productivity features, scan workflow enhancements, and manageability solutions to ease business operations for SMBs.</t>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Addresses the core value proposition of making business management easier for SMBs and differentiates from competitors.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>CISS system integration, IDS compatibility</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution stack.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Demonstrated AI productivity features in print and scan workflows; end-user can manage devices through provided solutions; meets user scenario tests.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.95</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REQ-002</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lowest Business TCO</t>
+          <t>Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The printer must deliver the lowest total cost of ownership (TCO) for SMB customers compared to HP's other business printers.</t>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top priority for SMBs and a key differentiator.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, End Users, Service Teams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Marketing, BA, Quality</t>
+          <t>Bottle and tank mechanical design, NOA-F integration</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Supply chain, pricing, and consumable costs.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Independent TCO analysis demonstrates lowest TCO among HP business printers for target use-case (AMPV ~500 pages/month).</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The printer must feature a maintenance box that can be replaced by customers without technical assistance, with service center fallback if needed.</t>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs for SMBs with limited IT resources.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Product Security, Compliance</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D Telemetry, Supplies Quality</t>
+          <t>NOA-F design, supply chain for metal foiling</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Design for serviceability, supply chain for replaceable parts.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>User can replace maintenance box following provided instructions; no tools or minimal tools required; validated in usability testing.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The printer must use keyed ink bottles to prevent incorrect refilling and ensure user safety and product reliability.</t>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prevents user error and damage, supports warranty claims, and enhances customer experience.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Supplies Quality, Quality, BA</t>
+          <t>Compatibility testing with new system</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ink bottle design, printer hardware design.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Only correct ink bottle fits and dispenses; passes misfill prevention tests.</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Enhanced Reliability and Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SMB Portal for Device Management</t>
+          <t>Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A consolidated web-based portal must be provided for SMBs to manage and monitor their fleet of printers, tailored for non-IT users.</t>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Enables SMBs to self-manage devices without dedicated IT staff, reducing support costs.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+          <t>IDS design, NOA-F integration</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cloud services, device firmware integration, user authentication.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Portal is accessible, user-friendly, supports core management tasks (status, configuration, alerts) for 6-15 printers.</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 10</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Support for Service Parts and Warranty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PaaS (Platform as a Service) Support</t>
+          <t>NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The printer and associated software must support integration with HP's PaaS offerings for enhanced solutions and services.</t>
+          <t>Improves serviceability and reduces downtime for end users.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Supports HP's goal for PaaS acceleration and coverage; enables future solution monetization.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tech Reg, Prod Steward, BA</t>
+          <t>Parts logistics, service documentation</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cloud infrastructure, HP PaaS APIs.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Printer can be registered and managed via HP's PaaS platform; integration validated in end-to-end tests.</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 6, 10</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REQ-007</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PDL/PS Support and Improved Print Speed</t>
+          <t>Integrate Acumen 6 feature on the bottle lid.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>For PDL SKU, the printer must support PDL/PS and achieve print speeds of at least 25/20 ppm (improved from current 25/19).</t>
+          <t>Supports authentication and anti-counterfeit measures.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meets business productivity needs and competitive benchmarks for print speed and compatibility.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Product Security, R&amp;D</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, DVAR, Tech Reg</t>
+          <t>Lid design, Acumen 6 technology integration</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hardware design, firmware, driver support.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PDL/PS compatibility verified; print speed meets or exceeds 25/20 ppm in standard test scenarios.</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REQ-008</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Factory Line Modifications for NOA-F</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The printer must meet Blue Angel environmental certification requirements for the relevant SKU.</t>
+          <t>Ensures manufacturing capability for new product configurations.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Supports sustainability goals and competitive positioning, particularly in regulated markets.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prod Steward, Quality, Marketing</t>
+          <t>Capex approval, line retooling</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Design, materials selection, manufacturing processes.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Certification documentation received; product listed as Blue Angel compliant.</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REQ-009</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>New Keyed Caps Mold Tooling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>60% Recycled Content Plastic (RCP)</t>
+          <t>Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Printer must utilize at least 60% recycled content plastic in its construction, exceeding key competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Differentiates HP on sustainability and supports marketing claims.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, BA</t>
+          <t>Bottle and cap design finalization</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Supply chain, materials engineering.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>BOM and supplier documentation confirm 60% RCP; validated by internal audit.</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REQ-010</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The printer must feature AI-powered solutions for optimizing print quality and scan accuracy, branded as Perfect Print and Perfect Scan.</t>
+          <t>Reduces development time and investment by building on proven platforms.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Addresses top customer needs for quality and efficiency; supports key differentiator claims.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Program Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry</t>
+          <t>Platform compatibility, CISS integration</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AI model integration, firmware/software development.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Demonstrated improvement in print/scan quality in benchmark tests; feature accessible via UI/portal.</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 11</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REQ-011</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Print Speed Requirements</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maintenance Free or Less Maintenance Design</t>
+          <t>Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Design the printer to be maintenance free or require less maintenance (i.e., fewer parts to replace over product lifetime).</t>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Reduces burden on SMBs with limited technical resources and aligns with competitor differentiation.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Product Management, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>Engine design, firmware optimization</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Component design, reliability engineering.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Product requires fewer maintenance interventions than comparable models; validated by field test data.</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REQ-012</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Support a new warranty page life target of 80,000 pages for the product.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The printer must include a warranty covering either 80,000 pages or 2 years, whichever comes first.</t>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Provides assurance to SMB customers and supports reliability claims.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Product Management, Warranty, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Quality, Marketing, BA</t>
+          <t>System reliability, consumables endurance</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Service policies, reliability engineering.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Warranty terms published; support system configured to track both criteria.</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.95</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REQ-013</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Printer must support mobile printing via HP App and standard mobile platforms.</t>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Addresses evolving work patterns and customer expectations for mobility.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Design, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Marketing, GXD, BA</t>
+          <t>Tank and chassis redesign, ID approval</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>App development, firmware integration.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Printer discoverable and usable from HP App and mobile OS print dialogs; passes connectivity and print tests from mobile devices.</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.85</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REQ-014</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Use EPS foam packaging for the new product.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Printer must support telemetry data collection for fleet management, diagnostics, and usage analytics.</t>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Enables proactive support, device management, and product improvement.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Logistics, Compliance</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, DVAR, BA</t>
+          <t>Packaging design, regulatory approval</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Firmware, cloud integration, privacy compliance.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Telemetry data is collected, securely transmitted, and accessible via management portal; passes privacy and compliance review.</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Input/Output Tray Modifications</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>Modify input and output trays to align with tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Develop NGB keyed ink bottles with 6,000-page yield for Black and CMY, with CMY bottle size supporting over 8,000 pages.</t>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Higher page yields reduce customer intervention and lower total cost of ownership, supporting competitive differentiation.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Design, R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Tray and tank design, mechanical integration</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Requires compatibility with existing and new printer platforms.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Bottles must deliver at least 6,000 pages for Black and CMY, and CMY bottle size must exceed 8,000 pages as validated by ISO testing.</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K16" t="inlineStr">
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REQ-002</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4.3-inch CGD Display</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Bottles</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Design ink bottles and system to ensure spill-free reliability during user handling and refilling.</t>
+          <t>Enhances user interaction and supports advanced features.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minimizes mess and waste, improving customer satisfaction and reducing service costs.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>UI design, hardware integration</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Depends on bottle design and printer ink tank interface.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>No ink spillage occurs during standard refill process in usability and reliability testing.</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K17" t="inlineStr">
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Implement NOA-F (Non-Original Accessory-Filter) with a metal foiled labyrinth and lid label, with no changes to click-on push-push and TDF mechanisms.</t>
+          <t>Improves ink flow and supports increased tank and page life.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Enhances security, anti-counterfeit, and operational reliability.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Service</t>
+          <t>Tube design, routing validation</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Requires integration with current NOA-F and push-push mechanisms.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>NOA-F must pass security validation and function seamlessly with existing mechanisms.</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K18" t="inlineStr">
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Support for Customer Replaceable PHA and NOA-F</t>
+          <t>Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Enable customer replacement of Print Head Assembly (PHA) and NOA-F parts to enhance serviceability.</t>
+          <t>Reduces contamination and maintains print quality.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs, improves user experience.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Service station and spit platform redesign</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Requires modular hardware design and user instructions.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Customers can replace PHA and NOA-F without tools, as verified by usability studies.</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K19" t="inlineStr">
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal of 80k Pages</t>
+          <t>Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Design product to support a new warranty page life goal of 80,000 pages per device.</t>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aligns with competitive benchmarks and reduces total cost of ownership for customers.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Engineering</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Carriage, tube, and tank design</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Impacts parts durability and consumables yield.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Device passes accelerated life tests simulating 80,000 printed pages without major failure.</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Paper Path for Increased Page Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Size Optimization for Larger Tank</t>
+          <t>Design paper path to support increased page life target of 80,000 pages.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Increase tank size to support higher ink capacity, with associated changes to input and output trays to accommodate tank protrusion.</t>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Supports higher page yield and reduces refill frequency.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>R&amp;D, Quality Assurance, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design, End Users</t>
+          <t>Paper path design, reliability testing</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Requires redesign of trays and enclosure.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Printer footprint remains within specified dimensions while supporting larger tank and functional trays.</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.9</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REQ-007</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Ink Maintenance Serviceable Part</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.3” CGD Touchscreen Interface</t>
+          <t>Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) touchscreen for improved user interface.</t>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Enhances usability and supports advanced features.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>End Users, UX/UI Team, Product Management</t>
+          <t>Maintenance part design, service documentation</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Requires updated firmware and hardware.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>All key functions accessible via the 4.3” touchscreen, validated by usability testing.</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K22" t="inlineStr">
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REQ-008</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Implement a new make-break and fluidic interconnect (FI) connection for the ink delivery system (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Implement aerosol management in the service station with platform changes due to larger tank.</t>
+          <t>Improves reliability, supports new bottle sizes, and enhances system security.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prevents ink aerosol contamination and maintains print quality and reliability.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>IDS and LEBI design, SHAID integration</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Requires changes to service station design.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Aerosol levels remain within acceptable limits during maintenance cycles.</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K23" t="inlineStr">
+          <t>IDS must pass all fluidic and electrical connection reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REQ-009</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paper Path for Increased Page Life</t>
+          <t>Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Redesign paper path components to support increased page life target of 80,000 pages.</t>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ensures durability and reliability over the extended warranty period.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>IDS design, firmware development</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Impacts material selection and mechanical design.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Paper path components pass durability testing for 80,000 pages without failure.</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>0.9</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REQ-010</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>New Print Quality (PQ) Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post-80k Life</t>
+          <t>Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable after 80,000-page life, available at service centers.</t>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Extends device life beyond warranty and reduces e-waste.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Product Management, QA, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Service, End Users, Sustainability Team</t>
+          <t>PQ test development, ink system calibration</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Requires modular design and availability of service parts.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Service centers can replace ink maintenance parts post-warranty, as validated by service documentation.</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>0.85</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REQ-011</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New IDS Make-break and FI Connection</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Develop new IDS (Ink Delivery System) make-break and fluidic interconnect (FI) connection with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
+          <t>Reduces development cost and leverages proven hardware.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supports new tank design and ensures secure, reliable ink delivery.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Hardware integration, compatibility testing</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Requires compatibility with new tank and bottle designs.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>IDS connections pass leak and connectivity tests for all supported configurations.</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>0.9</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REQ-012</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Implement a new IDS startup algorithm and air management system for optimized priming and reliability.</t>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Improves first-time setup experience and reduces startup failures.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Firmware support, hardware integration</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Requires firmware and IDS hardware updates.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Startup algorithm completes successfully in 99% of new device installations.</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0.85</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>REQ-013</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Gauss4.xx Security for Hardware and Firmware</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Define and implement new print quality (PQ) goals and depletion metrics to align with page yield definition.</t>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ensures consistent output and aligns with marketing claims.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>IT Security, Compliance, Enterprise Customers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R&amp;D, Marketing, Quality Assurance</t>
+          <t>HW/FW development, security validation</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Requires test protocol updates.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Print quality and depletion meet or exceed defined metrics in 95% of test runs.</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>0.9</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REQ-014</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for PDL SKU.</t>
+          <t>Required for market access and sustainability commitments.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Supports environmental sustainability goals and required certifications for market access.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Compliance, Marketing, End Users</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sustainability Team, Regulatory, Product Management</t>
+          <t>Design, materials, certification process</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Requires documentation and design alignment to standards.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Product passes third-party certification for EPEAT3, LOT4, and Blue Angel.</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>0.9</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REQ-015</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Business Model and Solution Support</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Use EPS foam for product packaging to improve protection during shipping.</t>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reduces damage during transit and supports logistics requirements.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Product Management, Sales, Channel Partners</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Logistics, R&amp;D, Quality Assurance</t>
+          <t>Solution integration, onboarding workflow development</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Requires packaging design update.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Product passes drop and vibration tests with EPS foam packaging.</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>0.85</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REQ-016</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Scan and SMB/Enterprise Manageability Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support for SMB, Consumer, and Enterprise Services</t>
+          <t>Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Provide solutions and business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker options.</t>
+          <t>Enhances value proposition for business and enterprise customers.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Expands market reach and offers flexible service models.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SMB/Enterprise IT, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Business Development, Service, End Users</t>
+          <t>Solution development, integration with HP software stack</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Requires integration with HPX, HP One, SMB Portal, and ECP.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Service options are available and functional for all target segments at launch.</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K31" t="inlineStr">
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>REQ-017</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Clients &amp; Drivers Support</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scan Solution and SMB Manageability</t>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Integrate scan solution and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meets needs of SMB and enterprise customers for device management and workflow integration.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>IT, End Users, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Enterprise IT, SMB Customers, Product Management</t>
+          <t>Driver development, compatibility testing</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Requires software and firmware integration.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Device supports scan and management features as validated by functional testing.</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>0.85</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REQ-018</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Strategic Protection of Micro/SMB Segments</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients and Drivers</t>
+          <t>Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad deployment.</t>
+          <t>Critical for HP’s market share retention and profitability.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Supports diverse customer IT environments and simplifies deployment.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Business Leadership, Product Management</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IT Administrators, End Users, Product Management</t>
+          <t>Feature set, pricing strategy</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Requires driver and client software updates.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Device installs and operates with all listed clients and drivers in supported OS environments.</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>REQ-019</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>LaserJet Leadership and PDL Flanking</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes with New Routing</t>
+          <t>Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Utilize Sayan Sibstar tubes for ink delivery, with new routing and integration for the 4-tube platform.</t>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Improves ink delivery reliability and supports new tank design.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Business Leadership, Marketing, Product Management</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Product portfolio alignment, marketing plan</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Requires mechanical and routing design updates.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Ink delivery system operates without leaks or flow interruptions in all test scenarios.</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>REQ-020</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>CISS Profitable Share Growth in New Segments</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Factory Configuration for NOA-F, Magi and Nessie Ink Cart, and Labelling Tool</t>
+          <t>Expand CISS offerings to new profitable market segments.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Modify existing factory line SA14 for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide mold for 1 to 4 new keyed caps.</t>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ensures efficient manufacturing and supports new product features.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Business Leadership, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D, Quality Assurance</t>
+          <t>Market analysis, product line expansion</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Requires factory process updates and tooling investments.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Factory lines are updated and validated for new production requirements before mass production.</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REQ-021</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Highly Leveraged Development Approach</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Support for SuperAmp PHA, Magi, and Nessie Pigment Inks</t>
+          <t>Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ensure product supports SuperAmp PHA, Magi, and Nessie pigment inks with new 140ml K bottles and new CMY bottles.</t>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maintains ink compatibility and supports high yield requirements.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Program Management</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>R&amp;D, Consumables Team, End Users</t>
+          <t>Platform integration, solution reuse</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Requires ink system and firmware compatibility.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Device operates reliably with all specified inks and bottle sizes.</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>REQ-022</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Schedule Constraint – High Priority</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reuse Marconi Hi PDL and Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU components for cost and time savings.</t>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Reduces development cost and time by reusing proven components.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Program Management, Business Leadership</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>Project management, resource allocation</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Requires compatibility validation with new design.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>All reused components pass functional and integration testing in new product.</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>REQ-023</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>SuperAmp PHA Life at 65,000 Pages</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Supports modern connectivity requirements for all customer segments.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>R&amp;D, Service, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>PHA design, reliability testing</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware integration.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Device connects to Wi-Fi networks using Stingray module in all supported regions.</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.9</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>REQ-024</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Warranty Life of 2 Years or 80,000 Pages</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Firmware (FW) Dune Platform</t>
+          <t>Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Utilize Dune firmware platform for device operation and feature support.</t>
+          <t>Aligns with customer expectations and competitive offerings.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ensures consistent firmware experience and supports new hardware features.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Product Management, Warranty, End Users</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware Team, End Users</t>
+          <t>System reliability, warranty policy</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Requires firmware customization and validation.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Device operates reliably with Dune firmware and supports all required features.</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>REQ-025</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Throughput of 25/20 PPM (PDL)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security for Hardware and Firmware</t>
+          <t>Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features for both hardware and firmware.</t>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Protects against unauthorized access and enhances device security posture.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Product Management, End Users</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Security Team, IT, Enterprise Customers</t>
+          <t>Engine and firmware optimization</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Requires security validation and integration.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Device passes HP security certification for Gauss4.xx features.</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
         <v>0.9</v>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>REQ-026</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Serviceability (Maintenance Box)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Schedule Adherence (Q3'25-Q4'27)</t>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Meet program schedule with key checkpoints from Q3'25 to Q4'27 as detailed in project plan.</t>
+          <t>Reduces service downtime and cost, improves user experience.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ensures timely market entry and aligns with business objectives.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Program Management, R&amp;D, Manufacturing</t>
+          <t>Maintenance box design, service documentation</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>All development and validation activities must align to schedule.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>All program milestones are completed on or before scheduled dates.</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>REQ-027</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>SMB Solution Optimization</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+          <t>Optimize product features and solutions for SMB customers.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Design SuperAmp PHA to support a life of 65,000 pages as a fixed constraint.</t>
+          <t>Addresses key needs of a major target segment.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sets a boundary for PHA durability and impacts service strategy.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>SMB Customers, Product Management</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>Feature set definition, solution development</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Impacts warranty and service parts planning.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA passes durability tests for 65,000 pages in accelerated testing.</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K42" t="inlineStr">
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>REQ-028</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>PaaS Schedule Optimization</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or Page Target</t>
+          <t>Optimize schedule for Platform as a Service (PaaS) offering.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Product warranty to cover 2 years or the specified page life, whichever comes first.</t>
+          <t>Aligns product launch with business model rollout.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aligns with industry norms and customer expectations.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Product Management, Service, Channel Partners</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>PaaS development, integration</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Impacts reliability and service parts planning.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Warranty documentation clearly states coverage terms and is validated by legal and service teams.</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K43" t="inlineStr">
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>REQ-029</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Implement advanced AI-driven productivity features and manageability solutions, including AI-assisted print, scan, and support workflows, to simplify business operations for SMB customers.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Printer must achieve a throughput of 25/20 pages per minute (ppm), with PDL variant achieving 25/19 ppm.</t>
+          <t>Addresses the need for increased efficiency and ease of management for SMBs with limited IT resources. Differentiates HP Magellan from competitors.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Meets competitive benchmarks for speed.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Marketing</t>
+          <t>Requires integration with SMB portal and AI solution stack.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Device achieves specified throughput in ISO speed tests.</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>0.9</v>
+          <t>AI-driven features are available at launch, demonstrably improve workflow efficiency, and are accessible via the SMB portal.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+        </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>REQ-030</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>Design Magellan to deliver HP's lowest business TCO for SMB customers, minimizing intervention and ongoing costs over the product lifecycle.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ensure printer includes a serviceable maintenance box for ink waste and maintenance cycles.</t>
+          <t>Cost efficiency is a top priority for SMBs and a key differentiator in the market.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Improves uptime and reduces service intervention frequency.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Marketing, BA, Prod Steward</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Requires sustainable components and efficient consumables management.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TCO is calculated and benchmarked to be lower than previous HP models and key competitors.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Introduce a replaceable maintenance box that can be serviced by the customer, reducing the need for technician intervention and downtime.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Addresses new SMB segment needs and pain points related to serviceability and maintenance costs.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, DVAR, Tech Reg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Design must ensure ease of replacement and clear instructions for end-users.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by an end-user without technical assistance; validated via usability testing.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SMB Portal for Printer Management</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Develop a consolidated portal specifically for SMBs to manage all Magellan printers, including device status, usage analytics, and support access.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT staff and require simple, centralized management tools.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Integration with AI solutions and Magellan device firmware.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Portal is live at launch, supports all required management functions, and is accessible to SMB users.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, Page 10, Page 11</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Keyed Bottles for Consumables</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Utilize keyed bottles for ink and other consumables to prevent incorrect refilling and ensure compatibility with Magellan devices.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Reduces consumable errors, minimizes service calls, and ensures product reliability.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Service, End Users, R&amp;D</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Requires modular design for easy replacement.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Maintenance box can be replaced by service personnel within 10 minutes as validated by service testing.</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Supplies Quality, Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Requires redesign of consumable packaging and printer interface.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Keyed bottles are available at launch and are not interchangeable with previous models.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
         <v>0.85</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability Standards</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Provide a warranty of 80,000 pages or 2 years (whichever is first). Support customer-replaceable parts (PHA) and service center replaceable parts (MINK), with a target for more parts to be customer replaceable.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Reduces downtime and increases customer satisfaction for SMBs with minimal IT support.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, DVAR, Tech Reg, Prod Steward</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Design for serviceability and robust part supply chain.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Warranty terms are met and documented; at least 80% of identified serviceable parts are customer replaceable.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Support for PaaS and Non-PDL/PDL SKUs</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ensure Magellan supports Platform-as-a-Service (PaaS) models and both Non-PDL and PDL SKUs, with specific speed and protocol support (PDL SKU: 25/20 ppm, PDL/PS support, Blue Angel compliance).</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Addresses diverse SMB needs and aligns with HP's strategic intent to expand service-based offerings.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, Tech Reg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Firmware and hardware compatibility, compliance with Blue Angel and other standards.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Both SKU types available at launch, meet specified speed and compliance requirements.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Manufacture Magellan with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and aligns with HP's environmental goals.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Supply chain and material sourcing for RCP.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Product BOM and external certification confirm at least 60% RCP.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Advanced Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Integrate telemetry features to monitor device health, usage, and proactively support SMB customers through the portal and AI solutions.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Enables predictive maintenance, reduces downtime, and provides valuable insights for SMBs and HP support teams.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, BA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Integration with SMB portal and AI stack.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Telemetry data is available in real-time via the portal and supports proactive support interventions.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, Page 12</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing capabilities through the HP App, supporting key SMB use cases for on-the-go printing and management.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Addresses modern SMB needs for flexibility and remote work support.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>App integration with Magellan firmware and SMB portal.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Mobile printing is available, reliable, and user-friendly at launch.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, Page 10</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,68 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>citation</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Requirement ID</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Verification_Status</t>
         </is>
       </c>
     </row>
@@ -527,8 +529,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,8 +579,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -631,8 +629,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -683,8 +679,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -735,8 +729,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -787,8 +779,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -839,8 +829,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -891,8 +879,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -943,8 +929,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -995,8 +979,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1047,8 +1029,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1099,8 +1079,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1151,8 +1129,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1203,8 +1179,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1255,8 +1229,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1307,8 +1279,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1359,8 +1329,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1411,8 +1379,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1463,8 +1429,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1515,8 +1479,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1567,8 +1529,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1619,8 +1579,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1671,8 +1629,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1723,8 +1679,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1775,8 +1729,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1827,8 +1779,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1879,8 +1829,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1931,8 +1879,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1983,8 +1929,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2035,8 +1979,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2087,8 +2029,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2139,8 +2079,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2191,8 +2129,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2243,8 +2179,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2295,8 +2229,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2347,8 +2279,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2399,8 +2329,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2451,8 +2379,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2503,8 +2429,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2555,8 +2479,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2607,8 +2529,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2659,8 +2579,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2670,17 +2588,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Business Ink Tank Printing Solution</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Implement advanced AI-driven productivity features and manageability solutions, including AI-assisted print, scan, and support workflows, to simplify business operations for SMB customers.</t>
+          <t>Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Addresses the need for increased efficiency and ease of management for SMBs with limited IT resources. Differentiates HP Magellan from competitors.</t>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2690,17 +2608,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution stack.</t>
+          <t>Requires support for tank technology, CISS PLE Hi segment, and SMB-specific manageability features.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>AI-driven features are available at launch, demonstrably improve workflow efficiency, and are accessible via the SMB portal.</t>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2708,17 +2626,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>REQ-001</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4, 5, 6, 7</t>
         </is>
       </c>
     </row>
@@ -2730,17 +2638,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver HP's lowest business TCO for SMB customers, minimizing intervention and ongoing costs over the product lifecycle.</t>
+          <t>Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top priority for SMBs and a key differentiator in the market.</t>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2750,17 +2658,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marketing, BA, Prod Steward</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Requires sustainable components and efficient consumables management.</t>
+          <t>Requires AI software integration and compatibility with hardware and SMB portal.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TCO is calculated and benchmarked to be lower than previous HP models and key competitors.</t>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2768,17 +2676,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>REQ-002</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -2790,17 +2688,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>SMB Device Management Portal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be serviced by the customer, reducing the need for technician intervention and downtime.</t>
+          <t>Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Addresses new SMB segment needs and pain points related to serviceability and maintenance costs.</t>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2810,35 +2708,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, DVAR, Tech Reg</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Design must ensure ease of replacement and clear instructions for end-users.</t>
+          <t>Requires portal software development and integration with printer firmware and AI features.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by an end-user without technical assistance; validated via usability testing.</t>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>REQ-003</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -2850,17 +2738,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal specifically for SMBs to manage all Magellan printers, including device status, usage analytics, and support access.</t>
+          <t>Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT staff and require simple, centralized management tools.</t>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2870,35 +2758,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA</t>
+          <t>Marketing, Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Integration with AI solutions and Magellan device firmware.</t>
+          <t>Requires efficient ink tank design, low maintenance, and sustainability features.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Portal is live at launch, supports all required management functions, and is accessible to SMB users.</t>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>REQ-004</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -2910,17 +2788,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Consumables</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Utilize keyed bottles for ink and other consumables to prevent incorrect refilling and ensure compatibility with Magellan devices.</t>
+          <t>Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Reduces consumable errors, minimizes service calls, and ensures product reliability.</t>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,17 +2808,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Supplies Quality, Quality, DVAR</t>
+          <t>Quality, Supplies Quality, DVAR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Requires redesign of consumable packaging and printer interface.</t>
+          <t>Requires hardware design supporting easy maintenance box replacement.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Keyed bottles are available at launch and are not interchangeable with previous models.</t>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2948,17 +2826,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>REQ-005</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -2970,55 +2838,45 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Warranty and Serviceability Standards</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Provide a warranty of 80,000 pages or 2 years (whichever is first). Support customer-replaceable parts (PHA) and service center replaceable parts (MINK), with a target for more parts to be customer replaceable.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Reduces downtime and increases customer satisfaction for SMBs with minimal IT support.</t>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, DVAR, Tech Reg, Prod Steward</t>
+          <t>Quality, Supplies Quality, Prod Steward</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Design for serviceability and robust part supply chain.</t>
+          <t>Requires supply chain and hardware compatibility with keyed bottles.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Warranty terms are met and documented; at least 80% of identified serviceable parts are customer replaceable.</t>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>REQ-006</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -3030,55 +2888,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Support for PaaS and Non-PDL/PDL SKUs</t>
+          <t>Non-PDL SKU Features</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports Platform-as-a-Service (PaaS) models and both Non-PDL and PDL SKUs, with specific speed and protocol support (PDL SKU: 25/20 ppm, PDL/PS support, Blue Angel compliance).</t>
+          <t>For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Addresses diverse SMB needs and aligns with HP's strategic intent to expand service-based offerings.</t>
+          <t>Addresses different SMB needs and supports new service models.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, Tech Reg</t>
+          <t>Marketing, GXD, BA, DVAR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Firmware and hardware compatibility, compliance with Blue Angel and other standards.</t>
+          <t>Requires software and hardware support for these features.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Both SKU types available at launch, meet specified speed and compliance requirements.</t>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>REQ-007</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -3090,55 +2938,45 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>PDL SKU Features</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Manufacture Magellan with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and aligns with HP's environmental goals.</t>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, BA</t>
+          <t>Marketing, Tech Reg, BA, DVAR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Supply chain and material sourcing for RCP.</t>
+          <t>Requires hardware/firmware for speed and PDL/PS, and Blue Angel certification process.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Product BOM and external certification confirm at least 60% RCP.</t>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>REQ-008</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -3150,17 +2988,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Advanced Telemetry Requirements</t>
+          <t>Sustainability: 60% RCP Content</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Integrate telemetry features to monitor device health, usage, and proactively support SMB customers through the portal and AI solutions.</t>
+          <t>Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Enables predictive maintenance, reduces downtime, and provides valuable insights for SMBs and HP support teams.</t>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3170,17 +3008,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, BA</t>
+          <t>Prod Steward, Marketing, Quality</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Integration with SMB portal and AI stack.</t>
+          <t>Requires sourcing and manufacturing with high RCP.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Telemetry data is available in real-time via the portal and supports proactive support interventions.</t>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3188,17 +3026,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>REQ-009</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 11</t>
         </is>
       </c>
     </row>
@@ -3210,55 +3038,195 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Warranty and Serviceability</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing capabilities through the HP App, supporting key SMB use cases for on-the-go printing and management.</t>
+          <t>Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Addresses modern SMB needs for flexibility and remote work support.</t>
+          <t>Ensures reliability and reduces SMB downtime.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Requires hardware/service design for warranty and customer replaceability.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Warranty and serviceability model is implemented and documented; validated by service/support teams.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, BA</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>App integration with Magellan firmware and SMB portal.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Mobile printing is available, reliable, and user-friendly at launch.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Requires secure telemetry software and privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
         <v>0.85</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>REQ-010</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Approved</t>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Requires app and firmware compatibility.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Requires business model and technical enablement for solution monetization.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 9, 10</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,56 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
@@ -488,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size must support &gt;8K yield.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+          <t>Increases ink yield per bottle, reducing frequency of replacement and supporting high-volume customers.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -508,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solutions platform.</t>
+          <t>Requires bottle redesign and compatibility with existing or new tank systems.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+          <t>New bottles pass reliability, spill-free, and integration testing; CMY bottles confirmed for &gt;8K yield; 6K yield for Black and CMY verified.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -526,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -538,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business TCO with Minimal Intervention</t>
+          <t>Spill-Free Reliability for Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+          <t>Ensure that the new bottles provide spill-free reliability during handling and installation.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+          <t>Reduces mess and improves user experience, critical for customer satisfaction.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -558,17 +546,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+          <t>End Users, R&amp;D, Customer Support</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires durable design, high-yield consumables, and reliable components.</t>
+          <t>Bottle and tank interface design.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+          <t>No ink spills during normal bottle handling and installation in &gt;99.5% of test cases.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -576,7 +564,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -588,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Business Ink Tank Printer for SMBs</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+          <t>Implement NOA-F (Non-Original Accessory Filter) with a metal foiled labyrinth and lid label; maintain current click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+          <t>Improves product security and reliability, while ensuring compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,25 +596,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+          <t>R&amp;D, Service, Product Security</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires new hardware platform; alignment with HP’s existing product portfolio.</t>
+          <t>NOA-F design and manufacturing capability.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+          <t>NOA-F units pass security and reliability tests, and are compatible with push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6, 7, 12</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -638,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Support for Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+          <t>Design the printer to allow customers to replace the PHA (Printhead Assembly) and NOA-F themselves.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+          <t>Improves serviceability, reduces downtime, and lowers service costs.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -658,25 +646,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires redesign of maintenance subsystem; must be customer-replaceable.</t>
+          <t>Mechanical design for easy access and replacement.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+          <t>End users can replace PHA and NOA-F with no tools and minimal instruction; verified in usability testing.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -688,45 +676,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK)</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+          <t>Extends service intervals and aligns with customer expectations for durability.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires modular design and documentation; warranty process alignment.</t>
+          <t>Component reliability and consumable design.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+          <t>Printer maintains print quality and reliability for at least 80,000 pages under normal usage.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -738,17 +726,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+          <t>Ensure the printer meets EPEAT3, LOT4, and Blue Angel environmental and efficiency requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+          <t>Enables sales in regulated markets and meets sustainability goals.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -758,17 +746,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Compliance, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires new bottle design and supply chain adjustments.</t>
+          <t>Design and certification processes.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+          <t>Printer receives EPEAT3, LOT4, and Blue Angel certifications for the PDL SKU.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -776,7 +764,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -788,17 +776,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+          <t>Redesign the input and output trays to accommodate the increased tank size and protrusion.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+          <t>Ensures mechanical compatibility and usability with the larger tank.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -808,25 +796,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing']</t>
+          <t>Mechanical Engineering, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires reliability testing and warranty program setup.</t>
+          <t>Tank and chassis design.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+          <t>Trays function without interference and support stated paper capacities with new tank design.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -838,45 +826,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the printer for enhanced user interface.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+          <t>Improves usability and access to advanced features.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>End Users, UI/UX Team, Product Management</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires portal and solution development; integration with printer firmware.</t>
+          <t>UI software and hardware integration.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+          <t>Display is functional, responsive, and passes usability testing.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -888,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PDL SKU: Speed and Protocol Support</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+          <t>Update the service station with aerosol management features to address changes due to larger tank.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+          <t>Prevents ink aerosol contamination and maintains internal cleanliness.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -908,25 +896,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware enhancements; certification processes.</t>
+          <t>Service station design updates.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PDL SKU achieves target speed, protocol support, and Blue Angel certification.</t>
+          <t>Aerosol levels within printer remain below safety thresholds during operation and servicing.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -938,45 +926,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sustainability: 60% RCP Content</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+          <t>Update the carriage dynamic and force model to account for new tube routing and increased component weights.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+          <t>Mechanical Engineering, R&amp;D</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires sourcing and supply chain alignment.</t>
+          <t>Tube routing and weight distribution analysis.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
+          <t>Carriage operates within force and speed tolerances in all print modes.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -988,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal for Manageability</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+          <t>Redesign paper path components to support increased page life and durability targets.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+          <t>Prevents wear and ensures consistent performance over 80,000 pages.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1008,25 +996,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['GXD', 'BA', 'Marketing']</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires portal development and integration with device firmware.</t>
+          <t>Material selection and mechanical design.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+          <t>Paper path components show no significant wear after 80,000 pages in testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1038,45 +1026,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AI Solutions: Print, Scan, Support</t>
+          <t>Ink Maintenance Serviceable Part (Post 80K Life)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+          <t>Design the ink maintenance box as a serviceable part to be replaced after 80,000 pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+          <t>Supports extended printer life and serviceability.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'GXD', 'BA']</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires AI platform integration and validation.</t>
+          <t>Maintenance box design and service documentation.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>AI features are functional and validated in real-world SMB environments.</t>
+          <t>Maintenance box can be replaced at service centers; replacement restores printer to operational status.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1088,45 +1076,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Platform Support for PaaS</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+          <t>Implement a new make-break and fluidic interface (FI) connection for the IDS (Ink Delivery System).</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+          <t>Improves reliability and supports new tank/bottle design.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires software and service integration.</t>
+          <t>IDS and tank design.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PaaS features are available and operational in production units.</t>
+          <t>New connection passes leak and reliability testing under all operating conditions.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1138,43 +1126,1393 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Increased Size, Keying, and LOI for LEBI Ink-Tank</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Increase the size and introduce keying and LOI (Level of Integration) features for the LEBI ink-tank.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Prevents incorrect installation and supports higher ink volumes.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, End Users</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tank and bottle design updates.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tanks only accept correct bottles and support increased ink volume; confirmed in assembly and user testing.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Develop a new startup algorithm and air management system for the IDS.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ensures reliable ink delivery and prevents air bubbles during initial setup and operation.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>IDS hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Startup algorithm initializes IDS without air entrapment in &gt;99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>New Print Quality Goals and Depletion Model</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Define new print quality (PQ) goals and depletion model to align with increased page yield and warranty targets.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ensures consistent print quality throughout the extended printer life.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ink, printhead, and firmware updates.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Print quality meets or exceeds specified metrics for 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp PHA, Magi, Nessie Pigment Inks</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Reuse existing SuperAmp PHA and Magi/Nessie pigment inks without reformulation for the Magellan program.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Leverages proven technology, reduces development time and cost.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Product Management</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Compatibility validation with new system.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>No ink reformulation required; confirmed compatibility with new bottles and tanks.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide molds for 1-4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Manufacturing, R&amp;D, Operations</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Capital expenditure approval and line reconfiguration.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Factory lines operational with new modifications and capable of meeting production targets.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Support for Services and Contractual Models</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Support services, contractual agreements, and warranty support for NOA-F as service parts.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enables new business models and post-sale support.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Service, Sales, Product Management</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Service parts logistics and documentation.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NOA-F available as service part and covered under warranty as specified.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Support for SMB Manageability and Enterprise Solutions</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Integrate SMB manageability and enterprise support features, including WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Meets requirements of business customers for fleet management and support.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SMB and Enterprise Customers, IT Admins, Product Management</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Software and firmware integration.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Printer integrates with WJA, HPSM, and JAM; verified in enterprise environment tests.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Support for Multiple Client and Driver Paths</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Provide support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility and ease of deployment across customer segments.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>End Users, IT Admins, Product Management</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Driver and client software updates.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>All listed clients/drivers install and function without errors on supported OS.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Security: Gauss4.xx (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx hardware and firmware security features.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Protects against security threats and meets enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Enterprise Customers, IT Security, Product Management</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Security hardware and firmware development.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Printer passes internal and third-party security audits for Gauss4.xx compliance.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Schedule Constraints: Launch in S’27</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Meet time-to-market goals for S’27 with minimal investment leveraging existing platforms and technologies.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ensures competitive positioning and timely revenue generation.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Executive Team, Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Project management and resource allocation.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>All critical path milestones achieved according to schedule.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ensure SuperAmp PHA (Printhead Assembly) achieves a minimum life of 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aligns with service interval and reliability targets for business users.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Printhead design and quality assurance.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes life testing for 65,000 pages without failure.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Offer a warranty life of 2 years for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Aligns with industry standards and customer expectations.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Sales</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Component reliability and service policies.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Warranty terms published and honored for 2 years from purchase.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Achieve print speeds of 25/20 pages per minute, with 25/19 ppm for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Meets performance expectations for target segments.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Print engine design and firmware.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Printers meet or exceed specified throughput in standard performance tests.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Serviceability: Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ensure the maintenance box is serviceable to support ongoing printer reliability and uptime.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Reduces downtime and cost of service for high-usage customers.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Maintenance box design and documentation.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by service personnel with minimal tools and time.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Requires integration with SMB portal and AI solutions platform.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO with Minimal Intervention</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Requires durable design, high-yield consumables, and reliable components.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>First Business Ink Tank Printer for SMBs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Requires new hardware platform; alignment with HP’s existing product portfolio.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 6, 7, 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Requires redesign of maintenance subsystem; must be customer-replaceable.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Requires modular design and documentation; warranty process alignment.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Requires new bottle design and supply chain adjustments.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['Quality', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Requires reliability testing and warranty program setup.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Requires portal and solution development; integration with printer firmware.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PDL SKU: Speed and Protocol Support</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Requires hardware and firmware enhancements; certification processes.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed, protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Requires sourcing and supply chain alignment.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal for Manageability</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>['GXD', 'BA', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Requires portal development and integration with device firmware.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AI Solutions: Print, Scan, Support</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'GXD', 'BA']</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Requires AI platform integration and validation.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Platform Support for PaaS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>['Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Requires software and service integration.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Mobile Printing via HP App</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>['GXD', 'Marketing']</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Requires app integration and testing with Magellan firmware.</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I42" t="n">
         <v>0.9</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 9, 10</t>
         </is>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Yield</t>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size must support &gt;8K yield.</t>
+          <t>Integrate advanced AI-powered productivity features, scan workflow automation, and manageability solutions into the Magellan printer to simplify business operations for SMBs.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Increases ink yield per bottle, reducing frequency of replacement and supporting high-volume customers.</t>
+          <t>To deliver breakthrough productivity and ease of management, differentiating HP from competitors and addressing SMB customer needs for efficiency.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires bottle redesign and compatibility with existing or new tank systems.</t>
+          <t>Requires AI software integration and SMB portal support.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New bottles pass reliability, spill-free, and integration testing; CMY bottles confirmed for &gt;8K yield; 6K yield for Black and CMY verified.</t>
+          <t>AI-powered productivity, scan, and management features are available and verifiable in the product UI; features function as documented and pass UAT.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Bottles</t>
+          <t>Lowest Business TCO (Total Cost of Ownership)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure that the new bottles provide spill-free reliability during handling and installation.</t>
+          <t>Design Magellan to deliver the lowest total cost of ownership for SMBs among HP business printers, including minimal intervention and optimized consumables.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reduces mess and improves user experience, critical for customer satisfaction.</t>
+          <t>To attract cost-conscious SMBs and compete effectively in the CISS PLE Hi segment.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,25 +546,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Customer Support</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and tank interface design.</t>
+          <t>Requires optimized hardware, ink tank design, and efficient consumables.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spills during normal bottle handling and installation in &gt;99.5% of test cases.</t>
+          <t>TCO calculations demonstrate lower ownership costs than previous HP models and key competitors in third-party benchmarks.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (Non-Original Accessory Filter) with a metal foiled labyrinth and lid label; maintain current click-on push-push and TDF mechanisms.</t>
+          <t>Introduce a replaceable maintenance box that customers can easily swap without technical support, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Improves product security and reliability, while ensuring compatibility with existing mechanisms.</t>
+          <t>Addresses new SMB customer segment needs and reduces reliance on service centers, increasing customer satisfaction.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Security</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design and manufacturing capability.</t>
+          <t>Design must ensure ease of replacement and minimal risk of error.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F units pass security and reliability tests, and are compatible with push-push and TDF mechanisms.</t>
+          <t>Customer can replace maintenance box within 5 minutes using only supplied instructions; no tools required; validated in usability testing.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Support for Customer-Replaceable PHA and NOA-F</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Design the printer to allow customers to replace the PHA (Printhead Assembly) and NOA-F themselves.</t>
+          <t>Utilize uniquely keyed ink bottles to prevent incorrect refilling and ensure compatibility, reducing user error and warranty claims.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and lowers service costs.</t>
+          <t>Improves user experience and reduces support costs due to incorrect ink usage.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,25 +646,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mechanical design for easy access and replacement.</t>
+          <t>Requires new bottle design and printer detection mechanism.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F with no tools and minimal instruction; verified in usability testing.</t>
+          <t>Ink bottles are physically keyed and only compatible with intended slots; verified in QA and field tests.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
+          <t>Develop a consolidated SMB portal for managing multiple printers, targeting unmanaged or lightly managed SMBs without dedicated IT staff.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Extends service intervals and aligns with customer expectations for durability.</t>
+          <t>Enables easy fleet management for SMBs, a key differentiator for Magellan.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,25 +696,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Component reliability and consumable design.</t>
+          <t>Requires backend infrastructure and secure authentication.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Printer maintains print quality and reliability for at least 80,000 pages under normal usage.</t>
+          <t>Portal is accessible, supports management of at least 15 printers, and passes security and usability tests.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -726,45 +726,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>PaaS (Platform as a Service) Support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure the printer meets EPEAT3, LOT4, and Blue Angel environmental and efficiency requirements for the PDL SKU.</t>
+          <t>Ensure Magellan is compatible with HP's PaaS offerings, enabling subscription-based services and remote management features.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enables sales in regulated markets and meets sustainability goals.</t>
+          <t>Supports HP's business model shift and customer demand for flexible, scalable solutions.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Marketing</t>
+          <t>['Marketing', 'DVAR', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Design and certification processes.</t>
+          <t>Integration with HP PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Printer receives EPEAT3, LOT4, and Blue Angel certifications for the PDL SKU.</t>
+          <t>Magellan can be provisioned, managed, and monitored via HP PaaS platform; validated in integration testing.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
     </row>
@@ -776,45 +776,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>PDL/PS Support for PDL SKU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redesign the input and output trays to accommodate the increased tank size and protrusion.</t>
+          <t>Provide full PDL (Page Description Language) and PostScript support for the PDL SKU, with print speeds of 25/20 ppm (improvement over current 25/19).</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and usability with the larger tank.</t>
+          <t>Enables compatibility with business printing workflows and differentiates Magellan in the SMB segment.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D, End Users</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tank and chassis design.</t>
+          <t>Firmware and driver development for PDL/PS support.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Trays function without interference and support stated paper capacities with new tank design.</t>
+          <t>PDL SKU achieves 25/20 ppm in standardized print tests; PDL/PS compatibility validated with common business software.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the printer for enhanced user interface.</t>
+          <t>Achieve Blue Angel environmental certification for the PDL SKU, demonstrating commitment to sustainability and eco-friendly design.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Improves usability and access to advanced features.</t>
+          <t>Meets regulatory requirements and enhances appeal to environmentally conscious SMBs.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>End Users, UI/UX Team, Product Management</t>
+          <t>['Prod Steward', 'Tech Reg', 'Quality']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UI software and hardware integration.</t>
+          <t>Design and materials must meet Blue Angel criteria.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Display is functional, responsive, and passes usability testing.</t>
+          <t>Certification is obtained and documented prior to launch.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -876,45 +876,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>80k/2 Year Warranty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Update the service station with aerosol management features to address changes due to larger tank.</t>
+          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Prevents ink aerosol contamination and maintains internal cleanliness.</t>
+          <t>Provides peace of mind for SMB customers and aligns with market expectations.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>['Quality', 'Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Service station design updates.</t>
+          <t>Requires reliability testing and service planning.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aerosol levels within printer remain below safety thresholds during operation and servicing.</t>
+          <t>Warranty terms are published and supported; warranty claims tracked for compliance.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Serviceability: PHA and MINK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Update the carriage dynamic and force model to account for new tube routing and increased component weights.</t>
+          <t>Enable customer-replaceable PHA components and MINK at service centers, with a target of making MINK customer-replaceable if out of warranty.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+          <t>Reduces downtime and service costs, improving SMB satisfaction and lowering HP support burden.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,25 +946,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tube routing and weight distribution analysis.</t>
+          <t>Component design for easy replacement; documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Carriage operates within force and speed tolerances in all print modes.</t>
+          <t>PHA and MINK can be replaced per service guide; validated in field trials.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Redesign paper path components to support increased page life and durability targets.</t>
+          <t>Integrate advanced AI algorithms for print and scan quality enhancement, ensuring optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Prevents wear and ensures consistent performance over 80,000 pages.</t>
+          <t>Delivers superior print/scan quality and differentiates Magellan from competitors.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,25 +996,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Material selection and mechanical design.</t>
+          <t>Requires AI software integration and hardware compatibility.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paper path components show no significant wear after 80,000 pages in testing.</t>
+          <t>AI features demonstrably improve print/scan quality in benchmark tests; user satisfaction &gt;90% in surveys.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
@@ -1026,45 +1026,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80K Life)</t>
+          <t>Sustainability: 60% RCP Content</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Design the ink maintenance box as a serviceable part to be replaced after 80,000 pages.</t>
+          <t>Ensure Magellan is manufactured with at least 60% recycled content plastic (RCP), exceeding competitor benchmarks (Epson 30%).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Supports extended printer life and serviceability.</t>
+          <t>Appeals to environmentally conscious customers and aligns with HP sustainability goals.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>['Prod Steward', 'Quality', 'Marketing']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Maintenance box design and service documentation.</t>
+          <t>Supply chain and manufacturing process updates.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced at service centers; replacement restores printer to operational status.</t>
+          <t>Product Bill of Materials demonstrates 60% RCP; verified by third-party audit.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Implement a new make-break and fluidic interface (FI) connection for the IDS (Ink Delivery System).</t>
+          <t>Support mobile printing workflows through the HP App, enabling users to print from smartphones and tablets.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Improves reliability and supports new tank/bottle design.</t>
+          <t>Addresses modern SMB mobility needs and enhances user convenience.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,25 +1096,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>['GXD', 'Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>App integration and cross-platform compatibility.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>New connection passes leak and reliability testing under all operating conditions.</t>
+          <t>Users can print from iOS and Android HP Apps; feature passes cross-device testing.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Increased Size, Keying, and LOI for LEBI Ink-Tank</t>
+          <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Increase the size and introduce keying and LOI (Level of Integration) features for the LEBI ink-tank.</t>
+          <t>Implement telemetry features for remote diagnostics, usage tracking, and predictive maintenance, aligned with HP enterprise standards.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Prevents incorrect installation and supports higher ink volumes.</t>
+          <t>Enables proactive support, reduces downtime, and supports PaaS business model.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,47 +1146,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>['R&amp;D Telemetry', 'Quality', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tank and bottle design updates.</t>
+          <t>Backend infrastructure and secure data handling.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tanks only accept correct bottles and support increased ink volume; confirmed in assembly and user testing.</t>
+          <t>Telemetry data is available in the SMB portal and HP support tools; GDPR compliance verified.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm and air management system for the IDS.</t>
+          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield; CMY bottle size must support &gt;8K pages.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures reliable ink delivery and prevents air bubbles during initial setup and operation.</t>
+          <t>To increase ink capacity and reduce customer intervention, supporting higher print volumes and competitive positioning.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,21 +1196,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IDS hardware and firmware.</t>
+          <t>Ink formulation compatibility, bottle manufacturing updates</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Startup algorithm initializes IDS without air entrapment in &gt;99% of test cycles.</t>
+          <t>Bottles must be able to deliver at least 6,000 pages (Black/CMY) and &gt;8,000 pages (CMY) as validated by standardized yield tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1221,22 +1221,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Model</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Define new print quality (PQ) goals and depletion model to align with increased page yield and warranty targets.</t>
+          <t>Ensure the new ink bottles and tank system deliver spill-free reliability during user refill and maintenance operations.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality throughout the extended printer life.</t>
+          <t>Improves user experience and minimizes mess/errors, reducing support costs and customer complaints.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,21 +1246,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Quality Assurance</t>
+          <t>End Users, Customer Support</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ink, printhead, and firmware updates.</t>
+          <t>Bottle and tank design, IDS integration</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Print quality meets or exceeds specified metrics for 80,000 pages.</t>
+          <t>Less than 1% of user refill events result in ink spills, as measured in field trials and lab tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1271,46 +1271,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp PHA, Magi, Nessie Pigment Inks</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reuse existing SuperAmp PHA and Magi/Nessie pigment inks without reformulation for the Magellan program.</t>
+          <t>Integrate NOA-F (Non-OEM Accessory-Filter) with a metal foiled labyrinth and lid label. No changes to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Leverages proven technology, reduces development time and cost.</t>
+          <t>Enhances security, reliability, and differentiation from competitors while maintaining user familiarity.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Product Security, End Users</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Compatibility validation with new system.</t>
+          <t>NOA-F supply chain, mechanical design constraints</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No ink reformulation required; confirmed compatibility with new bottles and tanks.</t>
+          <t>NOA-F units must pass reliability and security tests with the new labyrinth and label, and be compatible with existing mechanisms.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1321,22 +1321,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide molds for 1-4 new keyed caps.</t>
+          <t>Leverage existing SuperAmp Si PHA hardware and Magi/Nessie pigment ink without reformulation.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ensures manufacturing capability for new components.</t>
+          <t>Reduces R&amp;D cost, accelerates time-to-market, and leverages proven technology.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,21 +1346,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D, Operations</t>
+          <t>Engineering, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Capital expenditure approval and line reconfiguration.</t>
+          <t>Compatibility of new system with legacy components</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Factory lines operational with new modifications and capable of meeting production targets.</t>
+          <t>100% compatibility of reused components in prototype and pilot production builds.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1371,46 +1371,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Support for Services and Contractual Models</t>
+          <t>Ink System Reliability and Characterization</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Support services, contractual agreements, and warranty support for NOA-F as service parts.</t>
+          <t>Model and characterize reliability, water vapor transmission rate (WVTR), air gain, flow rate, and IDS including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Enables new business models and post-sale support.</t>
+          <t>Ensures consistent print quality and system reliability over product lifecycle.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Service, Sales, Product Management</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Service parts logistics and documentation.</t>
+          <t>IDS development, system integration</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NOA-F available as service part and covered under warranty as specified.</t>
+          <t>Validated models and test data for all key reliability metrics before design freeze.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1421,42 +1421,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Support for SMB Manageability and Enterprise Solutions</t>
+          <t>Ink Stability Modeling and PQ Impact Analysis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Integrate SMB manageability and enterprise support features, including WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM.</t>
+          <t>Model ink stability in the tank and analyze its impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Meets requirements of business customers for fleet management and support.</t>
+          <t>Maintains high print quality and reduces risk of ink degradation over time.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Customers, IT Admins, Product Management</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Software and firmware integration.</t>
+          <t>Access to ink chemistry data, tank design</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Printer integrates with WJA, HPSM, and JAM; verified in enterprise environment tests.</t>
+          <t>Documented ink stability model and PQ impact report reviewed and approved by R&amp;D.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1471,46 +1471,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Support for Multiple Client and Driver Paths</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Provide support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>NOA-F must be available as service parts for warranty support and field replacements.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures broad compatibility and ease of deployment across customer segments.</t>
+          <t>Ensures serviceability and customer satisfaction during warranty period.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>End Users, IT Admins, Product Management</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Driver and client software updates.</t>
+          <t>Service supply chain, inventory planning</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>All listed clients/drivers install and function without errors on supported OS.</t>
+          <t>NOA-F service parts available in service centers within 3 months of product launch.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1521,46 +1521,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Security: Gauss4.xx (HW &amp; FW)</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features.</t>
+          <t>Integrate Acumen 6 technology onto the ink bottle lid for authentication or tracking.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Protects against security threats and meets enterprise security standards.</t>
+          <t>Improves anti-counterfeiting and supply chain traceability.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT Security, Product Management</t>
+          <t>Product Security, Supply Chain</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Security hardware and firmware development.</t>
+          <t>Lid design, Acumen 6 system integration</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Printer passes internal and third-party security audits for Gauss4.xx compliance.</t>
+          <t>Acumen 6 feature fully functional and passes security validation tests.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1571,22 +1571,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Schedule Constraints: Launch in S’27</t>
+          <t>Modify Factory Line for NOA-F and New Bottles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Meet time-to-market goals for S’27 with minimal investment leveraging existing platforms and technologies.</t>
+          <t>Modify SA14 production line for NOA-F assembly; add Magi ink cart and labeling tool in Orcus 5. Mold for 1-4 new keyed caps required.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures competitive positioning and timely revenue generation.</t>
+          <t>Supports manufacturing of new consumables and assemblies.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Executive Team, Product Management, R&amp;D</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Project management and resource allocation.</t>
+          <t>Factory retooling schedules, cap design finalization</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>All critical path milestones achieved according to schedule.</t>
+          <t>Factory lines operational and producing new components at required yield rates before launch.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1614,29 +1614,29 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA (Printhead Assembly) achieves a minimum life of 65,000 pages.</t>
+          <t>Design the system to allow customers to easily replace PHA (Printhead Assembly) and NOA-F without professional service.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aligns with service interval and reliability targets for business users.</t>
+          <t>Improves user experience and reduces service costs.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1646,47 +1646,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>End Users, Service</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Printhead design and quality assurance.</t>
+          <t>Design for serviceability, user documentation</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing for 65,000 pages without failure.</t>
+          <t>Replacement process can be performed by end users in under 5 minutes with no tools, as validated in usability studies.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years</t>
+          <t>New Warranty Page Life Goal: 80K Pages</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Offer a warranty life of 2 years for the Magellan printer.</t>
+          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aligns with industry standards and customer expectations.</t>
+          <t>Extends product life and supports higher duty cycle use-cases, competitive advantage.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1696,97 +1696,97 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Sales</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Component reliability and service policies.</t>
+          <t>Component durability, consumable yield, warranty policy</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Warranty terms published and honored for 2 years from purchase.</t>
+          <t>Printer must reliably print 80,000 pages without major failure, as verified in accelerated life testing.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Achieve print speeds of 25/20 pages per minute, with 25/19 ppm for PDL SKU.</t>
+          <t>Adopt Reddington ID with a size increase for the ink tank. No change to Marconi-HI ADF (Automatic Document Feeder).</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Meets performance expectations for target segments.</t>
+          <t>Supports higher ink capacity and aligns with existing industrial design.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>End Users, Product Management, R&amp;D</t>
+          <t>Industrial Design, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Print engine design and firmware.</t>
+          <t>Tank design, chassis compatibility</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Printers meet or exceed specified throughput in standard performance tests.</t>
+          <t>New tank design integrated into Reddington ID and passes mechanical and aesthetic validation.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ensure the maintenance box is serviceable to support ongoing printer reliability and uptime.</t>
+          <t>Utilize EPS foam packaging for the printer and consumables.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Reduces downtime and cost of service for high-usage customers.</t>
+          <t>Protects product during shipping and handling.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,47 +1796,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>Logistics, Manufacturing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Maintenance box design and documentation.</t>
+          <t>Packaging design, material sourcing</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by service personnel with minimal tools and time.</t>
+          <t>Products pass drop and vibration tests with EPS packaging.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+          <t>Ensure compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+          <t>Meets regulatory and market requirements for sustainability and eco-labels.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,147 +1846,147 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>Regulatory, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solutions platform.</t>
+          <t>Design and material choices, certification processes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+          <t>PDL SKU achieves EPEAT3, LOT4, and Blue Angel certifications before launch.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lowest Business TCO with Minimal Intervention</t>
+          <t>Input/Output Tray Modifications for Tank Protrusion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+          <t>Modify input and output trays to align with the increased tank protrusion.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+          <t>Ensures mechanical compatibility and usability.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+          <t>Mechanical Design, End Users</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Requires durable design, high-yield consumables, and reliable components.</t>
+          <t>Tank design finalization</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+          <t>Trays function correctly with new tank and pass fit/form/function tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>First Business Ink Tank Printer for SMBs</t>
+          <t>Size Optimization of Printer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+          <t>Optimize overall printer size, considering the increased tank and new components.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+          <t>Maintains competitive footprint and maximizes desk space efficiency.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+          <t>Industrial Design, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Requires new hardware platform; alignment with HP’s existing product portfolio.</t>
+          <t>Component layout, tank design</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+          <t>Final product dimensions do not exceed agreed size envelope and pass ergonomic review.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6, 7, 12</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+          <t>Integrate a 4.3” CGD (Color Graphic Display) into the printer for enhanced user interface.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+          <t>Improves user experience and modernizes product appearance.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1996,147 +1996,147 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+          <t>End Users, UI/UX Team</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Requires redesign of maintenance subsystem; must be customer-replaceable.</t>
+          <t>Electrical and mechanical integration, UI software</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+          <t>Display is fully functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK)</t>
+          <t>4-Tube Platform with Sayan Sibstar Tubes and New Routing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+          <t>Leverage Sayan Sibstar tubes, introduce new tube routing and integration for the 4-tube platform.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+          <t>Supports new ink system architecture and reliability.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Requires modular design and documentation; warranty process alignment.</t>
+          <t>Tube design, routing validation</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+          <t>Tube routing supports reliable ink delivery and passes stress and reliability tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+          <t>Update service station for aerosol management with spit platform changes due to new tank design.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+          <t>Prevents contamination and maintains print quality.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Requires new bottle design and supply chain adjustments.</t>
+          <t>Service station and tank design</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+          <t>Aerosol emissions are within regulatory and HP internal limits.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and weights.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2146,47 +2146,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing']</t>
+          <t>Mechanical Engineering, R&amp;D</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Requires reliability testing and warranty program setup.</t>
+          <t>Tube and carriage design</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+          <t>Carriage operates within force budget and passes mechanical reliability tests.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+          <t>Redesign paper path to support increased page life (80K pages).</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+          <t>Ensures durability and reliability for higher duty cycles.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Requires portal and solution development; integration with printer firmware.</t>
+          <t>Paper path material and design updates</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+          <t>Paper path components pass 80K page accelerated wear tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2214,29 +2214,29 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PDL SKU: Speed and Protocol Support</t>
+          <t>Ink Maintenance Serviceable Part Post 80K Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+          <t>Design ink maintenance as a serviceable part to be replaced at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+          <t>Extends printer usable life and supports high-volume users.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,47 +2246,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware enhancements; certification processes.</t>
+          <t>Maintenance part design, service documentation</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PDL SKU achieves target speed, protocol support, and Blue Angel certification.</t>
+          <t>Service centers can replace part in &lt;30 minutes; validated in pilot service program.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sustainability: 60% RCP Content</t>
+          <t>140ml K and XXml CMY Bottles</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+          <t>Introduce new 140ml Black (K) bottles and appropriately sized CMY bottles for the new system.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+          <t>Aligns with increased yield and system design.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires sourcing and supply chain alignment.</t>
+          <t>Bottle design, supply chain</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
+          <t>Bottles meet yield and compatibility requirements in system validation tests.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2314,29 +2314,29 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal for Manageability</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+          <t>Develop new make-break and fluidic interconnect (FI) connection for the IDS (Ink Delivery System).</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+          <t>Improves reliability and serviceability of the ink system.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2346,47 +2346,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['GXD', 'BA', 'Marketing']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires portal development and integration with device firmware.</t>
+          <t>IDS and bottle design</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+          <t>New connection passes leak, durability, and usability tests.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AI Solutions: Print, Scan, Support</t>
+          <t>Increased Size, Keying, and LOI for LEBI Ink-Tank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+          <t>Increase LEBI (Low-End Bulk Ink) ink-tank size, implement new keying, and integrate LOI (Level of Integration) with one SHAID (Security Hardware Authentication ID).</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+          <t>Prevents misinstallation, supports higher capacity, and enhances security.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2396,125 +2396,575 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'GXD', 'BA']</t>
+          <t>Product Security, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires AI platform integration and validation.</t>
+          <t>Tank and keying design, SHAID integration</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AI features are functional and validated in real-world SMB environments.</t>
+          <t>Tank passes installation, capacity, and security validation tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Platform Support for PaaS</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+          <t>Develop a new IDS startup algorithm and air management system for reliable operation.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+          <t>Ensures consistent startup and prevents air entrapment issues.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires software and service integration.</t>
+          <t>IDS and firmware development</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PaaS features are available and operational in production units.</t>
+          <t>System starts up reliably in 99% of power-on cycles in lab and field tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
+          <t>Implement new servicing and startup algorithms for improved reliability and user experience.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
+          <t>Reduces errors and improves printer uptime.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires app integration and testing with Magellan firmware.</t>
+          <t>Firmware development, IDS integration</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+          <t>Algorithms reduce startup and servicing errors by 50% over previous generation in controlled trials.</t>
         </is>
       </c>
       <c r="I42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>New PQ Goals and Depletion Definition</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Establish new print quality (PQ) goals and depletion definitions to align with new page yield targets.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations and marketing claims.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yield testing, PQ evaluation</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics approved by cross-functional team and validated in system tests.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
         <v>0.9</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, 10</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi, Dune FW</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware for the new printer.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven, reliable components.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Engineering, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Compatibility with new platform</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>All reused components function as required in system integration tests.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Integrate Gauss4.xx hardware and firmware security features into the printer.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Protects product and user data from security threats.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Product Security, IT, End Users</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HW/FW integration, security validation</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Security features pass internal and external penetration testing.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Printer must support print speeds of 25/20 pages per minute (ppm) for standard and 25/19 ppm for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Meets market expectations for performance and competitiveness.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Marketing</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Print engine and firmware capability</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Printer achieves required speeds in standardized performance tests.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Serviceability: Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Design printer with a serviceable maintenance box for easy end-user or service center replacement.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Improves uptime and reduces repair costs.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Maintenance box design, service documentation</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Box can be replaced in under 10 minutes by trained personnel or end users.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SMB Solution and PaaS Support</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Support SMB solution features and Printer-as-a-Service (PaaS) business models.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports new revenue streams.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Business Development, SMB Customers, IT</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Solution software, service integration</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Printer integrates with SMB solution and PaaS platforms as required by business model.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Support hosting of 12K-CMYK and trade page yield of 6K as flexible business requirements.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Provides flexibility for different market segments and promotions.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yield validation, SKU management</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Printer supports 12K-CMYK and 6K trade page configurations as validated in market trials.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Solution and Services Integration: Scan, Manageability, Enterprise Support</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Integrate scan solutions, SMB manageability, and enterprise support including WJA (Web Jetadmin), HPSM, JAM.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Meets enterprise and SMB customer requirements for fleet management and workflow.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Enterprise IT, SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Software integration, platform compatibility</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>All solution features are functional and validated in enterprise and SMB pilot deployments.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Maximizes compatibility and ease of use for customers across segments.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>End Users, IT, Support</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Driver and client software updates</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity features, scan workflow automation, and manageability solutions into the Magellan printer to simplify business operations for SMBs.</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To deliver breakthrough productivity and ease of management, differentiating HP from competitors and addressing SMB customer needs for efficiency.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires AI software integration and SMB portal support.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI-powered productivity, scan, and management features are available and verifiable in the product UI; features function as documented and pass UAT.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver the lowest total cost of ownership for SMBs among HP business printers, including minimal intervention and optimized consumables.</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To attract cost-conscious SMBs and compete effectively in the CISS PLE Hi segment.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,25 +546,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires optimized hardware, ink tank design, and efficient consumables.</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TCO calculations demonstrate lower ownership costs than previous HP models and key competitors in third-party benchmarks.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that customers can easily swap without technical support, reducing downtime and service costs.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Addresses new SMB customer segment needs and reduces reliance on service centers, increasing customer satisfaction.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Design must ensure ease of replacement and minimal risk of error.</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Customer can replace maintenance box within 5 minutes using only supplied instructions; no tools required; validated in usability testing.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Utilize uniquely keyed ink bottles to prevent incorrect refilling and ensure compatibility, reducing user error and warranty claims.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs due to incorrect ink usage.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,21 +646,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires new bottle design and printer detection mechanism.</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ink bottles are physically keyed and only compatible with intended slots; verified in QA and field tests.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,45 +676,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMB Portal for Device Management</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers, targeting unmanaged or lightly managed SMBs without dedicated IT staff.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enables easy fleet management for SMBs, a key differentiator for Magellan.</t>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires backend infrastructure and secure authentication.</t>
+          <t>Requires design of bottle and tank interface.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Portal is accessible, supports management of at least 15 printers, and passes security and usability tests.</t>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -726,45 +726,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PaaS (Platform as a Service) Support</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure Magellan is compatible with HP's PaaS offerings, enabling subscription-based services and remote management features.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Supports HP's business model shift and customer demand for flexible, scalable solutions.</t>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Marketing', 'DVAR', 'Tech Reg', 'BA']</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Integration with HP PaaS infrastructure.</t>
+          <t>Requires durability testing and warranty policy alignment.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Magellan can be provisioned, managed, and monitored via HP PaaS platform; validated in integration testing.</t>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -776,41 +776,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PDL/PS Support for PDL SKU</t>
+          <t>Serviceability – PHA and MINK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide full PDL (Page Description Language) and PostScript support for the PDL SKU, with print speeds of 25/20 ppm (improvement over current 25/19).</t>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enables compatibility with business printing workflows and differentiates Magellan in the SMB segment.</t>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Firmware and driver development for PDL/PS support.</t>
+          <t>Requires design for replaceability and service documentation.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm in standardized print tests; PDL/PS compatibility validated with common business software.</t>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -826,17 +826,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Achieve Blue Angel environmental certification for the PDL SKU, demonstrating commitment to sustainability and eco-friendly design.</t>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meets regulatory requirements and enhances appeal to environmentally conscious SMBs.</t>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Quality']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Design and materials must meet Blue Angel criteria.</t>
+          <t>Requires software development and integration with hardware.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Certification is obtained and documented prior to launch.</t>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -876,41 +876,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80k/2 Year Warranty</t>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Provides peace of mind for SMB customers and aligns with market expectations.</t>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing', 'BA']</t>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires reliability testing and service planning.</t>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Warranty terms are published and supported; warranty claims tracked for compliance.</t>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -926,45 +926,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serviceability: PHA and MINK</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK at service centers, with a target of making MINK customer-replaceable if out of warranty.</t>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs, improving SMB satisfaction and lowering HP support burden.</t>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>['Marketing', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design for easy replacement; documentation.</t>
+          <t>Requires AI software and sensor integration.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PHA and MINK can be replaced per service guide; validated in field trials.</t>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Integrate advanced AI algorithms for print and scan quality enhancement, ensuring optimal output with minimal user intervention.</t>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Delivers superior print/scan quality and differentiates Magellan from competitors.</t>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,25 +996,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires AI software integration and hardware compatibility.</t>
+          <t>Requires sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>AI features demonstrably improve print/scan quality in benchmark tests; user satisfaction &gt;90% in surveys.</t>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -1026,37 +1026,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sustainability: 60% RCP Content</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure Magellan is manufactured with at least 60% recycled content plastic (RCP), exceeding competitor benchmarks (Epson 30%).</t>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Appeals to environmentally conscious customers and aligns with HP sustainability goals.</t>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Quality', 'Marketing']</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Supply chain and manufacturing process updates.</t>
+          <t>Requires app development and printer firmware support.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product Bill of Materials demonstrates 60% RCP; verified by third-party audit.</t>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
@@ -1076,45 +1076,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>PaaS Enablement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Support mobile printing workflows through the HP App, enabling users to print from smartphones and tablets.</t>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Addresses modern SMB mobility needs and enhances user convenience.</t>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'BA']</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>App integration and cross-platform compatibility.</t>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Users can print from iOS and Android HP Apps; feature passes cross-device testing.</t>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Advanced Telemetry Requirements</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Implement telemetry features for remote diagnostics, usage tracking, and predictive maintenance, aligned with HP enterprise standards.</t>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enables proactive support, reduces downtime, and supports PaaS business model.</t>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,47 +1146,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'Tech Reg', 'BA']</t>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Backend infrastructure and secure data handling.</t>
+          <t>Requires secure data collection and privacy compliance.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Telemetry data is available in the SMB portal and HP support tools; GDPR compliance verified.</t>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, 12</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>Advanced Security and Compliance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield; CMY bottle size must support &gt;8K pages.</t>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To increase ink capacity and reduce customer intervention, supporting higher print volumes and competitive positioning.</t>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,47 +1196,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ink formulation compatibility, bottle manufacturing updates</t>
+          <t>Requires security features and regulatory review.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bottles must be able to deliver at least 6,000 pages (Black/CMY) and &gt;8,000 pages (CMY) as validated by standardized yield tests.</t>
+          <t>Product passes security and compliance audits for target markets.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, inferred from multiple sections</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ensure the new ink bottles and tank system deliver spill-free reliability during user refill and maintenance operations.</t>
+          <t>Develop NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size supporting &gt;8K yield.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves user experience and minimizes mess/errors, reducing support costs and customer complaints.</t>
+          <t>To increase ink capacity and reduce frequency of bottle replacement, addressing customer demand for higher yield and convenience.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,21 +1246,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Customer Support</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bottle and tank design, IDS integration</t>
+          <t>Requires modifications to IDS, bottle design, and possibly packaging.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Less than 1% of user refill events result in ink spills, as measured in field trials and lab tests.</t>
+          <t>NGB keyed bottles are developed and tested to reliably deliver 6K Black and 6K CMY page yields (with CMY &gt;8K possible), verified by page yield tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1271,22 +1271,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Spill-Free Reliability in Ink Bottles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate NOA-F (Non-OEM Accessory-Filter) with a metal foiled labyrinth and lid label. No changes to click-on push-push and TDF mechanisms.</t>
+          <t>Ensure new ink bottles and refilling system provide spill-free reliability during user operation.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Enhances security, reliability, and differentiation from competitors while maintaining user familiarity.</t>
+          <t>Spill-free operation is critical to user satisfaction and competitive differentiation, especially for CISS systems.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Security, End Users</t>
+          <t>End Users, R&amp;D, Support Teams</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NOA-F supply chain, mechanical design constraints</t>
+          <t>Design of bottle, nozzle, and tank interface; compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NOA-F units must pass reliability and security tests with the new labyrinth and label, and be compatible with existing mechanisms.</t>
+          <t>No ink spills occur during standard user refilling in 100% of test cases.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1321,22 +1321,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA hardware and Magi/Nessie pigment ink without reformulation.</t>
+          <t>Integrate NOA-F (Non-Original Authentication-Feature) with a metal foiled labyrinth and lid label for enhanced security and authentication.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost, accelerates time-to-market, and leverages proven technology.</t>
+          <t>To prevent counterfeiting and ensure only genuine HP supplies are used, protecting revenue and brand integrity.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,21 +1346,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Engineering, Product Management, Manufacturing</t>
+          <t>Supplies, Security, R&amp;D</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Compatibility of new system with legacy components</t>
+          <t>Coordination with NOA-F component supplier and bottle design.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>100% compatibility of reused components in prototype and pilot production builds.</t>
+          <t>NOA-F feature with metal foiled labyrinth and lid label is validated for all new bottles in pilot production.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1371,22 +1371,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ink System Reliability and Characterization</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Model and characterize reliability, water vapor transmission rate (WVTR), air gain, flow rate, and IDS including startup and NOA-F end-of-life.</t>
+          <t>Design the printer and supplies system to allow customers to replace the Printhead Assembly (PHA) and NOA-F components without service center intervention.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and system reliability over product lifecycle.</t>
+          <t>Improves serviceability, reduces downtime, and lowers total cost of ownership for users.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IDS development, system integration</t>
+          <t>Redesign of access and mounting mechanisms for user-friendly replacement.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Validated models and test data for all key reliability metrics before design freeze.</t>
+          <t>End users can successfully replace PHA and NOA-F in under 10 minutes following included instructions, as verified by usability testing.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1421,46 +1421,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling and PQ Impact Analysis</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and analyze its impact on print quality (PQ).</t>
+          <t>The new product must support a warranty page life of 80,000 pages.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Maintains high print quality and reduces risk of ink degradation over time.</t>
+          <t>Higher warranty life increases product value and competitiveness, especially for SMB and enterprise customers.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Product Management, Quality, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Access to ink chemistry data, tank design</t>
+          <t>Durability of core components (PHA, tank, paper path, etc.).</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Documented ink stability model and PQ impact report reviewed and approved by R&amp;D.</t>
+          <t>Product passes reliability tests for 80,000 pages without major failure under standard operating conditions.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1471,22 +1471,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOA-F must be available as service parts for warranty support and field replacements.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and efficiency requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures serviceability and customer satisfaction during warranty period.</t>
+          <t>Environmental certifications are increasingly demanded by institutional buyers and required for market access in some regions.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1496,21 +1496,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>Compliance, Product Management, Sustainability Teams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Service supply chain, inventory planning</t>
+          <t>Design, materials, and energy consumption must align with certification criteria.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOA-F service parts available in service centers within 3 months of product launch.</t>
+          <t>Product achieves EPEAT3, LOT4, and Blue Angel certification prior to launch.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1521,22 +1521,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Input and Output Tray Redesign for Tank Protrusion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology onto the ink bottle lid for authentication or tracking.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves anti-counterfeiting and supply chain traceability.</t>
+          <t>Physical integration of larger tanks requires mechanical redesign to ensure usability and compact footprint.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1546,21 +1546,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Product Security, Supply Chain</t>
+          <t>Mechanical Engineering, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 system integration</t>
+          <t>Final tank and chassis design.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Acumen 6 feature fully functional and passes security validation tests.</t>
+          <t>Trays operate smoothly and printer maintains acceptable size despite tank protrusion, as verified by form/fit/function testing.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1571,42 +1571,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Modify Factory Line for NOA-F and New Bottles</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Modify SA14 production line for NOA-F assembly; add Magi ink cart and labeling tool in Orcus 5. Mold for 1-4 new keyed caps required.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the new printer for enhanced user interface.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Supports manufacturing of new consumables and assemblies.</t>
+          <t>Larger, color displays improve usability, support advanced features, and align with market expectations.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>UX/UI, Product Management, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Factory retooling schedules, cap design finalization</t>
+          <t>Electrical and mechanical design changes; UI software updates.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Factory lines operational and producing new components at required yield rates before launch.</t>
+          <t>4.3” CGD display is fully functional, passes usability and reliability tests, and supports all required UI features.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1621,46 +1621,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>New Tube Routing and Integration for 4-Tube Platform</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Design the system to allow customers to easily replace PHA (Printhead Assembly) and NOA-F without professional service.</t>
+          <t>Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube CISS platform.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces service costs.</t>
+          <t>To support new tank and ink delivery requirements, ensuring reliability and print quality.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>End Users, Service</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Design for serviceability, user documentation</t>
+          <t>Tank, carriage, and service station design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Replacement process can be performed by end users in under 5 minutes with no tools, as validated in usability studies.</t>
+          <t>Tube routing supports required ink flow, passes stress and durability tests, and integrates with new tank and carriage.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1671,46 +1671,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal: 80K Pages</t>
+          <t>Service Station Aerosol Management Redesign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
+          <t>Redesign service station aerosol management to accommodate changes from the new tank platform.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Extends product life and supports higher duty cycle use-cases, competitive advantage.</t>
+          <t>To prevent contamination and ensure reliable long-term operation with increased ink volumes.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>R&amp;D, Service, Quality</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Component durability, consumable yield, warranty policy</t>
+          <t>Service station and tank design.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Printer must reliably print 80,000 pages without major failure, as verified in accelerated life testing.</t>
+          <t>Aerosol management system passes internal contamination and air quality tests under all operating conditions.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1721,46 +1721,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Paper Path Upgrade for Increased Page Life</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID with a size increase for the ink tank. No change to Marconi-HI ADF (Automatic Document Feeder).</t>
+          <t>Upgrade the paper path to support the increased page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Supports higher ink capacity and aligns with existing industrial design.</t>
+          <t>Higher duty cycle requires more robust paper handling to avoid jams and wear.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Industrial Design, Product Management</t>
+          <t>R&amp;D, Quality, End Users</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tank design, chassis compatibility</t>
+          <t>Component durability and material selection.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>New tank design integrated into Reddington ID and passes mechanical and aesthetic validation.</t>
+          <t>Paper path operates reliably for 80,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1771,22 +1771,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Ink Maintenance Serviceable Part Post-80k Pages</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Utilize EPS foam packaging for the printer and consumables.</t>
+          <t>Design ink maintenance components to be serviceable at service centers after 80,000 pages.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Protects product during shipping and handling.</t>
+          <t>Enables extended product life and reduces total cost of ownership for high-volume users.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,21 +1796,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing</t>
+          <t>Service, End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Packaging design, material sourcing</t>
+          <t>Component modularity and accessibility.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Products pass drop and vibration tests with EPS packaging.</t>
+          <t>Service centers can replace ink maintenance parts post-80k pages in under 30 minutes.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1821,22 +1821,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ensure compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection in the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Meets regulatory and market requirements for sustainability and eco-labels.</t>
+          <t>To support new bottle/keying system and ensure secure, reliable ink connections.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,21 +1846,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Design and material choices, certification processes</t>
+          <t>IDS design, bottle/key interface, and LOI SHAID integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PDL SKU achieves EPEAT3, LOT4, and Blue Angel certifications before launch.</t>
+          <t>IDS passes all connection, leak, and reliability tests, and supports new keyed bottles.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1871,42 +1871,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Input/Output Tray Modifications for Tank Protrusion</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with the increased tank protrusion.</t>
+          <t>Develop a new startup algorithm and air management system for the IDS to ensure reliable operation with the new tank and bottle system.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and usability.</t>
+          <t>Prevents startup failures and ensures consistent print quality from first use.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mechanical Design, End Users</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tank design finalization</t>
+          <t>IDS hardware and firmware development.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Trays function correctly with new tank and pass fit/form/function tests.</t>
+          <t>Startup algorithm initializes system reliably in 100% of test cases, and air management prevents air lock or ink starvation.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1921,42 +1921,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Size Optimization of Printer</t>
+          <t>New Print Quality (PQ) Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Optimize overall printer size, considering the increased tank and new components.</t>
+          <t>Define and achieve new print quality (PQ) goals and ink depletion metrics to align with higher yield and page life targets.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Maintains competitive footprint and maximizes desk space efficiency.</t>
+          <t>Ensures product delivers consistent quality throughout its extended life and meets new performance benchmarks.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Industrial Design, Product Management</t>
+          <t>R&amp;D, Quality, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Component layout, tank design</t>
+          <t>Ink, IDS, and firmware updates.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Final product dimensions do not exceed agreed size envelope and pass ergonomic review.</t>
+          <t>PQ goals and depletion metrics are documented, tested, and met in all relevant test scenarios.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1971,42 +1971,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Reuse of Marconi Hi PDL Components</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Integrate a 4.3” CGD (Color Graphic Display) into the printer for enhanced user interface.</t>
+          <t>Leverage existing Marconi Hi PDL hardware and firmware components where possible to reduce development time and cost.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Improves user experience and modernizes product appearance.</t>
+          <t>Speeds time to market and reduces engineering investment.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>End Users, UI/UX Team</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Electrical and mechanical integration, UI software</t>
+          <t>Compatibility of legacy components with new system.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Display is fully functional and passes usability and reliability tests.</t>
+          <t>All reused components pass integration and reliability tests in the new product context.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2021,22 +2021,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-Tube Platform with Sayan Sibstar Tubes and New Routing</t>
+          <t>Integration of Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes, introduce new tube routing and integration for the 4-tube platform.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and device management.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Supports new ink system architecture and reliability.</t>
+          <t>Modern connectivity and device management features are essential for enterprise and SMB markets.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2046,21 +2046,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, IT, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tube design, routing validation</t>
+          <t>Firmware and hardware integration.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tube routing supports reliable ink delivery and passes stress and reliability tests.</t>
+          <t>Wi-Fi module and firmware operate seamlessly and pass all connectivity and security tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2071,42 +2071,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Gauss4.xx Security (HW &amp; FW) Implementation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Update service station for aerosol management with spit platform changes due to new tank design.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features to protect device and data.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Prevents contamination and maintains print quality.</t>
+          <t>Security is critical for enterprise and SMB customers, and to meet compliance requirements.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>Security, IT, Enterprise Customers</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Service station and tank design</t>
+          <t>Hardware and firmware readiness.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Aerosol emissions are within regulatory and HP internal limits.</t>
+          <t>Security features pass internal and external security audits and penetration testing.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2121,142 +2121,142 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and weights.</t>
+          <t>Design product and solution stack to support Consumer, SMB, and Enterprise business models, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+          <t>Expands addressable market and aligns with HP’s strategic intent to protect and grow share across segments.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tube and carriage design</t>
+          <t>Software, services, and onboarding path readiness.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Carriage operates within force budget and passes mechanical reliability tests.</t>
+          <t>Product is successfully launched and sold in all three segments with tailored onboarding and service options.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Scan Solution and SMB Manageability Integration</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life (80K pages).</t>
+          <t>Integrate advanced scan solutions and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ensures durability and reliability for higher duty cycles.</t>
+          <t>Enhances product value for SMB and enterprise customers and supports managed print services.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Product Management, R&amp;D, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Paper path material and design updates</t>
+          <t>Firmware and software development.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paper path components pass 80K page accelerated wear tests.</t>
+          <t>Scan and manageability features are available and functional in SMB/Enterprise configurations.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part Post 80K Life</t>
+          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part to be replaced at service centers after 80K page life.</t>
+          <t>Ensure full compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Extends printer usable life and supports high-volume users.</t>
+          <t>Critical for broad deployment and ease of use across customer environments.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>IT, End Users, Support</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Maintenance part design, service documentation</t>
+          <t>Driver and client software updates as needed.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Service centers can replace part in &lt;30 minutes; validated in pilot service program.</t>
+          <t>All listed clients and drivers are tested and certified for use with the new product.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2264,29 +2264,29 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>140ml K and XXml CMY Bottles</t>
+          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Introduce new 140ml Black (K) bottles and appropriately sized CMY bottles for the new system.</t>
+          <t>Maintain SuperAmp Printhead Assembly (PHA) life at 65,000 pages as a fixed constraint.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aligns with increased yield and system design.</t>
+          <t>Sets a design limit for component durability and replacement cycles.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,47 +2296,47 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>R&amp;D, Quality, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bottle design, supply chain</t>
+          <t>Printhead design and testing.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bottles meet yield and compatibility requirements in system validation tests.</t>
+          <t>SuperAmp PHA reliably operates for 65,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>Warranty Life of 2 Years (Optimized)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Develop new make-break and fluidic interconnect (FI) connection for the IDS (Ink Delivery System).</t>
+          <t>Design the product to meet a 2-year warranty life.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Improves reliability and serviceability of the ink system.</t>
+          <t>Aligns with industry standards and customer expectations for reliability.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2346,17 +2346,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Quality, Product Management, End Users</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IDS and bottle design</t>
+          <t>Component selection and reliability engineering.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>New connection passes leak, durability, and usability tests.</t>
+          <t>Product passes all reliability and quality tests for a 2-year warranty period.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2364,29 +2364,29 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Increased Size, Keying, and LOI for LEBI Ink-Tank</t>
+          <t>Throughput of 25/20 ppm (PDL)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Increase LEBI (Low-End Bulk Ink) ink-tank size, implement new keying, and integrate LOI (Level of Integration) with one SHAID (Security Hardware Authentication ID).</t>
+          <t>Achieve print throughput of 25 pages per minute (ppm) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Prevents misinstallation, supports higher capacity, and enhances security.</t>
+          <t>Meets market requirements for speed and productivity.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2396,575 +2396,75 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Product Security, R&amp;D, End Users</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tank and keying design, SHAID integration</t>
+          <t>Print engine performance and firmware optimization.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tank passes installation, capacity, and security validation tests.</t>
+          <t>Product achieves specified throughput in benchmark tests for both standard and PDL modes.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Serviceability of Maintenance Box</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Develop a new IDS startup algorithm and air management system for reliable operation.</t>
+          <t>Ensure the maintenance box is easily serviceable to optimize uptime and reduce service costs.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ensures consistent startup and prevents air entrapment issues.</t>
+          <t>Improves user experience and lowers total cost of ownership.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Service, End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>IDS and firmware development</t>
+          <t>Maintenance box design and accessibility.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>System starts up reliably in 99% of power-on cycles in lab and field tests.</t>
+          <t>Maintenance box can be replaced in under 5 minutes by a trained technician or user.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>New Servicing and Startup Algorithm</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Implement new servicing and startup algorithms for improved reliability and user experience.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Reduces errors and improves printer uptime.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>R&amp;D, End Users</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Firmware development, IDS integration</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Algorithms reduce startup and servicing errors by 50% over previous generation in controlled trials.</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>New PQ Goals and Depletion Definition</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Establish new print quality (PQ) goals and depletion definitions to align with new page yield targets.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Ensures product meets customer expectations and marketing claims.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Product Management, R&amp;D, Marketing</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Yield testing, PQ evaluation</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>PQ and depletion metrics approved by cross-functional team and validated in system tests.</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi, Dune FW</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware for the new printer.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages proven, reliable components.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Engineering, Manufacturing</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Compatibility with new platform</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>All reused components function as required in system integration tests.</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Integrate Gauss4.xx hardware and firmware security features into the printer.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Protects product and user data from security threats.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Product Security, IT, End Users</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>HW/FW integration, security validation</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Security features pass internal and external penetration testing.</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Printer must support print speeds of 25/20 pages per minute (ppm) for standard and 25/19 ppm for PDL SKU.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Meets market expectations for performance and competitiveness.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Product Management, End Users, Marketing</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Print engine and firmware capability</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Printer achieves required speeds in standardized performance tests.</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Serviceability: Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Design printer with a serviceable maintenance box for easy end-user or service center replacement.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Improves uptime and reduces repair costs.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Service, End Users</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Maintenance box design, service documentation</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Box can be replaced in under 10 minutes by trained personnel or end users.</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SMB Solution and PaaS Support</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Support SMB solution features and Printer-as-a-Service (PaaS) business models.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Expands addressable market and supports new revenue streams.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Business Development, SMB Customers, IT</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Solution software, service integration</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Printer integrates with SMB solution and PaaS platforms as required by business model.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Host 12K-CMYK and Trade Page 6K</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Support hosting of 12K-CMYK and trade page yield of 6K as flexible business requirements.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Provides flexibility for different market segments and promotions.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Product Management, Marketing</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Yield validation, SKU management</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Printer supports 12K-CMYK and 6K trade page configurations as validated in market trials.</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Solution and Services Integration: Scan, Manageability, Enterprise Support</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Integrate scan solutions, SMB manageability, and enterprise support including WJA (Web Jetadmin), HPSM, JAM.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Meets enterprise and SMB customer requirements for fleet management and workflow.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Enterprise IT, SMB Customers, Product Management</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Software integration, platform compatibility</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>All solution features are functional and validated in enterprise and SMB pilot deployments.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Maximizes compatibility and ease of use for customers across segments.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>End Users, IT, Support</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Driver and client software updates</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>Develop NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size supporting &gt;8K yield.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>To increase ink capacity and reduce frequency of bottle replacement, addressing customer demand for higher yield and convenience.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Requires modifications to IDS, bottle design, and possibly packaging.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>NGB keyed bottles are developed and tested to reliably deliver 6K Black and 6K CMY page yields (with CMY &gt;8K possible), verified by page yield tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>Spill-Free Reliability in Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>Ensure new ink bottles and refilling system provide spill-free reliability during user operation.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>Spill-free operation is critical to user satisfaction and competitive differentiation, especially for CISS systems.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,25 +546,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>End Users, R&amp;D, Support Teams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Design of bottle, nozzle, and tank interface; compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>No ink spills occur during standard user refilling in 100% of test cases.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Integrate NOA-F (Non-Original Authentication-Feature) with a metal foiled labyrinth and lid label for enhanced security and authentication.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>To prevent counterfeiting and ensure only genuine HP supplies are used, protecting revenue and brand integrity.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>Supplies, Security, R&amp;D</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>Coordination with NOA-F component supplier and bottle design.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>NOA-F feature with metal foiled labyrinth and lid label is validated for all new bottles in pilot production.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Design the printer and supplies system to allow customers to replace the Printhead Assembly (PHA) and NOA-F components without service center intervention.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>Improves serviceability, reduces downtime, and lowers total cost of ownership for users.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>Redesign of access and mounting mechanisms for user-friendly replacement.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>End users can successfully replace PHA and NOA-F in under 10 minutes following included instructions, as verified by usability testing.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -676,37 +676,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>The new product must support a warranty page life of 80,000 pages.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>Higher warranty life increases product value and competitiveness, especially for SMB and enterprise customers.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Product Management, Quality, End Users</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>Durability of core components (PHA, tank, paper path, etc.).</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>Product passes reliability tests for 80,000 pages without major failure under standard operating conditions.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -726,17 +726,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and efficiency requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>Environmental certifications are increasingly demanded by institutional buyers and required for market access in some regions.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,25 +746,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>Compliance, Product Management, Sustainability Teams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>Design, materials, and energy consumption must align with certification criteria.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>Product achieves EPEAT3, LOT4, and Blue Angel certification prior to launch.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Input and Output Tray Redesign for Tank Protrusion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>Physical integration of larger tanks requires mechanical redesign to ensure usability and compact footprint.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,25 +796,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Mechanical Engineering, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>Final tank and chassis design.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>Trays operate smoothly and printer maintains acceptable size despite tank protrusion, as verified by form/fit/function testing.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the new printer for enhanced user interface.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+          <t>Larger, color displays improve usability, support advanced features, and align with market expectations.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,25 +846,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>UX/UI, Product Management, End Users</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires software development and integration with hardware.</t>
+          <t>Electrical and mechanical design changes; UI software updates.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+          <t>4.3” CGD display is fully functional, passes usability and reliability tests, and supports all required UI features.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+          <t>New Tube Routing and Integration for 4-Tube Platform</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+          <t>Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube CISS platform.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+          <t>To support new tank and ink delivery requirements, ensuring reliability and print quality.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,25 +896,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
+          <t>Tank, carriage, and service station design.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+          <t>Tube routing supports required ink flow, passes stress and durability tests, and integrates with new tank and carriage.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -926,45 +926,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>Service Station Aerosol Management Redesign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+          <t>Redesign service station aerosol management to accommodate changes from the new tank platform.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+          <t>To prevent contamination and ensure reliable long-term operation with increased ink volumes.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
+          <t>R&amp;D, Service, Quality</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires AI software and sensor integration.</t>
+          <t>Service station and tank design.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+          <t>Aerosol management system passes internal contamination and air quality tests under all operating conditions.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Paper Path Upgrade for Increased Page Life</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+          <t>Upgrade the paper path to support the increased page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+          <t>Higher duty cycle requires more robust paper handling to avoid jams and wear.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,25 +996,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>R&amp;D, Quality, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
+          <t>Component durability and material selection.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+          <t>Paper path operates reliably for 80,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Ink Maintenance Serviceable Part Post-80k Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+          <t>Design ink maintenance components to be serviceable at service centers after 80,000 pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+          <t>Enables extended product life and reduces total cost of ownership for high-volume users.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,25 +1046,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>Service, End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires app development and printer firmware support.</t>
+          <t>Component modularity and accessibility.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+          <t>Service centers can replace ink maintenance parts post-80k pages in under 30 minutes.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1076,37 +1076,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PaaS Enablement</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection in the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+          <t>To support new bottle/keying system and ensure secure, reliable ink connections.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
+          <t>IDS design, bottle/key interface, and LOI SHAID integration.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+          <t>IDS passes all connection, leak, and reliability tests, and supports new keyed bottles.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1126,45 +1126,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+          <t>Develop a new startup algorithm and air management system for the IDS to ensure reliable operation with the new tank and bottle system.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+          <t>Prevents startup failures and ensures consistent print quality from first use.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Requires secure data collection and privacy compliance.</t>
+          <t>IDS hardware and firmware development.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+          <t>Startup algorithm initializes system reliably in 100% of test cases, and air management prevents air lock or ink starvation.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Advanced Security and Compliance</t>
+          <t>New Print Quality (PQ) Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+          <t>Define and achieve new print quality (PQ) goals and ink depletion metrics to align with higher yield and page life targets.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+          <t>Ensures product delivers consistent quality throughout its extended life and meets new performance benchmarks.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,71 +1196,71 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Quality, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Requires security features and regulatory review.</t>
+          <t>Ink, IDS, and firmware updates.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Product passes security and compliance audits for target markets.</t>
+          <t>PQ goals and depletion metrics are documented, tested, and met in all relevant test scenarios.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Magellan MRD, inferred from multiple sections</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>Reuse of Marconi Hi PDL Components</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Develop NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size supporting &gt;8K yield.</t>
+          <t>Leverage existing Marconi Hi PDL hardware and firmware components where possible to reduce development time and cost.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To increase ink capacity and reduce frequency of bottle replacement, addressing customer demand for higher yield and convenience.</t>
+          <t>Speeds time to market and reduces engineering investment.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Requires modifications to IDS, bottle design, and possibly packaging.</t>
+          <t>Compatibility of legacy components with new system.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NGB keyed bottles are developed and tested to reliably deliver 6K Black and 6K CMY page yields (with CMY &gt;8K possible), verified by page yield tests.</t>
+          <t>All reused components pass integration and reliability tests in the new product context.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1271,22 +1271,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability in Ink Bottles</t>
+          <t>Integration of Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ensure new ink bottles and refilling system provide spill-free reliability during user operation.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and device management.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Spill-free operation is critical to user satisfaction and competitive differentiation, especially for CISS systems.</t>
+          <t>Modern connectivity and device management features are essential for enterprise and SMB markets.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Support Teams</t>
+          <t>R&amp;D, IT, End Users</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Design of bottle, nozzle, and tank interface; compatibility with existing mechanisms.</t>
+          <t>Firmware and hardware integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No ink spills occur during standard user refilling in 100% of test cases.</t>
+          <t>Wi-Fi module and firmware operate seamlessly and pass all connectivity and security tests.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1321,22 +1321,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Gauss4.xx Security (HW &amp; FW) Implementation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Integrate NOA-F (Non-Original Authentication-Feature) with a metal foiled labyrinth and lid label for enhanced security and authentication.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features to protect device and data.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To prevent counterfeiting and ensure only genuine HP supplies are used, protecting revenue and brand integrity.</t>
+          <t>Security is critical for enterprise and SMB customers, and to meet compliance requirements.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,21 +1346,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Supplies, Security, R&amp;D</t>
+          <t>Security, IT, Enterprise Customers</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coordination with NOA-F component supplier and bottle design.</t>
+          <t>Hardware and firmware readiness.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NOA-F feature with metal foiled labyrinth and lid label is validated for all new bottles in pilot production.</t>
+          <t>Security features pass internal and external security audits and penetration testing.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1371,22 +1371,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Support for Customer Replaceable PHA and NOA-F</t>
+          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Design the printer and supplies system to allow customers to replace the Printhead Assembly (PHA) and NOA-F components without service center intervention.</t>
+          <t>Design product and solution stack to support Consumer, SMB, and Enterprise business models, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and lowers total cost of ownership for users.</t>
+          <t>Expands addressable market and aligns with HP’s strategic intent to protect and grow share across segments.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,97 +1396,97 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Redesign of access and mounting mechanisms for user-friendly replacement.</t>
+          <t>Software, services, and onboarding path readiness.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>End users can successfully replace PHA and NOA-F in under 10 minutes following included instructions, as verified by usability testing.</t>
+          <t>Product is successfully launched and sold in all three segments with tailored onboarding and service options.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>Scan Solution and SMB Manageability Integration</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The new product must support a warranty page life of 80,000 pages.</t>
+          <t>Integrate advanced scan solutions and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Higher warranty life increases product value and competitiveness, especially for SMB and enterprise customers.</t>
+          <t>Enhances product value for SMB and enterprise customers and supports managed print services.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Product Management, Quality, End Users</t>
+          <t>Product Management, R&amp;D, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Durability of core components (PHA, tank, paper path, etc.).</t>
+          <t>Firmware and software development.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Product passes reliability tests for 80,000 pages without major failure under standard operating conditions.</t>
+          <t>Scan and manageability features are available and functional in SMB/Enterprise configurations.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and efficiency requirements for the PDL SKU.</t>
+          <t>Ensure full compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Environmental certifications are increasingly demanded by institutional buyers and required for market access in some regions.</t>
+          <t>Critical for broad deployment and ease of use across customer environments.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Sustainability Teams</t>
+          <t>IT, End Users, Support</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Design, materials, and energy consumption must align with certification criteria.</t>
+          <t>Driver and client software updates as needed.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Product achieves EPEAT3, LOT4, and Blue Angel certification prior to launch.</t>
+          <t>All listed clients and drivers are tested and certified for use with the new product.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1514,99 +1514,99 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Input and Output Tray Redesign for Tank Protrusion</t>
+          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Maintain SuperAmp Printhead Assembly (PHA) life at 65,000 pages as a fixed constraint.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Physical integration of larger tanks requires mechanical redesign to ensure usability and compact footprint.</t>
+          <t>Sets a design limit for component durability and replacement cycles.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D, End Users</t>
+          <t>R&amp;D, Quality, Product Management</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Final tank and chassis design.</t>
+          <t>Printhead design and testing.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Trays operate smoothly and printer maintains acceptable size despite tank protrusion, as verified by form/fit/function testing.</t>
+          <t>SuperAmp PHA reliably operates for 65,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Warranty Life of 2 Years (Optimized)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the new printer for enhanced user interface.</t>
+          <t>Design the product to meet a 2-year warranty life.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Larger, color displays improve usability, support advanced features, and align with market expectations.</t>
+          <t>Aligns with industry standards and customer expectations for reliability.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UX/UI, Product Management, End Users</t>
+          <t>Quality, Product Management, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Electrical and mechanical design changes; UI software updates.</t>
+          <t>Component selection and reliability engineering.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.3” CGD display is fully functional, passes usability and reliability tests, and supports all required UI features.</t>
+          <t>Product passes all reliability and quality tests for a 2-year warranty period.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1614,79 +1614,79 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New Tube Routing and Integration for 4-Tube Platform</t>
+          <t>Throughput of 25/20 ppm (PDL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube CISS platform.</t>
+          <t>Achieve print throughput of 25 pages per minute (ppm) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To support new tank and ink delivery requirements, ensuring reliability and print quality.</t>
+          <t>Meets market requirements for speed and productivity.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tank, carriage, and service station design.</t>
+          <t>Print engine performance and firmware optimization.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tube routing supports required ink flow, passes stress and durability tests, and integrates with new tank and carriage.</t>
+          <t>Product achieves specified throughput in benchmark tests for both standard and PDL modes.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management Redesign</t>
+          <t>Serviceability of Maintenance Box</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Redesign service station aerosol management to accommodate changes from the new tank platform.</t>
+          <t>Ensure the maintenance box is easily serviceable to optimize uptime and reduce service costs.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To prevent contamination and ensure reliable long-term operation with increased ink volumes.</t>
+          <t>Improves user experience and lowers total cost of ownership.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality</t>
+          <t>Service, End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Service station and tank design.</t>
+          <t>Maintenance box design and accessibility.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Aerosol management system passes internal contamination and air quality tests under all operating conditions.</t>
+          <t>Maintenance box can be replaced in under 5 minutes by a trained technician or user.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1714,29 +1714,29 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Paper Path Upgrade for Increased Page Life</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Upgrade the paper path to support the increased page life goal of 80,000 pages.</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Higher duty cycle requires more robust paper handling to avoid jams and wear.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,97 +1746,97 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, End Users</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Component durability and material selection.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paper path operates reliably for 80,000 pages in accelerated life testing.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part Post-80k Pages</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable at service centers after 80,000 pages.</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Enables extended product life and reduces total cost of ownership for high-volume users.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Service, End Users, R&amp;D</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Component modularity and accessibility.</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts post-80k pages in under 30 minutes.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection in the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To support new bottle/keying system and ensure secure, reliable ink connections.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,47 +1846,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IDS design, bottle/key interface, and LOI SHAID integration.</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>IDS passes all connection, leak, and reliability tests, and supports new keyed bottles.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm and air management system for the IDS to ensure reliable operation with the new tank and bottle system.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Prevents startup failures and ensures consistent print quality from first use.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1896,217 +1896,217 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IDS hardware and firmware development.</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Startup algorithm initializes system reliably in 100% of test cases, and air management prevents air lock or ink starvation.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Definition</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Define and achieve new print quality (PQ) goals and ink depletion metrics to align with higher yield and page life targets.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures product delivers consistent quality throughout its extended life and meets new performance benchmarks.</t>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ink, IDS, and firmware updates.</t>
+          <t>Requires design of bottle and tank interface.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PQ goals and depletion metrics are documented, tested, and met in all relevant test scenarios.</t>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Hi PDL Components</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Hi PDL hardware and firmware components where possible to reduce development time and cost.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Speeds time to market and reduces engineering investment.</t>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Compatibility of legacy components with new system.</t>
+          <t>Requires durability testing and warranty policy alignment.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All reused components pass integration and reliability tests in the new product context.</t>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Integration of Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Serviceability – PHA and MINK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and device management.</t>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Modern connectivity and device management features are essential for enterprise and SMB markets.</t>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, IT, End Users</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Firmware and hardware integration.</t>
+          <t>Requires design for replaceability and service documentation.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Wi-Fi module and firmware operate seamlessly and pass all connectivity and security tests.</t>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW) Implementation</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features to protect device and data.</t>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Security is critical for enterprise and SMB customers, and to meet compliance requirements.</t>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Security, IT, Enterprise Customers</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hardware and firmware readiness.</t>
+          <t>Requires software development and integration with hardware.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Security features pass internal and external security audits and penetration testing.</t>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2114,129 +2114,129 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Design product and solution stack to support Consumer, SMB, and Enterprise business models, including PaaS and WorkFromHome/Flexworker services.</t>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Expands addressable market and aligns with HP’s strategic intent to protect and grow share across segments.</t>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Software, services, and onboarding path readiness.</t>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Product is successfully launched and sold in all three segments with tailored onboarding and service options.</t>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Scan Solution and SMB Manageability Integration</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Integrate advanced scan solutions and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Enhances product value for SMB and enterprise customers and supports managed print services.</t>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, SMB/Enterprise Customers</t>
+          <t>['Marketing', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Firmware and software development.</t>
+          <t>Requires AI software and sensor integration.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Scan and manageability features are available and functional in SMB/Enterprise configurations.</t>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ensure full compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Critical for broad deployment and ease of use across customer environments.</t>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,167 +2246,167 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IT, End Users, Support</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Driver and client software updates as needed.</t>
+          <t>Requires sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>All listed clients and drivers are tested and certified for use with the new product.</t>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maintain SuperAmp Printhead Assembly (PHA) life at 65,000 pages as a fixed constraint.</t>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sets a design limit for component durability and replacement cycles.</t>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Printhead design and testing.</t>
+          <t>Requires app development and printer firmware support.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SuperAmp PHA reliably operates for 65,000 pages in accelerated life testing.</t>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years (Optimized)</t>
+          <t>PaaS Enablement</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Design the product to meet a 2-year warranty life.</t>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Aligns with industry standards and customer expectations for reliability.</t>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quality, Product Management, End Users</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Component selection and reliability engineering.</t>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Product passes all reliability and quality tests for a 2-year warranty period.</t>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL)</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Achieve print throughput of 25 pages per minute (ppm) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Meets market requirements for speed and productivity.</t>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Print engine performance and firmware optimization.</t>
+          <t>Requires secure data collection and privacy compliance.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Product achieves specified throughput in benchmark tests for both standard and PDL modes.</t>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2414,57 +2414,57 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Advanced Security and Compliance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ensure the maintenance box is easily serviceable to optimize uptime and reduce service costs.</t>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Improves user experience and lowers total cost of ownership.</t>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Service, End Users, R&amp;D</t>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Maintenance box design and accessibility.</t>
+          <t>Requires security features and regulatory review.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in under 5 minutes by a trained technician or user.</t>
+          <t>Product passes security and compliance audits for target markets.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, inferred from multiple sections</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size supporting &gt;8K yield.</t>
+          <t>The printer must support new NGB keyed bottles with a minimum 6,000-page yield for black and 6,000-page yield for CMY, with CMY bottle size supporting over 8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase ink capacity and reduce frequency of bottle replacement, addressing customer demand for higher yield and convenience.</t>
+          <t>High-yield bottles reduce frequency of replacement, enhance user convenience, and lower total cost of ownership, supporting competitive differentiation in SMB and Enterprise markets.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires modifications to IDS, bottle design, and possibly packaging.</t>
+          <t>Integration with CISS, IDS, and NOA-F; compatible with Magi/Nessie ink; factory line modifications required.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NGB keyed bottles are developed and tested to reliably deliver 6K Black and 6K CMY page yields (with CMY &gt;8K possible), verified by page yield tests.</t>
+          <t>System accepts and recognizes new NGB keyed bottles; Black yields at least 6,000 pages, CMY yields at least 6,000 pages, CMY bottle supports &gt;8,000 pages; verified through yield testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability in Ink Bottles</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new ink bottles and refilling system provide spill-free reliability during user operation.</t>
+          <t>The ink bottle and tank system must ensure spill-free reliability during bottle installation and replacement.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spill-free operation is critical to user satisfaction and competitive differentiation, especially for CISS systems.</t>
+          <t>Prevents mess, improves customer experience, and reduces service incidents related to ink spills.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,21 +546,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Support Teams</t>
+          <t>End Users, Service, Product Quality</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Design of bottle, nozzle, and tank interface; compatibility with existing mechanisms.</t>
+          <t>Bottle and tank design, NOA-F integration.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spills occur during standard user refilling in 100% of test cases.</t>
+          <t>No ink spills occur during normal bottle installation/replacement in lab and field test scenarios.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -581,12 +581,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate NOA-F (Non-Original Authentication-Feature) with a metal foiled labyrinth and lid label for enhanced security and authentication.</t>
+          <t>The NOA-F (Non-Ozone Air Filter) must include a metal foiled labyrinth and a lid label, with no changes to click on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To prevent counterfeiting and ensure only genuine HP supplies are used, protecting revenue and brand integrity.</t>
+          <t>Enhances reliability and compliance with air filtration requirements while maintaining compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Supplies, Security, R&amp;D</t>
+          <t>R&amp;D, Compliance, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coordination with NOA-F component supplier and bottle design.</t>
+          <t>NOA-F component sourcing and design, push-push and TDF compatibility.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F feature with metal foiled labyrinth and lid label is validated for all new bottles in pilot production.</t>
+          <t>NOA-F units have metal foiled labyrinth and lid label; click on push-push and TDF mechanisms function as in previous models.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Design the printer and supplies system to allow customers to replace the Printhead Assembly (PHA) and NOA-F components without service center intervention.</t>
+          <t>The printer must allow end customers to replace the Printhead Assembly (PHA) and NOA-F components easily.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and lowers total cost of ownership for users.</t>
+          <t>Improves serviceability, reduces downtime, and lowers support costs by enabling user-replaceable key components.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Redesign of access and mounting mechanisms for user-friendly replacement.</t>
+          <t>PHA and NOA-F design for tool-less or simple replacement; documentation and packaging updates.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>End users can successfully replace PHA and NOA-F in under 10 minutes following included instructions, as verified by usability testing.</t>
+          <t>End users can replace PHA and NOA-F without special tools, as verified in usability testing.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -676,17 +676,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The new product must support a warranty page life of 80,000 pages.</t>
+          <t>The printer must achieve a new warranty page life goal of 80,000 printed pages.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Higher warranty life increases product value and competitiveness, especially for SMB and enterprise customers.</t>
+          <t>Supports higher duty cycles for SMB/Enterprise customers and aligns with market expectations for reliability and longevity.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,17 +696,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Product Management, Quality, End Users</t>
+          <t>Warranty/Service, Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Durability of core components (PHA, tank, paper path, etc.).</t>
+          <t>Component durability (PHA, paperpath, tubes, etc.), consumables life, firmware monitoring.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Product passes reliability tests for 80,000 pages without major failure under standard operating conditions.</t>
+          <t>Printer operates reliably for 80,000 pages under warranty conditions; verified by accelerated life testing.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -726,37 +726,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>Input/Output Tray and Tank Size Optimization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and efficiency requirements for the PDL SKU.</t>
+          <t>Input and output trays must be modified to align with the increased tank protrusion, and overall size optimization must be achieved.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Environmental certifications are increasingly demanded by institutional buyers and required for market access in some regions.</t>
+          <t>Accommodates larger ink tanks without compromising paper handling or increasing overall device footprint unnecessarily.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Sustainability Teams</t>
+          <t>Hardware Engineering, Industrial Design, Manufacturing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Design, materials, and energy consumption must align with certification criteria.</t>
+          <t>Tank design, mechanical layout, packaging requirements.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Product achieves EPEAT3, LOT4, and Blue Angel certification prior to launch.</t>
+          <t>Trays function with new tank size; device passes size and fit validation; no paper handling issues observed.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -776,17 +776,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Input and Output Tray Redesign for Tank Protrusion</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>The product must include a 4.3-inch color graphical display (CGD) for enhanced user interaction.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Physical integration of larger tanks requires mechanical redesign to ensure usability and compact footprint.</t>
+          <t>Improves user experience through better navigation, status reporting, and feature access.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,21 +796,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D, End Users</t>
+          <t>End Users, UI/UX, Product Management</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Final tank and chassis design.</t>
+          <t>Firmware support, mechanical integration, supply chain for display components.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Trays operate smoothly and printer maintains acceptable size despite tank protrusion, as verified by form/fit/function testing.</t>
+          <t>4.3” CGD is functional in prototype and production units; user feedback meets satisfaction criteria.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -826,37 +826,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Platform with 4 Tubes and New Routing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the new printer for enhanced user interface.</t>
+          <t>The printer must leverage Sayan Sibstar tubes, with new routing and integration for four tubes.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Larger, color displays improve usability, support advanced features, and align with market expectations.</t>
+          <t>Supports increased ink flow, reliability, and compatibility with CISS and new bottle sizes.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UX/UI, Product Management, End Users</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Electrical and mechanical design changes; UI software updates.</t>
+          <t>Tube sourcing, integration with IDS and ink tanks, mechanical design.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.3” CGD display is fully functional, passes usability and reliability tests, and supports all required UI features.</t>
+          <t>Four-tube system passes flow rate, reliability, and serviceability tests.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New Tube Routing and Integration for 4-Tube Platform</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube CISS platform.</t>
+          <t>Service station must include aerosol management features, with changes to accommodate the new tank system.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To support new tank and ink delivery requirements, ensuring reliability and print quality.</t>
+          <t>Prevents ink aerosol contamination inside the device, ensuring reliability and safety.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Service, Product Quality</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tank, carriage, and service station design.</t>
+          <t>Service station design, integration with tank and carriage systems.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tube routing supports required ink flow, passes stress and durability tests, and integrates with new tank and carriage.</t>
+          <t>Aerosol containment verified in environmental and reliability testing; no ink aerosol detected outside containment area.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -926,17 +926,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management Redesign</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Redesign service station aerosol management to accommodate changes from the new tank platform.</t>
+          <t>Update carriage dynamics and force model to account for new tube routing and increased component weights.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To prevent contamination and ensure reliable long-term operation with increased ink volumes.</t>
+          <t>Ensures print quality, mechanical reliability, and longevity with new hardware configuration.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality</t>
+          <t>R&amp;D, Hardware Engineering</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Service station and tank design.</t>
+          <t>Tube and tank design, carriage design updates.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Aerosol management system passes internal contamination and air quality tests under all operating conditions.</t>
+          <t>Carriage operates within force tolerances; no print artifacts or mechanical failures observed in testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paper Path Upgrade for Increased Page Life</t>
+          <t>Paperpath Upgrade for Increased Page Life</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Upgrade the paper path to support the increased page life goal of 80,000 pages.</t>
+          <t>The printer paperpath must be upgraded to support increased page life, aligning with the 80,000-page warranty goal.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Higher duty cycle requires more robust paper handling to avoid jams and wear.</t>
+          <t>Prevents paper jams and wear over extended duty cycles, critical for high-volume users.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, End Users</t>
+          <t>R&amp;D, Service, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Component durability and material selection.</t>
+          <t>Material selection, mechanical redesign, reliability testing.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paper path operates reliably for 80,000 pages in accelerated life testing.</t>
+          <t>Paperpath supports 80,000 pages with no more than X% jam rate (to be defined by quality standards).</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part Post-80k Pages</t>
+          <t>Ink Maintenance as Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable at service centers after 80,000 pages.</t>
+          <t>Ink maintenance components must be designed as serviceable parts, replaceable at service centers after 80,000 pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Enables extended product life and reduces total cost of ownership for high-volume users.</t>
+          <t>Extends overall device life and reduces total cost of ownership for high-usage customers.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,21 +1046,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Service, End Users, R&amp;D</t>
+          <t>Service, Warranty, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Component modularity and accessibility.</t>
+          <t>Component modularity, service documentation, supply chain for replacement parts.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts post-80k pages in under 30 minutes.</t>
+          <t>Service center can replace ink maintenance components in under Y minutes (TBD); component passes post-replacement validation.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>IDS with New Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection in the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Implement new make-break and FI (fluidic interconnect) connection for the Integrated Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To support new bottle/keying system and ensure secure, reliable ink connections.</t>
+          <t>Ensures secure, reliable ink delivery with larger tanks and keyed access, preventing misinstallation.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,21 +1096,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IDS design, bottle/key interface, and LOI SHAID integration.</t>
+          <t>IDS redesign, compatibility with new bottles and tanks.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>IDS passes all connection, leak, and reliability tests, and supports new keyed bottles.</t>
+          <t>IDS passes fluidic connection integrity tests and keying validation; no misinstallation observed in usability studies.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm and air management system for the IDS to ensure reliable operation with the new tank and bottle system.</t>
+          <t>Develop and implement a new startup algorithm for the IDS with advanced air management to optimize ink flow and print quality.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Prevents startup failures and ensures consistent print quality from first use.</t>
+          <t>Reduces startup issues, air entrapment, and print quality defects, especially with larger tanks and longer tube runs.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,21 +1146,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>IDS hardware and firmware development.</t>
+          <t>Firmware development, IDS hardware updates.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Startup algorithm initializes system reliably in 100% of test cases, and air management prevents air lock or ink starvation.</t>
+          <t>Startup algorithm enables consistent ink flow and print quality in lab and field tests; air management validated in system tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Definition</t>
+          <t>New Print Quality Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Define and achieve new print quality (PQ) goals and ink depletion metrics to align with higher yield and page life targets.</t>
+          <t>Establish new print quality (PQ) goals and ink depletion metrics to align with the defined page yield and warranty life.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures product delivers consistent quality throughout its extended life and meets new performance benchmarks.</t>
+          <t>Ensures customer satisfaction and compliance with page yield claims and warranty commitments.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,21 +1196,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>Quality, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ink, IDS, and firmware updates.</t>
+          <t>Print quality test protocols, firmware monitoring, consumables tracking.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PQ goals and depletion metrics are documented, tested, and met in all relevant test scenarios.</t>
+          <t>Print quality meets or exceeds new PQ goals over the stated page yield; depletion metrics align with warranty and marketing claims.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Hi PDL Components</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Hi PDL hardware and firmware components where possible to reduce development time and cost.</t>
+          <t>The printer must reuse the Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for cost and supply chain efficiency.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Speeds time to market and reduces engineering investment.</t>
+          <t>Reduces development costs, leverages proven components, and streamlines manufacturing.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,21 +1246,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>R&amp;D, Manufacturing, Procurement</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Compatibility of legacy components with new system.</t>
+          <t>Component compatibility with new hardware and firmware.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>All reused components pass integration and reliability tests in the new product context.</t>
+          <t>Components function as expected in the new design; no integration issues found in system testing.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1276,37 +1276,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Integration of Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and device management.</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Modern connectivity and device management features are essential for enterprise and SMB markets.</t>
+          <t>Supports modern wireless printing standards and enhances device connectivity for SMB/Enterprise environments.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, IT, End Users</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Firmware and hardware integration.</t>
+          <t>Firmware, hardware integration, regulatory compliance.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Wi-Fi module and firmware operate seamlessly and pass all connectivity and security tests.</t>
+          <t>Wi-Fi module passes connectivity, range, and security tests; certified for target markets.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features to protect device and data.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features to protect device, data, and network integrity.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Security is critical for enterprise and SMB customers, and to meet compliance requirements.</t>
+          <t>Addresses increasing security requirements in SMB and Enterprise environments.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,21 +1346,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Security, IT, Enterprise Customers</t>
+          <t>IT, Security, Compliance, End Users</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hardware and firmware readiness.</t>
+          <t>Hardware and firmware development, regulatory review.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Security features pass internal and external security audits and penetration testing.</t>
+          <t>Device passes HP and industry security certification; no critical vulnerabilities found in penetration testing.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Design product and solution stack to support Consumer, SMB, and Enterprise business models, including PaaS and WorkFromHome/Flexworker services.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and efficiency standards for the PDL SKU.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Expands addressable market and aligns with HP’s strategic intent to protect and grow share across segments.</t>
+          <t>Required for market access and competitive positioning, especially in government and large enterprise sectors.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,25 +1396,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>Compliance, Product Management, Enterprise Customers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Software, services, and onboarding path readiness.</t>
+          <t>Design, material selection, documentation, certification process.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Product is successfully launched and sold in all three segments with tailored onboarding and service options.</t>
+          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications for PDL SKU.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scan Solution and SMB Manageability Integration</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Integrate advanced scan solutions and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
+          <t>Use EPS foam for packaging to protect the product during shipping and handling.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Enhances product value for SMB and enterprise customers and supports managed print services.</t>
+          <t>Ensures product arrives undamaged, reducing returns and improving customer satisfaction.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1446,25 +1446,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, SMB/Enterprise Customers</t>
+          <t>Manufacturing, Logistics, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Firmware and software development.</t>
+          <t>Packaging design, supply chain sourcing.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Scan and manageability features are available and functional in SMB/Enterprise configurations.</t>
+          <t>Product passes drop and vibration tests in EPS foam packaging; no damage observed.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Support for Consumer, SMB, and Enterprise Business Models</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ensure full compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>The printer must support business models for consumers, SMB, and enterprise customers, including services such as PaaS, WorkFromHome/Flexworker, and onboarding via multiple HP paths.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Critical for broad deployment and ease of use across customer environments.</t>
+          <t>Enables flexible go-to-market strategies and broadens addressable market segments.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1496,25 +1496,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IT, End Users, Support</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Driver and client software updates as needed.</t>
+          <t>Firmware, drivers, onboarding flows, portal integration.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>All listed clients and drivers are tested and certified for use with the new product.</t>
+          <t>Business model features available in firmware and onboarding flows; validated in market pilots.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+          <t>Scan Solution and SMB Manageability</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maintain SuperAmp Printhead Assembly (PHA) life at 65,000 pages as a fixed constraint.</t>
+          <t>Include a scan solution and SMB manageability features, with enterprise support for WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sets a design limit for component durability and replacement cycles.</t>
+          <t>Addresses SMB and enterprise workflow needs and IT management requirements.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>SMB/Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Printhead design and testing.</t>
+          <t>Firmware, software, driver integration, support for WJA/HPSM/JAM.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SuperAmp PHA reliably operates for 65,000 pages in accelerated life testing.</t>
+          <t>Scan and manageability features functional in test and pilot deployments; integration with WJA, HPSM, JAM verified.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years (Optimized)</t>
+          <t>Client and Driver Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Design the product to meet a 2-year warranty life.</t>
+          <t>The product must support a broad range of client and driver software, including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aligns with industry standards and customer expectations for reliability.</t>
+          <t>Ensures compatibility with diverse IT environments and enhances user experience.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Quality, Product Management, End Users</t>
+          <t>IT, End Users, Product Management</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Component selection and reliability engineering.</t>
+          <t>Firmware, driver development, QA testing.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Product passes all reliability and quality tests for a 2-year warranty period.</t>
+          <t>All listed drivers are available, installable, and functional on supported platforms.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL)</t>
+          <t>25/20 ppm Print Speed (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Achieve print throughput of 25 pages per minute (ppm) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+          <t>The printer must achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for color, with PDL speeds at 25/19 ppm.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Meets market requirements for speed and productivity.</t>
+          <t>Meets competitive benchmarks and user productivity needs.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>End Users, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Print engine performance and firmware optimization.</t>
+          <t>Print engine design, firmware tuning, consumables performance.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Product achieves specified throughput in benchmark tests for both standard and PDL modes.</t>
+          <t>Printer achieves at least 25/20 ppm (25/19 ppm PDL) in standard benchmark tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1676,41 +1676,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>SuperAmp PHA Life at 65K Pages</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ensure the maintenance box is easily serviceable to optimize uptime and reduce service costs.</t>
+          <t>The SuperAmp Printhead Assembly (PHA) must achieve a life of at least 65,000 pages.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Improves user experience and lowers total cost of ownership.</t>
+          <t>Supports high duty cycles and reduces service frequency for high-volume users.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Service, End Users, R&amp;D</t>
+          <t>R&amp;D, Service, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Maintenance box design and accessibility.</t>
+          <t>PHA design, consumables compatibility, firmware monitoring.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in under 5 minutes by a trained technician or user.</t>
+          <t>SuperAmp PHA operates reliably for at least 65,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1721,22 +1721,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>Warranty Life of 2 Years or 80,000 Pages</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>The product warranty must cover 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>Aligns with industry standards and customer expectations for reliability and support.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,147 +1746,147 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>Warranty/Service, Product Management, End Users</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Component durability, service model, legal review.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>Warranty terms published and honored; verified through warranty tracking and customer feedback.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>Serviceability via Maintenance Box</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>The printer must include a serviceable maintenance box to facilitate easy servicing and maintenance.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>Improves service efficiency and reduces device downtime.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Maintenance box design, service documentation, supply chain.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>Maintenance box can be replaced in under Z minutes (TBD) by service personnel; passes serviceability testing.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Host 12K-CMYK and Trade Page 6K Support (Flexible)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Support for 12,000-page CMYK host and 6,000-page trade page configurations as flexible options.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>Allows for product line extension and customization for different market needs.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>Firmware, consumables configuration, SKU management.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>Product can be configured for 12K-CMYK and 6K trade page options; validated in configuration testing.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1964,29 +1964,29 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1996,67 +1996,67 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2071,22 +2071,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2096,21 +2096,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Requires software development and integration with hardware.</t>
+          <t>Requires design of bottle and tank interface.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2121,46 +2121,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
+          <t>Requires durability testing and warranty policy alignment.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2171,42 +2171,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>Serviceability – PHA and MINK</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Requires AI software and sensor integration.</t>
+          <t>Requires design for replaceability and service documentation.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2214,79 +2214,79 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
+          <t>Requires software development and integration with hardware.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires app development and printer firmware support.</t>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2314,155 +2314,305 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PaaS Enablement</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
+          <t>Requires AI software and sensor integration.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires secure data collection and privacy compliance.</t>
+          <t>Requires sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Advanced Security and Compliance</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires security features and regulatory review.</t>
+          <t>Requires app development and printer firmware support.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Product passes security and compliance audits for target markets.</t>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
         </is>
       </c>
       <c r="I41" t="n">
         <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PaaS Enablement</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>['Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Requires secure data collection and privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Advanced Security and Compliance</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Requires security features and regulatory review.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Product passes security and compliance audits for target markets.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Magellan MRD, inferred from multiple sections</t>
         </is>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The printer must support new NGB keyed bottles with a minimum 6,000-page yield for black and 6,000-page yield for CMY, with CMY bottle size supporting over 8,000 pages.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size greater than 8K.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>High-yield bottles reduce frequency of replacement, enhance user convenience, and lower total cost of ownership, supporting competitive differentiation in SMB and Enterprise markets.</t>
+          <t>To meet higher page yield requirements and remain competitive in the market.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, SMB/Enterprise Customers</t>
+          <t>R&amp;D, Product Management, Customers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Integration with CISS, IDS, and NOA-F; compatible with Magi/Nessie ink; factory line modifications required.</t>
+          <t>Requires compatibility with Magi/Nessie ink and NOA-F system.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>System accepts and recognizes new NGB keyed bottles; Black yields at least 6,000 pages, CMY yields at least 6,000 pages, CMY bottle supports &gt;8,000 pages; verified through yield testing.</t>
+          <t>New bottles are available, compatible with system, and deliver specified yields in testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -531,12 +531,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The ink bottle and tank system must ensure spill-free reliability during bottle installation and replacement.</t>
+          <t>Ensure the new ink bottles and system provide spill-free reliability during all use cases.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Prevents mess, improves customer experience, and reduces service incidents related to ink spills.</t>
+          <t>Improves user experience and reduces mess and maintenance issues.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,21 +546,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Quality</t>
+          <t>End Users, R&amp;D, Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and tank design, NOA-F integration.</t>
+          <t>Requires new bottle design and integration with NOA-F.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spills occur during normal bottle installation/replacement in lab and field test scenarios.</t>
+          <t>No ink spills detected in user and lab testing across defined scenarios.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -581,12 +581,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The NOA-F (Non-Ozone Air Filter) must include a metal foiled labyrinth and a lid label, with no changes to click on push-push and TDF mechanisms.</t>
+          <t>Integrate NOA-F (Next-Generation Output Assembly - Filter) with a metal foiled labyrinth and a labeled lid, maintaining current click on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances reliability and compliance with air filtration requirements while maintaining compatibility with existing mechanisms.</t>
+          <t>Enhances reliability and traceability while maintaining proven usability features.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,21 +596,21 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Compliance, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F component sourcing and design, push-push and TDF compatibility.</t>
+          <t>Dependent on NOA-F design and labeling process.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F units have metal foiled labyrinth and lid label; click on push-push and TDF mechanisms function as in previous models.</t>
+          <t>NOA-F units pass reliability and usability tests and are correctly labeled.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Support for Customer Replaceable PHA and NOA-F</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The printer must allow end customers to replace the Printhead Assembly (PHA) and NOA-F components easily.</t>
+          <t>Reuse the existing SuperAmp Si PHA and Magi/Nessie pigment inks with no reformulation required.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and lowers support costs by enabling user-replaceable key components.</t>
+          <t>Reduces development cost and leverages proven components.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,21 +646,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PHA and NOA-F design for tool-less or simple replacement; documentation and packaging updates.</t>
+          <t>Requires compatibility verification with new bottle and system designs.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F without special tools, as verified in usability testing.</t>
+          <t>No performance or compatibility issues observed in system integration tests.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,17 +676,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80,000 Pages</t>
+          <t>Reliability and Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The printer must achieve a new warranty page life goal of 80,000 printed pages.</t>
+          <t>Model and characterize reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and IDS, including startup and NOA-F End of Life. Model ink stability for both tank and its impact on Print Quality (PQ).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Supports higher duty cycles for SMB/Enterprise customers and aligns with market expectations for reliability and longevity.</t>
+          <t>Ensures the system meets durability and print quality targets over its lifecycle.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,21 +696,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warranty/Service, Product Management, SMB/Enterprise Customers</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Component durability (PHA, paperpath, tubes, etc.), consumables life, firmware monitoring.</t>
+          <t>Requires data from new bottle/system configurations.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Printer operates reliably for 80,000 pages under warranty conditions; verified by accelerated life testing.</t>
+          <t>Models are completed and validated with test data; PQ remains within defined limits across lifecycle.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -726,37 +726,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Input/Output Tray and Tank Size Optimization</t>
+          <t>Support for Services and Contractual Requirements</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Input and output trays must be modified to align with the increased tank protrusion, and overall size optimization must be achieved.</t>
+          <t>Provide support for services/contractual obligations including NOA-F as service parts during warranty.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Accommodates larger ink tanks without compromising paper handling or increasing overall device footprint unnecessarily.</t>
+          <t>Ensures warranty and serviceability commitments are met for customers.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hardware Engineering, Industrial Design, Manufacturing</t>
+          <t>Service, Product Management, Customers</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tank design, mechanical layout, packaging requirements.</t>
+          <t>Requires service part logistics and documentation.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Trays function with new tank size; device passes size and fit validation; no paper handling issues observed.</t>
+          <t>Service parts available and process documented for warranty period.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -776,17 +776,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The product must include a 4.3-inch color graphical display (CGD) for enhanced user interaction.</t>
+          <t>Integrate Acumen 6 (presumably a security or tracking feature) onto the lid of the product.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves user experience through better navigation, status reporting, and feature access.</t>
+          <t>Improves security or traceability of consumables.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,21 +796,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>End Users, UI/UX, Product Management</t>
+          <t>Security, Product Management</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Firmware support, mechanical integration, supply chain for display components.</t>
+          <t>Dependent on lid design and Acumen 6 integration.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.3” CGD is functional in prototype and production units; user feedback meets satisfaction criteria.</t>
+          <t>Acumen 6 is functional and verifiable on all production lids.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -826,17 +826,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Platform with 4 Tubes and New Routing</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The printer must leverage Sayan Sibstar tubes, with new routing and integration for four tubes.</t>
+          <t>Modify existing SA 14 production line for NOA-F, add Magi ink cartridge and labeling tool in Orcus 5, and prepare for assembly of PHA, Dry FI, USG, and push-push mechanisms in the printer factory.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Supports increased ink flow, reliability, and compatibility with CISS and new bottle sizes.</t>
+          <t>Enables efficient and scalable manufacturing for new components.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tube sourcing, integration with IDS and ink tanks, mechanical design.</t>
+          <t>Requires Capex investment and process engineering.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Four-tube system passes flow rate, reliability, and serviceability tests.</t>
+          <t>Lines are modified, validated, and achieve defined production yields.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Mold for 1 to 4 New Keyed Caps</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Service station must include aerosol management features, with changes to accommodate the new tank system.</t>
+          <t>Develop molds for up to four new keyed caps to support the new bottle system.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Prevents ink aerosol contamination inside the device, ensuring reliability and safety.</t>
+          <t>Supports differentiation and proper bottle-to-tank matching.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,21 +896,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Quality</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Service station design, integration with tank and carriage systems.</t>
+          <t>Dependent on finalized bottle/cap design.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aerosol containment verified in environmental and reliability testing; no ink aerosol detected outside containment area.</t>
+          <t>Molds are created, tested, and support production rates.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -926,41 +926,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Update carriage dynamics and force model to account for new tube routing and increased component weights.</t>
+          <t>Achieve print speeds of 25 pages per minute (ppm) for standard, and 25/19 ppm for PDL (Page Description Language) mode.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ensures print quality, mechanical reliability, and longevity with new hardware configuration.</t>
+          <t>Meets market expectations for productivity and competitiveness.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>R&amp;D, Hardware Engineering</t>
+          <t>Product Management, Customers</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tube and tank design, carriage design updates.</t>
+          <t>Dependent on platform and print engine.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Carriage operates within force tolerances; no print artifacts or mechanical failures observed in testing.</t>
+          <t>Printers achieve specified speeds in standard and PDL mode in benchmark tests.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paperpath Upgrade for Increased Page Life</t>
+          <t>Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The printer paperpath must be upgraded to support increased page life, aligning with the 80,000-page warranty goal.</t>
+          <t>Design PHA (Printhead Assembly) and NOA-F to be customer replaceable.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Prevents paper jams and wear over extended duty cycles, critical for high-volume users.</t>
+          <t>Improves serviceability and reduces downtime/costs for end users.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, SMB/Enterprise Customers</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Material selection, mechanical redesign, reliability testing.</t>
+          <t>Requires design for easy access and replacement.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paperpath supports 80,000 pages with no more than X% jam rate (to be defined by quality standards).</t>
+          <t>Users can replace components without tools; validated in usability studies.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1026,41 +1026,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part (Post 80k Life)</t>
+          <t>Warranty Page Life Goal: 80k Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ink maintenance components must be designed as serviceable parts, replaceable at service centers after 80,000 pages.</t>
+          <t>Support a new warranty page life goal of 80,000 printed pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Extends overall device life and reduces total cost of ownership for high-usage customers.</t>
+          <t>Extends product value and aligns with service expectations.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Service, Warranty, SMB/Enterprise Customers</t>
+          <t>Product Management, Service, Customers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Component modularity, service documentation, supply chain for replacement parts.</t>
+          <t>Requires durability across all components.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Service center can replace ink maintenance components in under Y minutes (TBD); component passes post-replacement validation.</t>
+          <t>Printers reliably print 80,000 pages without major failure in accelerated life tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1076,41 +1076,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IDS with New Make-Break and FI Connection</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS Offering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI (fluidic interconnect) connection for the Integrated Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Provide a SKU 2 configuration with both Hi and Hi PDL features as a Platform as a Service (PaaS) offering.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ensures secure, reliable ink delivery with larger tanks and keyed access, preventing misinstallation.</t>
+          <t>Addresses market segments needing flexible, scalable solutions.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>Product Management, SMB, Enterprise Customers</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IDS redesign, compatibility with new bottles and tanks.</t>
+          <t>Dependent on platform and software enablement.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>IDS passes fluidic connection integrity tests and keying validation; no misinstallation observed in usability studies.</t>
+          <t>SKU 2 with PaaS is available and functional in target markets.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Tank Size Increase and Input/Output Tray Alignment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Develop and implement a new startup algorithm for the IDS with advanced air management to optimize ink flow and print quality.</t>
+          <t>Increase tank size for higher yield and adjust input/output trays to align with tank protrusion and size optimization.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Reduces startup issues, air entrapment, and print quality defects, especially with larger tanks and longer tube runs.</t>
+          <t>Supports higher yield and maintains form factor usability.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Firmware development, IDS hardware updates.</t>
+          <t>Dependent on tank and tray design.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Startup algorithm enables consistent ink flow and print quality in lab and field tests; air management validated in system tests.</t>
+          <t>Trays and tanks are compatible, and fit within defined size envelope; validated in physical mockups.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1176,41 +1176,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Metrics</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Establish new print quality (PQ) goals and ink depletion metrics to align with the defined page yield and warranty life.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures customer satisfaction and compliance with page yield claims and warranty commitments.</t>
+          <t>Enhances user interface and accessibility.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D, Product Management</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Print quality test protocols, firmware monitoring, consumables tracking.</t>
+          <t>Requires display integration with system firmware.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Print quality meets or exceeds new PQ goals over the stated page yield; depletion metrics align with warranty and marketing claims.</t>
+          <t>Display is functional, clear, and passes user acceptance tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Platform with 4 Tubes and New Routing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The printer must reuse the Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for cost and supply chain efficiency.</t>
+          <t>Leverage Sayan Sibstar tubes, implement four-tube platform, and develop new tube routing and integration.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Reduces development costs, leverages proven components, and streamlines manufacturing.</t>
+          <t>Supports ink delivery efficiency and reliability.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Procurement</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Component compatibility with new hardware and firmware.</t>
+          <t>Dependent on tube design and integration with tank/system.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Components function as expected in the new design; no integration issues found in system testing.</t>
+          <t>Ink flows reliably in all conditions; no tube failures in stress tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Modify service station for improved aerosol management due to tank changes and spit platform modifications.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Supports modern wireless printing standards and enhances device connectivity for SMB/Enterprise environments.</t>
+          <t>Prevents contamination and maintains print quality.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Firmware, hardware integration, regulatory compliance.</t>
+          <t>Dependent on tank and service station design.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Wi-Fi module passes connectivity, range, and security tests; certified for target markets.</t>
+          <t>Aerosol containment meets defined standards in lab tests.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1326,41 +1326,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW) Implementation</t>
+          <t>Carriage Dynamics and Force Modeling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features to protect device, data, and network integrity.</t>
+          <t>Model carriage dynamics and force with new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Addresses increasing security requirements in SMB and Enterprise environments.</t>
+          <t>Ensures reliable print operation and longevity with new hardware configuration.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IT, Security, Compliance, End Users</t>
+          <t>R&amp;D, Engineering</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hardware and firmware development, regulatory review.</t>
+          <t>Dependent on finalized hardware design.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Device passes HP and industry security certification; no critical vulnerabilities found in penetration testing.</t>
+          <t>Carriage operates within force and speed tolerances in all test scenarios.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>Paper Path for Increased Page Life</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and efficiency standards for the PDL SKU.</t>
+          <t>Redesign paper path to support increased page life (80k pages).</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Required for market access and competitive positioning, especially in government and large enterprise sectors.</t>
+          <t>Ensures reliable paper handling over extended printer lifespan.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Enterprise Customers</t>
+          <t>R&amp;D, Product Management, Customers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Design, material selection, documentation, certification process.</t>
+          <t>Dependent on paper path and component durability.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications for PDL SKU.</t>
+          <t>Paper jams and misfeeds remain below threshold in extended life tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Ink Maintenance Serviceable Part (Post-80k Life)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Use EPS foam for packaging to protect the product during shipping and handling.</t>
+          <t>Design ink maintenance as a serviceable part at service centers after 80k page life.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures product arrives undamaged, reducing returns and improving customer satisfaction.</t>
+          <t>Extends printer value and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1446,21 +1446,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics, End Users</t>
+          <t>Service, Product Management, Customers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Packaging design, supply chain sourcing.</t>
+          <t>Requires service part logistics and documentation.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Product passes drop and vibration tests in EPS foam packaging; no damage observed.</t>
+          <t>Service part is available and process is documented for post-warranty support.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1476,41 +1476,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Business Models</t>
+          <t>140ml K Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The printer must support business models for consumers, SMB, and enterprise customers, including services such as PaaS, WorkFromHome/Flexworker, and onboarding via multiple HP paths.</t>
+          <t>Introduce new 140ml black (K) bottles and new capacity CMY bottles.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Enables flexible go-to-market strategies and broadens addressable market segments.</t>
+          <t>Supports higher yield and market differentiation.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Firmware, drivers, onboarding flows, portal integration.</t>
+          <t>Dependent on supply chain and bottle design.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Business model features available in firmware and onboarding flows; validated in market pilots.</t>
+          <t>New bottles are available and compatible with system; validated in yield tests.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Scan Solution and SMB Manageability</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Include a scan solution and SMB manageability features, with enterprise support for WJA, HPSM, and JAM.</t>
+          <t>Develop new IDS (Ink Delivery System) startup algorithm and air management.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Addresses SMB and enterprise workflow needs and IT management requirements.</t>
+          <t>Improves reliability of ink delivery and printer startup performance.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1546,21 +1546,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SMB/Enterprise Customers, IT, Product Management</t>
+          <t>R&amp;D, Engineering, Service</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware, software, driver integration, support for WJA/HPSM/JAM.</t>
+          <t>Dependent on IDS hardware and firmware.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Scan and manageability features functional in test and pilot deployments; integration with WJA, HPSM, JAM verified.</t>
+          <t>Startup success rate &gt; 99% in defined test scenarios.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1576,41 +1576,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Client and Driver Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
+          <t>New Make-break and FI Connection</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The product must support a broad range of client and driver software, including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Implement new make-break and FI (Fluidic Interface) connection in IDS.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures compatibility with diverse IT environments and enhances user experience.</t>
+          <t>Improves serviceability and robustness of ink connections.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Firmware, driver development, QA testing.</t>
+          <t>Dependent on IDS redesign.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>All listed drivers are available, installable, and functional on supported platforms.</t>
+          <t>Connections pass durability and leak tests per defined standards.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1626,41 +1626,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25/20 ppm Print Speed (PDL: 25/19 ppm)</t>
+          <t>Leverage LEBI Ink-tank with Increased Size, Keying and LOI One SHAID</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The printer must achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for color, with PDL speeds at 25/19 ppm.</t>
+          <t>Use LEBI ink-tank with increased size, new keying, and LOI One SHAID for improved reliability and security.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Meets competitive benchmarks and user productivity needs.</t>
+          <t>Supports new bottle system, prevents mis-insertion, and improves tracking.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Marketing</t>
+          <t>R&amp;D, Security, Manufacturing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Print engine design, firmware tuning, consumables performance.</t>
+          <t>Dependent on tank and SHAID design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Printer achieves at least 25/20 ppm (25/19 ppm PDL) in standard benchmark tests.</t>
+          <t>Tanks are keyed correctly and SHAID is readable in all units.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The SuperAmp Printhead Assembly (PHA) must achieve a life of at least 65,000 pages.</t>
+          <t>Develop new servicing and startup algorithms to support new hardware and IDS.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Supports high duty cycles and reduces service frequency for high-volume users.</t>
+          <t>Ensures optimal performance and reliability for new system.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1696,25 +1696,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, SMB/Enterprise Customers</t>
+          <t>R&amp;D, Service, Engineering</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PHA design, consumables compatibility, firmware monitoring.</t>
+          <t>Dependent on IDS and firmware.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SuperAmp PHA operates reliably for at least 65,000 pages in accelerated life testing.</t>
+          <t>Algorithms pass reliability and usability tests; no startup failures in defined scenarios.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or 80,000 Pages</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The product warranty must cover 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Set new print quality (PQ) goals and depletion definitions to align with new page yield targets.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aligns with industry standards and customer expectations for reliability and support.</t>
+          <t>Ensures consistent output and clear end-of-life criteria for consumables.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,25 +1746,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Warranty/Service, Product Management, End Users</t>
+          <t>R&amp;D, Product Management, Quality Assurance</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Component durability, service model, legal review.</t>
+          <t>Dependent on new ink and system configurations.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Warranty terms published and honored; verified through warranty tracking and customer feedback.</t>
+          <t>PQ and depletion thresholds are met in validation testing.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Serviceability via Maintenance Box</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The printer must include a serviceable maintenance box to facilitate easy servicing and maintenance.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new platform.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Improves service efficiency and reduces device downtime.</t>
+          <t>Reduces development cost and leverages proven electronics.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,25 +1796,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>R&amp;D, Engineering, Manufacturing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation, supply chain.</t>
+          <t>Requires compatibility with new system design.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in under Z minutes (TBD) by service personnel; passes serviceability testing.</t>
+          <t>No compatibility or performance issues observed in integration tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1826,67 +1826,67 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K Support (Flexible)</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Support for 12,000-page CMYK host and 6,000-page trade page configurations as flexible options.</t>
+          <t>Integrate Stingray Wi-Fi module into the printer platform.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Allows for product line extension and customization for different market needs.</t>
+          <t>Ensures wireless connectivity and modern user experience.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Firmware, consumables configuration, SKU management.</t>
+          <t>Requires firmware and hardware integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Product can be configured for 12K-CMYK and 6K trade page options; validated in configuration testing.</t>
+          <t>Wi-Fi module passes connectivity and performance tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>FW Dune Firmware Platform</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>Utilize FW Dune as the firmware platform for the printer.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>Ensures consistent software stack and supportability.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1896,47 +1896,47 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>R&amp;D, Software Engineering</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Dependent on firmware integration with hardware.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>Firmware is stable and passes all regression and feature tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>Gauss4.xx Security for HW &amp; FW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>Implement Gauss4.xx security features for both hardware and firmware.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>Ensures data protection and compliance with security standards.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1946,47 +1946,47 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>Security, Product Management, Customers</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Requires hardware and firmware support.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>Security features pass internal and external penetration tests.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>EPEAT3, LOT4, Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Ensure printer meets EPEAT3, LOT4, and Blue Angel environmental and performance requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>Supports sustainability and regulatory compliance.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1996,17 +1996,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>Product Management, Regulatory, Customers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>Dependent on product design and certification process.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>Product is certified for EPEAT3, LOT4, and Blue Angel standards.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2014,129 +2014,129 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Use EPS foam packaging for the printer.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>Protects product during shipping and meets packaging standards.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>Manufacturing, Logistics, Customers</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>Dependent on packaging design.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>Packaging passes drop and vibration tests as per HP standards.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>Business Model: Consumer, SMB, Enterprise; Services: PaaS, WorkFromHome/Flexworker</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>Support business models for Consumer, SMB, and Enterprise segments, including Platform as a Service (PaaS) and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>Expands market reach and adapts to evolving customer needs.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>Dependent on platform and service enablement.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>Business models and services are available and functional in target markets.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Solution Support: Scan, SMB Manageability, Enterprise Support (WJA, HPSM, JAM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Provide solution support for scan functionality, SMB manageability, and enterprise tools such as WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>Addresses diverse customer solution needs and enterprise integration.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2146,117 +2146,117 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>Product Management, SMB, Enterprise Customers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>Dependent on software and platform integration.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>Solutions are available, functional, and validated with key customers.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Clients &amp; Drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Support a range of client and driver software including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>Ensures broad compatibility and ease of installation for customers.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>End Users, IT Departments, Product Management</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>Requires software integration and validation.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>All drivers are available and pass installation and functionality tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Protect Micro/SMB Segments and HP's Profit Pool</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+          <t>Design product features and strategies to protect Micro/SMB segments and prevent HP's traditional ink/laser profit pool from shifting to competitors.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+          <t>Maintains HP's market position and profitability.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>Product Management, Sales, Executives</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires software development and integration with hardware.</t>
+          <t>Dependent on feature set and market response.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+          <t>Market share and profit pool metrics remain stable or improve post-launch.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2264,29 +2264,29 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+          <t>Lead with LaserJet, Flank with PDL in Medium/Enterprise</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+          <t>Position the product to lead with LaserJet and flank with PDL in medium and enterprise segments to win over Epson as CISS grows.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+          <t>Improves competitive positioning against key rivals.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,47 +2296,47 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
+          <t>Dependent on feature set and market strategy.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+          <t>Market share in target segments increases post-launch.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>Grow CISS Profitable Share in New Segments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+          <t>Expand CISS (Continuous Ink Supply System) into new market segments for profitable growth.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+          <t>Drives revenue and market expansion.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2346,47 +2346,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires AI software and sensor integration.</t>
+          <t>Dependent on platform and go-to-market strategy.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+          <t>CISS share and profitability increase in new segments post-launch.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Highly Leverage Watt-LE Mech Platform, Marconi-Hi Product, and Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+          <t>Leverage existing Watt-LE mechanical platform, Marconi-Hi product (Reddington ID), and solution stack for new product.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+          <t>Reduces development time and cost by building on proven platforms.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2396,67 +2396,67 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>R&amp;D, Engineering, Product Management</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
+          <t>Requires compatibility with new features and components.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+          <t>Integration with legacy platforms is validated and meets performance targets.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+          <t>Integrate CISS IDS, NOA-F, and new ink tanks into the platform.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+          <t>Supports expanded functionality and reliability for CISS.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>R&amp;D, Engineering, Product Management</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires app development and printer firmware support.</t>
+          <t>Dependent on system integration and design.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+          <t>All components function as an integrated system in validation tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2464,79 +2464,79 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PaaS Enablement</t>
+          <t>New NGB Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+          <t>Develop and integrate new NGB keyed ink bottles for the system.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+          <t>Supports differentiation and prevents incorrect bottle insertion.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
+          <t>Dependent on bottle and tank design.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+          <t>Bottles are keyed and pass usability and reliability tests.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+          <t>Ensure the printer includes a serviceable maintenance box for ink waste and other maintenance tasks.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+          <t>Improves serviceability and lowers total cost of ownership.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2546,47 +2546,47 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires secure data collection and privacy compliance.</t>
+          <t>Dependent on hardware design.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+          <t>Maintenance box is easily accessible and replaceable by service or users.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Advanced Security and Compliance</t>
+          <t>Warranty Life: 2 Years or 80k Pages</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+          <t>Support a warranty life of 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+          <t>Aligns with market and service expectations.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2596,23 +2596,923 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>Product Management, Service, Customers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires security features and regulatory review.</t>
+          <t>Dependent on durability and reliability of components.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Product passes security and compliance audits for target markets.</t>
+          <t>Warranty coverage is clearly defined and supported in documentation.</t>
         </is>
       </c>
       <c r="I44" t="n">
         <v>0.9</v>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Throughput: 25/20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Achieve throughput of 25/20 pages per minute in PDL mode.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Meets productivity requirements for target segments.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Product Management, Customers</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dependent on print engine and software.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Throughput is validated in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SMB Solution Support</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Provide solution support specifically for SMB segments, including manageability and serviceability features.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Addresses needs of small and medium business customers.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dependent on feature set and solution integration.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SMB features are available and validated with representative customers.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Optimize Platform as a Service (PaaS) offering schedule for timely delivery.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Ensures competitive go-to-market timing.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Product Management, Sales, Marketing</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dependent on platform readiness and market strategy.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PaaS offering is launched on or before scheduled date.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AI Productivity Solutions</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Requires AI software integration and compatible hardware.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Requires backend portal development and printer firmware support.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Keyed Bottles for Ink Refill</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Requires design of bottle and tank interface.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Requires durability testing and warranty policy alignment.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Serviceability – PHA and MINK</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Requires design for replaceability and service documentation.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'BA']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Requires software development and integration with hardware.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan Features</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Requires AI software and sensor integration.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Requires sourcing and manufacturing process changes.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['GXD', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Requires app development and printer firmware support.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PaaS Enablement</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>['Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Requires secure data collection and privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Advanced Security and Compliance</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Requires security features and regulatory review.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Product passes security and compliance audits for target markets.</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Magellan MRD, inferred from multiple sections</t>
         </is>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Page Yield</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size greater than 8K.</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To meet higher page yield requirements and remain competitive in the market.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Customers</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with Magi/Nessie ink and NOA-F system.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New bottles are available, compatible with system, and deliver specified yields in testing.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure the new ink bottles and system provide spill-free reliability during all use cases.</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces mess and maintenance issues.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,25 +546,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Service</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires new bottle design and integration with NOA-F.</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spills detected in user and lab testing across defined scenarios.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate NOA-F (Next-Generation Output Assembly - Filter) with a metal foiled labyrinth and a labeled lid, maintaining current click on push-push and TDF mechanisms.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances reliability and traceability while maintaining proven usability features.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,25 +596,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dependent on NOA-F design and labeling process.</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F units pass reliability and usability tests and are correctly labeled.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse the existing SuperAmp Si PHA and Magi/Nessie pigment inks with no reformulation required.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven components.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,25 +646,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires compatibility verification with new bottle and system designs.</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No performance or compatibility issues observed in system integration tests.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -676,45 +676,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and Ink Stability Modeling</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Model and characterize reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and IDS, including startup and NOA-F End of Life. Model ink stability for both tank and its impact on Print Quality (PQ).</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures the system meets durability and print quality targets over its lifecycle.</t>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires data from new bottle/system configurations.</t>
+          <t>Requires design of bottle and tank interface.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Models are completed and validated with test data; PQ remains within defined limits across lifecycle.</t>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -726,17 +726,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Support for Services and Contractual Requirements</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Provide support for services/contractual obligations including NOA-F as service parts during warranty.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ensures warranty and serviceability commitments are met for customers.</t>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,25 +746,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Service, Product Management, Customers</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires service part logistics and documentation.</t>
+          <t>Requires durability testing and warranty policy alignment.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Service parts available and process documented for warranty period.</t>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Serviceability – PHA and MINK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (presumably a security or tracking feature) onto the lid of the product.</t>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves security or traceability of consumables.</t>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,25 +796,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Security, Product Management</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dependent on lid design and Acumen 6 integration.</t>
+          <t>Requires design for replaceability and service documentation.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Acumen 6 is functional and verifiable on all production lids.</t>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -826,45 +826,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Modify existing SA 14 production line for NOA-F, add Magi ink cartridge and labeling tool in Orcus 5, and prepare for assembly of PHA, Dry FI, USG, and push-push mechanisms in the printer factory.</t>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enables efficient and scalable manufacturing for new components.</t>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires Capex investment and process engineering.</t>
+          <t>Requires software development and integration with hardware.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lines are modified, validated, and achieve defined production yields.</t>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mold for 1 to 4 New Keyed Caps</t>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop molds for up to four new keyed caps to support the new bottle system.</t>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Supports differentiation and proper bottle-to-tank matching.</t>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,25 +896,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dependent on finalized bottle/cap design.</t>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Molds are created, tested, and support production rates.</t>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Achieve print speeds of 25 pages per minute (ppm) for standard, and 25/19 ppm for PDL (Page Description Language) mode.</t>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Meets market expectations for productivity and competitiveness.</t>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,25 +946,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Product Management, Customers</t>
+          <t>['Marketing', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dependent on platform and print engine.</t>
+          <t>Requires AI software and sensor integration.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Printers achieve specified speeds in standard and PDL mode in benchmark tests.</t>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Customer Replaceable PHA and NOA-F</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design PHA (Printhead Assembly) and NOA-F to be customer replaceable.</t>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime/costs for end users.</t>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,25 +996,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires design for easy access and replacement.</t>
+          <t>Requires sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Users can replace components without tools; validated in usability studies.</t>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -1026,45 +1026,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal: 80k Pages</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Support a new warranty page life goal of 80,000 printed pages.</t>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Extends product value and aligns with service expectations.</t>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Service, Customers</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires durability across all components.</t>
+          <t>Requires app development and printer firmware support.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Printers reliably print 80,000 pages without major failure in accelerated life tests.</t>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS Offering</t>
+          <t>PaaS Enablement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Provide a SKU 2 configuration with both Hi and Hi PDL features as a Platform as a Service (PaaS) offering.</t>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Addresses market segments needing flexible, scalable solutions.</t>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,25 +1096,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Product Management, SMB, Enterprise Customers</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dependent on platform and software enablement.</t>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SKU 2 with PaaS is available and functional in target markets.</t>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
     </row>
@@ -1126,37 +1126,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tank Size Increase and Input/Output Tray Alignment</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Increase tank size for higher yield and adjust input/output trays to align with tank protrusion and size optimization.</t>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Supports higher yield and maintains form factor usability.</t>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dependent on tank and tray design.</t>
+          <t>Requires secure data collection and privacy compliance.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Trays and tanks are compatible, and fit within defined size envelope; validated in physical mockups.</t>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
     </row>
@@ -1176,91 +1176,91 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Advanced Security and Compliance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Enhances user interface and accessibility.</t>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Requires display integration with system firmware.</t>
+          <t>Requires security features and regulatory review.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Display is functional, clear, and passes user acceptance tests.</t>
+          <t>Product passes security and compliance audits for target markets.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, inferred from multiple sections</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Platform with 4 Tubes and New Routing</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes, implement four-tube platform, and develop new tube routing and integration.</t>
+          <t>Develop NGB keyed bottles for the Magellan printer with 6,000-page yield for Black and CMY, and &gt;8,000-page size for CMY.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Supports ink delivery efficiency and reliability.</t>
+          <t>To ensure high page yield and compatibility with the new printer, reducing user intervention and supporting high-volume printing.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dependent on tube design and integration with tank/system.</t>
+          <t>Dependent on new bottle design and compatibility with existing ink system.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ink flows reliably in all conditions; no tube failures in stress tests.</t>
+          <t>NGB bottles are available for Black and CMY; Black yields 6,000 pages, CMY bottles are &gt;8,000-page size, and bottles are keyed for system compatibility.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1271,46 +1271,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Spill-Free Bottle Reliability</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Modify service station for improved aerosol management due to tank changes and spit platform modifications.</t>
+          <t>Ensure new NGB bottles provide spill-free reliability when used with the Magellan printer.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Prevents contamination and maintains print quality.</t>
+          <t>To improve user experience and minimize mess or ink wastage during refilling.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dependent on tank and service station design.</t>
+          <t>Requires bottle and ink system integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aerosol containment meets defined standards in lab tests.</t>
+          <t>No spills occur during bottle installation or removal in 100% of test cases across 100 cycles.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1321,46 +1321,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Carriage Dynamics and Force Modeling</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Model carriage dynamics and force with new tube routing and increased weights.</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and lid label; maintain current click on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ensures reliable print operation and longevity with new hardware configuration.</t>
+          <t>To enhance reliability and maintain established user experience features.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Engineering</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dependent on finalized hardware design.</t>
+          <t>NOA-F design update, compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Carriage operates within force and speed tolerances in all test scenarios.</t>
+          <t>NOA-F units include metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms, verified in production samples.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1371,22 +1371,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paper Path for Increased Page Life</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life (80k pages).</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie ink formulations without requiring ink reformulation for Magellan.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures reliable paper handling over extended printer lifespan.</t>
+          <t>To reduce development time, leverage proven technology, and minimize risk.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,21 +1396,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Customers</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dependent on paper path and component durability.</t>
+          <t>Compatibility verification with new printer system.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paper jams and misfeeds remain below threshold in extended life tests.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie ink operate within performance specs in the Magellan system with no reformulation required.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1421,46 +1421,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post-80k Life)</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part at service centers after 80k page life.</t>
+          <t>NOA-F units must be available as service parts for warranty support.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Extends printer value and reduces total cost of ownership for customers.</t>
+          <t>To ensure serviceability and maintain warranty commitments for customers.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Service, Product Management, Customers</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Requires service part logistics and documentation.</t>
+          <t>Supply chain and service logistics.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Service part is available and process is documented for post-warranty support.</t>
+          <t>NOA-F service parts are available and supplied for warranty claims within standard SLA.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1471,22 +1471,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Introduce new 140ml black (K) bottles and new capacity CMY bottles.</t>
+          <t>Integrate Acumen 6 feature into the printer lid.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Supports higher yield and market differentiation.</t>
+          <t>To support advanced features or security as per platform standards.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1496,21 +1496,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Security, Product Management</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dependent on supply chain and bottle design.</t>
+          <t>Lid design update and platform integration.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>New bottles are available and compatible with system; validated in yield tests.</t>
+          <t>Acumen 6 feature is operational and tested on the production lid.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1521,22 +1521,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Develop new IDS (Ink Delivery System) startup algorithm and air management.</t>
+          <t>Modify existing SA14 factory line for NOA-F, and add Magi ink cart and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves reliability of ink delivery and printer startup performance.</t>
+          <t>To enable efficient manufacturing of the new printer and consumables.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1546,21 +1546,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Engineering, Service</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dependent on IDS hardware and firmware.</t>
+          <t>Capex approval, tool procurement, line reconfiguration.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Startup success rate &gt; 99% in defined test scenarios.</t>
+          <t>SA14 line is modified and operational for NOA-F; Magi ink cart and labelling tool are installed in Orcus 5.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1571,46 +1571,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Make-break and FI Connection</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI (Fluidic Interface) connection in IDS.</t>
+          <t>Design Magellan printer to allow customer-replaceable PHA and NOA-F units.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Improves serviceability and robustness of ink connections.</t>
+          <t>To improve user serviceability and reduce support costs.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>End Users, Service, Support</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dependent on IDS redesign.</t>
+          <t>Mechanical design for easy access and replacement.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Connections pass durability and leak tests per defined standards.</t>
+          <t>Users can replace PHA and NOA-F without tools in under 5 minutes, verified by usability testing.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1621,46 +1621,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-tank with Increased Size, Keying and LOI One SHAID</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Use LEBI ink-tank with increased size, new keying, and LOI One SHAID for improved reliability and security.</t>
+          <t>Set new warranty page life goal for Magellan printer at 80,000 pages.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Supports new bottle system, prevents mis-insertion, and improves tracking.</t>
+          <t>To meet market expectations for durability and reduce warranty claims.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Manufacturing</t>
+          <t>Product Management, Quality, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dependent on tank and SHAID design.</t>
+          <t>Component reliability, consumable life.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tanks are keyed correctly and SHAID is readable in all units.</t>
+          <t>Printer and consumables function to spec for 80,000 pages under standard test conditions.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1671,42 +1671,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Develop new servicing and startup algorithms to support new hardware and IDS.</t>
+          <t>Adopt Reddington ID for Magellan with increased tank size; no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ensures optimal performance and reliability for new system.</t>
+          <t>To support higher ink capacity while maintaining design identity.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Engineering</t>
+          <t>Design, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dependent on IDS and firmware.</t>
+          <t>Tank design update, compatibility with Reddington ID.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Algorithms pass reliability and usability tests; no startup failures in defined scenarios.</t>
+          <t>Tank size increased as per spec, Reddington ID is maintained, and ADF unchanged.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1721,22 +1721,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and depletion definitions to align with new page yield targets.</t>
+          <t>Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ensures consistent output and clear end-of-life criteria for consumables.</t>
+          <t>To comply with environmental regulations and market requirements.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,21 +1746,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Quality Assurance</t>
+          <t>Compliance, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dependent on new ink and system configurations.</t>
+          <t>Design and documentation for certification.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PQ and depletion thresholds are met in validation testing.</t>
+          <t>Printer is certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1771,22 +1771,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new platform.</t>
+          <t>Modify input and output trays to align with increased tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven electronics.</t>
+          <t>To ensure mechanical compatibility and optimize product footprint.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,21 +1796,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Engineering, Manufacturing</t>
+          <t>Design, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Requires compatibility with new system design.</t>
+          <t>Tray and tank design coordination.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>No compatibility or performance issues observed in integration tests.</t>
+          <t>Trays fit and operate correctly with new tank design; printer passes mechanical fit and finish tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1821,22 +1821,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module into the printer platform.</t>
+          <t>Integrate a 4.3-inch CGD display into the Magellan printer.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensures wireless connectivity and modern user experience.</t>
+          <t>To provide a modern and user-friendly interface.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>End Users, Product Management, Design</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Requires firmware and hardware integration.</t>
+          <t>Electrical and mechanical integration of display.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Wi-Fi module passes connectivity and performance tests.</t>
+          <t>4.3” CGD display is functional, passes UI and reliability testing.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1871,46 +1871,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FW Dune Firmware Platform</t>
+          <t>4-Tube Platform with New Tube Routing and Integration</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Utilize FW Dune as the firmware platform for the printer.</t>
+          <t>Leverage Sayan Sibstar tubes for a 4-tube platform, with new tube routing and integration for Magellan.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ensures consistent software stack and supportability.</t>
+          <t>To improve ink delivery and system reliability.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Software Engineering</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dependent on firmware integration with hardware.</t>
+          <t>Tube design and routing, system integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Firmware is stable and passes all regression and feature tests.</t>
+          <t>Four tubes are routed and integrated per design, system passes ink delivery and reliability tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1921,46 +1921,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security for HW &amp; FW</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features for both hardware and firmware.</t>
+          <t>Update service station for aerosol management with spit platform changes due to new tank.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures data protection and compliance with security standards.</t>
+          <t>To ensure proper aerosol handling and maintain print quality.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Security, Product Management, Customers</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware support.</t>
+          <t>Service station and tank design updates.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Security features pass internal and external penetration tests.</t>
+          <t>Service station manages aerosols effectively, verified by print quality and emissions testing.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1971,46 +1971,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, Blue Angel Compliance</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ensure printer meets EPEAT3, LOT4, and Blue Angel environmental and performance requirements for PDL SKU.</t>
+          <t>Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Supports sustainability and regulatory compliance.</t>
+          <t>To ensure reliable operation and print quality with new system configuration.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Product Management, Regulatory, Customers</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dependent on product design and certification process.</t>
+          <t>Tube and carriage design.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Product is certified for EPEAT3, LOT4, and Blue Angel standards.</t>
+          <t>Carriage operates within force and dynamic parameters with new tubes and weights in testing.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2021,46 +2021,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Paper Path Durability for Increased Page Life</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for the printer.</t>
+          <t>Enhance paper path to support increased page life of 80,000 pages.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Protects product during shipping and meets packaging standards.</t>
+          <t>To ensure printer reliability over its extended life expectancy.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics, Customers</t>
+          <t>R&amp;D, Quality, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dependent on packaging design.</t>
+          <t>Paper path component selection and testing.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Packaging passes drop and vibration tests as per HP standards.</t>
+          <t>Paper path components show no significant wear after 80,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2071,42 +2071,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Business Model: Consumer, SMB, Enterprise; Services: PaaS, WorkFromHome/Flexworker</t>
+          <t>Ink Maintenance Serviceable Part Post-80k Life</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Support business models for Consumer, SMB, and Enterprise segments, including Platform as a Service (PaaS) and WorkFromHome/Flexworker services.</t>
+          <t>Provide ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Expands market reach and adapts to evolving customer needs.</t>
+          <t>To extend printer service life and reduce total cost of ownership.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>Service, End Users, Support</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dependent on platform and service enablement.</t>
+          <t>Part design and service documentation.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Business models and services are available and functional in target markets.</t>
+          <t>Ink maintenance part can be replaced at service centers post-80k life, verified by service procedures.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2121,42 +2121,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Solution Support: Scan, SMB Manageability, Enterprise Support (WJA, HPSM, JAM)</t>
+          <t>140ml Black Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Provide solution support for scan functionality, SMB manageability, and enterprise tools such as WJA, HPSM, and JAM.</t>
+          <t>Provide 140ml Black bottles and new capacity CMY bottles for Magellan printer.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Addresses diverse customer solution needs and enterprise integration.</t>
+          <t>To support higher print volumes and reduce refill frequency.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Product Management, SMB, Enterprise Customers</t>
+          <t>Product Management, End Users, Supply Chain</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dependent on software and platform integration.</t>
+          <t>Bottle design and supply chain readiness.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Solutions are available, functional, and validated with key customers.</t>
+          <t>140ml Black bottles and new CMY bottles are available and compatible with Magellan system.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2171,42 +2171,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clients &amp; Drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Support a range of client and driver software including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Implement a new IDS startup algorithm and air management system for Magellan.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ensures broad compatibility and ease of installation for customers.</t>
+          <t>To optimize ink delivery system performance and startup reliability.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>End Users, IT Departments, Product Management</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Requires software integration and validation.</t>
+          <t>IDS design and firmware development.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>All drivers are available and pass installation and functionality tests.</t>
+          <t>IDS startup algorithm passes performance and reliability tests; air management is verified in system tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2221,222 +2221,222 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Protect Micro/SMB Segments and HP's Profit Pool</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Design product features and strategies to protect Micro/SMB segments and prevent HP's traditional ink/laser profit pool from shifting to competitors.</t>
+          <t>Develop new servicing and startup algorithm for Magellan printer.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Maintains HP's market position and profitability.</t>
+          <t>To improve reliability and user experience during initial setup and servicing.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Executives</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dependent on feature set and market response.</t>
+          <t>Firmware development and integration.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Market share and profit pool metrics remain stable or improve post-launch.</t>
+          <t>Servicing and startup algorithm passes reliability and usability testing.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lead with LaserJet, Flank with PDL in Medium/Enterprise</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Position the product to lead with LaserJet and flank with PDL in medium and enterprise segments to win over Epson as CISS grows.</t>
+          <t>Establish new print quality goals and depletion criteria to align with page yield definition for Magellan.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Improves competitive positioning against key rivals.</t>
+          <t>To ensure print quality and accurate yield reporting.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>Product Management, Quality, R&amp;D</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dependent on feature set and market strategy.</t>
+          <t>Print quality testing, documentation update.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Market share in target segments increases post-launch.</t>
+          <t>Print quality meets new goals and depletion is defined and measured per updated criteria.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Grow CISS Profitable Share in New Segments</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Expand CISS (Continuous Ink Supply System) into new market segments for profitable growth.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan printer.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Drives revenue and market expansion.</t>
+          <t>To leverage proven electronics and reduce development cost and risk.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dependent on platform and go-to-market strategy.</t>
+          <t>Compatibility verification with Magellan platform.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CISS share and profitability increase in new segments post-launch.</t>
+          <t>All reused components operate to spec in Magellan printer.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Highly Leverage Watt-LE Mech Platform, Marconi-Hi Product, and Solutions</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leverage existing Watt-LE mechanical platform, Marconi-Hi product (Reddington ID), and solution stack for new product.</t>
+          <t>Integrate Stingray Wi-Fi module into Magellan printer.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reduces development time and cost by building on proven platforms.</t>
+          <t>To provide wireless connectivity as per current standards.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>R&amp;D, Engineering, Product Management</t>
+          <t>End Users, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires compatibility with new features and components.</t>
+          <t>Electrical and firmware integration.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Integration with legacy platforms is validated and meets performance targets.</t>
+          <t>Wi-Fi module is operational and passes connectivity and compliance tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+          <t>FW Dune and Gauss4.xx Security Integration</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and new ink tanks into the platform.</t>
+          <t>Integrate FW Dune and Gauss4.xx security features into Magellan printer (hardware and firmware).</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Supports expanded functionality and reliability for CISS.</t>
+          <t>To ensure security compliance and protect user data.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R&amp;D, Engineering, Product Management</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dependent on system integration and design.</t>
+          <t>Firmware and hardware integration, compliance testing.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>All components function as an integrated system in validation tests.</t>
+          <t>FW Dune and Gauss4.xx security features are operational and pass security validation tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2464,29 +2464,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New NGB Keyed Ink Bottles</t>
+          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Develop and integrate new NGB keyed ink bottles for the system.</t>
+          <t>Magellan must support business models for Consumer, SMB, and Enterprise segments, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Supports differentiation and prevents incorrect bottle insertion.</t>
+          <t>To maximize market reach and adapt to diverse customer needs.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>Business, Sales, Product Management</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dependent on bottle and tank design.</t>
+          <t>Service and solution development.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bottles are keyed and pass usability and reliability tests.</t>
+          <t>Printer is offered in configurations and bundles supporting the specified segments and services.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2514,79 +2514,79 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ensure the printer includes a serviceable maintenance box for ink waste and other maintenance tasks.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into Magellan platform.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Improves serviceability and lowers total cost of ownership.</t>
+          <t>To enhance solution offering and address business customer requirements.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Business, R&amp;D, Product Management, Enterprise Customers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dependent on hardware design.</t>
+          <t>Solution and software integration.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maintenance box is easily accessible and replaceable by service or users.</t>
+          <t>All listed solutions are functional and pass integration and user acceptance testing.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Warranty Life: 2 Years or 80k Pages</t>
+          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Support a warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Provide client and driver support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Aligns with market and service expectations.</t>
+          <t>To ensure broad compatibility and ease of use across platforms and customer environments.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Product Management, Service, Customers</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dependent on durability and reliability of components.</t>
+          <t>Driver and software development.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Warranty coverage is clearly defined and supported in documentation.</t>
+          <t>All listed clients and drivers are available, tested, and documented for Magellan printer.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2614,29 +2614,29 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Throughput: 25/20 ppm (PDL)</t>
+          <t>Leverage Watt-LE/Marconi Hi Mech + CISS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Achieve throughput of 25/20 pages per minute in PDL mode.</t>
+          <t>Leverage Watt-LE/Marconi Hi mechanical platform and integrate with CISS for Magellan.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Meets productivity requirements for target segments.</t>
+          <t>To reduce development cost and time to market while incorporating CISS benefits.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Product Management, Customers</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dependent on print engine and software.</t>
+          <t>Mechanical and system integration.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Throughput is validated in benchmark tests.</t>
+          <t>Watt-LE/Marconi Hi Mech platform is used and CISS is integrated and passes system tests.</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2671,22 +2671,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SMB Solution Support</t>
+          <t>Schedule as Least Flexible Constraint</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Provide solution support specifically for SMB segments, including manageability and serviceability features.</t>
+          <t>Meet the schedule as the highest business constraint for Magellan program.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Addresses needs of small and medium business customers.</t>
+          <t>To ensure timely market entry and competitive positioning.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2696,21 +2696,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management</t>
+          <t>Business, Program Management, R&amp;D</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dependent on feature set and solution integration.</t>
+          <t>All critical path activities.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SMB features are available and validated with representative customers.</t>
+          <t>All program milestones are met as per published schedule.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2721,46 +2721,46 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PaaS Schedule Optimization</t>
+          <t>SuperAmp PHA Life at 65K as Least Flexible Constraint</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Optimize Platform as a Service (PaaS) offering schedule for timely delivery.</t>
+          <t>SuperAmp PHA must achieve a life of at least 65,000 pages for Magellan.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ensures competitive go-to-market timing.</t>
+          <t>To ensure reliability and meet business constraints for consumable life.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dependent on platform readiness and market strategy.</t>
+          <t>PHA design and testing.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>PaaS offering is launched on or before scheduled date.</t>
+          <t>SuperAmp PHA is verified to last at least 65,000 pages in standard test cycles.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2771,22 +2771,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>Warranty Life of 2 Years as Optimized Priority</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>Magellan printer must be warranted for 2 years or up to the page life goal, whichever comes first.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>To align with market expectations and business priorities.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2796,47 +2796,47 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>Product Management, End Users, Sales</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Component reliability, service policies.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>Product warranty is offered for 2 years or 80,000 pages, with support processes in place.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>Magellan printer must achieve throughput of 25 ppm (mono) and 20 ppm (color) for PDL SKU.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>To meet performance requirements and market competitiveness.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2846,97 +2846,97 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>End Users, Product Management, Sales</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Print engine and firmware performance.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>Printer achieves 25 ppm mono and 20 ppm color in PDL SKU during standard performance tests.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Serviceability of Maintenance Box as Optimized Priority</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Design Magellan printer for easy servicing of the maintenance box.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>To improve post-sale support and reduce downtime.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>Service, End Users, Support</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>Mechanical design for access and replacement.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>Maintenance box can be serviced or replaced within 10 minutes by service personnel.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>SMB Solution Support as Optimized Priority</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Magellan must support SMB solutions as an optimized business priority.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>To ensure the printer meets the needs of small and medium business customers.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>SMB Customers, Sales, Product Management</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>Solution integration and support.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>SMB solutions are available and functional for Magellan printer.</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -2964,557 +2964,157 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>PaaS Schedule as Optimized Priority</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>Ensure PaaS (Printing as a Service) is delivered according to schedule for Magellan.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>To support new business models and revenue streams.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>PaaS development and integration.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>PaaS is available for Magellan as per published schedule and passes customer acceptance.</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Host 12K-CMYK as Flexible Priority</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Provide support for hosting 12K-CMYK as a flexible business priority.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>To allow for future scalability and market adaptation.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>System design for scalability.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>System design can accommodate 12K-CMYK hosting if required in future roadmap.</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Trade Page 6K as Flexible Priority</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Support trade page 6K as a flexible business priority.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>To provide options for market-specific or promotional SKUs.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Product Management, Sales</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>SKU and configuration management.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>Trade page 6K option is available as a configurable SKU.</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Requires software development and integration with hardware.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Perfect Print and Perfect Scan Features</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Requires AI software and sensor integration.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>['GXD', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Requires app development and printer firmware support.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>PaaS Enablement</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>['Marketing', 'BA']</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Requires secure data collection and privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Advanced Security and Compliance</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Requires security features and regulatory review.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Product passes security and compliance audits for target markets.</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Magellan MRD, inferred from multiple sections</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>Develop NGB keyed bottles for the Magellan printer with 6,000-page yield for Black and CMY, and &gt;8,000-page size for CMY.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>To ensure high page yield and compatibility with the new printer, reducing user intervention and supporting high-volume printing.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Dependent on new bottle design and compatibility with existing ink system.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>NGB bottles are available for Black and CMY; Black yields 6,000 pages, CMY bottles are &gt;8,000-page size, and bottles are keyed for system compatibility.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>Spill-Free Bottle Reliability</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>Ensure new NGB bottles provide spill-free reliability when used with the Magellan printer.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>To improve user experience and minimize mess or ink wastage during refilling.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,25 +546,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Requires bottle and ink system integration.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>No spills occur during bottle installation or removal in 100% of test cases across 100 cycles.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and lid label; maintain current click on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>To enhance reliability and maintain established user experience features.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>NOA-F design update, compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>NOA-F units include metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms, verified in production samples.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie ink formulations without requiring ink reformulation for Magellan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>To reduce development time, leverage proven technology, and minimize risk.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,25 +646,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>Compatibility verification with new printer system.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie ink operate within performance specs in the Magellan system with no reformulation required.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -676,45 +676,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>NOA-F units must be available as service parts for warranty support.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>To ensure serviceability and maintain warranty commitments for customers.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>Supply chain and service logistics.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>NOA-F service parts are available and supplied for warranty claims within standard SLA.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -726,45 +726,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Integrate Acumen 6 feature into the printer lid.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>To support advanced features or security as per platform standards.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>R&amp;D, Security, Product Management</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>Lid design update and platform integration.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>Acumen 6 feature is operational and tested on the production lid.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -776,37 +776,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Modify existing SA14 factory line for NOA-F, and add Magi ink cart and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>To enable efficient manufacturing of the new printer and consumables.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>Capex approval, tool procurement, line reconfiguration.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>SA14 line is modified and operational for NOA-F; Magi ink cart and labelling tool are installed in Orcus 5.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -826,45 +826,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+          <t>Design Magellan printer to allow customer-replaceable PHA and NOA-F units.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+          <t>To improve user serviceability and reduce support costs.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>End Users, Service, Support</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires software development and integration with hardware.</t>
+          <t>Mechanical design for easy access and replacement.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+          <t>Users can replace PHA and NOA-F without tools in under 5 minutes, verified by usability testing.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -876,37 +876,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+          <t>Set new warranty page life goal for Magellan printer at 80,000 pages.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+          <t>To meet market expectations for durability and reduce warranty claims.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+          <t>Product Management, Quality, End Users</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
+          <t>Component reliability, consumable life.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+          <t>Printer and consumables function to spec for 80,000 pages under standard test conditions.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -926,45 +926,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+          <t>Adopt Reddington ID for Magellan with increased tank size; no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+          <t>To support higher ink capacity while maintaining design identity.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
+          <t>Design, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires AI software and sensor integration.</t>
+          <t>Tank design update, compatibility with Reddington ID.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+          <t>Tank size increased as per spec, Reddington ID is maintained, and ADF unchanged.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+          <t>Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+          <t>To comply with environmental regulations and market requirements.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,25 +996,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>Compliance, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
+          <t>Design and documentation for certification.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+          <t>Printer is certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+          <t>Modify input and output trays to align with increased tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+          <t>To ensure mechanical compatibility and optimize product footprint.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,25 +1046,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>Design, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires app development and printer firmware support.</t>
+          <t>Tray and tank design coordination.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+          <t>Trays fit and operate correctly with new tank design; printer passes mechanical fit and finish tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PaaS Enablement</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+          <t>Integrate a 4.3-inch CGD display into the Magellan printer.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+          <t>To provide a modern and user-friendly interface.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>End Users, Product Management, Design</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
+          <t>Electrical and mechanical integration of display.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+          <t>4.3” CGD display is functional, passes UI and reliability testing.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>4-Tube Platform with New Tube Routing and Integration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+          <t>Leverage Sayan Sibstar tubes for a 4-tube platform, with new tube routing and integration for Magellan.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+          <t>To improve ink delivery and system reliability.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,25 +1146,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Requires secure data collection and privacy compliance.</t>
+          <t>Tube design and routing, system integration.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+          <t>Four tubes are routed and integrated per design, system passes ink delivery and reliability tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1176,91 +1176,91 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Advanced Security and Compliance</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+          <t>Update service station for aerosol management with spit platform changes due to new tank.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+          <t>To ensure proper aerosol handling and maintain print quality.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Requires security features and regulatory review.</t>
+          <t>Service station and tank design updates.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Product passes security and compliance audits for target markets.</t>
+          <t>Service station manages aerosols effectively, verified by print quality and emissions testing.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Magellan MRD, inferred from multiple sections</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Develop NGB keyed bottles for the Magellan printer with 6,000-page yield for Black and CMY, and &gt;8,000-page size for CMY.</t>
+          <t>Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To ensure high page yield and compatibility with the new printer, reducing user intervention and supporting high-volume printing.</t>
+          <t>To ensure reliable operation and print quality with new system configuration.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dependent on new bottle design and compatibility with existing ink system.</t>
+          <t>Tube and carriage design.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NGB bottles are available for Black and CMY; Black yields 6,000 pages, CMY bottles are &gt;8,000-page size, and bottles are keyed for system compatibility.</t>
+          <t>Carriage operates within force and dynamic parameters with new tubes and weights in testing.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1271,22 +1271,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spill-Free Bottle Reliability</t>
+          <t>Paper Path Durability for Increased Page Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ensure new NGB bottles provide spill-free reliability when used with the Magellan printer.</t>
+          <t>Enhance paper path to support increased page life of 80,000 pages.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To improve user experience and minimize mess or ink wastage during refilling.</t>
+          <t>To ensure printer reliability over its extended life expectancy.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D</t>
+          <t>R&amp;D, Quality, End Users</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Requires bottle and ink system integration.</t>
+          <t>Paper path component selection and testing.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No spills occur during bottle installation or removal in 100% of test cases across 100 cycles.</t>
+          <t>Paper path components show no significant wear after 80,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1321,46 +1321,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Ink Maintenance Serviceable Part Post-80k Life</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Integrate NOA-F with a metal foiled labyrinth and lid label; maintain current click on push-push and TDF mechanisms.</t>
+          <t>Provide ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To enhance reliability and maintain established user experience features.</t>
+          <t>To extend printer service life and reduce total cost of ownership.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Service, End Users, Support</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NOA-F design update, compatibility with existing mechanisms.</t>
+          <t>Part design and service documentation.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NOA-F units include metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms, verified in production samples.</t>
+          <t>Ink maintenance part can be replaced at service centers post-80k life, verified by service procedures.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1371,46 +1371,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>140ml Black Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie ink formulations without requiring ink reformulation for Magellan.</t>
+          <t>Provide 140ml Black bottles and new capacity CMY bottles for Magellan printer.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To reduce development time, leverage proven technology, and minimize risk.</t>
+          <t>To support higher print volumes and reduce refill frequency.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>Product Management, End Users, Supply Chain</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Compatibility verification with new printer system.</t>
+          <t>Bottle design and supply chain readiness.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie ink operate within performance specs in the Magellan system with no reformulation required.</t>
+          <t>140ml Black bottles and new CMY bottles are available and compatible with Magellan system.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1421,46 +1421,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOA-F units must be available as service parts for warranty support.</t>
+          <t>Implement a new IDS startup algorithm and air management system for Magellan.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To ensure serviceability and maintain warranty commitments for customers.</t>
+          <t>To optimize ink delivery system performance and startup reliability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Supply chain and service logistics.</t>
+          <t>IDS design and firmware development.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NOA-F service parts are available and supplied for warranty claims within standard SLA.</t>
+          <t>IDS startup algorithm passes performance and reliability tests; air management is verified in system tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1471,22 +1471,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 feature into the printer lid.</t>
+          <t>Develop new servicing and startup algorithm for Magellan printer.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To support advanced features or security as per platform standards.</t>
+          <t>To improve reliability and user experience during initial setup and servicing.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Product Management</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lid design update and platform integration.</t>
+          <t>Firmware development and integration.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Acumen 6 feature is operational and tested on the production lid.</t>
+          <t>Servicing and startup algorithm passes reliability and usability testing.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1521,22 +1521,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Modify existing SA14 factory line for NOA-F, and add Magi ink cart and labelling tool in Orcus 5.</t>
+          <t>Establish new print quality goals and depletion criteria to align with page yield definition for Magellan.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To enable efficient manufacturing of the new printer and consumables.</t>
+          <t>To ensure print quality and accurate yield reporting.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1546,21 +1546,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Product Management, Quality, R&amp;D</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Capex approval, tool procurement, line reconfiguration.</t>
+          <t>Print quality testing, documentation update.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SA14 line is modified and operational for NOA-F; Magi ink cart and labelling tool are installed in Orcus 5.</t>
+          <t>Print quality meets new goals and depletion is defined and measured per updated criteria.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1571,42 +1571,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Design Magellan printer to allow customer-replaceable PHA and NOA-F units.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan printer.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To improve user serviceability and reduce support costs.</t>
+          <t>To leverage proven electronics and reduce development cost and risk.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>End Users, Service, Support</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mechanical design for easy access and replacement.</t>
+          <t>Compatibility verification with Magellan platform.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Users can replace PHA and NOA-F without tools in under 5 minutes, verified by usability testing.</t>
+          <t>All reused components operate to spec in Magellan printer.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1621,46 +1621,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Set new warranty page life goal for Magellan printer at 80,000 pages.</t>
+          <t>Integrate Stingray Wi-Fi module into Magellan printer.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To meet market expectations for durability and reduce warranty claims.</t>
+          <t>To provide wireless connectivity as per current standards.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Product Management, Quality, End Users</t>
+          <t>End Users, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Component reliability, consumable life.</t>
+          <t>Electrical and firmware integration.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Printer and consumables function to spec for 80,000 pages under standard test conditions.</t>
+          <t>Wi-Fi module is operational and passes connectivity and compliance tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1671,46 +1671,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>FW Dune and Gauss4.xx Security Integration</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID for Magellan with increased tank size; no change to Marconi-HI ADF.</t>
+          <t>Integrate FW Dune and Gauss4.xx security features into Magellan printer (hardware and firmware).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To support higher ink capacity while maintaining design identity.</t>
+          <t>To ensure security compliance and protect user data.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Design, Product Management, Manufacturing</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tank design update, compatibility with Reddington ID.</t>
+          <t>Firmware and hardware integration, compliance testing.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tank size increased as per spec, Reddington ID is maintained, and ADF unchanged.</t>
+          <t>FW Dune and Gauss4.xx security features are operational and pass security validation tests.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1721,22 +1721,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification</t>
+          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
+          <t>Magellan must support business models for Consumer, SMB, and Enterprise segments, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To comply with environmental regulations and market requirements.</t>
+          <t>To maximize market reach and adapt to diverse customer needs.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Marketing</t>
+          <t>Business, Sales, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Design and documentation for certification.</t>
+          <t>Service and solution development.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Printer is certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+          <t>Printer is offered in configurations and bundles supporting the specified segments and services.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1771,46 +1771,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with increased tank protrusion and optimize size.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into Magellan platform.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To ensure mechanical compatibility and optimize product footprint.</t>
+          <t>To enhance solution offering and address business customer requirements.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Design, Manufacturing, End Users</t>
+          <t>Business, R&amp;D, Product Management, Enterprise Customers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tray and tank design coordination.</t>
+          <t>Solution and software integration.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Trays fit and operate correctly with new tank design; printer passes mechanical fit and finish tests.</t>
+          <t>All listed solutions are functional and pass integration and user acceptance testing.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1821,46 +1821,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD display into the Magellan printer.</t>
+          <t>Provide client and driver support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To provide a modern and user-friendly interface.</t>
+          <t>To ensure broad compatibility and ease of use across platforms and customer environments.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Design</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Electrical and mechanical integration of display.</t>
+          <t>Driver and software development.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.3” CGD display is functional, passes UI and reliability testing.</t>
+          <t>All listed clients and drivers are available, tested, and documented for Magellan printer.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1871,172 +1871,172 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4-Tube Platform with New Tube Routing and Integration</t>
+          <t>Leverage Watt-LE/Marconi Hi Mech + CISS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes for a 4-tube platform, with new tube routing and integration for Magellan.</t>
+          <t>Leverage Watt-LE/Marconi Hi mechanical platform and integrate with CISS for Magellan.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To improve ink delivery and system reliability.</t>
+          <t>To reduce development cost and time to market while incorporating CISS benefits.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tube design and routing, system integration.</t>
+          <t>Mechanical and system integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Four tubes are routed and integrated per design, system passes ink delivery and reliability tests.</t>
+          <t>Watt-LE/Marconi Hi Mech platform is used and CISS is integrated and passes system tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Schedule as Least Flexible Constraint</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Update service station for aerosol management with spit platform changes due to new tank.</t>
+          <t>Meet the schedule as the highest business constraint for Magellan program.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To ensure proper aerosol handling and maintain print quality.</t>
+          <t>To ensure timely market entry and competitive positioning.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>Business, Program Management, R&amp;D</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Service station and tank design updates.</t>
+          <t>All critical path activities.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Service station manages aerosols effectively, verified by print quality and emissions testing.</t>
+          <t>All program milestones are met as per published schedule.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>SuperAmp PHA Life at 65K as Least Flexible Constraint</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
+          <t>SuperAmp PHA must achieve a life of at least 65,000 pages for Magellan.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To ensure reliable operation and print quality with new system configuration.</t>
+          <t>To ensure reliability and meet business constraints for consumable life.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tube and carriage design.</t>
+          <t>PHA design and testing.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Carriage operates within force and dynamic parameters with new tubes and weights in testing.</t>
+          <t>SuperAmp PHA is verified to last at least 65,000 pages in standard test cycles.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paper Path Durability for Increased Page Life</t>
+          <t>Warranty Life of 2 Years as Optimized Priority</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Enhance paper path to support increased page life of 80,000 pages.</t>
+          <t>Magellan printer must be warranted for 2 years or up to the page life goal, whichever comes first.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To ensure printer reliability over its extended life expectancy.</t>
+          <t>To align with market expectations and business priorities.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, End Users</t>
+          <t>Product Management, End Users, Sales</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paper path component selection and testing.</t>
+          <t>Component reliability, service policies.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paper path components show no significant wear after 80,000 pages in accelerated life testing.</t>
+          <t>Product warranty is offered for 2 years or 80,000 pages, with support processes in place.</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2064,79 +2064,79 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part Post-80k Life</t>
+          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Provide ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
+          <t>Magellan printer must achieve throughput of 25 ppm (mono) and 20 ppm (color) for PDL SKU.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To extend printer service life and reduce total cost of ownership.</t>
+          <t>To meet performance requirements and market competitiveness.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Service, End Users, Support</t>
+          <t>End Users, Product Management, Sales</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Part design and service documentation.</t>
+          <t>Print engine and firmware performance.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ink maintenance part can be replaced at service centers post-80k life, verified by service procedures.</t>
+          <t>Printer achieves 25 ppm mono and 20 ppm color in PDL SKU during standard performance tests.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>140ml Black Bottles and New CMY Bottle Sizes</t>
+          <t>Serviceability of Maintenance Box as Optimized Priority</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Provide 140ml Black bottles and new capacity CMY bottles for Magellan printer.</t>
+          <t>Design Magellan printer for easy servicing of the maintenance box.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To support higher print volumes and reduce refill frequency.</t>
+          <t>To improve post-sale support and reduce downtime.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2146,17 +2146,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Supply Chain</t>
+          <t>Service, End Users, Support</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bottle design and supply chain readiness.</t>
+          <t>Mechanical design for access and replacement.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>140ml Black bottles and new CMY bottles are available and compatible with Magellan system.</t>
+          <t>Maintenance box can be serviced or replaced within 10 minutes by service personnel.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2164,279 +2164,279 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>SMB Solution Support as Optimized Priority</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Implement a new IDS startup algorithm and air management system for Magellan.</t>
+          <t>Magellan must support SMB solutions as an optimized business priority.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To optimize ink delivery system performance and startup reliability.</t>
+          <t>To ensure the printer meets the needs of small and medium business customers.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>SMB Customers, Sales, Product Management</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>IDS design and firmware development.</t>
+          <t>Solution integration and support.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>IDS startup algorithm passes performance and reliability tests; air management is verified in system tests.</t>
+          <t>SMB solutions are available and functional for Magellan printer.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>PaaS Schedule as Optimized Priority</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Develop new servicing and startup algorithm for Magellan printer.</t>
+          <t>Ensure PaaS (Printing as a Service) is delivered according to schedule for Magellan.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To improve reliability and user experience during initial setup and servicing.</t>
+          <t>To support new business models and revenue streams.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Firmware development and integration.</t>
+          <t>PaaS development and integration.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Servicing and startup algorithm passes reliability and usability testing.</t>
+          <t>PaaS is available for Magellan as per published schedule and passes customer acceptance.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>Host 12K-CMYK as Flexible Priority</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Establish new print quality goals and depletion criteria to align with page yield definition for Magellan.</t>
+          <t>Provide support for hosting 12K-CMYK as a flexible business priority.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>To ensure print quality and accurate yield reporting.</t>
+          <t>To allow for future scalability and market adaptation.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Product Management, Quality, R&amp;D</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Print quality testing, documentation update.</t>
+          <t>System design for scalability.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Print quality meets new goals and depletion is defined and measured per updated criteria.</t>
+          <t>System design can accommodate 12K-CMYK hosting if required in future roadmap.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Trade Page 6K as Flexible Priority</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan printer.</t>
+          <t>Support trade page 6K as a flexible business priority.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>To leverage proven electronics and reduce development cost and risk.</t>
+          <t>To provide options for market-specific or promotional SKUs.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>Product Management, Sales</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Compatibility verification with Magellan platform.</t>
+          <t>SKU and configuration management.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>All reused components operate to spec in Magellan printer.</t>
+          <t>Trade page 6K option is available as a configurable SKU.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module into Magellan printer.</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>To provide wireless connectivity as per current standards.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Product Management</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Electrical and firmware integration.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Wi-Fi module is operational and passes connectivity and compliance tests.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FW Dune and Gauss4.xx Security Integration</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Integrate FW Dune and Gauss4.xx security features into Magellan printer (hardware and firmware).</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>To ensure security compliance and protect user data.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,47 +2446,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Firmware and hardware integration, compliance testing.</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>FW Dune and Gauss4.xx security features are operational and pass security validation tests.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Magellan must support business models for Consumer, SMB, and Enterprise segments, including PaaS and WorkFromHome/Flexworker services.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>To maximize market reach and adapt to diverse customer needs.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Business, Sales, Product Management</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Service and solution development.</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Printer is offered in configurations and bundles supporting the specified segments and services.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2514,29 +2514,29 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into Magellan platform.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>To enhance solution offering and address business customer requirements.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Business, R&amp;D, Product Management, Enterprise Customers</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Solution and software integration.</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>All listed solutions are functional and pass integration and user acceptance testing.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2564,79 +2564,79 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Provide client and driver support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>To ensure broad compatibility and ease of use across platforms and customer environments.</t>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Driver and software development.</t>
+          <t>Requires design of bottle and tank interface.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>All listed clients and drivers are available, tested, and documented for Magellan printer.</t>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Leverage Watt-LE/Marconi Hi Mech + CISS</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Leverage Watt-LE/Marconi Hi mechanical platform and integrate with CISS for Magellan.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>To reduce development cost and time to market while incorporating CISS benefits.</t>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2646,167 +2646,167 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mechanical and system integration.</t>
+          <t>Requires durability testing and warranty policy alignment.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Watt-LE/Marconi Hi Mech platform is used and CISS is integrated and passes system tests.</t>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Schedule as Least Flexible Constraint</t>
+          <t>Serviceability – PHA and MINK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Meet the schedule as the highest business constraint for Magellan program.</t>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>To ensure timely market entry and competitive positioning.</t>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Business, Program Management, R&amp;D</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>All critical path activities.</t>
+          <t>Requires design for replaceability and service documentation.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>All program milestones are met as per published schedule.</t>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K as Least Flexible Constraint</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must achieve a life of at least 65,000 pages for Magellan.</t>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>To ensure reliability and meet business constraints for consumable life.</t>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PHA design and testing.</t>
+          <t>Requires software development and integration with hardware.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SuperAmp PHA is verified to last at least 65,000 pages in standard test cycles.</t>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years as Optimized Priority</t>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Magellan printer must be warranted for 2 years or up to the page life goal, whichever comes first.</t>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>To align with market expectations and business priorities.</t>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Sales</t>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Component reliability, service policies.</t>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Product warranty is offered for 2 years or 80,000 pages, with support processes in place.</t>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2814,29 +2814,29 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Magellan printer must achieve throughput of 25 ppm (mono) and 20 ppm (color) for PDL SKU.</t>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>To meet performance requirements and market competitiveness.</t>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Sales</t>
+          <t>['Marketing', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Print engine and firmware performance.</t>
+          <t>Requires AI software and sensor integration.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Printer achieves 25 ppm mono and 20 ppm color in PDL SKU during standard performance tests.</t>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2864,99 +2864,99 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box as Optimized Priority</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Design Magellan printer for easy servicing of the maintenance box.</t>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>To improve post-sale support and reduce downtime.</t>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Service, End Users, Support</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Mechanical design for access and replacement.</t>
+          <t>Requires sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maintenance box can be serviced or replaced within 10 minutes by service personnel.</t>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SMB Solution Support as Optimized Priority</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Magellan must support SMB solutions as an optimized business priority.</t>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>To ensure the printer meets the needs of small and medium business customers.</t>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SMB Customers, Sales, Product Management</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Solution integration and support.</t>
+          <t>Requires app development and printer firmware support.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SMB solutions are available and functional for Magellan printer.</t>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -2964,157 +2964,157 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PaaS Schedule as Optimized Priority</t>
+          <t>PaaS Enablement</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ensure PaaS (Printing as a Service) is delivered according to schedule for Magellan.</t>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>To support new business models and revenue streams.</t>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PaaS development and integration.</t>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PaaS is available for Magellan as per published schedule and passes customer acceptance.</t>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK as Flexible Priority</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Provide support for hosting 12K-CMYK as a flexible business priority.</t>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>To allow for future scalability and market adaptation.</t>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>System design for scalability.</t>
+          <t>Requires secure data collection and privacy compliance.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>System design can accommodate 12K-CMYK hosting if required in future roadmap.</t>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trade Page 6K as Flexible Priority</t>
+          <t>Advanced Security and Compliance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Support trade page 6K as a flexible business priority.</t>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>To provide options for market-specific or promotional SKUs.</t>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Product Management, Sales</t>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SKU and configuration management.</t>
+          <t>Requires security features and regulatory review.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Trade page 6K option is available as a configurable SKU.</t>
+          <t>Product passes security and compliance audits for target markets.</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, inferred from multiple sections</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop NGB keyed bottles for the Magellan printer with 6,000-page yield for Black and CMY, and &gt;8,000-page size for CMY.</t>
+          <t>Develop new NGB keyed ink bottles that support 6,000 pages for Black and 6,000 pages for CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To ensure high page yield and compatibility with the new printer, reducing user intervention and supporting high-volume printing.</t>
+          <t>To increase ink supply efficiency and meet higher usage demands for SMB and enterprise customers.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Product Management, SMB &amp; Enterprise Customers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dependent on new bottle design and compatibility with existing ink system.</t>
+          <t>Requires compatibility with NOA-F, Magi/Nessie inks, and IDS system.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NGB bottles are available for Black and CMY; Black yields 6,000 pages, CMY bottles are &gt;8,000-page size, and bottles are keyed for system compatibility.</t>
+          <t>New bottles must achieve specified page yields in internal and customer testing; bottles must be keyed for correct installation.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -531,12 +531,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new NGB bottles provide spill-free reliability when used with the Magellan printer.</t>
+          <t>Ensure that the new NGB bottles provide spill-free operation during installation and use.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To improve user experience and minimize mess or ink wastage during refilling.</t>
+          <t>To reduce customer complaints and warranty claims related to ink spills.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,17 +546,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D</t>
+          <t>End Users, Customer Service, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires bottle and ink system integration.</t>
+          <t>Design of bottle and NOA-F interface.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No spills occur during bottle installation or removal in 100% of test cases across 100 cycles.</t>
+          <t>Less than 0.1% reported spill incidents in field testing and warranty period.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -581,36 +581,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate NOA-F with a metal foiled labyrinth and lid label; maintain current click on push-push and TDF mechanisms.</t>
+          <t>Integrate a metal foiled labyrinth and lid label into the NOA-F component, with no changes to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To enhance reliability and maintain established user experience features.</t>
+          <t>To improve reliability and traceability of the NOA-F component.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design update, compatibility with existing mechanisms.</t>
+          <t>Existing NOA-F design, push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F units include metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms, verified in production samples.</t>
+          <t>All NOA-F units must include metal foil labyrinth and lid label, verified by QA inspection.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie ink formulations without requiring ink reformulation for Magellan.</t>
+          <t>Reuse the existing SuperAmp Si PHA and Magi/Nessie pigment inks with no reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To reduce development time, leverage proven technology, and minimize risk.</t>
+          <t>To leverage proven components and reduce development time and cost.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,21 +646,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility verification with new printer system.</t>
+          <t>Compatibility with new bottle and tank design.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie ink operate within performance specs in the Magellan system with no reformulation required.</t>
+          <t>System passes all reliability and PQ tests using existing inks and PHA.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,17 +676,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>Reliability and IDS Characterization &amp; Modelling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NOA-F units must be available as service parts for warranty support.</t>
+          <t>Perform full reliability, WVTR, air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F EOL.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To ensure serviceability and maintain warranty commitments for customers.</t>
+          <t>To ensure robust performance and accurate modeling for maintenance and support planning.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,17 +696,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Supply chain and service logistics.</t>
+          <t>Access to prototypes and test data.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NOA-F service parts are available and supplied for warranty claims within standard SLA.</t>
+          <t>Comprehensive reports and models delivered and reviewed by R&amp;D and QA.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Ink Stability Modelling for Tank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 feature into the printer lid.</t>
+          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To support advanced features or security as per platform standards.</t>
+          <t>To predict and mitigate potential ink degradation and ensure consistent PQ.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,21 +746,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Product Management</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lid design update and platform integration.</t>
+          <t>Tank material and design, ink chemistry.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Acumen 6 feature is operational and tested on the production lid.</t>
+          <t>Modeling results reviewed and approved by R&amp;D; test results confirm predictions.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -776,37 +776,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Modify existing SA14 factory line for NOA-F, and add Magi ink cart and labelling tool in Orcus 5.</t>
+          <t>Provide NOA-F components as service parts for in-warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To enable efficient manufacturing of the new printer and consumables.</t>
+          <t>To enable field replacement and reduce turnaround time for warranty claims.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Service, Warranty, End Customers</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Capex approval, tool procurement, line reconfiguration.</t>
+          <t>Availability of NOA-F as separate SKU.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SA14 line is modified and operational for NOA-F; Magi ink cart and labelling tool are installed in Orcus 5.</t>
+          <t>NOA-F listed and available as a service part; documented in service manuals.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -826,41 +826,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Design Magellan printer to allow customer-replaceable PHA and NOA-F units.</t>
+          <t>Integrate Acumen 6 (presumed security/authentication feature) on the ink bottle lid.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To improve user serviceability and reduce support costs.</t>
+          <t>To enhance product security and prevent counterfeiting.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>End Users, Service, Support</t>
+          <t>R&amp;D, Security, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mechanical design for easy access and replacement.</t>
+          <t>Bottle lid design, Acumen 6 component availability.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Users can replace PHA and NOA-F without tools in under 5 minutes, verified by usability testing.</t>
+          <t>All lids feature Acumen 6; passes authentication tests.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Set new warranty page life goal for Magellan printer at 80,000 pages.</t>
+          <t>Modify existing SA14 line for NOA-F, and add Magi ink cartridge and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To meet market expectations for durability and reduce warranty claims.</t>
+          <t>To support new product configuration and ensure manufacturing readiness.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Product Management, Quality, End Users</t>
+          <t>Manufacturing, Operations, R&amp;D</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Component reliability, consumable life.</t>
+          <t>Existing line capacity, tool availability.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Printer and consumables function to spec for 80,000 pages under standard test conditions.</t>
+          <t>Line modifications completed and validated before pilot run.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -926,41 +926,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID for Magellan with increased tank size; no change to Marconi-HI ADF.</t>
+          <t>Design printer to allow customers to replace PHA and NOA-F components without professional service.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To support higher ink capacity while maintaining design identity.</t>
+          <t>To improve serviceability, reduce downtime, and enhance user experience.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Design, Product Management, Manufacturing</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tank design update, compatibility with Reddington ID.</t>
+          <t>Design of PHA/NOA-F modules, user documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tank size increased as per spec, Reddington ID is maintained, and ADF unchanged.</t>
+          <t>Replacement process validated by usability testing with non-technical users.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
+          <t>Ensure the printer platform supports a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To comply with environmental regulations and market requirements.</t>
+          <t>To meet the needs of high-usage environments and competitive warranty offerings.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,21 +996,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Marketing</t>
+          <t>End Users, Product Management, Service</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Design and documentation for certification.</t>
+          <t>Platform durability, consumable life.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printer is certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+          <t>Printer passes accelerated life testing for 80,000 pages without major failures.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>Support for Multiple Business Models (Consumer, SMB, Enterprise)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with increased tank protrusion and optimize size.</t>
+          <t>Enable the product to be configurable for Consumer, SMB, and Enterprise business models, including services like PaaS and WorkFromHome/Flexworker.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To ensure mechanical compatibility and optimize product footprint.</t>
+          <t>To address diverse market segments and maximize market coverage.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Design, Manufacturing, End Users</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tray and tank design coordination.</t>
+          <t>Feature configuration, software/firmware options.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Trays fit and operate correctly with new tank design; printer passes mechanical fit and finish tests.</t>
+          <t>Product configurations and service options documented and available for all target segments.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
         </is>
       </c>
     </row>
@@ -1076,41 +1076,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD display into the Magellan printer.</t>
+          <t>Ensure the product (PDL SKU) meets EPEAT3, LOT4, and Blue Angel environmental certification requirements.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To provide a modern and user-friendly interface.</t>
+          <t>To comply with environmental regulations and enhance marketability in eco-conscious regions.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Design</t>
+          <t>Regulatory, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Electrical and mechanical integration of display.</t>
+          <t>Design, materials selection, manufacturing process.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.3” CGD display is functional, passes UI and reliability testing.</t>
+          <t>Certifications obtained prior to product launch.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4-Tube Platform with New Tube Routing and Integration</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes for a 4-tube platform, with new tube routing and integration for Magellan.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To improve ink delivery and system reliability.</t>
+          <t>To ensure mechanical compatibility and minimize footprint.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,21 +1146,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Mechanical Engineering, Product Design, Manufacturing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tube design and routing, system integration.</t>
+          <t>Tank design, printer chassis.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Four tubes are routed and integrated per design, system passes ink delivery and reliability tests.</t>
+          <t>Prototypes pass fit and function tests with new tank design.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>4.3” CGD Touchscreen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Update service station for aerosol management with spit platform changes due to new tank.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) touchscreen for user interaction.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To ensure proper aerosol handling and maintain print quality.</t>
+          <t>To enhance user experience and align with modern product expectations.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,21 +1196,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>End Users, Product Management, UI/UX Design</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Service station and tank design updates.</t>
+          <t>Display sourcing, UI software.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Service station manages aerosols effectively, verified by print quality and emissions testing.</t>
+          <t>Touchscreen passes usability and reliability tests; meets brightness and resolution specs.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Leverage Sayan Sibstar Tubes with New Routing and Integration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
+          <t>Use Sayan Sibstar tubes with new tube routing and integration for the ink delivery system (4-tube platform).</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To ensure reliable operation and print quality with new system configuration.</t>
+          <t>To optimize ink flow and reliability while leveraging existing components.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,21 +1246,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tube and carriage design.</t>
+          <t>Tube compatibility, routing constraints.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Carriage operates within force and dynamic parameters with new tubes and weights in testing.</t>
+          <t>System passes flow and reliability tests with new routing.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1276,41 +1276,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paper Path Durability for Increased Page Life</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enhance paper path to support increased page life of 80,000 pages.</t>
+          <t>Implement aerosol management in the service station, with spit platform changes due to tank design.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To ensure printer reliability over its extended life expectancy.</t>
+          <t>To maintain print quality and prevent contamination from aerosolized ink.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, End Users</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Paper path component selection and testing.</t>
+          <t>Service station and tank design.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paper path components show no significant wear after 80,000 pages in accelerated life testing.</t>
+          <t>Aerosol levels measured and within acceptable limits during operation.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part Post-80k Life</t>
+          <t>Carriage Dynamic and Force Model with New Tube and Weights</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Provide ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
+          <t>Update the carriage dynamic and force model to account for new tube routing and additional weights.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To extend printer service life and reduce total cost of ownership.</t>
+          <t>To ensure reliable printhead movement and avoid mechanical failures.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,21 +1346,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service, End Users, Support</t>
+          <t>Mechanical Engineering, R&amp;D</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Part design and service documentation.</t>
+          <t>Tube and tank design, carriage design.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ink maintenance part can be replaced at service centers post-80k life, verified by service procedures.</t>
+          <t>Carriage system passes dynamic stress and reliability tests.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1376,41 +1376,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140ml Black Bottles and New CMY Bottle Sizes</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Provide 140ml Black bottles and new capacity CMY bottles for Magellan printer.</t>
+          <t>Design the paper path to support increased printer page life.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To support higher print volumes and reduce refill frequency.</t>
+          <t>To ensure reliable operation over the extended warranty period and page life goal.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Supply Chain</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bottle design and supply chain readiness.</t>
+          <t>Paper path materials and design.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>140ml Black bottles and new CMY bottles are available and compatible with Magellan system.</t>
+          <t>Paper path passes accelerated life and reliability testing for 80,000 pages.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Implement a new IDS startup algorithm and air management system for Magellan.</t>
+          <t>Design an ink maintenance component that is serviceable at the service center after 80,000 page life.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To optimize ink delivery system performance and startup reliability.</t>
+          <t>To extend printer usability and reduce total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IDS design and firmware development.</t>
+          <t>Component design, service documentation.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>IDS startup algorithm passes performance and reliability tests; air management is verified in system tests.</t>
+          <t>Part can be replaced at service center; process documented and validated.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1476,41 +1476,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Develop new servicing and startup algorithm for Magellan printer.</t>
+          <t>Implement a new make-break and FI (fluidic interconnect) connection in the Ink Delivery System, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To improve reliability and user experience during initial setup and servicing.</t>
+          <t>To improve fluidic reliability and prevent incorrect installation.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Firmware development and integration.</t>
+          <t>IDS and LEBI tank design.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Servicing and startup algorithm passes reliability and usability testing.</t>
+          <t>Connection passes reliability and usability tests; keying prevents misinstallation.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Establish new print quality goals and depletion criteria to align with page yield definition for Magellan.</t>
+          <t>Develop a new startup algorithm and air management system for the IDS.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To ensure print quality and accurate yield reporting.</t>
+          <t>To ensure reliable startup and prevent air bubbles in the ink system.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1546,21 +1546,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Product Management, Quality, R&amp;D</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Print quality testing, documentation update.</t>
+          <t>IDS design, firmware.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Print quality meets new goals and depletion is defined and measured per updated criteria.</t>
+          <t>Algorithm validated in lab and field testing; startup success rate &gt;99%.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1576,41 +1576,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan printer.</t>
+          <t>Implement new servicing and startup algorithms to support new hardware and consumables.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To leverage proven electronics and reduce development cost and risk.</t>
+          <t>To ensure optimal operation and user experience with new system components.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Compatibility verification with Magellan platform.</t>
+          <t>Firmware, hardware changes.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>All reused components operate to spec in Magellan printer.</t>
+          <t>Algorithms pass validation in simulated and real-world conditions.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1626,41 +1626,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>New Print Quality (PQ) Goals and Depletion to Meet Page Yield Definition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module into Magellan printer.</t>
+          <t>Define and validate new print quality goals and depletion algorithms to meet updated page yield definitions.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To provide wireless connectivity as per current standards.</t>
+          <t>To ensure customer satisfaction and compliance with page yield claims.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Product Management</t>
+          <t>R&amp;D, Product Management, Quality Assurance</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Electrical and firmware integration.</t>
+          <t>Firmware, ink system design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Wi-Fi module is operational and passes connectivity and compliance tests.</t>
+          <t>PQ and depletion metrics meet or exceed targets in internal and field testing.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1676,41 +1676,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FW Dune and Gauss4.xx Security Integration</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi Module, and Dune FW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Integrate FW Dune and Gauss4.xx security features into Magellan printer (hardware and firmware).</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware for the new platform.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To ensure security compliance and protect user data.</t>
+          <t>To reduce development time, cost, and risk by reusing proven hardware and software components.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Firmware and hardware integration, compliance testing.</t>
+          <t>Compatibility with new platform and features.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FW Dune and Gauss4.xx security features are operational and pass security validation tests.</t>
+          <t>Components function correctly in system integration and validation tests.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Magellan must support business models for Consumer, SMB, and Enterprise segments, including PaaS and WorkFromHome/Flexworker services.</t>
+          <t>Integrate Gauss4.xx hardware and firmware-based security features.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To maximize market reach and adapt to diverse customer needs.</t>
+          <t>To enhance product security and meet corporate security standards.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Business, Sales, Product Management</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Service and solution development.</t>
+          <t>HW/FW integration, security compliance.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Printer is offered in configurations and bundles supporting the specified segments and services.</t>
+          <t>Security features pass internal and external penetration tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support</t>
+          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into Magellan platform.</t>
+          <t>Ensure printer achieves print speeds of 25 ppm (pages per minute) for standard and 25/19 ppm for PDL.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To enhance solution offering and address business customer requirements.</t>
+          <t>To meet competitive benchmarks and customer expectations in target segments.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,21 +1796,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Business, R&amp;D, Product Management, Enterprise Customers</t>
+          <t>Product Management, End Users, Marketing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Solution and software integration.</t>
+          <t>Print engine design, firmware.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>All listed solutions are functional and pass integration and user acceptance testing.</t>
+          <t>Printer achieves specified speeds in standard and PDL tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Warranty Life of Pages, 2 Years</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Provide client and driver support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Support a warranty life of pages (as specified) for 2 years.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To ensure broad compatibility and ease of use across platforms and customer environments.</t>
+          <t>To align with market expectations and competitive offerings.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Driver and software development.</t>
+          <t>Consumable and hardware durability.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>All listed clients and drivers are available, tested, and documented for Magellan printer.</t>
+          <t>Warranty terms validated and supported by accelerated life testing.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
@@ -1876,41 +1876,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leverage Watt-LE/Marconi Hi Mech + CISS</t>
+          <t>Serviceability (Maintenance Box)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leverage Watt-LE/Marconi Hi mechanical platform and integrate with CISS for Magellan.</t>
+          <t>Design the maintenance box for easy serviceability, allowing for quick replacement or maintenance.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To reduce development cost and time to market while incorporating CISS benefits.</t>
+          <t>To reduce downtime and service costs for customers.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Service, End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mechanical and system integration.</t>
+          <t>Maintenance box design, documentation.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Watt-LE/Marconi Hi Mech platform is used and CISS is integrated and passes system tests.</t>
+          <t>Box can be serviced in under 10 minutes by trained personnel.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1926,41 +1926,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Schedule as Least Flexible Constraint</t>
+          <t>SMB Solution Support</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Meet the schedule as the highest business constraint for Magellan program.</t>
+          <t>Include features and manageability tailored for SMB customers, such as SMB portal and management tools.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To ensure timely market entry and competitive positioning.</t>
+          <t>To increase adoption in the SMB segment and provide value-added services.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Business, Program Management, R&amp;D</t>
+          <t>SMB Customers, Product Management, IT Admins</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>All critical path activities.</t>
+          <t>Software features, portal integration.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>All program milestones are met as per published schedule.</t>
+          <t>SMB management features available and tested with pilot SMB customers.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1976,41 +1976,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K as Least Flexible Constraint</t>
+          <t>PaaS (Printing as a Service) Enablement</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must achieve a life of at least 65,000 pages for Magellan.</t>
+          <t>Enable the product for Printing as a Service (PaaS) business model, including necessary software and service hooks.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To ensure reliability and meet business constraints for consumable life.</t>
+          <t>To support new business models and recurring revenue streams.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Product Management, Service, Marketing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PHA design and testing.</t>
+          <t>Software/firmware integration, service backend.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SuperAmp PHA is verified to last at least 65,000 pages in standard test cycles.</t>
+          <t>PaaS features enabled and validated in end-to-end testing.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2026,41 +2026,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years as Optimized Priority</t>
+          <t>Scan Solution Integration</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Magellan printer must be warranted for 2 years or up to the page life goal, whichever comes first.</t>
+          <t>Integrate scan solutions for consumer, SMB, and enterprise use cases.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To align with market expectations and business priorities.</t>
+          <t>To provide a complete multifunction device and address diverse customer needs.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Sales</t>
+          <t>End Users, Product Management, SMB/Enterprise IT</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Component reliability, service policies.</t>
+          <t>Scanner hardware, software integration.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Product warranty is offered for 2 years or 80,000 pages, with support processes in place.</t>
+          <t>Scanning functions validated across all target segments and use cases.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2076,41 +2076,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
+          <t>Enterprise Support: WJA, HPSM, JAM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Magellan printer must achieve throughput of 25 ppm (mono) and 20 ppm (color) for PDL SKU.</t>
+          <t>Support for enterprise management tools: Web Jetadmin (WJA), HP Smart Management (HPSM), and JAM.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To meet performance requirements and market competitiveness.</t>
+          <t>To enable enterprise customers to manage and monitor devices at scale.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Sales</t>
+          <t>Enterprise IT, Product Management</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Print engine and firmware performance.</t>
+          <t>Software integration, compatibility testing.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Printer achieves 25 ppm mono and 20 ppm color in PDL SKU during standard performance tests.</t>
+          <t>Device is discoverable and manageable in WJA, HPSM, and JAM environments.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2126,41 +2126,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box as Optimized Priority</t>
+          <t>Client &amp; Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Design Magellan printer for easy servicing of the maintenance box.</t>
+          <t>Ensure compatibility and support for a range of client and driver solutions: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To improve post-sale support and reduce downtime.</t>
+          <t>To maximize compatibility and ease of deployment for all customer segments.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Service, End Users, Support</t>
+          <t>End Users, IT Admins, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mechanical design for access and replacement.</t>
+          <t>Driver development, certification.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maintenance box can be serviced or replaced within 10 minutes by service personnel.</t>
+          <t>All drivers and client solutions tested and available at launch.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2171,22 +2171,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SMB Solution Support as Optimized Priority</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Magellan must support SMB solutions as an optimized business priority.</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To ensure the printer meets the needs of small and medium business customers.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2196,47 +2196,47 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SMB Customers, Sales, Product Management</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Solution integration and support.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SMB solutions are available and functional for Magellan printer.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PaaS Schedule as Optimized Priority</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ensure PaaS (Printing as a Service) is delivered according to schedule for Magellan.</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To support new business models and revenue streams.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,167 +2246,167 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PaaS development and integration.</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PaaS is available for Magellan as per published schedule and passes customer acceptance.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK as Flexible Priority</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Provide support for hosting 12K-CMYK as a flexible business priority.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>To allow for future scalability and market adaptation.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>System design for scalability.</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>System design can accommodate 12K-CMYK hosting if required in future roadmap.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trade Page 6K as Flexible Priority</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Support trade page 6K as a flexible business priority.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>To provide options for market-specific or promotional SKUs.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Product Management, Sales</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SKU and configuration management.</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Trade page 6K option is available as a configurable SKU.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Requires design of bottle and tank interface.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2414,29 +2414,29 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,67 +2446,67 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Requires durability testing and warranty policy alignment.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Serviceability – PHA and MINK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>Requires design for replaceability and service documentation.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2514,53 +2514,53 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>Requires software development and integration with hardware.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2571,22 +2571,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2596,21 +2596,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2621,22 +2621,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2646,97 +2646,97 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>Requires AI software and sensor integration.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>Requires sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2746,47 +2746,47 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires software development and integration with hardware.</t>
+          <t>Requires app development and printer firmware support.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+          <t>PaaS Enablement</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2796,67 +2796,67 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Requires AI software and sensor integration.</t>
+          <t>Requires secure data collection and privacy compliance.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2864,29 +2864,29 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Advanced Security and Compliance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2896,223 +2896,23 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
+          <t>Requires security features and regulatory review.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+          <t>Product passes security and compliance audits for target markets.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['GXD', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Requires app development and printer firmware support.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>PaaS Enablement</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>['Marketing', 'BA']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Requires secure data collection and privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Advanced Security and Compliance</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Requires security features and regulatory review.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Product passes security and compliance audits for target markets.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J54" t="inlineStr">
         <is>
           <t>Magellan MRD, inferred from multiple sections</t>
         </is>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles that support 6,000 pages for Black and 6,000 pages for CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size supporting &gt;8K pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase ink supply efficiency and meet higher usage demands for SMB and enterprise customers.</t>
+          <t>To increase consumables’ page yield, reduce frequency of replacements, and stay competitive in the CISS market segment.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,21 +496,21 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, SMB &amp; Enterprise Customers</t>
+          <t>R&amp;D, Product Management, Supply Chain, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with NOA-F, Magi/Nessie inks, and IDS system.</t>
+          <t>Requires compatibility with existing and new printer hardware; dependent on ink stability modeling.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New bottles must achieve specified page yields in internal and customer testing; bottles must be keyed for correct installation.</t>
+          <t>Bottles are developed and validated to deliver at least 6,000 pages for Black and CMY, with CMY bottle physically sized for &gt;8,000 pages, verified via print testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Bottle Reliability</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure that the new NGB bottles provide spill-free operation during installation and use.</t>
+          <t>Design and implement a spill-free mechanism for the new ink bottles to minimize ink spillage during user handling and refilling.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To reduce customer complaints and warranty claims related to ink spills.</t>
+          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service claims.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,21 +546,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Customer Service, R&amp;D</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Design of bottle and NOA-F interface.</t>
+          <t>Dependent on bottle and tank interface design.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Less than 0.1% reported spill incidents in field testing and warranty period.</t>
+          <t>Spill-free performance is demonstrated in at least 99% of refilling operations during testing.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -581,32 +581,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate a metal foiled labyrinth and lid label into the NOA-F component, with no changes to click-on push-push and TDF mechanisms.</t>
+          <t>Introduce NOA-F (non-ozone air filter) with a metal foiled labyrinth and lid label, while maintaining compatibility with existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To improve reliability and traceability of the NOA-F component.</t>
+          <t>Enhances air management and supports reliability requirements for the new platform.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Existing NOA-F design, push-push and TDF mechanisms.</t>
+          <t>Requires redesign of NOA-F and alignment with current assembly processes.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All NOA-F units must include metal foil labyrinth and lid label, verified by QA inspection.</t>
+          <t>NOA-F passes air management and reliability qualification tests; is compatible with push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks</t>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse the existing SuperAmp Si PHA and Magi/Nessie pigment inks with no reformulation.</t>
+          <t>Reuse existing Superamp Si PHA and Magi/Nessie pigment inks, with no reformulation required.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To leverage proven components and reduce development time and cost.</t>
+          <t>Reduces R&amp;D investment, speeds time to market, and leverages proven components.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,21 +646,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and tank design.</t>
+          <t>Compatibility with new bottle and tank design must be confirmed.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>System passes all reliability and PQ tests using existing inks and PHA.</t>
+          <t>Superamp Si PHA and Magi/Nessie inks function as expected in new system without reformulation.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,17 +676,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and IDS Characterization &amp; Modelling</t>
+          <t>Reliability and Characterization Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Perform full reliability, WVTR, air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F EOL.</t>
+          <t>Perform detailed reliability, WVTR (water vapor transmission rate), air gain, flow rate, and IDS (ink delivery system) characterization and modeling, including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To ensure robust performance and accurate modeling for maintenance and support planning.</t>
+          <t>Ensures robust performance and longevity under various operating conditions.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,21 +696,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Access to prototypes and test data.</t>
+          <t>Requires test hardware and analytics support.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Comprehensive reports and models delivered and reviewed by R&amp;D and QA.</t>
+          <t>Comprehensive modeling reports delivered; system meets all reliability targets under defined conditions.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -726,41 +726,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modelling for Tank</t>
+          <t>Ink Stability Modeling for Tank Impact and Print Quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
+          <t>Model ink stability in the tank and its impact on print quality (PQ) across product lifetime.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To predict and mitigate potential ink degradation and ensure consistent PQ.</t>
+          <t>Critical to ensure consistent print quality and minimize maintenance issues.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tank material and design, ink chemistry.</t>
+          <t>Requires data from ink and tank interaction studies.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Modeling results reviewed and approved by R&amp;D; test results confirm predictions.</t>
+          <t>Ink stability confirmed through simulation and empirical testing; print quality remains within spec for target page yield.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F components as service parts for in-warranty support.</t>
+          <t>Provide NOA-F as serviceable parts for warranty support, enabling replacement during the warranty period.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To enable field replacement and reduce turnaround time for warranty claims.</t>
+          <t>Improves serviceability and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,21 +796,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Customers</t>
+          <t>Service, End Users, Warranty Team</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Availability of NOA-F as separate SKU.</t>
+          <t>Requires logistics planning for spare part distribution.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F listed and available as a service part; documented in service manuals.</t>
+          <t>NOA-F parts are available as service spares and can be replaced in field within warranty period.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -831,12 +831,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (presumed security/authentication feature) on the ink bottle lid.</t>
+          <t>Integrate Acumen 6 (likely a security or authentication feature) on the ink bottle lid.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To enhance product security and prevent counterfeiting.</t>
+          <t>Enhances security and traceability of consumables.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,21 +846,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>Security, R&amp;D, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bottle lid design, Acumen 6 component availability.</t>
+          <t>Requires integration with lid manufacturing and supply chain systems.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>All lids feature Acumen 6; passes authentication tests.</t>
+          <t>All lids for the new bottles include Acumen 6; security features pass validation tests.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F, and add Magi ink cartridge and labelling tool in Orcus 5.</t>
+          <t>Modify existing SA14 line for NOA-F production; add Magi ink cart and labelling tool in Orcus 5; ensure assembly of PHA, Dry FI, USG, and push-push in printer factory.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To support new product configuration and ensure manufacturing readiness.</t>
+          <t>Factory readiness is essential for launch and scale-up.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, R&amp;D</t>
+          <t>Manufacturing, R&amp;D, Operations</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Existing line capacity, tool availability.</t>
+          <t>Capex approval and line reconfiguration scheduling.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Line modifications completed and validated before pilot run.</t>
+          <t>Production lines are modified and validated for new components prior to pilot build.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -926,17 +926,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>New Keyed Caps for Bottles</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design printer to allow customers to replace PHA and NOA-F components without professional service.</t>
+          <t>Develop molds for 1 to 4 new keyed caps, supporting differentiation and error-proofing in ink bottle usage.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To improve serviceability, reduce downtime, and enhance user experience.</t>
+          <t>Prevents cross-contamination and user error during refilling.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,21 +946,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Design of PHA/NOA-F modules, user documentation.</t>
+          <t>Capex for mold development, bottle design finalization.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Replacement process validated by usability testing with non-technical users.</t>
+          <t>Keyed caps are manufactured and validated for fit and function with corresponding bottles and tanks.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -976,17 +976,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>Leverage Watt LE/Marconi Hi Mech + CISS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure the printer platform supports a new warranty page life goal of 80,000 pages.</t>
+          <t>Utilize the Watt LE and Marconi Hi mechanical platforms, integrating with CISS (Continuous Ink Supply System).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To meet the needs of high-usage environments and competitive warranty offerings.</t>
+          <t>Accelerates development and leverages proven mechanical systems.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,21 +996,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Service</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platform durability, consumable life.</t>
+          <t>Compatibility with new ink delivery and tank systems.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printer passes accelerated life testing for 80,000 pages without major failures.</t>
+          <t>Mechanical integration validated and passes system-level tests.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1026,45 +1026,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support for Multiple Business Models (Consumer, SMB, Enterprise)</t>
+          <t>Print Speed Requirement: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Enable the product to be configurable for Consumer, SMB, and Enterprise business models, including services like PaaS and WorkFromHome/Flexworker.</t>
+          <t>Ensure the printer achieves a speed of 25 ppm (pages per minute) for standard, 20 ppm for color (PDL: 25/19ppm).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To address diverse market segments and maximize market coverage.</t>
+          <t>Meets market and segment expectations for performance.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>Product Management, Marketing, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Feature configuration, software/firmware options.</t>
+          <t>Dependent on hardware and firmware optimization.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product configurations and service options documented and available for all target segments.</t>
+          <t>Printer achieves specified speeds in standardized performance tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ensure the product (PDL SKU) meets EPEAT3, LOT4, and Blue Angel environmental certification requirements.</t>
+          <t>Design the system so that both PHA (printhead assembly) and NOA-F can be replaced by customers without service technician intervention.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To comply with environmental regulations and enhance marketability in eco-conscious regions.</t>
+          <t>Improves serviceability and reduces downtime for end users.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Design, materials selection, manufacturing process.</t>
+          <t>Requires user-friendly design and clear instructions.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Certifications obtained prior to product launch.</t>
+          <t>End users can replace PHA and NOA-F with no tools and within 5 minutes, as validated in usability studies.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1126,41 +1126,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>New Warranty Page Life Goal: 80k Pages</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize size.</t>
+          <t>Set new warranty page life target at 80,000 pages for the product.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To ensure mechanical compatibility and minimize footprint.</t>
+          <t>Aligns with competitive benchmarks and reduces total cost of ownership.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Product Design, Manufacturing</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tank design, printer chassis.</t>
+          <t>Requires robust design and component reliability.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Prototypes pass fit and function tests with new tank design.</t>
+          <t>Product passes accelerated life testing to 80,000 pages with no major failures.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.3” CGD Touchscreen</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS Support</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) touchscreen for user interaction.</t>
+          <t>Support a second SKU (Hi + Hi PDL) for Printer-as-a-Service (PaaS) offering.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To enhance user experience and align with modern product expectations.</t>
+          <t>Expands market reach and supports recurring revenue models.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,21 +1196,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UI/UX Design</t>
+          <t>Product Management, Sales, Service</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Display sourcing, UI software.</t>
+          <t>SKU definition and supply chain readiness.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Touchscreen passes usability and reliability tests; meets brightness and resolution specs.</t>
+          <t>SKU 2 is available for order and supported in all relevant systems.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1226,37 +1226,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes with New Routing and Integration</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Use Sayan Sibstar tubes with new tube routing and integration for the ink delivery system (4-tube platform).</t>
+          <t>Implement Reddington ID with an increased tank size; no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To optimize ink flow and reliability while leveraging existing components.</t>
+          <t>Accommodates higher ink capacity and supports increased page yield.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tube compatibility, routing constraints.</t>
+          <t>Tank design and integration with printer chassis.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>System passes flow and reliability tests with new routing.</t>
+          <t>Tank size increase validated; no impact on ADF functionality.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Implement aerosol management in the service station, with spit platform changes due to tank design.</t>
+          <t>Use EPS foam packaging for the product.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To maintain print quality and prevent contamination from aerosolized ink.</t>
+          <t>Protects product during shipping and meets regulatory/retailer requirements.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>Logistics, Manufacturing, Retail Partners</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Service station and tank design.</t>
+          <t>Packaging design and material sourcing.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aerosol levels measured and within acceptable limits during operation.</t>
+          <t>EPS packaging passes drop and vibration tests per HP standards.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1326,41 +1326,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with New Tube and Weights</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Update the carriage dynamic and force model to account for new tube routing and additional weights.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements (for PDL SKU).</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To ensure reliable printhead movement and avoid mechanical failures.</t>
+          <t>Required for market access and sustainability positioning.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D</t>
+          <t>Regulatory, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tube and tank design, carriage design.</t>
+          <t>Design and documentation compliance.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Carriage system passes dynamic stress and reliability tests.</t>
+          <t>Product certifications obtained for EPEAT3, LOT4, and Blue Angel.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Design the paper path to support increased printer page life.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To ensure reliable operation over the extended warranty period and page life goal.</t>
+          <t>Ensures smooth paper handling and compact form factor.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,21 +1396,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Paper path materials and design.</t>
+          <t>Tank and chassis design finalization.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paper path passes accelerated life and reliability testing for 80,000 pages.</t>
+          <t>Trays function reliably with new tank; pass all paper handling tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Design an ink maintenance component that is serviceable at the service center after 80,000 page life.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) into the printer.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To extend printer usability and reduce total cost of ownership for customers.</t>
+          <t>Improves user interface and usability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1446,21 +1446,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>End Users, Product Management, UI/UX Team</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Component design, service documentation.</t>
+          <t>Display sourcing and firmware integration.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Part can be replaced at service center; process documented and validated.</t>
+          <t>Display is functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>Platform with 4 Tubes and New Routing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Implement a new make-break and FI (fluidic interconnect) connection in the Ink Delivery System, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Leverage Sayan Sibstar tubes, implement new tube routing and integration for ink delivery system.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To improve fluidic reliability and prevent incorrect installation.</t>
+          <t>Supports increased ink flow and reliability with new tank system.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1496,21 +1496,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IDS and LEBI tank design.</t>
+          <t>Tube design and integration with tank and printhead.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Connection passes reliability and usability tests; keying prevents misinstallation.</t>
+          <t>Ink flow is consistent and reliable in all print modes; passes stress testing.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1526,22 +1526,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm and air management system for the IDS.</t>
+          <t>Implement aerosol management in the service station, with spit platform changes due to new tank system.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To ensure reliable startup and prevent air bubbles in the ink system.</t>
+          <t>Reduces contamination and maintenance frequency.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1551,16 +1551,16 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IDS design, firmware.</t>
+          <t>Service station and spit platform redesign.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Algorithm validated in lab and field testing; startup success rate &gt;99%.</t>
+          <t>Aerosol levels are within defined limits during operation; passes service interval targets.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithms to support new hardware and consumables.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To ensure optimal operation and user experience with new system components.</t>
+          <t>Ensures reliable carriage motion and print quality.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1596,21 +1596,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Firmware, hardware changes.</t>
+          <t>Final tube and tank design.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Algorithms pass validation in simulated and real-world conditions.</t>
+          <t>Carriage operates reliably under all load conditions; passes print quality tests.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion to Meet Page Yield Definition</t>
+          <t>Paper Path to Support Increased Page Life</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Define and validate new print quality goals and depletion algorithms to meet updated page yield definitions.</t>
+          <t>Redesign paper path to support increased warranty page life (80k pages).</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To ensure customer satisfaction and compliance with page yield claims.</t>
+          <t>Prevents wear and paper jams over extended use.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1646,21 +1646,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Quality Assurance</t>
+          <t>R&amp;D, Quality Assurance, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Firmware, ink system design.</t>
+          <t>Component selection and durability testing.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics meet or exceed targets in internal and field testing.</t>
+          <t>Paper path components last at least 80,000 pages with no major failures.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi Module, and Dune FW</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware for the new platform.</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80,000 pages.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To reduce development time, cost, and risk by reusing proven hardware and software components.</t>
+          <t>Supports extended product life and reduces total cost for customers.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1696,21 +1696,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Compatibility with new platform and features.</t>
+          <t>Maintenance part design and service documentation.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Components function correctly in system integration and validation tests.</t>
+          <t>Maintenance part can be replaced at service centers; process validated in service trials.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>SuperAmp PHA, NOA-F, Keyed Bottles, Magi and Nessie Inks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integrate Gauss4.xx hardware and firmware-based security features.</t>
+          <t>Ensure all listed components are available as supplies for the new printer.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To enhance product security and meet corporate security standards.</t>
+          <t>Supports full ecosystem and consumables strategy.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,21 +1746,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>Supply Chain, Product Management, End Users</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HW/FW integration, security compliance.</t>
+          <t>Supply chain readiness.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Security features pass internal and external penetration tests.</t>
+          <t>All supplies are available at launch and compatible with new system.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
+          <t>140ml K Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ensure printer achieves print speeds of 25 ppm (pages per minute) for standard and 25/19 ppm for PDL.</t>
+          <t>Introduce 140ml black bottles and new CMY bottle sizes (volume to be defined).</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To meet competitive benchmarks and customer expectations in target segments.</t>
+          <t>Aligns with increased page yield and customer expectations for fewer refills.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,21 +1796,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Marketing</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Print engine design, firmware.</t>
+          <t>Bottle design finalization and supply chain readiness.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Printer achieves specified speeds in standard and PDL tests.</t>
+          <t>140ml K and new CMY bottles are available and validated for use in the system.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Warranty Life of Pages, 2 Years</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Support a warranty life of pages (as specified) for 2 years.</t>
+          <t>Develop new make-break (connector) and FI (fluidic interface) connection for the ink delivery system (IDS).</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To align with market expectations and competitive offerings.</t>
+          <t>Ensures reliable and user-friendly connection/disconnection of ink system components.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Consumable and hardware durability.</t>
+          <t>IDS redesign and component sourcing.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Warranty terms validated and supported by accelerated life testing.</t>
+          <t>Connections pass reliability and ease-of-use tests; no leaks or failures in 99% of uses.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1876,37 +1876,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Serviceability (Maintenance Box)</t>
+          <t>Leverage LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Design the maintenance box for easy serviceability, allowing for quick replacement or maintenance.</t>
+          <t>Use LEBI ink-tank system with increased size, keying for error-proofing, and a single SHAID (security/authentication ID).</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To reduce downtime and service costs for customers.</t>
+          <t>Supports higher capacity, prevents user error, and secures consumables ecosystem.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Service, End Users, R&amp;D</t>
+          <t>R&amp;D, Security, Supply Chain</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Maintenance box design, documentation.</t>
+          <t>Tank and SHAID integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Box can be serviced in under 10 minutes by trained personnel.</t>
+          <t>Tank passes capacity, keying, and authentication tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1926,45 +1926,45 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SMB Solution Support</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Include features and manageability tailored for SMB customers, such as SMB portal and management tools.</t>
+          <t>Develop a new startup algorithm and air management system for the ink delivery system.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To increase adoption in the SMB segment and provide value-added services.</t>
+          <t>Ensures rapid and reliable printer startup and minimizes air-related print defects.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management, IT Admins</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Software features, portal integration.</t>
+          <t>IDS hardware and firmware development.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SMB management features available and tested with pilot SMB customers.</t>
+          <t>Startup and air management processes validated in system tests; no startup failures in 99% of cases.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PaaS (Printing as a Service) Enablement</t>
+          <t>Reuse Marconi Hi PDL for WS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Enable the product for Printing as a Service (PaaS) business model, including necessary software and service hooks.</t>
+          <t>Leverage Marconi Hi PDL for the WS (likely workflow solution or wireless system).</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To support new business models and recurring revenue streams.</t>
+          <t>Reduces development effort and leverages proven technology.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1996,25 +1996,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Product Management, Service, Marketing</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Software/firmware integration, service backend.</t>
+          <t>Compatibility with new platform.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PaaS features enabled and validated in end-to-end testing.</t>
+          <t>WS functions as required with Marconi Hi PDL integration.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2026,45 +2026,45 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Scan Solution Integration</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Integrate scan solutions for consumer, SMB, and enterprise use cases.</t>
+          <t>Develop new algorithms for servicing and startup to align with new hardware and consumables.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To provide a complete multifunction device and address diverse customer needs.</t>
+          <t>Ensures optimal operation and maintenance of the printer system.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>End Users, Product Management, SMB/Enterprise IT</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scanner hardware, software integration.</t>
+          <t>Hardware readiness and firmware development.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Scanning functions validated across all target segments and use cases.</t>
+          <t>Algorithms validated in system integration and field tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2076,45 +2076,45 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Enterprise Support: WJA, HPSM, JAM</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Support for enterprise management tools: Web Jetadmin (WJA), HP Smart Management (HPSM), and JAM.</t>
+          <t>Define new print quality (PQ) goals and depletion thresholds to align with increased page yield definition.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To enable enterprise customers to manage and monitor devices at scale.</t>
+          <t>Ensures consistent output quality throughout consumable life.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Enterprise IT, Product Management</t>
+          <t>R&amp;D, Quality Assurance, End Users</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Software integration, compatibility testing.</t>
+          <t>Consumables and system integration.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Device is discoverable and manageable in WJA, HPSM, and JAM environments.</t>
+          <t>PQ goals and depletion points validated in print testing across full consumable life.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2126,17 +2126,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Client &amp; Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ensure compatibility and support for a range of client and driver solutions: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics subsystem.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To maximize compatibility and ease of deployment for all customer segments.</t>
+          <t>Reduces cost and leverages proven reliability.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2146,47 +2146,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>End Users, IT Admins, Product Management</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Driver development, certification.</t>
+          <t>Compatibility with new platform and system requirements.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>All drivers and client solutions tested and available at launch.</t>
+          <t>Electronics subsystem passes all functional and reliability tests.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>Enables modern wireless printing features expected by customers.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2196,47 +2196,47 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>End Users, R&amp;D, IT</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Wi-Fi module sourcing and firmware integration.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>Wireless printing and connectivity pass all functional and interoperability tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>FW Dune Firmware Platform</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>Utilize FW Dune as the firmware platform for the new printer.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>Aligns with HP firmware strategy and streamlines development.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,47 +2246,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>R&amp;D, Firmware Team</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Firmware compatibility with new hardware.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>Printer boots and operates with FW Dune; passes all functional tests.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Gauss4.xx Security Hardware and Firmware</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Implement Gauss4.xx for security hardware and firmware.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>Enhances security to meet modern enterprise requirements.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,47 +2296,47 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>Security, IT, R&amp;D, Enterprise Customers</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>Security hardware integration and firmware readiness.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>Security features pass all validation and compliance tests.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Business Model: Consumer, SMB, and Enterprise Segments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Support business models for consumer, SMB, and enterprise segments, including PaaS and work-from-home/flexworker solutions.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>Expands addressable market and supports varied customer needs.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2346,97 +2346,97 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>SKU definition, services integration.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>Business models are supported in product launch and go-to-market plans.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>Solution and Services Integration</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>Meets enterprise and SMB requirements for manageability and workflow.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Enterprise Customers, SMBs, IT, Product Management</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>Solution software and hardware integration.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>All listed solutions are available and functional at launch.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Client and Driver Support</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>Ensures broad compatibility and ease of deployment in varied environments.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,117 +2446,117 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>IT, End Users, Product Management</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>Driver and client software readiness.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>All drivers and clients are available and functional at launch.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Warranty Life: 2 Years or 80k Pages</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Product must provide a warranty of 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>Aligns with business priorities and customer expectations.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>Reliability and durability of components.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>Warranty terms are met in field and lab testing.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+          <t>Design and implement a serviceable maintenance box to support easy maintenance and reduce downtime.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+          <t>Improves service experience and reduces cost of ownership.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires software development and integration with hardware.</t>
+          <t>Maintenance box design and integration.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+          <t>Maintenance box can be serviced or replaced by end users or service technicians within 5 minutes.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2564,299 +2564,299 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+          <t>SMB Solution Support</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+          <t>Provide solution features specifically for SMBs, such as manageability and workflow tools.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+          <t>Addresses unique needs of SMB customers and increases market share.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+          <t>SMB Customers, Product Management, Sales</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
+          <t>Solution software development and integration.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+          <t>SMB solution features are available and functional at launch.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>Host 12K-CMYK (Flexible Priority)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+          <t>Optionally support hosting 12,000-page CMYK bottles as a flexible feature.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+          <t>Provides future scalability and competitive differentiation.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Requires AI software and sensor integration.</t>
+          <t>Bottle and tank design readiness.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+          <t>12K-CMYK hosting is validated and available as an option if required.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Trade Page 6K (Flexible Priority)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+          <t>Optionally support trade page yield of 6,000 pages as a flexible feature.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+          <t>Allows for market-specific customization of consumable yields.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>Product Management, R&amp;D, Marketing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
+          <t>Consumables definition and regional requirements.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+          <t>6K trade page support available for relevant SKUs if needed.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires app development and printer firmware support.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PaaS Enablement</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Requires secure data collection and privacy compliance.</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2864,29 +2864,29 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Advanced Security and Compliance</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2896,23 +2896,573 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Requires security features and regulatory review.</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Product passes security and compliance audits for target markets.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I50" t="n">
         <v>0.9</v>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Keyed Bottles for Ink Refill</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Requires design of bottle and tank interface.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Requires durability testing and warranty policy alignment.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Serviceability – PHA and MINK</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Requires design for replaceability and service documentation.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'BA']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Requires software development and integration with hardware.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan Features</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Requires AI software and sensor integration.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Requires sourcing and manufacturing process changes.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>['GXD', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Requires app development and printer firmware support.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PaaS Enablement</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Requires secure data collection and privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Advanced Security and Compliance</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Requires security features and regulatory review.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Product passes security and compliance audits for target markets.</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>Magellan MRD, inferred from multiple sections</t>
         </is>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size supporting &gt;8K pages.</t>
+          <t>Implement new NGB keyed ink bottles with 6K Black and 6K CMY page yield, and ensure CMY bottles are available in sizes &gt;8K.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase consumables’ page yield, reduce frequency of replacements, and stay competitive in the CISS market segment.</t>
+          <t>To increase page yield and reduce frequency of ink replacement, supporting higher volume users and competitive positioning.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,21 +496,21 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Supply Chain, End Users</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with existing and new printer hardware; dependent on ink stability modeling.</t>
+          <t>Bottle design, IDS compatibility, tank size increase</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles are developed and validated to deliver at least 6,000 pages for Black and CMY, with CMY bottle physically sized for &gt;8,000 pages, verified via print testing.</t>
+          <t>Given new NGB bottles are installed, the system must recognize the keying and deliver 6,000 pages for Black and CMY; CMY bottles should be available in &gt;8K capacity.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Spill-Free Bottle Reliability</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design and implement a spill-free mechanism for the new ink bottles to minimize ink spillage during user handling and refilling.</t>
+          <t>Ensure that the new NGB bottles provide spill-free operation during installation and replacement.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service claims.</t>
+          <t>To improve user experience and reduce mess or damage from ink spills, a key differentiator in CISS market.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,17 +546,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>End Users, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dependent on bottle and tank interface design.</t>
+          <t>Bottle design, IDS integration</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Spill-free performance is demonstrated in at least 99% of refilling operations during testing.</t>
+          <t>When a user installs or replaces an ink bottle, there should be no ink spillage under normal use conditions.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -581,12 +581,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduce NOA-F (non-ozone air filter) with a metal foiled labyrinth and lid label, while maintaining compatibility with existing push-push and TDF mechanisms.</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and a lid label, without changing the click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances air management and supports reliability requirements for the new platform.</t>
+          <t>To enhance product security, ensure compatibility with existing mechanisms, and improve anti-counterfeiting.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,21 +596,21 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Security, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires redesign of NOA-F and alignment with current assembly processes.</t>
+          <t>NOA-F design, existing click-on and TDF mechanisms</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F passes air management and reliability qualification tests; is compatible with push-push and TDF mechanisms.</t>
+          <t>NOA-F must include a metal foiled labyrinth and lid label, and install using the same push-push and TDF mechanisms as current products.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse existing Superamp Si PHA and Magi/Nessie pigment inks, with no reformulation required.</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie pigment inks without any reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D investment, speeds time to market, and leverages proven components.</t>
+          <t>To leverage existing investments and proven technology, reducing R&amp;D costs and time to market.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and tank design must be confirmed.</t>
+          <t>Compatibility with new system design</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Superamp Si PHA and Magi/Nessie inks function as expected in new system without reformulation.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks are used as-is without reformulation in the Magellan system.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -676,17 +676,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and Characterization Modeling</t>
+          <t>Reliability and Performance Characterization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Perform detailed reliability, WVTR (water vapor transmission rate), air gain, flow rate, and IDS (ink delivery system) characterization and modeling, including startup and NOA-F end-of-life.</t>
+          <t>Characterize and model reliability, WVTR, air gain, flow rate, IDS performance, including startup and NOA-F end-of-life (EOL).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures robust performance and longevity under various operating conditions.</t>
+          <t>To ensure robust operation, meet performance targets, and support warranty claims.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires test hardware and analytics support.</t>
+          <t>IDS, NOA-F, ink system integration</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Comprehensive modeling reports delivered; system meets all reliability targets under defined conditions.</t>
+          <t>Documented models and test data for reliability, WVTR, air gain, flow rate, IDS, with startup and NOA-F EOL scenarios covered.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -726,22 +726,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling for Tank Impact and Print Quality</t>
+          <t>Ink Stability Modelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and its impact on print quality (PQ) across product lifetime.</t>
+          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Critical to ensure consistent print quality and minimize maintenance issues.</t>
+          <t>To ensure long-term print quality and reliability for high-yield systems.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires data from ink and tank interaction studies.</t>
+          <t>Ink, tank design</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ink stability confirmed through simulation and empirical testing; print quality remains within spec for target page yield.</t>
+          <t>Ink stability model and PQ impact report available for review.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -776,41 +776,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as serviceable parts for warranty support, enabling replacement during the warranty period.</t>
+          <t>Provide NOA-F as service parts for warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces total cost of ownership for customers.</t>
+          <t>To enable in-warranty replacement and maintenance, reducing downtime and improving customer satisfaction.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, End Users, Warranty Team</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires logistics planning for spare part distribution.</t>
+          <t>NOA-F supply chain</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F parts are available as service spares and can be replaced in field within warranty period.</t>
+          <t>NOA-F available as service part for all warranty claims within specified period.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -831,12 +831,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (likely a security or authentication feature) on the ink bottle lid.</t>
+          <t>Integrate Acumen 6 on the lid of the product.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enhances security and traceability of consumables.</t>
+          <t>To support product authentication, tracking, or advanced features as defined by Acumen 6.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,21 +846,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Supply Chain</t>
+          <t>Security, R&amp;D</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires integration with lid manufacturing and supply chain systems.</t>
+          <t>Lid design, Acumen 6 technology</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>All lids for the new bottles include Acumen 6; security features pass validation tests.</t>
+          <t>Acumen 6 feature is present and functional on the product lid.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Factory Line Modifications for NOA-F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F production; add Magi ink cart and labelling tool in Orcus 5; ensure assembly of PHA, Dry FI, USG, and push-push in printer factory.</t>
+          <t>Modify existing SA14 line to support NOA-F production.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Factory readiness is essential for launch and scale-up.</t>
+          <t>To ensure manufacturing readiness for new NOA-F features.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D, Operations</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Capex approval and line reconfiguration scheduling.</t>
+          <t>SA14 line, NOA-F design</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Production lines are modified and validated for new components prior to pilot build.</t>
+          <t>SA14 line is modified and validated for NOA-F production.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -926,17 +926,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New Keyed Caps for Bottles</t>
+          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop molds for 1 to 4 new keyed caps, supporting differentiation and error-proofing in ink bottle usage.</t>
+          <t>Equip Orcus 5 line with Magi ink cartridge and labelling tool to support new product.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Prevents cross-contamination and user error during refilling.</t>
+          <t>To enable assembly of new ink system and proper product labelling.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,21 +946,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Capex for mold development, bottle design finalization.</t>
+          <t>Orcus 5 line, Magi ink system</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Keyed caps are manufactured and validated for fit and function with corresponding bottles and tanks.</t>
+          <t>Orcus 5 line operational with Magi ink cart and labelling tool integrated.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -976,37 +976,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Leverage Watt LE/Marconi Hi Mech + CISS</t>
+          <t>Assemble PHA, Dry FI, USG, Push-Push in Printer Factory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Utilize the Watt LE and Marconi Hi mechanical platforms, integrating with CISS (Continuous Ink Supply System).</t>
+          <t>Ensure PHA, Dry FI, USG, and push-push mechanisms are assembled in the printer factory.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Accelerates development and leverages proven mechanical systems.</t>
+          <t>To streamline assembly and ensure quality control.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Compatibility with new ink delivery and tank systems.</t>
+          <t>Printer factory processes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mechanical integration validated and passes system-level tests.</t>
+          <t>All specified components are assembled in-printer at the factory.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Print Speed Requirement: 25/20ppm (PDL: 25/19ppm)</t>
+          <t>ISDO Capex for NOA-F and Ink Cart Tooling</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure the printer achieves a speed of 25 ppm (pages per minute) for standard, 20 ppm for color (PDL: 25/19ppm).</t>
+          <t>Allocate ISDO Capex for SA14 line (NOA-F), Magi and Nessie ink cart, labelling tool in Orcus 5, and mold for 1-4 new keyed caps.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Meets market and segment expectations for performance.</t>
+          <t>To fund necessary manufacturing upgrades for new product requirements.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,21 +1046,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, End Users</t>
+          <t>Finance, Manufacturing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dependent on hardware and firmware optimization.</t>
+          <t>Capex approval, tool design</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Printer achieves specified speeds in standardized performance tests.</t>
+          <t>Capex allocated and tools/molds procured for production.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Design the system so that both PHA (printhead assembly) and NOA-F can be replaced by customers without service technician intervention.</t>
+          <t>Design product to allow end-users to replace PHA and NOA-F components easily.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime for end users.</t>
+          <t>To improve serviceability and reduce downtime for customers.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires user-friendly design and clear instructions.</t>
+          <t>Component design, user documentation</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F with no tools and within 5 minutes, as validated in usability studies.</t>
+          <t>End-users can replace PHA and NOA-F without special tools, as validated by usability testing.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal: 80k Pages</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Set new warranty page life target at 80,000 pages for the product.</t>
+          <t>Set new warranty page life goal to 80,000 pages for the product.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aligns with competitive benchmarks and reduces total cost of ownership.</t>
+          <t>To meet competitive warranty standards and support high-volume users.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,21 +1146,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>Product Management, End Users, Warranty</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Requires robust design and component reliability.</t>
+          <t>Component reliability, ink system durability</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product passes accelerated life testing to 80,000 pages with no major failures.</t>
+          <t>Product maintains print quality and reliability up to 80,000 pages under normal use.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS Support</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Support a second SKU (Hi + Hi PDL) for Printer-as-a-Service (PaaS) offering.</t>
+          <t>Adopt Reddington ID with an increase in tank size, but no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Expands market reach and supports recurring revenue models.</t>
+          <t>To accommodate higher ink volumes while maintaining product identity.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,21 +1196,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Service</t>
+          <t>Design, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SKU definition and supply chain readiness.</t>
+          <t>Tank design, Reddington ID guidelines</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SKU 2 is available for order and supported in all relevant systems.</t>
+          <t>Product design includes increased tank size as per Reddington ID, with ADF unchanged.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1226,41 +1226,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Implement Reddington ID with an increased tank size; no change to Marconi-HI ADF.</t>
+          <t>Use EPS foam for product packaging.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Accommodates higher ink capacity and supports increased page yield.</t>
+          <t>To protect the product during shipping and handling.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Logistics, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tank design and integration with printer chassis.</t>
+          <t>Packaging design</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tank size increase validated; no impact on ADF functionality.</t>
+          <t>All shipped units use EPS foam packaging, validated by drop/impact tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1276,41 +1276,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for the product.</t>
+          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel (for PDL SKU) environmental standards.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Protects product during shipping and meets regulatory/retailer requirements.</t>
+          <t>To meet regulatory and market requirements for eco-friendly products.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing, Retail Partners</t>
+          <t>Compliance, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Packaging design and material sourcing.</t>
+          <t>Product design, certification processes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>EPS packaging passes drop and vibration tests per HP standards.</t>
+          <t>Product is certified as compliant with EPEAT3, LOT4, and Blue Angel for applicable SKUs.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1326,37 +1326,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements (for PDL SKU).</t>
+          <t>Redesign input and output trays to align with the new tank protrusion.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Required for market access and sustainability positioning.</t>
+          <t>To ensure mechanical compatibility and user convenience with larger tanks.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>Design, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Design and documentation compliance.</t>
+          <t>Tank design, tray mechanisms</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Product certifications obtained for EPEAT3, LOT4, and Blue Angel.</t>
+          <t>Trays function properly and accommodate the tank protrusion without interference.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1376,37 +1376,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize size.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures smooth paper handling and compact form factor.</t>
+          <t>To enhance user interface and experience with a larger, clearer display.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>End Users, Product Management, Design</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tank and chassis design finalization.</t>
+          <t>Display sourcing, UI design</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Trays function reliably with new tank; pass all paper handling tests.</t>
+          <t>Product includes a 4.3” CGD that passes usability and readability tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1426,41 +1426,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Leverage Sayan Sibstar Tubes with New Routing and Integration</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) into the printer.</t>
+          <t>Use Sayan Sibstar tubes and implement new tube routing and integration in the platform (4 tubes).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Improves user interface and usability.</t>
+          <t>To improve ink delivery and system reliability in the new tank design.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UI/UX Team</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Display sourcing and firmware integration.</t>
+          <t>Tube sourcing, platform design</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Display is functional and passes usability and reliability tests.</t>
+          <t>Product uses specified tubes with validated routing and integration.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1476,41 +1476,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Platform with 4 Tubes and New Routing</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes, implement new tube routing and integration for ink delivery system.</t>
+          <t>Update service station for improved aerosol management, accommodating changes due to the new tank.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Supports increased ink flow and reliability with new tank system.</t>
+          <t>To maintain clean operation and prolong service station life.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tube design and integration with tank and printhead.</t>
+          <t>Service station design, tank design</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ink flow is consistent and reliable in all print modes; passes stress testing.</t>
+          <t>Service station manages aerosols effectively in all operational modes.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Implement aerosol management in the service station, with spit platform changes due to new tank system.</t>
+          <t>Update carriage dynamic and force models to account for tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Reduces contamination and maintenance frequency.</t>
+          <t>To ensure reliable printhead movement and avoid mechanical failures.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Service station and spit platform redesign.</t>
+          <t>Tube integration, carriage design</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Aerosol levels are within defined limits during operation; passes service interval targets.</t>
+          <t>Carriage operates within force and speed tolerances with updated tube and weight configuration.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Paper Path to Support Increased Page Life</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Redesign paper path to support increased page life (80k pages).</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures reliable carriage motion and print quality.</t>
+          <t>To ensure durability and reliability for higher duty cycles.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Final tube and tank design.</t>
+          <t>Paper path design, page life goal</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Carriage operates reliably under all load conditions; passes print quality tests.</t>
+          <t>Paper path components maintain functionality for at least 80,000 pages.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1626,41 +1626,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paper Path to Support Increased Page Life</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased warranty page life (80k pages).</t>
+          <t>Design the ink maintenance component as a serviceable part for replacement after 80,000 pages (service center).</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Prevents wear and paper jams over extended use.</t>
+          <t>To extend product life and maintain print quality beyond warranty period.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, End Users</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Component selection and durability testing.</t>
+          <t>Ink maintenance component design, service documentation</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paper path components last at least 80,000 pages with no major failures.</t>
+          <t>Ink maintenance part can be replaced by service center after 80,000 pages.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1676,41 +1676,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>140ml K Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80,000 pages.</t>
+          <t>Introduce new 140ml Black (K) bottles and new capacity CMY bottles for the product.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Supports extended product life and reduces total cost for customers.</t>
+          <t>To support higher page yields and reduce refill frequency.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Maintenance part design and service documentation.</t>
+          <t>Bottle design, IDS compatibility</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maintenance part can be replaced at service centers; process validated in service trials.</t>
+          <t>Product supports 140ml K bottles and new CMY bottles as specified.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SuperAmp PHA, NOA-F, Keyed Bottles, Magi and Nessie Inks</t>
+          <t>IDS Make-Break and FI Connection Update</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ensure all listed components are available as supplies for the new printer.</t>
+          <t>Implement new make-break and FI connection for the IDS system, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Supports full ecosystem and consumables strategy.</t>
+          <t>To improve ink delivery, security, and compatibility with new bottle/tank system.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Supply Chain, Product Management, End Users</t>
+          <t>R&amp;D, Security, Manufacturing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Supply chain readiness.</t>
+          <t>IDS design, LEBI tank, SHAID integration</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>All supplies are available at launch and compatible with new system.</t>
+          <t>IDS system operates reliably with new connections and security features.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Introduce 140ml black bottles and new CMY bottle sizes (volume to be defined).</t>
+          <t>Develop a new IDS startup algorithm and air management process for the ink system.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aligns with increased page yield and customer expectations for fewer refills.</t>
+          <t>To ensure reliable startup and minimize air-related failures in the ink path.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,21 +1796,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bottle design finalization and supply chain readiness.</t>
+          <t>IDS system design</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>140ml K and new CMY bottles are available and validated for use in the system.</t>
+          <t>Startup algorithm and air management validated through reliability testing.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Develop new make-break (connector) and FI (fluidic interface) connection for the ink delivery system (IDS).</t>
+          <t>Set new print quality (PQ) goals and define depletion to align with page yield targets.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensures reliable and user-friendly connection/disconnection of ink system components.</t>
+          <t>To ensure print quality is maintained throughout the specified yield.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Product Management, Quality Assurance</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IDS redesign and component sourcing.</t>
+          <t>PQ testing, page yield definition</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Connections pass reliability and ease-of-use tests; no leaks or failures in 99% of uses.</t>
+          <t>Product maintains PQ within defined limits for full page yield.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1876,37 +1876,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Use LEBI ink-tank system with increased size, keying for error-proofing, and a single SHAID (security/authentication ID).</t>
+          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU components in the new product.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Supports higher capacity, prevents user error, and secures consumables ecosystem.</t>
+          <t>To reduce development cost and leverage proven hardware.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tank and SHAID integration.</t>
+          <t>Component compatibility</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tank passes capacity, keying, and authentication tests.</t>
+          <t>Product uses specified ASICs and PSU without modification.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1926,41 +1926,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm and air management system for the ink delivery system.</t>
+          <t>Integrate the Stingray Wi-Fi module into the product for wireless connectivity.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures rapid and reliable printer startup and minimizes air-related print defects.</t>
+          <t>To provide up-to-date wireless networking capability.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IDS hardware and firmware development.</t>
+          <t>Wi-Fi module sourcing, FW integration</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Startup and air management processes validated in system tests; no startup failures in 99% of cases.</t>
+          <t>Product passes Wi-Fi certification and user connectivity tests with Stingray module.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Reuse Marconi Hi PDL for WS</t>
+          <t>FW Dune Integration</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leverage Marconi Hi PDL for the WS (likely workflow solution or wireless system).</t>
+          <t>Use Dune firmware (FW) for the product platform.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Reduces development effort and leverages proven technology.</t>
+          <t>To unify firmware development and leverage existing features.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1996,21 +1996,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>Firmware Engineering, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Compatibility with new platform.</t>
+          <t>HW/FW compatibility</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WS functions as required with Marconi Hi PDL integration.</t>
+          <t>Product operates reliably with Dune FW and passes all FW validation tests.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2026,17 +2026,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Gauss4.xx Security Integration</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Develop new algorithms for servicing and startup to align with new hardware and consumables.</t>
+          <t>Integrate Gauss4.xx security features at both hardware and firmware levels.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ensures optimal operation and maintenance of the printer system.</t>
+          <t>To meet current security requirements and protect user data.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2046,21 +2046,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Security, IT, Product Management</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hardware readiness and firmware development.</t>
+          <t>HW/FW design, Gauss4.xx feature set</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Algorithms validated in system integration and field tests.</t>
+          <t>Product passes security certification and penetration testing with Gauss4.xx features enabled.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2076,17 +2076,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>Support for Consumer, SMB, and Enterprise Segments</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Define new print quality (PQ) goals and depletion thresholds to align with increased page yield definition.</t>
+          <t>Product must support business models and services for Consumer, SMB, and Enterprise customers.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ensures consistent output quality throughout consumable life.</t>
+          <t>To maximize market reach and address different customer needs.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2096,21 +2096,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, End Users</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Consumables and system integration.</t>
+          <t>Feature set, software integration</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PQ goals and depletion points validated in print testing across full consumable life.</t>
+          <t>Product SKUs and software/services available for all three segments.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2126,37 +2126,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Scan Solution Integration</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics subsystem.</t>
+          <t>Integrate scan solution for all supported business segments.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reduces cost and leverages proven reliability.</t>
+          <t>To provide a complete MFP (multi-function printer) offering.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Compatibility with new platform and system requirements.</t>
+          <t>Scanner hardware, software integration</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Electronics subsystem passes all functional and reliability tests.</t>
+          <t>Product includes scan functionality that meets segment requirements.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2176,41 +2176,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>SMB Manageability Features</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Include manageability features targeted at SMB customers.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Enables modern wireless printing features expected by customers.</t>
+          <t>To improve product appeal and ease of management for SMBs.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, IT</t>
+          <t>SMB Customers, Product Management</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Wi-Fi module sourcing and firmware integration.</t>
+          <t>Software, UI features</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Wireless printing and connectivity pass all functional and interoperability tests.</t>
+          <t>Product includes SMB management features as defined in requirements doc.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FW Dune Firmware Platform</t>
+          <t>Enterprise Support for WJA, HPSM, JAM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Utilize FW Dune as the firmware platform for the new printer.</t>
+          <t>Provide support for enterprise management solutions: Web Jetadmin (WJA), HP Smart Management (HPSM), and JAM.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aligns with HP firmware strategy and streamlines development.</t>
+          <t>To ensure seamless integration into enterprise IT environments.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,21 +2246,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware Team</t>
+          <t>Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Firmware compatibility with new hardware.</t>
+          <t>Software integration, certification</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Printer boots and operates with FW Dune; passes all functional tests.</t>
+          <t>Product passes integration and functionality tests with WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security Hardware and Firmware</t>
+          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx for security hardware and firmware.</t>
+          <t>Ensure product compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Enhances security to meet modern enterprise requirements.</t>
+          <t>To maximize compatibility and ease of use across platforms.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,21 +2296,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Security, IT, R&amp;D, Enterprise Customers</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Security hardware integration and firmware readiness.</t>
+          <t>Driver development, client integration</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Security features pass all validation and compliance tests.</t>
+          <t>Product installs and operates with all listed clients and drivers.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2326,17 +2326,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Business Model: Consumer, SMB, and Enterprise Segments</t>
+          <t>Leverage Watt-LE/Marconi-Hi Mech + CISS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Support business models for consumer, SMB, and enterprise segments, including PaaS and work-from-home/flexworker solutions.</t>
+          <t>Leverage existing Watt-LE/Marconi-Hi mechanical platform and CISS technology for product development.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Expands addressable market and supports varied customer needs.</t>
+          <t>To minimize development time and capitalize on proven architectures.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2346,21 +2346,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SKU definition, services integration.</t>
+          <t>Platform compatibility</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Business models are supported in product launch and go-to-market plans.</t>
+          <t>Product is built on specified mechanical and CISS platforms.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2376,17 +2376,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Solution and Services Integration</t>
+          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
+          <t>Product must achieve print speeds of 25/20 ppm (pages per minute), and for PDL, 25/19 ppm.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Meets enterprise and SMB requirements for manageability and workflow.</t>
+          <t>To meet market expectations for speed and competitiveness.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2396,21 +2396,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Enterprise Customers, SMBs, IT, Product Management</t>
+          <t>End Users, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Solution software and hardware integration.</t>
+          <t>Print engine design, PDL support</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>All listed solutions are available and functional at launch.</t>
+          <t>Product achieves specified speeds in standard test conditions.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2426,37 +2426,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Client and Driver Support</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Design the maintenance box for easy serviceability.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ensures broad compatibility and ease of deployment in varied environments.</t>
+          <t>To reduce service time and improve end-user experience.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Driver and client software readiness.</t>
+          <t>Maintenance box design</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>All drivers and clients are available and functional at launch.</t>
+          <t>Maintenance box can be serviced/replaced within defined time and tool constraints.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
@@ -2476,17 +2476,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Warranty Life: 2 Years or 80k Pages</t>
+          <t>Warranty Life: 2 Years</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Product must provide a warranty of 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Product must offer a warranty life of 2 years or the equivalent page count, whichever comes first.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Aligns with business priorities and customer expectations.</t>
+          <t>To align with market standards and provide customer assurance.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2496,21 +2496,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Product Management, End Users, Warranty</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Reliability and durability of components.</t>
+          <t>Component reliability, warranty policy</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Warranty terms are met in field and lab testing.</t>
+          <t>Product is covered under warranty for 2 years or up to 80,000 pages.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2526,17 +2526,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>SuperAmp PHA Life at 65K Pages</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Design and implement a serviceable maintenance box to support easy maintenance and reduce downtime.</t>
+          <t>SuperAmp PHA must be rated for a minimum life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Improves service experience and reduces cost of ownership.</t>
+          <t>To ensure reliability and reduce service interventions.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2546,21 +2546,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Maintenance box design and integration.</t>
+          <t>PHA design, reliability testing</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maintenance box can be serviced or replaced by end users or service technicians within 5 minutes.</t>
+          <t>SuperAmp PHA passes reliability tests for at least 65,000 pages.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2571,22 +2571,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SMB Solution Support</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Provide solution features specifically for SMBs, such as manageability and workflow tools.</t>
+          <t>Integrate AI-driven productivity and manageability solutions for printing and scanning workflows, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Addresses unique needs of SMB customers and increases market share.</t>
+          <t>Addresses the need for ease of use and efficiency for SMBs lacking dedicated IT teams; differentiates HP from competitors.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2596,197 +2596,197 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management, Sales</t>
+          <t>Marketing, R&amp;D, SMB Customers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Solution software development and integration.</t>
+          <t>Requires AI software integration; depends on consolidated SMB portal.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SMB solution features are available and functional at launch.</t>
+          <t>AI features are fully integrated and accessible via device and portal; user feedback confirms improved productivity and manageability.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK (Flexible Priority)</t>
+          <t>HP’s Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Optionally support hosting 12,000-page CMYK bottles as a flexible feature.</t>
+          <t>Deliver a cost-efficient color printing solution with the lowest TCO in HP’s SMB portfolio, including minimized intervention and consumable costs.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Provides future scalability and competitive differentiation.</t>
+          <t>SMBs are highly cost-sensitive and seek ROI; this is a core purchase driver.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>Marketing, Quality, SMB Customers</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bottle and tank design readiness.</t>
+          <t>Depends on tank technology, keyed bottles, and maintenance design.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12K-CMYK hosting is validated and available as an option if required.</t>
+          <t>Validated by internal TCO analysis and external benchmarks; published TCO is lower than competitors for target segment.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trade Page 6K (Flexible Priority)</t>
+          <t>Sustainable SMB Tank Printer (60% RCP)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Optionally support trade page yield of 6,000 pages as a flexible feature.</t>
+          <t>Design the printer to use at least 60% recycled content plastic (RCP), exceeding competitor benchmarks (Epson 30%).</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Allows for market-specific customization of consumable yields.</t>
+          <t>Sustainability is a key differentiator and increasingly demanded by customers and regulations.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>Prod Steward, Marketing, SMB Customers</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Consumables definition and regional requirements.</t>
+          <t>Material sourcing and manufacturing process adjustments.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6K trade page support available for relevant SKUs if needed.</t>
+          <t>Product BOM and manufacturing reports confirm 60% RCP; validated by third-party audit if required.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+          <t>Introduce a customer-replaceable maintenance box to minimize service intervention and downtime.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+          <t>Reduces maintenance burden for SMBs without IT staff; new feature for this segment.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>R&amp;D, Quality, SMB Customers</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Design and supply chain for replaceable parts; service documentation.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+          <t>End users can replace maintenance box without service call; instructional material is clear and effective.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal</t>
+          <t>Consolidated SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+          <t>Develop a unified portal for SMBs to manage multiple printers, access AI solutions, and monitor device status.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+          <t>SMBs need simple, centralized management due to limited IT resources.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
+          <t>R&amp;D, Marketing, BA, SMB Customers</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Requires backend portal development and printer firmware support.</t>
+          <t>Requires integration with AI solutions and device firmware.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+          <t>Portal is accessible, user-friendly, supports management of 6-15 devices, and integrates with AI features.</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2821,42 +2821,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure ease of use.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+          <t>Reduces user error and service issues, improving reliability for SMBs.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>Supplies Quality, R&amp;D, SMB Customers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
+          <t>Design of bottle and printer interface; supply chain for new bottles.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+          <t>Field testing shows error rate below 1% for incorrect refilling; positive user feedback.</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2864,29 +2864,29 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Warranty and Serviceability Model</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+          <t>Provide warranty coverage for 80k pages or 2 years (whichever is first), with customer-replaceable parts (PHA) and service center support (MINK) for out-of-warranty situations.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+          <t>Ensures reliability and lowers TCO for SMBs; aligns with business purchase expectations.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>Quality, Service, Marketing, SMB Customers</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Requires hardware redesign and documentation for end-user replacement.</t>
+          <t>Service documentation, supply of spare parts.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+          <t>Warranty policy is published; service procedures are documented and operational.</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -2921,22 +2921,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>PDL/PS Support and Speed Improvement</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+          <t>For PDL SKU, support PDL/PS and achieve print speeds of 25/20 ppm (improved from current 25/19).</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+          <t>Meets advanced SMB requirements for document processing and performance.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2946,21 +2946,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>R&amp;D, Marketing, SMB Customers</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Requires design of bottle and tank interface.</t>
+          <t>Firmware and hardware design; performance testing.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+          <t>PDL/PS support validated; print speeds meet or exceed targets in benchmark tests.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2971,46 +2971,46 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+          <t>Obtain Blue Angel environmental certification for PDL SKU.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+          <t>Meets regulatory and customer sustainability requirements, especially in specific markets.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>Tech Reg, Prod Steward, Marketing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Requires durability testing and warranty policy alignment.</t>
+          <t>Design and documentation for certification process.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
+          <t>Certification is awarded before product launch in relevant markets.</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3021,22 +3021,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Serviceability – PHA and MINK</t>
+          <t>Support for PaaS (Printing as a Service)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+          <t>Ensure printer and portal support integration with HP’s Printing as a Service (PaaS) offerings.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+          <t>Supports HP’s strategic goal for PaaS acceleration and coverage.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3046,47 +3046,47 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>BA, Marketing, R&amp;D, SMB Customers</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Requires design for replaceability and service documentation.</t>
+          <t>Portal and firmware development; business model alignment.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+          <t>Printer and portal are compatible with current and planned PaaS offerings.</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 6, 10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+          <t>Integrate advanced telemetry for real-time monitoring of device health, usage, and consumables.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+          <t>Enables proactive support and analytics for SMBs and HP service teams.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>R&amp;D Telemetry, Service, Marketing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Requires software development and integration with hardware.</t>
+          <t>Firmware development; portal integration.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+          <t>Telemetry data is accessible via portal; supports automated alerts and reporting.</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3114,29 +3114,29 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+          <t>Enable seamless mobile printing and printer management via the HP App.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+          <t>SMBs increasingly rely on mobile devices for business operations.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+          <t>Marketing, R&amp;D, SMB Customers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, compliance testing.</t>
+          <t>HP App compatibility and integration with device firmware.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+          <t>Mobile printing and management features are tested and validated with HP App.</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3164,307 +3164,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Perfect Print and Perfect Scan Features</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Requires AI software and sensor integration.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Requires sourcing and manufacturing process changes.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>['GXD', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Requires app development and printer firmware support.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
           <t>Magellan MRD, Page 9, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>PaaS Enablement</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>['Marketing', 'BA']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Requires integration with HP’s PaaS infrastructure.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>PaaS features available and functional for eligible SKUs at launch.</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Requires secure data collection and privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Advanced Security and Compliance</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Requires security features and regulatory review.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Product passes security and compliance audits for target markets.</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Magellan MRD, inferred from multiple sections</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,58 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>citation</t>
         </is>
       </c>
     </row>
@@ -481,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Implement new NGB keyed ink bottles with 6K Black and 6K CMY page yield, and ensure CMY bottles are available in sizes &gt;8K.</t>
+          <t>Develop new NGB keyed bottles with 6,000-page yield for Black and CMY, and a larger bottle size for CMY (&gt;8,000 pages).</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase page yield and reduce frequency of ink replacement, supporting higher volume users and competitive positioning.</t>
+          <t>To support higher printing volumes and reduce frequency of bottle replacement, improving user convenience and competitiveness in high-volume segments.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bottle design, IDS compatibility, tank size increase</t>
+          <t>Requires compatibility with existing ink system and printer hardware.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Given new NGB bottles are installed, the system must recognize the keying and deliver 6,000 pages for Black and CMY; CMY bottles should be available in &gt;8K capacity.</t>
+          <t>Printer accepts new NGB keyed bottles, Black and CMY yield meets or exceeds 6,000 pages, CMY bottle size supports &gt;8,000 pages as validated by yield tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -517,6 +522,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Bottle Reliability</t>
+          <t>Spill-Free Reliability in Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure that the new NGB bottles provide spill-free operation during installation and replacement.</t>
+          <t>Ensure the ink bottle and tank system achieves spill-free reliability during user handling and refilling.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To improve user experience and reduce mess or damage from ink spills, a key differentiator in CISS market.</t>
+          <t>Minimizes mess and potential damage, improving customer satisfaction and reducing support incidents.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,27 +552,28 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Quality Assurance</t>
+          <t>End Users, Support, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle design, IDS integration</t>
+          <t>Requires design of bottle interface and tank opening.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>When a user installs or replaces an ink bottle, there should be no ink spillage under normal use conditions.</t>
+          <t>No ink spills in 99% of user refill scenarios as demonstrated in usability and reliability testing.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -581,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate NOA-F with a metal foiled labyrinth and a lid label, without changing the click-on push-push and TDF mechanisms.</t>
+          <t>Integrate NOA-F (Next-Gen Output Assembly - Filter) featuring a metal foiled labyrinth and a lid label, with no change to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To enhance product security, ensure compatibility with existing mechanisms, and improve anti-counterfeiting.</t>
+          <t>Enhances filtration and identification, while maintaining user familiarity with existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,27 +603,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design, existing click-on and TDF mechanisms</t>
+          <t>Dependent on existing push-push and TDF design.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F must include a metal foiled labyrinth and lid label, and install using the same push-push and TDF mechanisms as current products.</t>
+          <t>NOA-F incorporates metal foiled labyrinth and lid label, and passes all functional and reliability tests without changes to click-on push-push and TDF.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -631,12 +639,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie pigment inks without any reformulation.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without ink reformulation for the Magellan printer.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To leverage existing investments and proven technology, reducing R&amp;D costs and time to market.</t>
+          <t>Reduces development time and cost, leveraging proven technologies.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,17 +654,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new system design</t>
+          <t>Requires compatibility validation with new system.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks are used as-is without reformulation in the Magellan system.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks function reliably in Magellan with no reformulation required.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -667,6 +675,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -676,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and Performance Characterization</t>
+          <t>Reliability, WVTR, Air Gain, Flow Rate, and IDS Characterization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Characterize and model reliability, WVTR, air gain, flow rate, IDS performance, including startup and NOA-F end-of-life (EOL).</t>
+          <t>Perform comprehensive characterization and modeling of reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and Ink Delivery System (IDS) including startup and NOA-F End-of-Life (EOL).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To ensure robust operation, meet performance targets, and support warranty claims.</t>
+          <t>Ensures robust, predictable printer operation and ink system performance throughout the product lifecycle.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -701,12 +710,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IDS, NOA-F, ink system integration</t>
+          <t>Requires test platform and simulation models.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Documented models and test data for reliability, WVTR, air gain, flow rate, IDS, with startup and NOA-F EOL scenarios covered.</t>
+          <t>Documented test reports and models showing all parameters within specified tolerances under expected use conditions.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -717,6 +726,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,17 +736,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modelling</t>
+          <t>Ink Stability Modeling for Tank and PQ Impact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
+          <t>Develop models for ink stability in the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To ensure long-term print quality and reliability for high-yield systems.</t>
+          <t>Prevents print defects and ensures consistent output over time.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,17 +756,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ink, tank design</t>
+          <t>Requires access to ink formulation data and tank environment parameters.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ink stability model and PQ impact report available for review.</t>
+          <t>Model predicts ink stability and PQ impact; test results confirm predictions within acceptable margins.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -767,6 +777,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -776,17 +787,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>NOA-F as Service Part in Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts for warranty support.</t>
+          <t>Make NOA-F available as a service part for warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To enable in-warranty replacement and maintenance, reducing downtime and improving customer satisfaction.</t>
+          <t>Enables efficient servicing and minimizes downtime for users under warranty.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,17 +807,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NOA-F supply chain</t>
+          <t>Requires service logistics and inventory planning.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F available as service part for all warranty claims within specified period.</t>
+          <t>NOA-F is listed and available as a service part in warranty system; service teams trained on replacement.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -817,6 +828,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -831,12 +843,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 on the lid of the product.</t>
+          <t>Implement Acumen 6 identification/technology on the bottle lid.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To support product authentication, tracking, or advanced features as defined by Acumen 6.</t>
+          <t>Improves traceability, anti-counterfeiting, or smart feature enablement.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,17 +858,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Security, R&amp;D</t>
+          <t>R&amp;D, Manufacturing, Security</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 technology</t>
+          <t>Requires integration with lid manufacturing process.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Acumen 6 feature is present and functional on the product lid.</t>
+          <t>Acumen 6 is present and functional on all bottle lids as verified in production samples.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -867,6 +879,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -876,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F</t>
+          <t>Modify SA14 Line for NOA-F and Add Magi Ink Cart &amp; Labelling Tool in Orcus 5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line to support NOA-F production.</t>
+          <t>Update factory configuration to modify the existing SA14 line for NOA-F and add Magi ink cartridge and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To ensure manufacturing readiness for new NOA-F features.</t>
+          <t>Supports new component integration and ensures manufacturing readiness.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -901,22 +914,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SA14 line, NOA-F design</t>
+          <t>Dependent on final NOA-F and Magi ink design.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA14 line is modified and validated for NOA-F production.</t>
+          <t>SA14 line and Orcus 5 updated, validated by successful pilot builds.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -926,17 +940,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Equip Orcus 5 line with Magi ink cartridge and labelling tool to support new product.</t>
+          <t>Design the printer to support customer-replaceable PHA (Printhead Assembly) and NOA-F components.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To enable assembly of new ink system and proper product labelling.</t>
+          <t>Improves serviceability and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,17 +960,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orcus 5 line, Magi ink system</t>
+          <t>Requires mechanical design enabling easy access and replacement.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Orcus 5 line operational with Magi ink cart and labelling tool integrated.</t>
+          <t>End users can replace PHA and NOA-F without tools, verified by usability testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -967,6 +981,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -976,47 +991,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Assemble PHA, Dry FI, USG, Push-Push in Printer Factory</t>
+          <t>New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure PHA, Dry FI, USG, and push-push mechanisms are assembled in the printer factory.</t>
+          <t>Set a new warranty page life target for the printer at 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To streamline assembly and ensure quality control.</t>
+          <t>Aligns with higher usage expectations and competitive offerings.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Printer factory processes</t>
+          <t>Requires validation of all components for 80k page life.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>All specified components are assembled in-printer at the factory.</t>
+          <t>Printer and key components meet or exceed 80,000 pages in accelerated life tests and warranty documentation reflects new target.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1026,37 +1042,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ISDO Capex for NOA-F and Ink Cart Tooling</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allocate ISDO Capex for SA14 line (NOA-F), Magi and Nessie ink cart, labelling tool in Orcus 5, and mold for 1-4 new keyed caps.</t>
+          <t>Adopt Reddington ID design with an increased tank size. No changes to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To fund necessary manufacturing upgrades for new product requirements.</t>
+          <t>Accommodates higher ink capacity for extended printing without increasing device footprint unnecessarily.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finance, Manufacturing</t>
+          <t>Design, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Capex approval, tool design</t>
+          <t>Dependent on tank and chassis design constraints.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Capex allocated and tools/molds procured for production.</t>
+          <t>Device incorporates larger tank as per new design, validated by fit, form, and function tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1067,6 +1083,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1076,17 +1093,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Design product to allow end-users to replace PHA and NOA-F components easily.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To improve serviceability and reduce downtime for customers.</t>
+          <t>Compliance with environmental and energy standards is required for market access and sustainability goals.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,17 +1113,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Compliance, Product Management, Sustainability</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Component design, user documentation</t>
+          <t>Requires certification process and documentation.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>End-users can replace PHA and NOA-F without special tools, as validated by usability testing.</t>
+          <t>Product passes all relevant certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1117,6 +1134,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1126,47 +1144,48 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Set new warranty page life goal to 80,000 pages for the product.</t>
+          <t>Redesign input and output trays to align with the new tank protrusion.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To meet competitive warranty standards and support high-volume users.</t>
+          <t>Ensures paper handling reliability and maintains device compactness despite larger tank.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Warranty</t>
+          <t>R&amp;D, Mechanical Design, Manufacturing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Component reliability, ink system durability</t>
+          <t>Dependent on final tank design and printer layout.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product maintains print quality and reliability up to 80,000 pages under normal use.</t>
+          <t>Trays operate smoothly and reliably with new tank design, confirmed by paper path and mechanical tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1176,17 +1195,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID with an increase in tank size, but no change to Marconi-HI ADF.</t>
+          <t>Integrate a 4.3-inch Color Graphic Display (CGD) as the main user interface.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To accommodate higher ink volumes while maintaining product identity.</t>
+          <t>Enhances user experience with a larger, clearer interface for settings and status.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,17 +1215,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Design, Product Management</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tank design, Reddington ID guidelines</t>
+          <t>Requires updated UI design and hardware integration.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Product design includes increased tank size as per Reddington ID, with ADF unchanged.</t>
+          <t>4.3” CGD is functional, passes usability and reliability tests, and supports all required UI features.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1217,6 +1236,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1226,17 +1246,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Use EPS foam for product packaging.</t>
+          <t>Utilize Sayan Sibstar tubes with a new routing and integration approach for ink delivery.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To protect the product during shipping and handling.</t>
+          <t>Improves ink flow reliability and supports new tank layout.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,17 +1266,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Packaging design</t>
+          <t>Dependent on tank and chassis design.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>All shipped units use EPS foam packaging, validated by drop/impact tests.</t>
+          <t>Tube routing supports reliable ink delivery and passes all system tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1267,6 +1287,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1276,47 +1297,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>Service Station Aerosol Management with Spit Platform Changes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel (for PDL SKU) environmental standards.</t>
+          <t>Update service station design for improved aerosol management due to tank changes and spit platform modifications.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To meet regulatory and market requirements for eco-friendly products.</t>
+          <t>Prevents contamination and maintains print quality with new ink/tank configuration.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Marketing</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Product design, certification processes</t>
+          <t>Requires validation with new tank and spit platform.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Product is certified as compliant with EPEAT3, LOT4, and Blue Angel for applicable SKUs.</t>
+          <t>Aerosol levels remain within safe limits during operation, as verified by environmental and reliability tests.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1326,17 +1348,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to align with the new tank protrusion.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased component weights.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To ensure mechanical compatibility and user convenience with larger tanks.</t>
+          <t>Ensures reliable printhead movement and system longevity with new mechanical configuration.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,27 +1368,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Design, Manufacturing, End Users</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tank design, tray mechanisms</t>
+          <t>Dependent on finalized component weights and tube layout.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Trays function properly and accommodate the tank protrusion without interference.</t>
+          <t>Carriage operates within specified force and speed limits, validated by dynamic testing.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1376,47 +1399,48 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
+          <t>Redesign paper path to reliably support the new 80,000-page life goal.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To enhance user interface and experience with a larger, clearer display.</t>
+          <t>Prevents jams and wear, ensuring consistent operation over extended product life.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Design</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Display sourcing, UI design</t>
+          <t>Dependent on new page life and component durability requirements.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Product includes a 4.3” CGD that passes usability and readability tests.</t>
+          <t>Paper path components show no significant wear or failure after 80,000 cycles in accelerated life tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1426,37 +1450,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes with New Routing and Integration</t>
+          <t>Serviceable Ink Maintenance Part Post 80k Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Use Sayan Sibstar tubes and implement new tube routing and integration in the platform (4 tubes).</t>
+          <t>Designate an ink maintenance part as serviceable at service centers after 80,000-page life is reached.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To improve ink delivery and system reliability in the new tank design.</t>
+          <t>Facilitates post-warranty maintenance and extends device usability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tube sourcing, platform design</t>
+          <t>Requires part identification and service documentation.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Product uses specified tubes with validated routing and integration.</t>
+          <t>Part is listed as serviceable, and service procedures are documented and tested.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1467,6 +1491,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1476,47 +1501,48 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Update service station for improved aerosol management, accommodating changes due to the new tank.</t>
+          <t>Implement a new make-break and fluidic interface (FI) connection for the Ink Delivery System.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To maintain clean operation and prolong service station life.</t>
+          <t>Improves reliability and serviceability of ink connections.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Service station design, tank design</t>
+          <t>Requires design and validation of new connection system.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Service station manages aerosols effectively in all operational modes.</t>
+          <t>New FI connection passes reliability and leak tests under all use conditions.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1526,47 +1552,48 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Increase LEBI Ink Tank Size, Keying, and LOI SHAID</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for tube routing and increased weights.</t>
+          <t>Increase the size of the LEBI ink tank, add keying features, and implement LOI (Line of Identity) SHAID (Security Hardware Authentication ID).</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To ensure reliable printhead movement and avoid mechanical failures.</t>
+          <t>Supports higher page yield, prevents incorrect installation, and enhances security.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Security, Manufacturing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tube integration, carriage design</t>
+          <t>Dependent on tank design and SHAID implementation.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Carriage operates within force and speed tolerances with updated tube and weight configuration.</t>
+          <t>Tank meets new size and keying requirements, LOI SHAID is functional and validated.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1576,47 +1603,48 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Paper Path to Support Increased Page Life</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life (80k pages).</t>
+          <t>Develop a new startup algorithm and air management process for the Ink Delivery System.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To ensure durability and reliability for higher duty cycles.</t>
+          <t>Ensures reliable operation and prevents air-related print issues.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Paper path design, page life goal</t>
+          <t>Requires integration with IDS hardware and firmware.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paper path components maintain functionality for at least 80,000 pages.</t>
+          <t>Startup process reliably primes ink system and prevents air locks, as verified in system tests.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1626,47 +1654,48 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Design the ink maintenance component as a serviceable part for replacement after 80,000 pages (service center).</t>
+          <t>Establish new print quality (PQ) goals and define depletion criteria to match page yield definitions.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To extend product life and maintain print quality beyond warranty period.</t>
+          <t>Ensures consistent output quality and transparent yield claims for customers.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>Product Management, Marketing, Quality</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ink maintenance component design, service documentation</t>
+          <t>Requires updated test protocols and documentation.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ink maintenance part can be replaced by service center after 80,000 pages.</t>
+          <t>Print quality meets or exceeds new goals through the defined depletion period, as validated in tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1676,47 +1705,48 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+          <t>Reuse Marconi Hi PDL for Workspace (WS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Introduce new 140ml Black (K) bottles and new capacity CMY bottles for the product.</t>
+          <t>Leverage the existing Marconi Hi PDL (Page Description Language) for workspace functionality.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To support higher page yields and reduce refill frequency.</t>
+          <t>Reduces development effort and leverages proven technology.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Software Engineering</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bottle design, IDS compatibility</t>
+          <t>Requires compatibility with new system software.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Product supports 140ml K bottles and new CMY bottles as specified.</t>
+          <t>Workspace supports Marconi Hi PDL without functional regressions.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1726,17 +1756,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IDS Make-Break and FI Connection Update</t>
+          <t>MISR and EE Reuse of Existing Components</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI connection for the IDS system, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, and Stingray Wi-Fi module for the Magellan printer.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To improve ink delivery, security, and compatibility with new bottle/tank system.</t>
+          <t>Reduces development time, cost, and risk by leveraging existing, validated components.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,27 +1776,28 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Manufacturing</t>
+          <t>R&amp;D, Hardware Engineering, Manufacturing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>IDS design, LEBI tank, SHAID integration</t>
+          <t>Requires compatibility validation with new platform.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>IDS system operates reliably with new connections and security features.</t>
+          <t>Components function as intended in Magellan system integration tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1776,17 +1807,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>FW Dune Firmware Platform</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Develop a new IDS startup algorithm and air management process for the ink system.</t>
+          <t>Adopt the Dune firmware platform for Magellan.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To ensure reliable startup and minimize air-related failures in the ink path.</t>
+          <t>Provides a modern, flexible firmware base for new features and updates.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,17 +1827,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Firmware Engineering, R&amp;D</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>IDS system design</t>
+          <t>Requires porting and validation for Magellan hardware.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Startup algorithm and air management validated through reliability testing.</t>
+          <t>Dune firmware runs on Magellan hardware and passes all functional and reliability tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1817,6 +1848,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1826,17 +1858,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and define depletion to align with page yield targets.</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware for Magellan.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To ensure print quality is maintained throughout the specified yield.</t>
+          <t>Ensures product security and compliance with HP security standards.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,17 +1878,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Quality Assurance</t>
+          <t>Security, R&amp;D, Firmware</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PQ testing, page yield definition</t>
+          <t>Requires integration with hardware and firmware platforms.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Product maintains PQ within defined limits for full page yield.</t>
+          <t>Gauss4.xx security features pass all penetration and compliance tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1867,6 +1899,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1876,47 +1909,48 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU components in the new product.</t>
+          <t>Printer must achieve print speeds of 25 ppm (pages per minute) for standard and 25/19 ppm for PDL mode.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To reduce development cost and leverage proven hardware.</t>
+          <t>Meets competitive benchmarks and user expectations for throughput.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Product Management, End Users</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Component compatibility</t>
+          <t>Dependent on system performance and print engine capability.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Product uses specified ASICs and PSU without modification.</t>
+          <t>Printer achieves specified speeds in standard and PDL modes in performance tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1926,17 +1960,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Support for PaaS, WorkFromHome/Flexworker, and Onboarding Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module into the product for wireless connectivity.</t>
+          <t>Provide support for Printer-as-a-Service (PaaS), WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To provide up-to-date wireless networking capability.</t>
+          <t>Expands market reach and supports modern business models and customer onboarding.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1946,27 +1980,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>Product Management, Services, IT</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Wi-Fi module sourcing, FW integration</t>
+          <t>Requires software and service integration.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Product passes Wi-Fi certification and user connectivity tests with Stingray module.</t>
+          <t>All solution paths are documented and functional in pilot deployments.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1976,37 +2011,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FW Dune Integration</t>
+          <t>Scan Solution, SMB Manageability, and Enterprise Support (WJA, HPSM, JAM)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Use Dune firmware (FW) for the product platform.</t>
+          <t>Integrate scan solutions, SMB manageability, and enterprise support including WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (JetAdvantage Management).</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To unify firmware development and leverage existing features.</t>
+          <t>Meets business customer requirements for device management and workflow integration.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Firmware Engineering, Product Management</t>
+          <t>Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HW/FW compatibility</t>
+          <t>Requires software integration and testing.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Product operates reliably with Dune FW and passes all FW validation tests.</t>
+          <t>Scan, manageability, and enterprise support features function as specified in enterprise environments.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2017,6 +2052,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2026,17 +2062,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security Integration</t>
+          <t>Clients &amp; Drivers Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Integrate Gauss4.xx security features at both hardware and firmware levels.</t>
+          <t>Support a range of client software and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To meet current security requirements and protect user data.</t>
+          <t>Ensures broad compatibility and ease of deployment for various customer segments.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2046,17 +2082,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Security, IT, Product Management</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HW/FW design, Gauss4.xx feature set</t>
+          <t>Requires driver and software development and validation.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Product passes security certification and penetration testing with Gauss4.xx features enabled.</t>
+          <t>All listed clients and drivers are supported and pass compatibility tests on launch.</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2067,6 +2103,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2076,17 +2113,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>SuperAmp PHA Life at 65K (Constraint)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Product must support business models and services for Consumer, SMB, and Enterprise customers.</t>
+          <t>SuperAmp PHA component life is constrained to 65,000 pages.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To maximize market reach and address different customer needs.</t>
+          <t>Defines maintenance and replacement intervals for critical printhead assembly.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2096,27 +2133,28 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>Service, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Feature set, software integration</t>
+          <t>Requires alignment with warranty and service parts planning.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Product SKUs and software/services available for all three segments.</t>
+          <t>SuperAmp PHA consistently achieves 65,000-page life in accelerated tests.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2126,47 +2164,48 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Scan Solution Integration</t>
+          <t>Warranty Life: 80,000 Pages or 2 Years</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Integrate scan solution for all supported business segments.</t>
+          <t>Printer warranty covers up to 80,000 pages or 2 years, whichever comes first.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To provide a complete MFP (multi-function printer) offering.</t>
+          <t>Aligns warranty with expected usage and market standards.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scanner hardware, software integration</t>
+          <t>Dependent on component reliability and service documentation.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Product includes scan functionality that meets segment requirements.</t>
+          <t>Warranty terms are clearly documented and communicated to customers.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2176,17 +2215,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SMB Manageability Features</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Include manageability features targeted at SMB customers.</t>
+          <t>Design the printer for easy maintenance box replacement to improve serviceability.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To improve product appeal and ease of management for SMBs.</t>
+          <t>Reduces downtime and service costs for end users and service providers.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2196,27 +2235,28 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Software, UI features</t>
+          <t>Requires mechanical design for easy access.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Product includes SMB management features as defined in requirements doc.</t>
+          <t>Maintenance box can be replaced by service personnel in under 5 minutes as validated by service tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2226,287 +2266,288 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Enterprise Support for WJA, HPSM, JAM</t>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Provide support for enterprise management solutions: Web Jetadmin (WJA), HP Smart Management (HPSM), and JAM.</t>
+          <t>Optionally support host 12,000-page CMYK and trade page 6,000-page yields as flexible features.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To ensure seamless integration into enterprise IT environments.</t>
+          <t>Provides flexibility for different market segments and promotional offerings.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dependent on ink system and SKU definition.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Printer can be configured to support these yields as needed for specific SKUs.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Solution</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Develop HP's first business ink tank printer targeting the SMB segment with 5-250 employees, focusing on ROI, efficiency, and low total cost of ownership (TCO).</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Addresses a gap in HP's portfolio for CISS PLE Hi segment and competes with market trends toward CISS in SMBs.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Enterprise Customers, IT, Product Management</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Software integration, certification</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Product passes integration and functionality tests with WJA, HPSM, and JAM.</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ensure product compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>To maximize compatibility and ease of use across platforms.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Marketing, R&amp;D Telemetry, BA, GXD, Quality, Supplies Quality, DVAR, Tech Reg, Prod Steward</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CISS technology, business ink tank design, market research</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Product is launched as HP's first business ink tank printer, available to SMBs with 5-250 employees, and achieves targeted TCO benchmarks.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 6, 7, 11, 12</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AI Productivity &amp; Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Integrate AI-powered productivity features and scan workflow enhancements, including Perfect Print and Perfect Scan, to simplify device management for non-IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT staff and require easy-to-manage solutions; differentiates HP from competitors with advanced AI features.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>End Users, IT, Product Management</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Driver development, client integration</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Product installs and operates with all listed clients and drivers.</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Leverage Watt-LE/Marconi-Hi Mech + CISS</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Leverage existing Watt-LE/Marconi-Hi mechanical platform and CISS technology for product development.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>To minimize development time and capitalize on proven architectures.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>AI software development, device management portal integration</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AI features (Perfect Print, Perfect Scan) are implemented and validated to improve productivity and manageability for non-IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Device Management Portal</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Develop a consolidated portal for SMBs to manage their printers, targeting unmanaged or lightly managed businesses with no dedicated IT staff.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Simplifies multi-device management for office managers/generalist IT in SMBs, a key pain point for the segment.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>R&amp;D, Product Management</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Platform compatibility</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Product is built on specified mechanical and CISS platforms.</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Product must achieve print speeds of 25/20 ppm (pages per minute), and for PDL, 25/19 ppm.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>To meet market expectations for speed and competitiveness.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Portal software development, integration with printer firmware and AI features</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Portal is accessible to SMBs, supports management of multiple devices, and is validated in customer environments with positive feedback.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Design printer and supplies to deliver the lowest total cost of ownership in HP's business segment, including cost-efficient ink tanks and reduced maintenance.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TCO is a top priority for SMBs; needed to compete with CISS offerings from competitors and drive adoption.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>End Users, Product Management, Marketing</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Print engine design, PDL support</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Product achieves specified speeds in standard test conditions.</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Serviceability: Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Design the maintenance box for easy serviceability.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>To reduce service time and improve end-user experience.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Marketing, Supplies Quality, BA, Prod Steward</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ink tank design, supply chain, cost optimization</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TCO analysis demonstrates Magellan has the lowest business TCO compared to HP’s current portfolio and key competitors.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Implement a replaceable maintenance box that can be serviced by customers, with service center fallback if out of warranty.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs for SMBs without IT staff; meets new use-case requirements.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Service, End Users</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Maintenance box design</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Maintenance box can be serviced/replaced within defined time and tool constraints.</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Warranty Life: 2 Years</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Product must offer a warranty life of 2 years or the equivalent page count, whichever comes first.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>To align with market standards and provide customer assurance.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Warranty</t>
+          <t>Quality, R&amp;D Telemetry, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Component reliability, warranty policy</t>
+          <t>Hardware design, service documentation, warranty policy</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Product is covered under warranty for 2 years or up to 80,000 pages.</t>
+          <t>Maintenance box is user-replaceable under warranty; service center support is available out of warranty; validated in user testing.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2514,229 +2555,234 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must be rated for a minimum life of 65,000 pages.</t>
+          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure supply quality.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>To ensure reliability and reduce service interventions.</t>
+          <t>Prevents user error and maintains print quality; supports sustainability and supply chain integrity.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Supplies Quality, Prod Steward, Quality</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ink bottle design, supply chain integration</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Keyed bottles are implemented and prevent incorrect usage in field testing.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ensure the printer uses at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%).</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; provides a competitive differentiator.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>R&amp;D, Service, End Users</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>PHA design, reliability testing</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA passes reliability tests for at least 65,000 pages.</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>AI Productivity and Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Integrate AI-driven productivity and manageability solutions for printing and scanning workflows, tailored for SMBs with minimal IT support.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Addresses the need for ease of use and efficiency for SMBs lacking dedicated IT teams; differentiates HP from competitors.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Prod Steward, Tech Reg, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Material sourcing, manufacturing process</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Product is verified to contain at least 60% RCP through supply chain and third-party audits.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first), with customer-replaceable parts and service center support post-warranty.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Meets SMB expectations for reliability and ease of service; reduces service costs and downtime.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Marketing, R&amp;D, SMB Customers</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Requires AI software integration; depends on consolidated SMB portal.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>AI features are fully integrated and accessible via device and portal; user feedback confirms improved productivity and manageability.</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>HP’s Lowest Business Total Cost of Ownership (TCO)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Deliver a cost-efficient color printing solution with the lowest TCO in HP’s SMB portfolio, including minimized intervention and consumable costs.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SMBs are highly cost-sensitive and seek ROI; this is a core purchase driver.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marketing, Quality, SMB Customers</t>
+          <t>Quality, R&amp;D Telemetry, BA, Supplies Quality</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Depends on tank technology, keyed bottles, and maintenance design.</t>
+          <t>Service policy, hardware design for replaceability</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Validated by internal TCO analysis and external benchmarks; published TCO is lower than competitors for target segment.</t>
+          <t>Warranty terms are clearly communicated; customer-replaceable parts are available; service center support is operational post-warranty.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sustainable SMB Tank Printer (60% RCP)</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Design the printer to use at least 60% recycled content plastic (RCP), exceeding competitor benchmarks (Epson 30%).</t>
+          <t>For non-PDL SKUs, support SMB2.0 Solutions and Advanced View SMB portal, including PaaS support.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and increasingly demanded by customers and regulations.</t>
+          <t>Expands solution offerings for SMBs and supports platform-as-a-service (PaaS) business models.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, SMB Customers</t>
+          <t>Marketing, R&amp;D Telemetry, BA, DVAR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Material sourcing and manufacturing process adjustments.</t>
+          <t>Software integration, portal development</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Product BOM and manufacturing reports confirm 60% RCP; validated by third-party audit if required.</t>
+          <t>Non-PDL SKUs are compatible with SMB2.0 Solutions, Advanced View SMB portal, and PaaS.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>PDL SKU: Improved Speed and PDL/PS Support</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Introduce a customer-replaceable maintenance box to minimize service intervention and downtime.</t>
+          <t>For PDL SKUs, achieve print speeds of 25/20 ppm (improved from 25/19), and ensure PDL/PS support and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Reduces maintenance burden for SMBs without IT staff; new feature for this segment.</t>
+          <t>Meets higher performance and compliance requirements for certain SMB customers; aligns with competitive benchmarks.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2746,97 +2792,99 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, SMB Customers</t>
+          <t>Quality, R&amp;D Telemetry, Tech Reg, BA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Design and supply chain for replaceable parts; service documentation.</t>
+          <t>Firmware development, hardware optimization, certification process</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>End users can replace maintenance box without service call; instructional material is clear and effective.</t>
+          <t>PDL SKU achieves specified speeds, supports PDL/PS, and obtains Blue Angel certification.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 4</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal for Device Management</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Develop a unified portal for SMBs to manage multiple printers, access AI solutions, and monitor device status.</t>
+          <t>Enable mobile printing capabilities and integration with the HP App for seamless printing from smartphones and tablets.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SMBs need simple, centralized management due to limited IT resources.</t>
+          <t>Addresses the need for flexible, modern workflows in SMBs; meets customer expectations for mobile compatibility.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>R&amp;D, Marketing, BA, SMB Customers</t>
+          <t>GXD, Marketing, BA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Requires integration with AI solutions and device firmware.</t>
+          <t>HP App development, mobile OS compatibility</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Portal is accessible, user-friendly, supports management of 6-15 devices, and integrates with AI features.</t>
+          <t>Mobile printing is functional and validated via the HP App on major platforms (iOS, Android).</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Telemetry and Analytics Requirements</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure ease of use.</t>
+          <t>Implement telemetry features to collect device usage, health, and performance data for ongoing product improvement and proactive support.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Reduces user error and service issues, improving reliability for SMBs.</t>
+          <t>Enables HP and customers to monitor device health, optimize usage, and provide proactive support; supports PaaS.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2846,17 +2894,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Supplies Quality, R&amp;D, SMB Customers</t>
+          <t>R&amp;D Telemetry, BA, Quality, DVAR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Design of bottle and printer interface; supply chain for new bottles.</t>
+          <t>Telemetry software, privacy compliance, analytics platform</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Field testing shows error rate below 1% for incorrect refilling; positive user feedback.</t>
+          <t>Telemetry data is collected, securely transmitted, and actionable insights are provided to HP and customers.</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2864,307 +2912,63 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Warranty and Serviceability Model</t>
+          <t>PaaS (Platform as a Service) Enablement</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Provide warranty coverage for 80k pages or 2 years (whichever is first), with customer-replaceable parts (PHA) and service center support (MINK) for out-of-warranty situations.</t>
+          <t>Ensure the printer platform supports HP's PaaS offerings for SMBs, including device management, analytics, and solution deployment.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ensures reliability and lowers TCO for SMBs; aligns with business purchase expectations.</t>
+          <t>Supports HP’s strategic goal for PaaS acceleration and monetization in SMB segments.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quality, Service, Marketing, SMB Customers</t>
+          <t>Marketing, BA, R&amp;D Telemetry, DVAR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Service documentation, supply of spare parts.</t>
+          <t>Platform architecture, software integration</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Warranty policy is published; service procedures are documented and operational.</t>
+          <t>Printer is PaaS-ready and validated with HP’s PaaS solutions for SMBs.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>PDL/PS Support and Speed Improvement</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>For PDL SKU, support PDL/PS and achieve print speeds of 25/20 ppm (improved from current 25/19).</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Meets advanced SMB requirements for document processing and performance.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>R&amp;D, Marketing, SMB Customers</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Firmware and hardware design; performance testing.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>PDL/PS support validated; print speeds meet or exceed targets in benchmark tests.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Blue Angel Certification</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Obtain Blue Angel environmental certification for PDL SKU.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Meets regulatory and customer sustainability requirements, especially in specific markets.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Tech Reg, Prod Steward, Marketing</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Design and documentation for certification process.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Certification is awarded before product launch in relevant markets.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Support for PaaS (Printing as a Service)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ensure printer and portal support integration with HP’s Printing as a Service (PaaS) offerings.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Supports HP’s strategic goal for PaaS acceleration and coverage.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>BA, Marketing, R&amp;D, SMB Customers</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Portal and firmware development; business model alignment.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Printer and portal are compatible with current and planned PaaS offerings.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 6, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Advanced Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Integrate advanced telemetry for real-time monitoring of device health, usage, and consumables.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Enables proactive support and analytics for SMBs and HP service teams.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, Service, Marketing</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Firmware development; portal integration.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Telemetry data is accessible via portal; supports automated alerts and reporting.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing and printer management via the HP App.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SMBs increasingly rely on mobile devices for business operations.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Marketing, R&amp;D, SMB Customers</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>HP App compatibility and integration with device firmware.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Mobile printing and management features are tested and validated with HP App.</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,58 +425,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>citation</t>
         </is>
       </c>
     </row>
@@ -476,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>NGB Keyed Bottles with 6K Black and 6K CMY Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
+          <t>Develop new NGB keyed ink bottles capable of delivering 6,000 pages for both black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,27 +513,28 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>R&amp;D, Consumables Team, Product Management</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution development.</t>
+          <t>Requires compatibility with NOA-F, IDS, and existing ink systems.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
+          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business TCO for SMB Segment</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
+          <t>Ensure ink bottles and bottle-to-tank interface are designed for spill-free operation during user installation and replacement.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,27 +564,28 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marketing, BA, Quality, Supplies Quality</t>
+          <t>End Users, R&amp;D, Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
+          <t>Linked to bottle design, NOA-F interface, and IDS system.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
+          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,17 +595,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+          <t>Implement NOA-F (New On-demand Air-Filter) with a metal foiled labyrinth design and a lid label, maintaining current push-push and TDF features.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+          <t>Enhances air management, reliability, and product differentiation.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,27 +615,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>R&amp;D, Service, Consumables Team</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires hardware and packaging design for easy replacement.</t>
+          <t>Bottle design, IDS, printer assembly process.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the Magellan platform.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Prevents user error and potential damage, reducing support incidents.</t>
+          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,17 +666,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires bottle and tank redesign.</t>
+          <t>Compatibility with new bottle and tank systems.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -664,9 +684,10 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -676,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Reliability and IDS Characterization &amp; Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+          <t>Model and characterize system reliability, including Water Vapor Transmission Rate (WVTR), air gain, flow rate, IDS (Ink Delivery System) performance, startup, and NOA-F End of Life (EOL).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,27 +717,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
+          <t>Requires finalized IDS and NOA-F design.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+          <t>Model ink stability in the tank and assess impact on print quality (PQ) over time.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+          <t>Prevents degradation of print quality and supports warranty claims.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,27 +768,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marketing, GXD, DVAR, BA</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires integration with HP cloud and service platforms.</t>
+          <t>Dependent on ink formulation and tank design.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -776,17 +799,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Compatibility</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+          <t>Provide NOA-F as service parts for warranty support, ensuring availability during the warranty period.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ensures competitive performance and compliance for managed office environments.</t>
+          <t>Improves serviceability and supports contractual service obligations.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,17 +819,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marketing, Tech Reg, Quality, DVAR</t>
+          <t>Service, Support, Supply Chain</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
+          <t>NOA-F design finalization and supply chain planning.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+          <t>NOA-F parts are available for all warranty claims within service SLAs.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -814,9 +837,10 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -826,47 +850,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+          <t>Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+          <t>R&amp;D, Security, Quality Assurance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires AI software development and hardware compatibility.</t>
+          <t>Dependent on Acumen 6 technology readiness.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -876,17 +901,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Modify Existing SA 14 Line for NOA-F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+          <t>Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+          <t>Enables efficient manufacturing and quality control for new components.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,27 +921,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Tech Reg</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires sourcing and validation of recycled materials.</t>
+          <t>Final NOA-F design, factory retooling schedule.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -926,17 +952,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Minimal Maintenance Design</t>
+          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+          <t>Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reduces operational costs and downtime for SMBs.</t>
+          <t>Supports production of new ink system and traceability.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -946,17 +972,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>Manufacturing, Operations, Supply Chain</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pending investigation and design validation.</t>
+          <t>Orcus 5 readiness, tool procurement.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -964,9 +990,10 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -976,17 +1003,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Comprehensive Telemetry Support</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+          <t>Reduces service costs and increases customer satisfaction.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,17 +1023,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires firmware and cloud integration.</t>
+          <t>Requires robust design for user handling.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1014,9 +1041,10 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1026,17 +1054,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Support New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
+          <t>Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Supports modern SMB workflows and BYOD environments.</t>
+          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,17 +1074,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GXD, Marketing, BA</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires app and firmware compatibility.</t>
+          <t>All system components must meet durability targets.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
+          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1064,7 +1092,1946 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Product Reddington ID with Increased Tank Size</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Adopt Reddington industrial design (ID) with modifications for increased tank size; maintain Marconi-HI ADF and EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Accommodates higher capacity while leveraging existing design elements.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Design, Product Management, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tank and chassis design, packaging updates.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Product passes design review and packaging tests with new tank size and EPS foam.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Regulatory, Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Product design and documentation updates.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ensures physical compatibility and maintains compact product footprint.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Design, Manufacturing, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tank size and chassis design.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Improves usability and aligns with market expectations for modern printers.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, UX Design</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Display sourcing, UI software.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Display is functional and passes user experience testing.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Improves reliability and supports new tank configuration.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tube design finalization, chassis integration.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management with Tank Changes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Update service station for aerosol management, accounting for changes due to new tank design.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Prevents contamination and ensures long-term reliability.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Service station and tank design.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Aerosol levels remain within safe limits in endurance testing.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model with New Tubes and Weights</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ensures print quality and mechanical reliability.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>R&amp;D, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Final tube and tank design.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paper Path Support for Increased Page Life</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ensures consistent reliability and performance over extended use.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, End Users</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chassis and component durability.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paper path components pass 80k page accelerated life test.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Facilitates extended product life and supports service contracts.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Service, Support, End Users</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Service center readiness, part design.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>140ml Black and New CMY Bottles</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Introduce 140ml black bottles and new capacity CMY bottles for Magellan platform.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Consumables Team, R&amp;D, Product Management</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bottle and tank design.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bottles meet capacity and compatibility requirements in production units.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>New IDS Make-Break and FI Connection</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Improves reliability and serviceability of ink connections.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IDS and tank design.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Prevents cross-contamination and supports secure supply chain.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>R&amp;D, Security, Supply Chain</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tank and bottle design, SHAID technology.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>IDS and tank design.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>New Servicing and Startup Algorithm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Improves system uptime and reduces service calls.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, End Users</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>IDS, firmware development.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>New PQ Goals and Depletion Definition</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Page yield testing, IDS design.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven, reliable components.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Compatibility with new system design.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Components pass integration and system validation tests in Magellan units.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Module sourcing, firmware integration.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ensures compliance with security standards and protects against threats.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Security, R&amp;D, Product Management</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HW/FW development, certification.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Expands market reach and supports diverse customer requirements.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Business, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Service and solution development.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Enterprise Customers, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Software development and integration.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Support for Multiple Clients and Drivers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IT, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Driver and client software development.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Critical for product reliability and competitive positioning.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PHA design and validation.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80k Pages</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Product Management, Service, End Users</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>System reliability, consumable capacity.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Meets market performance benchmarks and customer needs.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, End Users</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Engine design, firmware optimization.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Printer achieves specified throughput in ISO test conditions.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Serviceability of Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Maintenance box design.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Allows adaptation to changing market and business needs.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Product Management, Business</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>System design flexibility.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Configurations are validated and available as business needs arise.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Requires integration with SMB portal and AI solution development.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO for SMB Segment</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Marketing, BA, Quality, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, Page 11</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Requires hardware and packaging design for easy replacement.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Prevents user error and potential damage, reducing support incidents.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Requires bottle and tank redesign.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SMB Portal for Printer Management</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, Page 10</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Requires integration with HP cloud and service platforms.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PDL SKU Performance and Compatibility</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ensures competitive performance and compliance for managed office environments.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Marketing, Tech Reg, Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Requires AI software development and hardware compatibility.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, Page 11</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Tech Reg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Requires sourcing and validation of recycled materials.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Minimal Maintenance Design</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Reduces operational costs and downtime for SMBs.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pending investigation and design validation.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Comprehensive Telemetry Support</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Requires firmware and cloud integration.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, Page 12</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Supports modern SMB workflows and BYOD environments.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Requires app and firmware compatibility.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Magellan MRD, Page 9, Page 10</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with 6K Black and 6K CMY Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles capable of delivering 6,000 pages for both black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+          <t>Develop new NGB keyed bottles supporting 6,000 pages for Black and CMY, and increase CMY bottle size to support over 8,000 pages yield.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
+          <t>To meet higher page yield requirements and reduce frequency of bottle replacement, improving customer experience and cost efficiency.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,21 +513,21 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Consumables Team, Product Management</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with NOA-F, IDS, and existing ink systems.</t>
+          <t>Requires bottle design changes and compatibility with existing and new ink systems.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
+          <t>New bottles are available for Black and CMY, support at least 6K yield (Black and CMY), and CMY bottle size supports &gt;8K yield as verified by lab and field tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,12 +549,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure ink bottles and bottle-to-tank interface are designed for spill-free operation during user installation and replacement.</t>
+          <t>Ensure the new ink bottles provide spill-free reliability during handling, installation, and use.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
+          <t>To minimize mess and customer complaints, and to differentiate from competitors.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,17 +564,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Service</t>
+          <t>End Users, Customer Support, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Linked to bottle design, NOA-F interface, and IDS system.</t>
+          <t>Bottle design, NOA-F integration, manufacturing process.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
+          <t>Less than 0.5% of bottle installations result in spills in controlled and field environments.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -600,12 +600,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (New On-demand Air-Filter) with a metal foiled labyrinth design and a lid label, maintaining current push-push and TDF features.</t>
+          <t>Integrate a NOA-F (Non-Ozone Air Filter) with a metal foiled labyrinth and a lid label, without changing the click-on push-push and TDF (Tactile Feedback) mechanism.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances air management, reliability, and product differentiation.</t>
+          <t>To maintain air management and filtration performance while ensuring backward compatibility with current mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Consumables Team</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, printer assembly process.</t>
+          <t>Existing NOA-F design, push-push mechanism.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
+          <t>NOA-F unit passes filtration, durability, and usability tests and is compatible with push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -646,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the Magellan platform.</t>
+          <t>Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the new product.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
+          <t>To leverage existing investments, reduce risk, and speed up time to market.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,21 +666,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and tank systems.</t>
+          <t>Compatibility verification with new hardware and consumables.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks function as intended in the new printer with no reformulation needed.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -697,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and IDS Characterization &amp; Modeling</t>
+          <t>Enhanced Reliability and Characterization Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Model and characterize system reliability, including Water Vapor Transmission Rate (WVTR), air gain, flow rate, IDS (Ink Delivery System) performance, startup, and NOA-F End of Life (EOL).</t>
+          <t>Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life (EOL) scenarios.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
+          <t>To ensure robust performance and longevity under diverse conditions.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires finalized IDS and NOA-F design.</t>
+          <t>Access to new hardware and consumable prototypes.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
+          <t>All models and characterizations completed and reviewed by R&amp;D, with results meeting internal reliability thresholds.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -748,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling</t>
+          <t>Ink Stability Modeling for Tank Impact on Print Quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and assess impact on print quality (PQ) over time.</t>
+          <t>Model ink stability in the tank and assess its impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prevents degradation of print quality and supports warranty claims.</t>
+          <t>To prevent print quality degradation over time due to ink instability.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dependent on ink formulation and tank design.</t>
+          <t>Tank design, ink chemistry.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
+          <t>Modeling completed and print quality remains within specified tolerances throughout expected tank life.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -799,17 +799,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>NOA-F as Service Part with Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts for warranty support, ensuring availability during the warranty period.</t>
+          <t>Provide NOA-F as a service part available for warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves serviceability and supports contractual service obligations.</t>
+          <t>To ensure continued product functionality and customer satisfaction during and after warranty period.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Support, Supply Chain</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NOA-F design finalization and supply chain planning.</t>
+          <t>Supply chain, service documentation.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F parts are available for all warranty claims within service SLAs.</t>
+          <t>NOA-F is available as a service part, and process documentation is in place for warranty claims.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -855,12 +855,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
+          <t>Integrate Acumen 6 (presumed tracking or anti-counterfeit technology) on the lid of the new bottles or tanks.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+          <t>To enhance tracking, authentication, or anti-counterfeit measures.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Quality Assurance</t>
+          <t>R&amp;D, Security, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dependent on Acumen 6 technology readiness.</t>
+          <t>Lid design, Acumen 6 tech availability.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+          <t>Acumen 6 is present and operational on all lids as verified by QA.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -901,17 +901,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Modify Existing SA 14 Line for NOA-F</t>
+          <t>Modify Existing Factory Line SA14 for NOA-F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
+          <t>Modify the existing SA14 factory line to support NOA-F production.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enables efficient manufacturing and quality control for new components.</t>
+          <t>To enable manufacturing of the new NOA-F units without building a new line.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Final NOA-F design, factory retooling schedule.</t>
+          <t>Existing SA14 line capabilities, NOA-F design.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+          <t>SA14 line is validated for NOA-F output with no significant downtime or yield loss.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -957,12 +957,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
+          <t>Integrate Magi ink cartridge and a new labeling tool into the Orcus 5 production line.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Supports production of new ink system and traceability.</t>
+          <t>To support new consumables and ensure accurate labeling for traceability and compliance.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orcus 5 readiness, tool procurement.</t>
+          <t>Orcus 5 line capabilities, Magi ink cart design.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+          <t>Orcus 5 line produces correctly labeled Magi ink cartridges at required throughput.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
+          <t>Design product so that both the Print Head Assembly (PHA) and NOA-F can be replaced by customers without technical assistance.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reduces service costs and increases customer satisfaction.</t>
+          <t>To improve serviceability, reduce downtime, and lower support costs.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1028,16 +1028,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires robust design for user handling.</t>
+          <t>PHA and NOA-F design, user documentation.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+          <t>Customers can replace PHA and NOA-F in under 10 minutes using only included tools, as verified in usability testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support New Warranty Page Life Goal of 80k Pages</t>
+          <t>New Warranty Page Life Goal: 80K Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
+          <t>Set the new warranty page life goal for the product at 80,000 pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
+          <t>To increase product value proposition and reduce total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1074,21 +1074,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Product Management, Marketing, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>All system components must meet durability targets.</t>
+          <t>Component durability, consumable life.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
+          <t>Warranty documentation specifies 80K page life and all major components meet this target in reliability testing.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Product Reddington ID with Increased Tank Size</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adopt Reddington industrial design (ID) with modifications for increased tank size; maintain Marconi-HI ADF and EPS foam packaging.</t>
+          <t>Adopt Reddington ID with a larger tank size, but no change to Marconi-HI ADF (Automatic Document Feeder).</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Accommodates higher capacity while leveraging existing design elements.</t>
+          <t>To accommodate increased ink volume and support higher page yields without impacting ADF.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1125,21 +1125,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Design, Product Management, Manufacturing</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank and chassis design, packaging updates.</t>
+          <t>Tank design, ADF compatibility.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Product passes design review and packaging tests with new tank size and EPS foam.</t>
+          <t>New tank fits within product ID and does not interfere with ADF operation; tank size increase validated in design review.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1156,41 +1156,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+          <t>Use EPS (Expanded Polystyrene) foam packaging for the new printer.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+          <t>To ensure product protection during shipping and handling, and potentially align with EPEAT3 and LOT4 requirements.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>Logistics, Product Management, Compliance</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Product design and documentation updates.</t>
+          <t>Packaging design, regulatory requirements.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+          <t>All shipped units use EPS foam packaging, and packaging passes drop and vibration tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1207,41 +1207,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental certification requirements.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures physical compatibility and maintains compact product footprint.</t>
+          <t>To comply with environmental standards and enhance product marketability in regulated regions.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Design, Manufacturing, R&amp;D</t>
+          <t>Compliance, Marketing, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tank size and chassis design.</t>
+          <t>Design, materials, documentation for certification.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
+          <t>PDL SKU is certified for EPEAT3, LOT4, and Blue Angel prior to product launch.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1258,17 +1258,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
+          <t>Modify input and output trays to accommodate the new tank's protrusion and optimize overall product size.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves usability and aligns with market expectations for modern printers.</t>
+          <t>To ensure paper handling is not impacted by the increased tank size and to maintain compactness.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1278,17 +1278,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UX Design</t>
+          <t>R&amp;D, Product Design, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Display sourcing, UI software.</t>
+          <t>Tank and tray design.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Display is functional and passes user experience testing.</t>
+          <t>Trays accommodate tank protrusion with no paper jams or misfeeds in reliability testing.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1309,17 +1309,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphics Display) for user interface.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Improves reliability and supports new tank configuration.</t>
+          <t>To provide a modern, user-friendly interface for configuration and operation.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1329,21 +1329,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>End Users, Product Management, UI/UX Team</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tube design finalization, chassis integration.</t>
+          <t>Display sourcing, UI development.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
+          <t>All units ship with functional 4.3” CGD display and pass usability tests.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management with Tank Changes</t>
+          <t>Leverage Sayan Sibstar Tubes with New Routing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Update service station for aerosol management, accounting for changes due to new tank design.</t>
+          <t>Use Sayan Sibstar tubes and implement new tube routing and integration for the platform.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Prevents contamination and ensures long-term reliability.</t>
+          <t>To optimize ink delivery and support new tank and bottle configurations.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Manufacturing</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service station and tank design.</t>
+          <t>Tube design, tank and carriage integration.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aerosol levels remain within safe limits in endurance testing.</t>
+          <t>New routing supports reliable ink delivery and passes stress and durability tests.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with New Tubes and Weights</t>
+          <t>Service Station Aerosol Management with Tank Changes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
+          <t>Update service station aerosol management systems to accommodate spit platform changes due to the new tank.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures print quality and mechanical reliability.</t>
+          <t>To maintain air quality and prevent ink misting issues with the new tank design.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1431,21 +1431,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Final tube and tank design.</t>
+          <t>Tank and service station design.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
+          <t>Aerosol management system passes air quality and containment tests with new tank configuration.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1462,41 +1462,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased component weights.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures consistent reliability and performance over extended use.</t>
+          <t>To ensure mechanical reliability and print quality with the new hardware configuration.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chassis and component durability.</t>
+          <t>Tube routing, carriage design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paper path components pass 80k page accelerated life test.</t>
+          <t>Carriage operates within force and speed specifications in all test scenarios with new configuration.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1513,41 +1513,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>Paper Path Upgrade for Increased Page Life</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
+          <t>Upgrade the printer paper path to support the increased page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Facilitates extended product life and supports service contracts.</t>
+          <t>To ensure consistent performance and reliability over the extended life cycle.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Service center readiness, part design.</t>
+          <t>Paper path design, component durability.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
+          <t>Paper path components meet or exceed 80K page life in accelerated life testing.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>140ml Black and New CMY Bottles</t>
+          <t>Ink Maintenance as Serviceable Part Post 80K Life</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Introduce 140ml black bottles and new capacity CMY bottles for Magellan platform.</t>
+          <t>Make ink maintenance a serviceable part at service centers after the printer reaches 80,000 pages.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Supports higher page yields and reduces refill frequency.</t>
+          <t>To extend printer usability and support post-warranty maintenance.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Consumables Team, R&amp;D, Product Management</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bottle and tank design.</t>
+          <t>Service documentation, parts supply.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bottles meet capacity and compatibility requirements in production units.</t>
+          <t>Service centers can replace ink maintenance parts for printers beyond 80K page life.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1615,41 +1615,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
+          <t>Implement a new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Improves reliability and serviceability of ink connections.</t>
+          <t>To ensure secure and reliable ink connections with new tank and bottle designs.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>IDS design, LEBI tank integration.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
+          <t>All IDS connections meet leak, durability, and usability standards in lab and field tests.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1666,41 +1666,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
+          <t>Develop a new startup algorithm and air management system for the IDS to accommodate new hardware and consumables.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Prevents cross-contamination and supports secure supply chain.</t>
+          <t>To ensure reliable printer startup and ink delivery with new configurations.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tank and bottle design, SHAID technology.</t>
+          <t>IDS design, firmware development.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
+          <t>Printer starts up reliably and air management maintains ink flow integrity in all tested scenarios.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1717,41 +1717,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
+          <t>Establish new print quality (PQ) goals and define depletion criteria to match the new page yield definition.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+          <t>To ensure print quality remains high throughout the extended yield and is clearly defined for warranty and support.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>PQ testing, yield modeling.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+          <t>PQ goals and depletion criteria are documented and met in all production units.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1768,17 +1768,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
+          <t>Reuse the Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new printer.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Improves system uptime and reduces service calls.</t>
+          <t>To leverage proven components and reduce development time and cost.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1788,21 +1788,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>IDS, firmware development.</t>
+          <t>Compatibility with new system architecture.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+          <t>All reused components function correctly in new printer configuration.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1819,41 +1819,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion Definition</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+          <t>To provide modern wireless features and maintain competitive parity.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>End Users, Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Page yield testing, IDS design.</t>
+          <t>Module sourcing, firmware integration.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+          <t>All printers support wireless connectivity with Stingray module and pass connectivity tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1870,41 +1870,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Dune Firmware Platform</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
+          <t>Utilize the Dune firmware platform for printer operation.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven, reliable components.</t>
+          <t>To standardize firmware across new products and leverage existing development.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Compatibility with new system design.</t>
+          <t>Hardware compatibility, firmware features.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Components pass integration and system validation tests in Magellan units.</t>
+          <t>Printer operates on Dune firmware platform with all required features enabled.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1921,41 +1921,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+          <t>To enhance product security and protect against threats.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Security, IT</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration.</t>
+          <t>Hardware support, firmware integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+          <t>All printers pass security certification and vulnerability testing for Gauss4.xx.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Business Model Support: Consumer, SMB, Enterprise</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Support multiple business models including Consumer, SMB, and Enterprise, with tailored services and solutions.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures compliance with security standards and protects against threats.</t>
+          <t>To maximize addressable market and provide value to different customer segments.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1992,17 +1992,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HW/FW development, certification.</t>
+          <t>Solution and service integration, pricing models.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+          <t>Product and services are available for all three segments with appropriate features and support.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2023,17 +2023,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Expands market reach and supports diverse customer requirements.</t>
+          <t>To meet the needs of business customers and enhance solution offerings.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2043,21 +2043,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>Enterprise Customers, SMBs, Product Management, IT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Service and solution development.</t>
+          <t>Software integration, platform support.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+          <t>All listed solutions are available and functional at launch.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2074,41 +2074,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
+          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+          <t>To provide broad compatibility for deployment and management.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT, Product Management</t>
+          <t>IT, End Users, Product Management</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Software development and integration.</t>
+          <t>Driver development, QA.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+          <t>All drivers and clients are available and pass certification with the new printer.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2125,41 +2125,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Support for Multiple Clients and Drivers</t>
+          <t>Schedule Adherence</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+          <t>Meet the defined development and production schedule as outlined (Q3'25 to Q4'27).</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+          <t>To achieve timely market entry and meet business objectives.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>Project Management, Product Management, Leadership</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Driver and client software development.</t>
+          <t>All development and manufacturing activities.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+          <t>All major milestones are met per the published schedule.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+          <t>Ensure SuperAmp Print Head Assembly (PHA) achieves a minimum life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Critical for product reliability and competitive positioning.</t>
+          <t>To deliver reliable print performance and meet service expectations.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PHA design and validation.</t>
+          <t>PHA design, reliability testing.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
+          <t>SuperAmp PHA meets or exceeds 65K page life in accelerated life tests.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2227,17 +2227,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or 80k Pages</t>
+          <t>Warranty Life: 2 Years or 80K Pages</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Offer a warranty covering 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Aligns with customer expectations and competitive offerings.</t>
+          <t>To provide clear customer assurance and align with product durability goals.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Product Management, End Users, Marketing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>System reliability, consumable capacity.</t>
+          <t>Component reliability, service policy.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
+          <t>Warranty documentation and support processes are aligned with this policy.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
+          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+          <t>Ensure print throughput of 25/20 pages per minute (ppm), and 25/19 ppm for PDL (Page Description Language) SKU.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Meets market performance benchmarks and customer needs.</t>
+          <t>To meet market expectations for print speed and maintain competitiveness.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2298,25 +2298,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>End Users, Marketing, Product Management</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Engine design, firmware optimization.</t>
+          <t>Engine design, firmware, consumables.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Printer achieves specified throughput in ISO test conditions.</t>
+          <t>Printers achieve specified ppm rates in standardized print speed tests.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2329,17 +2329,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
+          <t>Design product for easy maintenance box replacement to improve serviceability.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs.</t>
+          <t>To minimize downtime and enable user or technician servicing.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2354,16 +2354,16 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Maintenance box design.</t>
+          <t>Maintenance box design, documentation.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+          <t>Maintenance box can be replaced in under 5 minutes by trained personnel or users.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2380,41 +2380,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
+          <t>SMB Solution Integration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
+          <t>Provide solutions tailored for Small and Medium Business (SMB) needs.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Allows adaptation to changing market and business needs.</t>
+          <t>To increase adoption and satisfaction in the SMB market segment.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Product Management, Business</t>
+          <t>SMB Customers, Product Management, Sales</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>System design flexibility.</t>
+          <t>Solution development, integration.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Configurations are validated and available as business needs arise.</t>
+          <t>SMB-specific solutions are available and functional at launch.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2424,20 +2424,24 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>PaaS (Printing as a Service) Enablement</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
+          <t>Enable Printing as a Service (PaaS) offering for the Magellan printer.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+          <t>To address evolving business models and customer preferences for service-based offerings.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2447,48 +2451,44 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>Product Management, Sales, Enterprise Customers</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution development.</t>
+          <t>Service platform integration, billing, support.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
+          <t>PaaS is available for the printer at launch with all core features enabled.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lowest Business TCO for SMB Segment</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
+          <t>Integrate advanced AI-powered productivity solutions for print, scan, and device management workflows to enhance SMB efficiency.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+          <t>SMBs require automation and efficiency due to limited IT resources. AI solutions are a key differentiator.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2498,30 +2498,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marketing, BA, Quality, Supplies Quality</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
+          <t>Requires compatible hardware and software integration.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
+          <t>AI-powered print, scan, and management features are available and functional in the product UI; user testing validates workflow improvements.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
+          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2529,17 +2529,17 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Lowest Business TCO (Total Cost of Ownership)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+          <t>Design the printer to deliver the lowest business TCO in HP's SMB portfolio, through efficient ink tank design and minimal maintenance requirements.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+          <t>Cost efficiency is a top SMB need and a competitive differentiator.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2549,30 +2549,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires hardware and packaging design for easy replacement.</t>
+          <t>Requires efficient ink delivery system and durable components.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+          <t>Independent TCO analysis confirms Magellan's TCO is the lowest among HP SMB printers.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, Page 11</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2580,17 +2580,17 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+          <t>Implement a replaceable maintenance box that can be serviced directly by customers without requiring professional support.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Prevents user error and potential damage, reducing support incidents.</t>
+          <t>SMBs often lack dedicated IT support and require easy self-service features.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2600,21 +2600,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires bottle and tank redesign.</t>
+          <t>Design must ensure user safety and straightforward replacement process.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+          <t>End-user documentation and testing demonstrate that the maintenance box can be replaced by non-IT staff within 5 minutes.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2631,17 +2631,17 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>SMB Device Management Portal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+          <t>Develop a consolidated online portal for SMB customers to manage multiple printers, monitor usage, and access support resources.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+          <t>Unmanaged and lightly managed SMBs need easy, centralized control over their devices due to lack of IT staff.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2651,21 +2651,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
+          <t>Requires secure cloud infrastructure and integration with printer firmware.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+          <t>Portal allows registration, monitoring, and management of at least 6-15 printers per SMB; user acceptance tests show &gt;90% satisfaction.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2682,17 +2682,17 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding major competitors.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+          <t>Sustainability is a key customer and regulatory requirement and a competitive differentiator.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2702,30 +2702,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marketing, GXD, DVAR, BA</t>
+          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Requires integration with HP cloud and service platforms.</t>
+          <t>Supply chain sourcing of recycled plastics; compliance with regulations.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+          <t>Bill of materials and independent audit confirm 60% RCP in shipped units.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2733,17 +2733,17 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Compatibility</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+          <t>Implement keyed ink bottles to prevent misfilling and ensure user-friendly, error-proof refilling.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ensures competitive performance and compliance for managed office environments.</t>
+          <t>Prevents user error and reduces support incidents related to ink refilling.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2753,17 +2753,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Marketing, Tech Reg, Quality, DVAR</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
+          <t>Ink tank design must match bottle keying system.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+          <t>User testing shows a 0% misfill rate during refills by non-IT staff.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2784,17 +2784,17 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Warranty: 80k pages or 2 years (whichever first)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+          <t>Offer a warranty covering 80,000 pages printed or 2 years of use, whichever comes first.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+          <t>SMBs value predictable costs and reliability guarantees.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2804,30 +2804,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+          <t>['Quality', 'Marketing']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires AI software development and hardware compatibility.</t>
+          <t>Durability of printer components must meet warranty terms.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+          <t>Warranty documentation and support systems are in place; field failure rates meet targets within warranty period.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2835,50 +2835,50 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Serviceability: Customer Replaceable Parts and Service Center Thresholds</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+          <t>Design printer so that most maintenance can be performed by customers (PHA), with only complex repairs requiring service center (MINK) intervention.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+          <t>Minimizes downtime and support costs for SMBs with limited IT resources.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Tech Reg</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Requires sourcing and validation of recycled materials.</t>
+          <t>Clear documentation and part design for easy replacement.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+          <t>At least 80% of common maintenance tasks can be performed by end users as validated by usability studies.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2886,17 +2886,17 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Minimal Maintenance Design</t>
+          <t>Support for SMB2.0 Solutions and Advanced View SMB Portal (Non-PDL SKU)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+          <t>Ensure that Non-PDL SKUs support SMB2.0 Solutions and the Advanced View SMB portal.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Reduces operational costs and downtime for SMBs.</t>
+          <t>Aligns with product segmentation and feature differentiation for SMB customers.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2906,30 +2906,30 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>['GXD', 'Marketing', 'Quality']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pending investigation and design validation.</t>
+          <t>Software development and firmware integration.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+          <t>Non-PDL SKUs pass integration tests with SMB2.0 Solutions and portal features.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2937,50 +2937,50 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Comprehensive Telemetry Support</t>
+          <t>PaaS (Platform as a Service) Support</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+          <t>Enable PaaS capabilities for remote device management, monitoring, and value-added services.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+          <t>Supports HP's strategic goal to accelerate PaaS adoption in SMB segments.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+          <t>['R&amp;D Telemetry', 'Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Requires firmware and cloud integration.</t>
+          <t>Requires cloud infrastructure and secure connectivity.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+          <t>PaaS features are available and functional for enrolled devices; security and compliance checks passed.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
+          <t>Magellan MRD, Page 4, Page 10</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2988,50 +2988,305 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
+          <t>PDL/PS Support and Print Speed Targets (PDL SKU)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Provide PDL/PS support and achieve print speed targets of 25/20 ppm for PDL SKUs (improving from 25/19).</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Meets needs of higher-end SMB users and competitive benchmarks.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['Quality', 'GXD', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hardware and firmware optimizations for speed and language support.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PDL SKUs independently tested to achieve 25/20 ppm and full PDL/PS functionality.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Blue Angel Certification (PDL SKU)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ensure PDL SKUs are compliant with Blue Angel environmental standards.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Environmental certifications are required in many markets and valued by customers.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Design and materials must meet Blue Angel criteria.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PDL SKUs achieve Blue Angel certification prior to launch.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Supports modern SMB workflows and BYOD environments.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Support mobile printing workflows and seamless integration with the HP App for SMB users.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mobile device usage is high among SMBs; simplifies printing and management.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>App development and device compatibility.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Mobile printing tested with major OS; HP App integration validated with user acceptance tests.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 10</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Implement telemetry features to monitor device health, usage, and enable proactive support.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Telemetry enables predictive maintenance, reduces downtime, and supports PaaS.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Secure data collection and privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Telemetry data is securely transmitted and actionable insights are available to HP and customers.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, Page 12</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Minimal Maintenance Design</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Engineer the printer for minimal maintenance, reducing the number of parts that require replacement over the device's lifetime.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SMBs want reliable devices with low intervention and maintenance costs.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Component durability and design simplification.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Field test data shows reduced maintenance events vs. comparable products.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Launch Timeline: Spring 27 (1 Jun 27)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Product must be ready for market launch by June 1, 2027.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Meets business planning and market entry objectives.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>GXD, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Requires app and firmware compatibility.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>All development and validation activities must be completed before launch date.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Product available for sale and shipping by 1 Jun 27.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed bottles supporting 6,000 pages for Black and CMY, and increase CMY bottle size to support over 8,000 pages yield.</t>
+          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To meet higher page yield requirements and reduce frequency of bottle replacement, improving customer experience and cost efficiency.</t>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Supply Chain, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires bottle design changes and compatibility with existing and new ink systems.</t>
+          <t>Requires bottle design, compatibility with NOA-F and IDS, and supply chain adjustments.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New bottles are available for Black and CMY, support at least 6K yield (Black and CMY), and CMY bottle size supports &gt;8K yield as verified by lab and field tests.</t>
+          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -549,12 +549,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure the new ink bottles provide spill-free reliability during handling, installation, and use.</t>
+          <t>Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To minimize mess and customer complaints, and to differentiate from competitors.</t>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,21 +564,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Customer Support, R&amp;D</t>
+          <t>R&amp;D, End Users, Customer Support</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle design, NOA-F integration, manufacturing process.</t>
+          <t>Bottle design and IDS compatibility.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Less than 0.5% of bottle installations result in spills in controlled and field environments.</t>
+          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -600,12 +600,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate a NOA-F (Non-Ozone Air Filter) with a metal foiled labyrinth and a lid label, without changing the click-on push-push and TDF (Tactile Feedback) mechanism.</t>
+          <t>Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To maintain air management and filtration performance while ensuring backward compatibility with current mechanisms.</t>
+          <t>Improves reliability and security of the ink delivery system.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Manufacturing, QA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Existing NOA-F design, push-push mechanism.</t>
+          <t>NOA-F component design, assembly process.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F unit passes filtration, durability, and usability tests and is compatible with push-push and TDF mechanisms.</t>
+          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -646,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the new product.</t>
+          <t>Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To leverage existing investments, reduce risk, and speed up time to market.</t>
+          <t>Reduces development time and leverages proven components for reliability.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,21 +666,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility verification with new hardware and consumables.</t>
+          <t>Compatibility with new bottle and tank designs.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks function as intended in the new printer with no reformulation needed.</t>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -697,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Enhanced Reliability and Characterization Modeling</t>
+          <t>Reliability and Performance Characterization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life (EOL) scenarios.</t>
+          <t>Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To ensure robust performance and longevity under diverse conditions.</t>
+          <t>Ensures long-term product reliability and performance.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Access to new hardware and consumable prototypes.</t>
+          <t>Testing infrastructure, finalized designs.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>All models and characterizations completed and reviewed by R&amp;D, with results meeting internal reliability thresholds.</t>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -748,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling for Tank Impact on Print Quality</t>
+          <t>Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and assess its impact on print quality (PQ).</t>
+          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To prevent print quality degradation over time due to ink instability.</t>
+          <t>Prevents ink degradation and maintains consistent print quality.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tank design, ink chemistry.</t>
+          <t>Access to tank samples, ink formulations.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Modeling completed and print quality remains within specified tolerances throughout expected tank life.</t>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -799,17 +799,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Part with Warranty Support</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as a service part available for warranty support.</t>
+          <t>Make NOA-F available as service parts for in-warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To ensure continued product functionality and customer satisfaction during and after warranty period.</t>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>Customer Support, Service Centers, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Supply chain, service documentation.</t>
+          <t>Parts supply chain, service documentation.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F is available as a service part, and process documentation is in place for warranty claims.</t>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -855,12 +855,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (presumed tracking or anti-counterfeit technology) on the lid of the new bottles or tanks.</t>
+          <t>Integrate Acumen 6 technology into the lid component.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To enhance tracking, authentication, or anti-counterfeit measures.</t>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>R&amp;D, Security, QA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 tech availability.</t>
+          <t>Lid component design.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Acumen 6 is present and operational on all lids as verified by QA.</t>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -901,17 +901,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Modify Existing Factory Line SA14 for NOA-F</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify the existing SA14 factory line to support NOA-F production.</t>
+          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To enable manufacturing of the new NOA-F units without building a new line.</t>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -921,21 +921,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Existing SA14 line capabilities, NOA-F design.</t>
+          <t>Line modification schedules, tool procurement.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA14 line is validated for NOA-F output with no significant downtime or yield loss.</t>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -952,41 +952,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Integrate Magi ink cartridge and a new labeling tool into the Orcus 5 production line.</t>
+          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To support new consumables and ensure accurate labeling for traceability and compliance.</t>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, Supply Chain</t>
+          <t>End Users, Service Centers, Customer Support</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orcus 5 line capabilities, Magi ink cart design.</t>
+          <t>Component design, user documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Orcus 5 line produces correctly labeled Magi ink cartridges at required throughput.</t>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design product so that both the Print Head Assembly (PHA) and NOA-F can be replaced by customers without technical assistance.</t>
+          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To improve serviceability, reduce downtime, and lower support costs.</t>
+          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>End Users, Marketing, Service</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PHA and NOA-F design, user documentation.</t>
+          <t>Component durability, consumables yield.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Customers can replace PHA and NOA-F in under 10 minutes using only included tools, as verified in usability testing.</t>
+          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal: 80K Pages</t>
+          <t>Support for 25/20ppm Print Speed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Set the new warranty page life goal for the product at 80,000 pages.</t>
+          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To increase product value proposition and reduce total cost of ownership for customers.</t>
+          <t>Competitive print speeds are required to meet market demands.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1074,21 +1074,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, End Users</t>
+          <t>End Users, Marketing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Component durability, consumable life.</t>
+          <t>Print engine design, firmware.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Warranty documentation specifies 80K page life and all major components meet this target in reliability testing.</t>
+          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID with a larger tank size, but no change to Marconi-HI ADF (Automatic Document Feeder).</t>
+          <t>Use EPS foam packaging for the product.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To accommodate increased ink volume and support higher page yields without impacting ADF.</t>
+          <t>Provides protection during shipping and handling.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>Manufacturing, Logistics, QA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank design, ADF compatibility.</t>
+          <t>Packaging design, supplier availability.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>New tank fits within product ID and does not interfere with ADF operation; tank size increase validated in design review.</t>
+          <t>Packaging passes drop and vibration tests as per HP standards.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1156,41 +1156,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Use EPS (Expanded Polystyrene) foam packaging for the new printer.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To ensure product protection during shipping and handling, and potentially align with EPEAT3 and LOT4 requirements.</t>
+          <t>Meets environmental and regulatory standards, enabling market access.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Logistics, Product Management, Compliance</t>
+          <t>Regulatory, Marketing, QA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Packaging design, regulatory requirements.</t>
+          <t>Product design, documentation.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>All shipped units use EPS foam packaging, and packaging passes drop and vibration tests.</t>
+          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1207,41 +1207,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental certification requirements.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To comply with environmental standards and enhance product marketability in regulated regions.</t>
+          <t>Ensures usability and compactness despite larger tank size.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Compliance, Marketing, Product Management</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Design, materials, documentation for certification.</t>
+          <t>Tank design finalization.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PDL SKU is certified for EPEAT3, LOT4, and Blue Angel prior to product launch.</t>
+          <t>Trays fit seamlessly with tank and pass usability tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1258,17 +1258,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate the new tank's protrusion and optimize overall product size.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To ensure paper handling is not impacted by the increased tank size and to maintain compactness.</t>
+          <t>Improves user interface and accessibility.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1278,21 +1278,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Design, End Users</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tank and tray design.</t>
+          <t>UI design, hardware integration.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Trays accommodate tank protrusion with no paper jams or misfeeds in reliability testing.</t>
+          <t>Display is functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1309,41 +1309,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>4-Tube Ink Delivery Platform</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphics Display) for user interface.</t>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To provide a modern, user-friendly interface for configuration and operation.</t>
+          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UI/UX Team</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Display sourcing, UI development.</t>
+          <t>Tube sourcing, design integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>All units ship with functional 4.3” CGD display and pass usability tests.</t>
+          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes with New Routing</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Use Sayan Sibstar tubes and implement new tube routing and integration for the platform.</t>
+          <t>Modify the service station for improved aerosol management due to tank changes.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To optimize ink delivery and support new tank and bottle configurations.</t>
+          <t>Prevents ink mist and maintains print quality and internal cleanliness.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1380,21 +1380,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, QA, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tube design, tank and carriage integration.</t>
+          <t>Service station redesign.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>New routing supports reliable ink delivery and passes stress and durability tests.</t>
+          <t>Aerosol levels remain within safe limits in all operating conditions.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management with Tank Changes</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Update service station aerosol management systems to accommodate spit platform changes due to the new tank.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To maintain air quality and prevent ink misting issues with the new tank design.</t>
+          <t>Ensures mechanical reliability and print quality.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1431,21 +1431,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tank and service station design.</t>
+          <t>Tube and tank design finalization.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Aerosol management system passes air quality and containment tests with new tank configuration.</t>
+          <t>Carriage system passes stress and dynamic motion tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1462,41 +1462,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased component weights.</t>
+          <t>Redesign paper path to support increased page life up to 80K pages.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To ensure mechanical reliability and print quality with the new hardware configuration.</t>
+          <t>Ensures consistent operation and reliability over extended use.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tube routing, carriage design.</t>
+          <t>Paper path component design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Carriage operates within force and speed specifications in all test scenarios with new configuration.</t>
+          <t>Paper path passes durability tests for 80K page cycles.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1513,41 +1513,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paper Path Upgrade for Increased Page Life</t>
+          <t>Ink Maintenance as Serviceable Part</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Upgrade the printer paper path to support the increased page life goal of 80,000 pages.</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To ensure consistent performance and reliability over the extended life cycle.</t>
+          <t>Reduces TCO and supports extended product lifecycle.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paper path design, component durability.</t>
+          <t>Component design, service documentation.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paper path components meet or exceed 80K page life in accelerated life testing.</t>
+          <t>Maintenance part replacement process is validated at service centers.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1564,41 +1564,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post 80K Life</t>
+          <t>New Make-Break and FI Connection in IDS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Make ink maintenance a serviceable part at service centers after the printer reaches 80,000 pages.</t>
+          <t>Implement new make-break and FI (Fluidic Interface) connection in the Ink Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To extend printer usability and support post-warranty maintenance.</t>
+          <t>Improves reliability and security of ink delivery.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>R&amp;D, QA, Manufacturing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Service documentation, parts supply.</t>
+          <t>IDS redesign, tank and bottle compatibility.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts for printers beyond 80K page life.</t>
+          <t>IDS passes connection reliability and security tests.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1615,17 +1615,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement a new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
+          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To ensure secure and reliable ink connections with new tank and bottle designs.</t>
+          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1635,21 +1635,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IDS design, LEBI tank integration.</t>
+          <t>Firmware, IDS hardware.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>All IDS connections meet leak, durability, and usability standards in lab and field tests.</t>
+          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1666,41 +1666,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New Print Quality Goals and Depletion Definitions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm and air management system for the IDS to accommodate new hardware and consumables.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To ensure reliable printer startup and ink delivery with new configurations.</t>
+          <t>Ensures customer satisfaction and accurate yield claims.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>R&amp;D, Marketing, QA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IDS design, firmware development.</t>
+          <t>Yield testing, PQ benchmarking.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Printer starts up reliably and air management maintains ink flow integrity in all tested scenarios.</t>
+          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1717,41 +1717,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Establish new print quality (PQ) goals and define depletion criteria to match the new page yield definition.</t>
+          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To ensure print quality remains high throughout the extended yield and is clearly defined for warranty and support.</t>
+          <t>Reduces development costs and leverages proven electronics.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PQ testing, yield modeling.</t>
+          <t>Component compatibility.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PQ goals and depletion criteria are documented and met in all production units.</t>
+          <t>Product passes functional and reliability tests with reused components.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1768,17 +1768,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reuse the Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new printer.</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To leverage proven components and reduce development time and cost.</t>
+          <t>Provides modern wireless networking capabilities.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1788,21 +1788,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>End Users, IT, QA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Compatibility with new system architecture.</t>
+          <t>Firmware, hardware integration.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>All reused components function correctly in new printer configuration.</t>
+          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1819,41 +1819,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Firmware Dune Integration</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Use Dune firmware in the product.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To provide modern wireless features and maintain competitive parity.</t>
+          <t>Standardizes software stack and leverages existing capabilities.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>End Users, Product Management, R&amp;D</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration.</t>
+          <t>Firmware compatibility.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>All printers support wireless connectivity with Stingray module and pass connectivity tests.</t>
+          <t>Product passes all functional and regression firmware tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1870,41 +1870,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dune Firmware Platform</t>
+          <t>Gauss4.xx Security for HW &amp; FW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Utilize the Dune firmware platform for printer operation.</t>
+          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To standardize firmware across new products and leverage existing development.</t>
+          <t>Enhances product security and protects against unauthorized access.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>Security, R&amp;D, QA, End Users</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hardware compatibility, firmware features.</t>
+          <t>HW and FW integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Printer operates on Dune firmware platform with all required features enabled.</t>
+          <t>Security features pass penetration and vulnerability tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1921,37 +1921,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>SMB and Enterprise Solution Integration</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To enhance product security and protect against threats.</t>
+          <t>Expands product applicability to business and enterprise segments.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, IT</t>
+          <t>SMB and Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hardware support, firmware integration.</t>
+          <t>Software and hardware integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>All printers pass security certification and vulnerability testing for Gauss4.xx.</t>
+          <t>All solutions are functional and pass customer acceptance tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1972,41 +1972,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Business Model Support: Consumer, SMB, Enterprise</t>
+          <t>Clients &amp; Drivers Support</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support multiple business models including Consumer, SMB, and Enterprise, with tailored services and solutions.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To maximize addressable market and provide value to different customer segments.</t>
+          <t>Maximizes customer compatibility and ease of onboarding.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Solution and service integration, pricing models.</t>
+          <t>Firmware, driver development.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Product and services are available for all three segments with appropriate features and support.</t>
+          <t>All listed drivers and clients are tested and certified for compatibility.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2023,41 +2023,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support</t>
+          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
+          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To meet the needs of business customers and enhance solution offerings.</t>
+          <t>Increases market reach and adapts to evolving customer needs.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enterprise Customers, SMBs, Product Management, IT</t>
+          <t>Business Development, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Software integration, platform support.</t>
+          <t>Solution and service integration.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All listed solutions are available and functional at launch.</t>
+          <t>Product and services are available and functional for all targeted business models.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2074,41 +2074,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Onboarding and S&amp;O Path Support</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To provide broad compatibility for deployment and management.</t>
+          <t>Streamlines customer onboarding and setup.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Driver development, QA.</t>
+          <t>Software integration.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>All drivers and clients are available and pass certification with the new printer.</t>
+          <t>All onboarding paths are tested and documented for smooth user experience.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Schedule Adherence</t>
+          <t>SuperAmp PHA Life at 65K</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Meet the defined development and production schedule as outlined (Q3'25 to Q4'27).</t>
+          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To achieve timely market entry and meet business objectives.</t>
+          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Project Management, Product Management, Leadership</t>
+          <t>R&amp;D, QA, Service</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>All development and manufacturing activities.</t>
+          <t>Component durability testing.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>All major milestones are met per the published schedule.</t>
+          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2176,17 +2176,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>Warranty Life of 2 Years</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp Print Head Assembly (PHA) achieves a minimum life of 65,000 pages.</t>
+          <t>Product must support a warranty life of 2 years.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To deliver reliable print performance and meet service expectations.</t>
+          <t>Meets standard industry warranty expectations.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2196,21 +2196,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Marketing, End Users, Service</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PHA design, reliability testing.</t>
+          <t>Component reliability, service support.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SuperAmp PHA meets or exceeds 65K page life in accelerated life tests.</t>
+          <t>Product warranty is validated for 2 years under normal use conditions.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2227,41 +2227,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Warranty Life: 2 Years or 80K Pages</t>
+          <t>Serviceability (Maintenance Box)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Design the maintenance box for easy serviceability.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To provide clear customer assurance and align with product durability goals.</t>
+          <t>Reduces service time and cost.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Marketing</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Component reliability, service policy.</t>
+          <t>Maintenance box design.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Warranty documentation and support processes are aligned with this policy.</t>
+          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2278,250 +2278,250 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ensure print throughput of 25/20 pages per minute (ppm), and 25/19 ppm for PDL (Page Description Language) SKU.</t>
+          <t>Host support for 12K-CMYK and trade page 6K as flexible requirements.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To meet market expectations for print speed and maintain competitiveness.</t>
+          <t>Allows future scalability and market adaptation.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Platform capability.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Product can be configured to support 12K-CMYK and trade page 6K if required.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>End Users, Marketing, Product Management</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Engine design, firmware, consumables.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Printers achieve specified ppm rates in standardized print speed tests.</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
         <v>0.9</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Serviceability: Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Design product for easy maintenance box replacement to improve serviceability.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>To minimize downtime and enable user or technician servicing.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Service, End Users, Product Management</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Maintenance box design, documentation.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Maintenance box can be replaced in under 5 minutes by trained personnel or users.</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SMB Solution Integration</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Provide solutions tailored for Small and Medium Business (SMB) needs.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>To increase adoption and satisfaction in the SMB market segment.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Serviceability – Customer Replaceable Parts</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SMB Customers, Product Management, Sales</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Solution development, integration.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>SMB-specific solutions are available and functional at launch.</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>PaaS (Printing as a Service) Enablement</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Enable Printing as a Service (PaaS) offering for the Magellan printer.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>To address evolving business models and customer preferences for service-based offerings.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Enterprise Customers</t>
+          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Service platform integration, billing, support.</t>
+          <t>Design for serviceability, documentation, and part supply chain.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PaaS is available for the printer at launch with all core features enabled.</t>
+          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity solutions for print, scan, and device management workflows to enhance SMB efficiency.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMBs require automation and efficiency due to limited IT resources. AI solutions are a key differentiator.</t>
+          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires compatible hardware and software integration.</t>
+          <t>Requires unique bottle design and printer detection mechanism.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>AI-powered print, scan, and management features are available and functional in the product UI; user testing validates workflow improvements.</t>
+          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2529,17 +2529,17 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Design the printer to deliver the lowest business TCO in HP's SMB portfolio, through efficient ink tank design and minimal maintenance requirements.</t>
+          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top SMB need and a competitive differentiator.</t>
+          <t>SMB customers require centralized, simple management and flexible service models.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2549,17 +2549,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires efficient ink delivery system and durable components.</t>
+          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Independent TCO analysis confirms Magellan's TCO is the lowest among HP SMB printers.</t>
+          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2580,17 +2580,17 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Implement a replaceable maintenance box that can be serviced directly by customers without requiring professional support.</t>
+          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SMBs often lack dedicated IT support and require easy self-service features.</t>
+          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2600,21 +2600,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Design must ensure user safety and straightforward replacement process.</t>
+          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>End-user documentation and testing demonstrate that the maintenance box can be replaced by non-IT staff within 5 minutes.</t>
+          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2631,50 +2631,50 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SMB Device Management Portal</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Develop a consolidated online portal for SMB customers to manage multiple printers, monitor usage, and access support resources.</t>
+          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Unmanaged and lightly managed SMBs need easy, centralized control over their devices due to lack of IT staff.</t>
+          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires secure cloud infrastructure and integration with printer firmware.</t>
+          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Portal allows registration, monitoring, and management of at least 6-15 printers per SMB; user acceptance tests show &gt;90% satisfaction.</t>
+          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2682,50 +2682,50 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding major competitors.</t>
+          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sustainability is a key customer and regulatory requirement and a competitive differentiator.</t>
+          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+          <t>['Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Supply chain sourcing of recycled plastics; compliance with regulations.</t>
+          <t>Design for user replacement, supply chain for maintenance boxes.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bill of materials and independent audit confirm 60% RCP in shipped units.</t>
+          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2733,17 +2733,17 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Consolidated Device Management Portal (SMB Portal)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent misfilling and ensure user-friendly, error-proof refilling.</t>
+          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Prevents user error and reduces support incidents related to ink refilling.</t>
+          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2753,30 +2753,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ink tank design must match bottle keying system.</t>
+          <t>Portal software development, printer integration, security compliance.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>User testing shows a 0% misfill rate during refills by non-IT staff.</t>
+          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2784,17 +2784,17 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Warranty: 80k pages or 2 years (whichever first)</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages printed or 2 years of use, whichever comes first.</t>
+          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SMBs value predictable costs and reliability guarantees.</t>
+          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2804,30 +2804,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Durability of printer components must meet warranty terms.</t>
+          <t>HP App compatibility and printer firmware support.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Warranty documentation and support systems are in place; field failure rates meet targets within warranty period.</t>
+          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2835,17 +2835,17 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Serviceability: Customer Replaceable Parts and Service Center Thresholds</t>
+          <t>High Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Design printer so that most maintenance can be performed by customers (PHA), with only complex repairs requiring service center (MINK) intervention.</t>
+          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Minimizes downtime and support costs for SMBs with limited IT resources.</t>
+          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2855,30 +2855,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Clear documentation and part design for easy replacement.</t>
+          <t>Supply chain sourcing, manufacturing process adaptation.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>At least 80% of common maintenance tasks can be performed by end users as validated by usability studies.</t>
+          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2886,41 +2886,41 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Support for SMB2.0 Solutions and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>Warranty – 80,000 Pages or 2 Years</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ensure that Non-PDL SKUs support SMB2.0 Solutions and the Advanced View SMB portal.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aligns with product segmentation and feature differentiation for SMB customers.</t>
+          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'Quality']</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Software development and firmware integration.</t>
+          <t>Hardware reliability and warranty support infrastructure.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs pass integration tests with SMB2.0 Solutions and portal features.</t>
+          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -2937,17 +2937,17 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PaaS (Platform as a Service) Support</t>
+          <t>Telemetry and Advanced Analytics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Enable PaaS capabilities for remote device management, monitoring, and value-added services.</t>
+          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Supports HP's strategic goal to accelerate PaaS adoption in SMB segments.</t>
+          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2957,336 +2957,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Marketing', 'BA']</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Requires cloud infrastructure and secure connectivity.</t>
+          <t>Telemetry module integration, data privacy compliance.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>PaaS features are available and functional for enrolled devices; security and compliance checks passed.</t>
+          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 10</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>PDL/PS Support and Print Speed Targets (PDL SKU)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Provide PDL/PS support and achieve print speed targets of 25/20 ppm for PDL SKUs (improving from 25/19).</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Meets needs of higher-end SMB users and competitive benchmarks.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['Quality', 'GXD', 'R&amp;D Telemetry']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Hardware and firmware optimizations for speed and language support.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>PDL SKUs independently tested to achieve 25/20 ppm and full PDL/PS functionality.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Blue Angel Certification (PDL SKU)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ensure PDL SKUs are compliant with Blue Angel environmental standards.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Environmental certifications are required in many markets and valued by customers.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>['Tech Reg', 'Prod Steward']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Design and materials must meet Blue Angel criteria.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>PDL SKUs achieve Blue Angel certification prior to launch.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Support mobile printing workflows and seamless integration with the HP App for SMB users.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Mobile device usage is high among SMBs; simplifies printing and management.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>App development and device compatibility.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Mobile printing tested with major OS; HP App integration validated with user acceptance tests.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 10</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
           <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Implement telemetry features to monitor device health, usage, and enable proactive support.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Telemetry enables predictive maintenance, reduces downtime, and supports PaaS.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Secure data collection and privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Telemetry data is securely transmitted and actionable insights are available to HP and customers.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Minimal Maintenance Design</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Engineer the printer for minimal maintenance, reducing the number of parts that require replacement over the device's lifetime.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SMBs want reliable devices with low intervention and maintenance costs.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['Quality', 'Supplies Quality']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Component durability and design simplification.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Field test data shows reduced maintenance events vs. comparable products.</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Launch Timeline: Spring 27 (1 Jun 27)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Product must be ready for market launch by June 1, 2027.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Meets business planning and market entry objectives.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>All development and validation activities must be completed before launch date.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Product available for sale and shipping by 1 Jun 27.</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>
